--- a/database/controller_excel/FO-DSP-TI-06 Reporte de mantenimiento preventivo a equipo de computo Rev.01.xlsx
+++ b/database/controller_excel/FO-DSP-TI-06 Reporte de mantenimiento preventivo a equipo de computo Rev.01.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
   </bookViews>
   <sheets>
     <sheet name="Reporte Mantto TI" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="68">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTRES</t>
   </si>
@@ -36,9 +36,6 @@
     <t>REPORTE DE MANTENIMIENTO PREVENTIVO A EQUIPO DE COMPUTO</t>
   </si>
   <si>
-    <t xml:space="preserve">                                                                                                                                                                                                                                                               FECHA:            /               /</t>
-  </si>
-  <si>
     <t>1. DATOS DEL CLIENTE</t>
   </si>
   <si>
@@ -220,13 +217,19 @@
   </si>
   <si>
     <t>RECIBE SERVICIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                                                                                                                                                                                                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FECHA: </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -287,6 +290,17 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -945,7 +959,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1215,129 +1229,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1346,31 +1261,147 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1702,163 +1733,163 @@
     </row>
     <row r="2" spans="1:35" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="148" t="s">
+      <c r="B2" s="96"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="102" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="91"/>
-      <c r="L2" s="91"/>
-      <c r="M2" s="91"/>
-      <c r="N2" s="91"/>
-      <c r="O2" s="91"/>
-      <c r="P2" s="91"/>
-      <c r="Q2" s="91"/>
-      <c r="R2" s="91"/>
-      <c r="S2" s="91"/>
-      <c r="T2" s="91"/>
-      <c r="U2" s="91"/>
-      <c r="V2" s="91"/>
-      <c r="W2" s="91"/>
-      <c r="X2" s="91"/>
-      <c r="Y2" s="92"/>
-      <c r="Z2" s="150" t="s">
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97"/>
+      <c r="L2" s="97"/>
+      <c r="M2" s="97"/>
+      <c r="N2" s="97"/>
+      <c r="O2" s="97"/>
+      <c r="P2" s="97"/>
+      <c r="Q2" s="97"/>
+      <c r="R2" s="97"/>
+      <c r="S2" s="97"/>
+      <c r="T2" s="97"/>
+      <c r="U2" s="97"/>
+      <c r="V2" s="97"/>
+      <c r="W2" s="97"/>
+      <c r="X2" s="97"/>
+      <c r="Y2" s="103"/>
+      <c r="Z2" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="AA2" s="151"/>
-      <c r="AB2" s="151"/>
-      <c r="AC2" s="151"/>
-      <c r="AD2" s="151"/>
-      <c r="AE2" s="151"/>
-      <c r="AF2" s="151"/>
-      <c r="AG2" s="151"/>
-      <c r="AH2" s="152"/>
+      <c r="AA2" s="110"/>
+      <c r="AB2" s="110"/>
+      <c r="AC2" s="110"/>
+      <c r="AD2" s="110"/>
+      <c r="AE2" s="110"/>
+      <c r="AF2" s="110"/>
+      <c r="AG2" s="110"/>
+      <c r="AH2" s="111"/>
       <c r="AI2" s="4"/>
     </row>
     <row r="3" spans="1:35" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="149"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="94"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="94"/>
-      <c r="L3" s="94"/>
-      <c r="M3" s="94"/>
-      <c r="N3" s="94"/>
-      <c r="O3" s="94"/>
-      <c r="P3" s="94"/>
-      <c r="Q3" s="94"/>
-      <c r="R3" s="94"/>
-      <c r="S3" s="94"/>
-      <c r="T3" s="94"/>
-      <c r="U3" s="94"/>
-      <c r="V3" s="94"/>
-      <c r="W3" s="94"/>
-      <c r="X3" s="94"/>
-      <c r="Y3" s="95"/>
-      <c r="Z3" s="153" t="s">
+      <c r="B3" s="98"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="99"/>
+      <c r="K3" s="99"/>
+      <c r="L3" s="99"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="99"/>
+      <c r="O3" s="99"/>
+      <c r="P3" s="99"/>
+      <c r="Q3" s="99"/>
+      <c r="R3" s="99"/>
+      <c r="S3" s="99"/>
+      <c r="T3" s="99"/>
+      <c r="U3" s="99"/>
+      <c r="V3" s="99"/>
+      <c r="W3" s="99"/>
+      <c r="X3" s="99"/>
+      <c r="Y3" s="105"/>
+      <c r="Z3" s="112" t="s">
         <v>2</v>
       </c>
-      <c r="AA3" s="122"/>
-      <c r="AB3" s="122"/>
-      <c r="AC3" s="122"/>
-      <c r="AD3" s="122"/>
-      <c r="AE3" s="122"/>
-      <c r="AF3" s="122"/>
-      <c r="AG3" s="122"/>
-      <c r="AH3" s="154"/>
+      <c r="AA3" s="113"/>
+      <c r="AB3" s="113"/>
+      <c r="AC3" s="113"/>
+      <c r="AD3" s="113"/>
+      <c r="AE3" s="113"/>
+      <c r="AF3" s="113"/>
+      <c r="AG3" s="113"/>
+      <c r="AH3" s="114"/>
       <c r="AI3" s="4"/>
     </row>
     <row r="4" spans="1:35" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="93"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="139"/>
-      <c r="I4" s="139"/>
-      <c r="J4" s="139"/>
-      <c r="K4" s="139"/>
-      <c r="L4" s="139"/>
-      <c r="M4" s="139"/>
-      <c r="N4" s="139"/>
-      <c r="O4" s="139"/>
-      <c r="P4" s="139"/>
-      <c r="Q4" s="139"/>
-      <c r="R4" s="139"/>
-      <c r="S4" s="139"/>
-      <c r="T4" s="139"/>
-      <c r="U4" s="139"/>
-      <c r="V4" s="139"/>
-      <c r="W4" s="139"/>
-      <c r="X4" s="139"/>
-      <c r="Y4" s="140"/>
-      <c r="Z4" s="153" t="s">
+      <c r="B4" s="98"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="107"/>
+      <c r="L4" s="107"/>
+      <c r="M4" s="107"/>
+      <c r="N4" s="107"/>
+      <c r="O4" s="107"/>
+      <c r="P4" s="107"/>
+      <c r="Q4" s="107"/>
+      <c r="R4" s="107"/>
+      <c r="S4" s="107"/>
+      <c r="T4" s="107"/>
+      <c r="U4" s="107"/>
+      <c r="V4" s="107"/>
+      <c r="W4" s="107"/>
+      <c r="X4" s="107"/>
+      <c r="Y4" s="108"/>
+      <c r="Z4" s="112" t="s">
         <v>3</v>
       </c>
-      <c r="AA4" s="122"/>
-      <c r="AB4" s="122"/>
-      <c r="AC4" s="122"/>
-      <c r="AD4" s="122"/>
-      <c r="AE4" s="122"/>
-      <c r="AF4" s="122"/>
-      <c r="AG4" s="122"/>
-      <c r="AH4" s="154"/>
+      <c r="AA4" s="113"/>
+      <c r="AB4" s="113"/>
+      <c r="AC4" s="113"/>
+      <c r="AD4" s="113"/>
+      <c r="AE4" s="113"/>
+      <c r="AF4" s="113"/>
+      <c r="AG4" s="113"/>
+      <c r="AH4" s="114"/>
       <c r="AI4" s="4"/>
     </row>
     <row r="5" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="114"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="155" t="s">
+      <c r="B5" s="100"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="115" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="97"/>
-      <c r="K5" s="97"/>
-      <c r="L5" s="97"/>
-      <c r="M5" s="97"/>
-      <c r="N5" s="97"/>
-      <c r="O5" s="97"/>
-      <c r="P5" s="97"/>
-      <c r="Q5" s="97"/>
-      <c r="R5" s="97"/>
-      <c r="S5" s="97"/>
-      <c r="T5" s="97"/>
-      <c r="U5" s="97"/>
-      <c r="V5" s="97"/>
-      <c r="W5" s="97"/>
-      <c r="X5" s="97"/>
-      <c r="Y5" s="97"/>
-      <c r="Z5" s="97"/>
-      <c r="AA5" s="97"/>
-      <c r="AB5" s="97"/>
-      <c r="AC5" s="97"/>
-      <c r="AD5" s="97"/>
-      <c r="AE5" s="97"/>
-      <c r="AF5" s="97"/>
-      <c r="AG5" s="97"/>
-      <c r="AH5" s="156"/>
+      <c r="H5" s="116"/>
+      <c r="I5" s="116"/>
+      <c r="J5" s="116"/>
+      <c r="K5" s="116"/>
+      <c r="L5" s="116"/>
+      <c r="M5" s="116"/>
+      <c r="N5" s="116"/>
+      <c r="O5" s="116"/>
+      <c r="P5" s="116"/>
+      <c r="Q5" s="116"/>
+      <c r="R5" s="116"/>
+      <c r="S5" s="116"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="116"/>
+      <c r="V5" s="116"/>
+      <c r="W5" s="116"/>
+      <c r="X5" s="116"/>
+      <c r="Y5" s="116"/>
+      <c r="Z5" s="116"/>
+      <c r="AA5" s="116"/>
+      <c r="AB5" s="116"/>
+      <c r="AC5" s="116"/>
+      <c r="AD5" s="116"/>
+      <c r="AE5" s="116"/>
+      <c r="AF5" s="116"/>
+      <c r="AG5" s="116"/>
+      <c r="AH5" s="117"/>
       <c r="AI5" s="4"/>
     </row>
-    <row r="6" spans="1:35" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -1895,46 +1926,48 @@
       <c r="AH6" s="5"/>
       <c r="AI6" s="5"/>
     </row>
-    <row r="7" spans="1:35" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
-      <c r="B7" s="157" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="99"/>
-      <c r="D7" s="99"/>
-      <c r="E7" s="99"/>
-      <c r="F7" s="99"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="99"/>
-      <c r="I7" s="99"/>
-      <c r="J7" s="99"/>
-      <c r="K7" s="99"/>
-      <c r="L7" s="99"/>
-      <c r="M7" s="99"/>
-      <c r="N7" s="99"/>
-      <c r="O7" s="99"/>
-      <c r="P7" s="99"/>
-      <c r="Q7" s="99"/>
-      <c r="R7" s="99"/>
-      <c r="S7" s="99"/>
-      <c r="T7" s="99"/>
-      <c r="U7" s="99"/>
-      <c r="V7" s="99"/>
-      <c r="W7" s="99"/>
-      <c r="X7" s="99"/>
-      <c r="Y7" s="99"/>
-      <c r="Z7" s="99"/>
-      <c r="AA7" s="99"/>
-      <c r="AB7" s="99"/>
-      <c r="AC7" s="99"/>
-      <c r="AD7" s="99"/>
-      <c r="AE7" s="99"/>
-      <c r="AF7" s="99"/>
-      <c r="AG7" s="99"/>
-      <c r="AH7" s="100"/>
+      <c r="B7" s="166" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="167"/>
+      <c r="D7" s="167"/>
+      <c r="E7" s="167"/>
+      <c r="F7" s="167"/>
+      <c r="G7" s="167"/>
+      <c r="H7" s="167"/>
+      <c r="I7" s="167"/>
+      <c r="J7" s="167"/>
+      <c r="K7" s="167"/>
+      <c r="L7" s="167"/>
+      <c r="M7" s="167"/>
+      <c r="N7" s="167"/>
+      <c r="O7" s="167"/>
+      <c r="P7" s="167"/>
+      <c r="Q7" s="167"/>
+      <c r="R7" s="167"/>
+      <c r="S7" s="167"/>
+      <c r="T7" s="167"/>
+      <c r="U7" s="167"/>
+      <c r="V7" s="167"/>
+      <c r="W7" s="167"/>
+      <c r="X7" s="167"/>
+      <c r="Y7" s="167"/>
+      <c r="Z7" s="167"/>
+      <c r="AA7" s="167"/>
+      <c r="AB7" s="168" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC7" s="169"/>
+      <c r="AD7" s="169"/>
+      <c r="AE7" s="169"/>
+      <c r="AF7" s="169"/>
+      <c r="AG7" s="169"/>
+      <c r="AH7" s="170"/>
       <c r="AI7" s="7"/>
     </row>
-    <row r="8" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="9"/>
       <c r="C8" s="10"/>
@@ -1973,41 +2006,41 @@
     </row>
     <row r="9" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
-      <c r="B9" s="98" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="99"/>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="99"/>
-      <c r="H9" s="99"/>
-      <c r="I9" s="99"/>
-      <c r="J9" s="99"/>
-      <c r="K9" s="99"/>
-      <c r="L9" s="99"/>
-      <c r="M9" s="99"/>
-      <c r="N9" s="99"/>
-      <c r="O9" s="99"/>
-      <c r="P9" s="99"/>
-      <c r="Q9" s="99"/>
-      <c r="R9" s="99"/>
-      <c r="S9" s="99"/>
-      <c r="T9" s="99"/>
-      <c r="U9" s="99"/>
-      <c r="V9" s="99"/>
-      <c r="W9" s="99"/>
-      <c r="X9" s="99"/>
-      <c r="Y9" s="99"/>
-      <c r="Z9" s="99"/>
-      <c r="AA9" s="99"/>
-      <c r="AB9" s="99"/>
-      <c r="AC9" s="99"/>
-      <c r="AD9" s="99"/>
-      <c r="AE9" s="99"/>
-      <c r="AF9" s="99"/>
-      <c r="AG9" s="99"/>
-      <c r="AH9" s="100"/>
+      <c r="B9" s="120" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="118"/>
+      <c r="D9" s="118"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="118"/>
+      <c r="G9" s="118"/>
+      <c r="H9" s="118"/>
+      <c r="I9" s="118"/>
+      <c r="J9" s="118"/>
+      <c r="K9" s="118"/>
+      <c r="L9" s="118"/>
+      <c r="M9" s="118"/>
+      <c r="N9" s="118"/>
+      <c r="O9" s="118"/>
+      <c r="P9" s="118"/>
+      <c r="Q9" s="118"/>
+      <c r="R9" s="118"/>
+      <c r="S9" s="118"/>
+      <c r="T9" s="118"/>
+      <c r="U9" s="118"/>
+      <c r="V9" s="118"/>
+      <c r="W9" s="118"/>
+      <c r="X9" s="118"/>
+      <c r="Y9" s="118"/>
+      <c r="Z9" s="118"/>
+      <c r="AA9" s="118"/>
+      <c r="AB9" s="118"/>
+      <c r="AC9" s="118"/>
+      <c r="AD9" s="118"/>
+      <c r="AE9" s="118"/>
+      <c r="AF9" s="118"/>
+      <c r="AG9" s="118"/>
+      <c r="AH9" s="119"/>
       <c r="AI9" s="12"/>
     </row>
     <row r="10" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2050,156 +2083,156 @@
     <row r="11" spans="1:35" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="14"/>
-      <c r="C11" s="166" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="167"/>
-      <c r="E11" s="167"/>
-      <c r="F11" s="167"/>
-      <c r="G11" s="164"/>
-      <c r="H11" s="164"/>
-      <c r="I11" s="164"/>
-      <c r="J11" s="164"/>
-      <c r="K11" s="164"/>
-      <c r="L11" s="164"/>
-      <c r="M11" s="164"/>
-      <c r="N11" s="164"/>
-      <c r="O11" s="164"/>
-      <c r="P11" s="164"/>
-      <c r="Q11" s="164"/>
-      <c r="R11" s="164"/>
-      <c r="S11" s="164"/>
-      <c r="T11" s="164"/>
-      <c r="U11" s="164"/>
-      <c r="V11" s="164"/>
-      <c r="W11" s="164"/>
-      <c r="X11" s="164"/>
-      <c r="Y11" s="164"/>
-      <c r="Z11" s="164"/>
-      <c r="AA11" s="164"/>
-      <c r="AB11" s="164"/>
-      <c r="AC11" s="164"/>
-      <c r="AD11" s="164"/>
-      <c r="AE11" s="164"/>
-      <c r="AF11" s="164"/>
-      <c r="AG11" s="165"/>
+      <c r="C11" s="123" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="165"/>
+      <c r="E11" s="165"/>
+      <c r="F11" s="165"/>
+      <c r="G11" s="171"/>
+      <c r="H11" s="171"/>
+      <c r="I11" s="171"/>
+      <c r="J11" s="171"/>
+      <c r="K11" s="171"/>
+      <c r="L11" s="171"/>
+      <c r="M11" s="171"/>
+      <c r="N11" s="171"/>
+      <c r="O11" s="171"/>
+      <c r="P11" s="171"/>
+      <c r="Q11" s="171"/>
+      <c r="R11" s="171"/>
+      <c r="S11" s="171"/>
+      <c r="T11" s="171"/>
+      <c r="U11" s="171"/>
+      <c r="V11" s="171"/>
+      <c r="W11" s="171"/>
+      <c r="X11" s="171"/>
+      <c r="Y11" s="171"/>
+      <c r="Z11" s="171"/>
+      <c r="AA11" s="171"/>
+      <c r="AB11" s="171"/>
+      <c r="AC11" s="171"/>
+      <c r="AD11" s="171"/>
+      <c r="AE11" s="171"/>
+      <c r="AF11" s="171"/>
+      <c r="AG11" s="172"/>
       <c r="AH11" s="16"/>
       <c r="AI11" s="13"/>
     </row>
     <row r="12" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="14"/>
-      <c r="C12" s="144" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="122"/>
-      <c r="K12" s="122"/>
-      <c r="L12" s="122"/>
-      <c r="M12" s="122"/>
-      <c r="N12" s="122"/>
-      <c r="O12" s="122"/>
-      <c r="P12" s="122"/>
-      <c r="Q12" s="122"/>
-      <c r="R12" s="122"/>
-      <c r="S12" s="122"/>
-      <c r="T12" s="122"/>
-      <c r="U12" s="122"/>
-      <c r="V12" s="122"/>
-      <c r="W12" s="122"/>
-      <c r="X12" s="122"/>
-      <c r="Y12" s="122"/>
-      <c r="Z12" s="122"/>
-      <c r="AA12" s="122"/>
-      <c r="AB12" s="122"/>
-      <c r="AC12" s="122"/>
-      <c r="AD12" s="122"/>
-      <c r="AE12" s="122"/>
-      <c r="AF12" s="122"/>
-      <c r="AG12" s="123"/>
+      <c r="C12" s="123" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="165"/>
+      <c r="E12" s="165"/>
+      <c r="F12" s="165"/>
+      <c r="G12" s="171"/>
+      <c r="H12" s="171"/>
+      <c r="I12" s="171"/>
+      <c r="J12" s="171"/>
+      <c r="K12" s="171"/>
+      <c r="L12" s="171"/>
+      <c r="M12" s="171"/>
+      <c r="N12" s="171"/>
+      <c r="O12" s="171"/>
+      <c r="P12" s="171"/>
+      <c r="Q12" s="171"/>
+      <c r="R12" s="171"/>
+      <c r="S12" s="171"/>
+      <c r="T12" s="171"/>
+      <c r="U12" s="171"/>
+      <c r="V12" s="171"/>
+      <c r="W12" s="171"/>
+      <c r="X12" s="171"/>
+      <c r="Y12" s="171"/>
+      <c r="Z12" s="171"/>
+      <c r="AA12" s="171"/>
+      <c r="AB12" s="171"/>
+      <c r="AC12" s="171"/>
+      <c r="AD12" s="171"/>
+      <c r="AE12" s="171"/>
+      <c r="AF12" s="171"/>
+      <c r="AG12" s="172"/>
       <c r="AH12" s="16"/>
       <c r="AI12" s="13"/>
     </row>
     <row r="13" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>
       <c r="B13" s="14"/>
-      <c r="C13" s="144" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="122"/>
-      <c r="K13" s="122"/>
-      <c r="L13" s="122"/>
-      <c r="M13" s="122"/>
-      <c r="N13" s="122"/>
-      <c r="O13" s="122"/>
-      <c r="P13" s="122"/>
-      <c r="Q13" s="122"/>
-      <c r="R13" s="122"/>
-      <c r="S13" s="122"/>
-      <c r="T13" s="122"/>
-      <c r="U13" s="122"/>
-      <c r="V13" s="122"/>
-      <c r="W13" s="122"/>
-      <c r="X13" s="122"/>
-      <c r="Y13" s="122"/>
-      <c r="Z13" s="122"/>
-      <c r="AA13" s="122"/>
-      <c r="AB13" s="122"/>
-      <c r="AC13" s="122"/>
-      <c r="AD13" s="122"/>
-      <c r="AE13" s="122"/>
-      <c r="AF13" s="122"/>
-      <c r="AG13" s="123"/>
+      <c r="C13" s="123" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="165"/>
+      <c r="E13" s="165"/>
+      <c r="F13" s="165"/>
+      <c r="G13" s="171"/>
+      <c r="H13" s="171"/>
+      <c r="I13" s="171"/>
+      <c r="J13" s="171"/>
+      <c r="K13" s="171"/>
+      <c r="L13" s="171"/>
+      <c r="M13" s="171"/>
+      <c r="N13" s="171"/>
+      <c r="O13" s="171"/>
+      <c r="P13" s="171"/>
+      <c r="Q13" s="171"/>
+      <c r="R13" s="171"/>
+      <c r="S13" s="171"/>
+      <c r="T13" s="171"/>
+      <c r="U13" s="171"/>
+      <c r="V13" s="171"/>
+      <c r="W13" s="171"/>
+      <c r="X13" s="171"/>
+      <c r="Y13" s="171"/>
+      <c r="Z13" s="171"/>
+      <c r="AA13" s="171"/>
+      <c r="AB13" s="171"/>
+      <c r="AC13" s="171"/>
+      <c r="AD13" s="171"/>
+      <c r="AE13" s="171"/>
+      <c r="AF13" s="171"/>
+      <c r="AG13" s="172"/>
       <c r="AH13" s="16"/>
       <c r="AI13" s="13"/>
     </row>
     <row r="14" spans="1:35" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17"/>
       <c r="B14" s="14"/>
-      <c r="C14" s="144" t="s">
-        <v>10</v>
+      <c r="C14" s="121" t="s">
+        <v>9</v>
       </c>
       <c r="D14" s="122"/>
       <c r="E14" s="122"/>
       <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="122"/>
-      <c r="K14" s="122"/>
-      <c r="L14" s="122"/>
-      <c r="M14" s="122"/>
-      <c r="N14" s="122"/>
-      <c r="O14" s="122"/>
-      <c r="P14" s="122"/>
-      <c r="Q14" s="122"/>
-      <c r="R14" s="122"/>
-      <c r="S14" s="122"/>
-      <c r="T14" s="122"/>
-      <c r="U14" s="122"/>
-      <c r="V14" s="122"/>
-      <c r="W14" s="122"/>
-      <c r="X14" s="122"/>
-      <c r="Y14" s="122"/>
-      <c r="Z14" s="122"/>
-      <c r="AA14" s="122"/>
-      <c r="AB14" s="122"/>
-      <c r="AC14" s="122"/>
-      <c r="AD14" s="122"/>
-      <c r="AE14" s="122"/>
-      <c r="AF14" s="122"/>
-      <c r="AG14" s="123"/>
+      <c r="G14" s="171"/>
+      <c r="H14" s="171"/>
+      <c r="I14" s="171"/>
+      <c r="J14" s="171"/>
+      <c r="K14" s="171"/>
+      <c r="L14" s="171"/>
+      <c r="M14" s="171"/>
+      <c r="N14" s="171"/>
+      <c r="O14" s="171"/>
+      <c r="P14" s="171"/>
+      <c r="Q14" s="171"/>
+      <c r="R14" s="171"/>
+      <c r="S14" s="171"/>
+      <c r="T14" s="171"/>
+      <c r="U14" s="171"/>
+      <c r="V14" s="171"/>
+      <c r="W14" s="171"/>
+      <c r="X14" s="171"/>
+      <c r="Y14" s="171"/>
+      <c r="Z14" s="171"/>
+      <c r="AA14" s="171"/>
+      <c r="AB14" s="171"/>
+      <c r="AC14" s="171"/>
+      <c r="AD14" s="171"/>
+      <c r="AE14" s="171"/>
+      <c r="AF14" s="171"/>
+      <c r="AG14" s="172"/>
       <c r="AH14" s="18"/>
       <c r="AI14" s="2"/>
     </row>
@@ -2259,61 +2292,61 @@
       <c r="P16" s="20"/>
       <c r="Q16" s="20"/>
       <c r="R16" s="125"/>
-      <c r="S16" s="94"/>
-      <c r="T16" s="94"/>
-      <c r="U16" s="94"/>
-      <c r="V16" s="94"/>
-      <c r="W16" s="94"/>
-      <c r="X16" s="94"/>
+      <c r="S16" s="99"/>
+      <c r="T16" s="99"/>
+      <c r="U16" s="99"/>
+      <c r="V16" s="99"/>
+      <c r="W16" s="99"/>
+      <c r="X16" s="99"/>
       <c r="Y16" s="125"/>
-      <c r="Z16" s="94"/>
-      <c r="AA16" s="94"/>
-      <c r="AB16" s="94"/>
-      <c r="AC16" s="94"/>
-      <c r="AD16" s="94"/>
-      <c r="AE16" s="94"/>
-      <c r="AF16" s="94"/>
-      <c r="AG16" s="94"/>
+      <c r="Z16" s="99"/>
+      <c r="AA16" s="99"/>
+      <c r="AB16" s="99"/>
+      <c r="AC16" s="99"/>
+      <c r="AD16" s="99"/>
+      <c r="AE16" s="99"/>
+      <c r="AF16" s="99"/>
+      <c r="AG16" s="99"/>
       <c r="AH16" s="16"/>
       <c r="AI16" s="13"/>
     </row>
     <row r="17" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="25"/>
-      <c r="B17" s="145" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="99"/>
-      <c r="D17" s="99"/>
-      <c r="E17" s="99"/>
-      <c r="F17" s="99"/>
-      <c r="G17" s="99"/>
-      <c r="H17" s="99"/>
-      <c r="I17" s="99"/>
-      <c r="J17" s="99"/>
-      <c r="K17" s="99"/>
-      <c r="L17" s="99"/>
-      <c r="M17" s="99"/>
-      <c r="N17" s="99"/>
-      <c r="O17" s="99"/>
-      <c r="P17" s="99"/>
-      <c r="Q17" s="99"/>
-      <c r="R17" s="99"/>
-      <c r="S17" s="99"/>
-      <c r="T17" s="99"/>
-      <c r="U17" s="99"/>
-      <c r="V17" s="99"/>
-      <c r="W17" s="99"/>
-      <c r="X17" s="99"/>
-      <c r="Y17" s="99"/>
-      <c r="Z17" s="99"/>
-      <c r="AA17" s="99"/>
-      <c r="AB17" s="99"/>
-      <c r="AC17" s="99"/>
-      <c r="AD17" s="99"/>
-      <c r="AE17" s="99"/>
-      <c r="AF17" s="99"/>
-      <c r="AG17" s="99"/>
-      <c r="AH17" s="100"/>
+      <c r="B17" s="127" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="118"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="118"/>
+      <c r="H17" s="118"/>
+      <c r="I17" s="118"/>
+      <c r="J17" s="118"/>
+      <c r="K17" s="118"/>
+      <c r="L17" s="118"/>
+      <c r="M17" s="118"/>
+      <c r="N17" s="118"/>
+      <c r="O17" s="118"/>
+      <c r="P17" s="118"/>
+      <c r="Q17" s="118"/>
+      <c r="R17" s="118"/>
+      <c r="S17" s="118"/>
+      <c r="T17" s="118"/>
+      <c r="U17" s="118"/>
+      <c r="V17" s="118"/>
+      <c r="W17" s="118"/>
+      <c r="X17" s="118"/>
+      <c r="Y17" s="118"/>
+      <c r="Z17" s="118"/>
+      <c r="AA17" s="118"/>
+      <c r="AB17" s="118"/>
+      <c r="AC17" s="118"/>
+      <c r="AD17" s="118"/>
+      <c r="AE17" s="118"/>
+      <c r="AF17" s="118"/>
+      <c r="AG17" s="118"/>
+      <c r="AH17" s="119"/>
       <c r="AI17" s="26"/>
     </row>
     <row r="18" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2356,357 +2389,357 @@
     <row r="19" spans="1:35" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="33"/>
       <c r="B19" s="34"/>
-      <c r="C19" s="146" t="s">
+      <c r="C19" s="128" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="113"/>
+      <c r="E19" s="113"/>
+      <c r="F19" s="124"/>
+      <c r="G19" s="129" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="122"/>
-      <c r="E19" s="122"/>
-      <c r="F19" s="123"/>
-      <c r="G19" s="147" t="s">
+      <c r="H19" s="113"/>
+      <c r="I19" s="113"/>
+      <c r="J19" s="113"/>
+      <c r="K19" s="124"/>
+      <c r="L19" s="129" t="s">
         <v>13</v>
       </c>
-      <c r="H19" s="122"/>
-      <c r="I19" s="122"/>
-      <c r="J19" s="122"/>
-      <c r="K19" s="123"/>
-      <c r="L19" s="147" t="s">
+      <c r="M19" s="113"/>
+      <c r="N19" s="113"/>
+      <c r="O19" s="113"/>
+      <c r="P19" s="124"/>
+      <c r="Q19" s="129" t="s">
         <v>14</v>
       </c>
-      <c r="M19" s="122"/>
-      <c r="N19" s="122"/>
-      <c r="O19" s="122"/>
-      <c r="P19" s="123"/>
-      <c r="Q19" s="147" t="s">
+      <c r="R19" s="113"/>
+      <c r="S19" s="113"/>
+      <c r="T19" s="113"/>
+      <c r="U19" s="113"/>
+      <c r="V19" s="124"/>
+      <c r="W19" s="129" t="s">
         <v>15</v>
       </c>
-      <c r="R19" s="122"/>
-      <c r="S19" s="122"/>
-      <c r="T19" s="122"/>
-      <c r="U19" s="122"/>
-      <c r="V19" s="123"/>
-      <c r="W19" s="147" t="s">
-        <v>16</v>
-      </c>
-      <c r="X19" s="122"/>
-      <c r="Y19" s="122"/>
-      <c r="Z19" s="122"/>
-      <c r="AA19" s="122"/>
-      <c r="AB19" s="122"/>
-      <c r="AC19" s="122"/>
-      <c r="AD19" s="122"/>
-      <c r="AE19" s="122"/>
-      <c r="AF19" s="122"/>
-      <c r="AG19" s="123"/>
+      <c r="X19" s="113"/>
+      <c r="Y19" s="113"/>
+      <c r="Z19" s="113"/>
+      <c r="AA19" s="113"/>
+      <c r="AB19" s="113"/>
+      <c r="AC19" s="113"/>
+      <c r="AD19" s="113"/>
+      <c r="AE19" s="113"/>
+      <c r="AF19" s="113"/>
+      <c r="AG19" s="124"/>
       <c r="AH19" s="35"/>
       <c r="AI19" s="26"/>
     </row>
     <row r="20" spans="1:35" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="33"/>
       <c r="B20" s="34"/>
-      <c r="C20" s="124" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="122"/>
-      <c r="E20" s="122"/>
-      <c r="F20" s="123"/>
-      <c r="G20" s="121"/>
-      <c r="H20" s="122"/>
-      <c r="I20" s="122"/>
-      <c r="J20" s="122"/>
-      <c r="K20" s="123"/>
-      <c r="L20" s="121"/>
-      <c r="M20" s="122"/>
-      <c r="N20" s="122"/>
-      <c r="O20" s="122"/>
-      <c r="P20" s="123"/>
-      <c r="Q20" s="121"/>
-      <c r="R20" s="122"/>
-      <c r="S20" s="122"/>
-      <c r="T20" s="122"/>
-      <c r="U20" s="122"/>
-      <c r="V20" s="123"/>
-      <c r="W20" s="121"/>
-      <c r="X20" s="122"/>
-      <c r="Y20" s="122"/>
-      <c r="Z20" s="122"/>
-      <c r="AA20" s="122"/>
-      <c r="AB20" s="122"/>
-      <c r="AC20" s="122"/>
-      <c r="AD20" s="122"/>
-      <c r="AE20" s="122"/>
-      <c r="AF20" s="122"/>
-      <c r="AG20" s="123"/>
+      <c r="C20" s="130" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="113"/>
+      <c r="E20" s="113"/>
+      <c r="F20" s="124"/>
+      <c r="G20" s="126"/>
+      <c r="H20" s="113"/>
+      <c r="I20" s="113"/>
+      <c r="J20" s="113"/>
+      <c r="K20" s="124"/>
+      <c r="L20" s="126"/>
+      <c r="M20" s="113"/>
+      <c r="N20" s="113"/>
+      <c r="O20" s="113"/>
+      <c r="P20" s="124"/>
+      <c r="Q20" s="126"/>
+      <c r="R20" s="113"/>
+      <c r="S20" s="113"/>
+      <c r="T20" s="113"/>
+      <c r="U20" s="113"/>
+      <c r="V20" s="124"/>
+      <c r="W20" s="126"/>
+      <c r="X20" s="113"/>
+      <c r="Y20" s="113"/>
+      <c r="Z20" s="113"/>
+      <c r="AA20" s="113"/>
+      <c r="AB20" s="113"/>
+      <c r="AC20" s="113"/>
+      <c r="AD20" s="113"/>
+      <c r="AE20" s="113"/>
+      <c r="AF20" s="113"/>
+      <c r="AG20" s="124"/>
       <c r="AH20" s="35"/>
       <c r="AI20" s="26"/>
     </row>
     <row r="21" spans="1:35" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="33"/>
       <c r="B21" s="34"/>
-      <c r="C21" s="124" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="122"/>
-      <c r="E21" s="122"/>
-      <c r="F21" s="123"/>
-      <c r="G21" s="121"/>
-      <c r="H21" s="122"/>
-      <c r="I21" s="122"/>
-      <c r="J21" s="122"/>
-      <c r="K21" s="123"/>
-      <c r="L21" s="121"/>
-      <c r="M21" s="122"/>
-      <c r="N21" s="122"/>
-      <c r="O21" s="122"/>
-      <c r="P21" s="123"/>
-      <c r="Q21" s="121"/>
-      <c r="R21" s="122"/>
-      <c r="S21" s="122"/>
-      <c r="T21" s="122"/>
-      <c r="U21" s="122"/>
-      <c r="V21" s="123"/>
-      <c r="W21" s="121"/>
-      <c r="X21" s="122"/>
-      <c r="Y21" s="122"/>
-      <c r="Z21" s="122"/>
-      <c r="AA21" s="122"/>
-      <c r="AB21" s="122"/>
-      <c r="AC21" s="122"/>
-      <c r="AD21" s="122"/>
-      <c r="AE21" s="122"/>
-      <c r="AF21" s="122"/>
-      <c r="AG21" s="123"/>
+      <c r="C21" s="130" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="124"/>
+      <c r="G21" s="126"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="113"/>
+      <c r="J21" s="113"/>
+      <c r="K21" s="124"/>
+      <c r="L21" s="126"/>
+      <c r="M21" s="113"/>
+      <c r="N21" s="113"/>
+      <c r="O21" s="113"/>
+      <c r="P21" s="124"/>
+      <c r="Q21" s="126"/>
+      <c r="R21" s="113"/>
+      <c r="S21" s="113"/>
+      <c r="T21" s="113"/>
+      <c r="U21" s="113"/>
+      <c r="V21" s="124"/>
+      <c r="W21" s="126"/>
+      <c r="X21" s="113"/>
+      <c r="Y21" s="113"/>
+      <c r="Z21" s="113"/>
+      <c r="AA21" s="113"/>
+      <c r="AB21" s="113"/>
+      <c r="AC21" s="113"/>
+      <c r="AD21" s="113"/>
+      <c r="AE21" s="113"/>
+      <c r="AF21" s="113"/>
+      <c r="AG21" s="124"/>
       <c r="AH21" s="35"/>
       <c r="AI21" s="26"/>
     </row>
     <row r="22" spans="1:35" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="33"/>
       <c r="B22" s="34"/>
-      <c r="C22" s="124" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="122"/>
-      <c r="E22" s="122"/>
-      <c r="F22" s="123"/>
-      <c r="G22" s="121"/>
-      <c r="H22" s="122"/>
-      <c r="I22" s="122"/>
-      <c r="J22" s="122"/>
-      <c r="K22" s="123"/>
-      <c r="L22" s="121"/>
-      <c r="M22" s="122"/>
-      <c r="N22" s="122"/>
-      <c r="O22" s="122"/>
-      <c r="P22" s="123"/>
-      <c r="Q22" s="121"/>
-      <c r="R22" s="122"/>
-      <c r="S22" s="122"/>
-      <c r="T22" s="122"/>
-      <c r="U22" s="122"/>
-      <c r="V22" s="123"/>
-      <c r="W22" s="121"/>
-      <c r="X22" s="122"/>
-      <c r="Y22" s="122"/>
-      <c r="Z22" s="122"/>
-      <c r="AA22" s="122"/>
-      <c r="AB22" s="122"/>
-      <c r="AC22" s="122"/>
-      <c r="AD22" s="122"/>
-      <c r="AE22" s="122"/>
-      <c r="AF22" s="122"/>
-      <c r="AG22" s="123"/>
+      <c r="C22" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="113"/>
+      <c r="E22" s="113"/>
+      <c r="F22" s="124"/>
+      <c r="G22" s="126"/>
+      <c r="H22" s="113"/>
+      <c r="I22" s="113"/>
+      <c r="J22" s="113"/>
+      <c r="K22" s="124"/>
+      <c r="L22" s="126"/>
+      <c r="M22" s="113"/>
+      <c r="N22" s="113"/>
+      <c r="O22" s="113"/>
+      <c r="P22" s="124"/>
+      <c r="Q22" s="126"/>
+      <c r="R22" s="113"/>
+      <c r="S22" s="113"/>
+      <c r="T22" s="113"/>
+      <c r="U22" s="113"/>
+      <c r="V22" s="124"/>
+      <c r="W22" s="126"/>
+      <c r="X22" s="113"/>
+      <c r="Y22" s="113"/>
+      <c r="Z22" s="113"/>
+      <c r="AA22" s="113"/>
+      <c r="AB22" s="113"/>
+      <c r="AC22" s="113"/>
+      <c r="AD22" s="113"/>
+      <c r="AE22" s="113"/>
+      <c r="AF22" s="113"/>
+      <c r="AG22" s="124"/>
       <c r="AH22" s="35"/>
       <c r="AI22" s="26"/>
     </row>
     <row r="23" spans="1:35" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="33"/>
       <c r="B23" s="34"/>
-      <c r="C23" s="124" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="122"/>
-      <c r="E23" s="122"/>
-      <c r="F23" s="123"/>
-      <c r="G23" s="121"/>
-      <c r="H23" s="122"/>
-      <c r="I23" s="122"/>
-      <c r="J23" s="122"/>
-      <c r="K23" s="123"/>
-      <c r="L23" s="121"/>
-      <c r="M23" s="122"/>
-      <c r="N23" s="122"/>
-      <c r="O23" s="122"/>
-      <c r="P23" s="123"/>
-      <c r="Q23" s="121"/>
-      <c r="R23" s="122"/>
-      <c r="S23" s="122"/>
-      <c r="T23" s="122"/>
-      <c r="U23" s="122"/>
-      <c r="V23" s="123"/>
-      <c r="W23" s="121"/>
-      <c r="X23" s="122"/>
-      <c r="Y23" s="122"/>
-      <c r="Z23" s="122"/>
-      <c r="AA23" s="122"/>
-      <c r="AB23" s="122"/>
-      <c r="AC23" s="122"/>
-      <c r="AD23" s="122"/>
-      <c r="AE23" s="122"/>
-      <c r="AF23" s="122"/>
-      <c r="AG23" s="123"/>
+      <c r="C23" s="130" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="113"/>
+      <c r="E23" s="113"/>
+      <c r="F23" s="124"/>
+      <c r="G23" s="126"/>
+      <c r="H23" s="113"/>
+      <c r="I23" s="113"/>
+      <c r="J23" s="113"/>
+      <c r="K23" s="124"/>
+      <c r="L23" s="126"/>
+      <c r="M23" s="113"/>
+      <c r="N23" s="113"/>
+      <c r="O23" s="113"/>
+      <c r="P23" s="124"/>
+      <c r="Q23" s="126"/>
+      <c r="R23" s="113"/>
+      <c r="S23" s="113"/>
+      <c r="T23" s="113"/>
+      <c r="U23" s="113"/>
+      <c r="V23" s="124"/>
+      <c r="W23" s="126"/>
+      <c r="X23" s="113"/>
+      <c r="Y23" s="113"/>
+      <c r="Z23" s="113"/>
+      <c r="AA23" s="113"/>
+      <c r="AB23" s="113"/>
+      <c r="AC23" s="113"/>
+      <c r="AD23" s="113"/>
+      <c r="AE23" s="113"/>
+      <c r="AF23" s="113"/>
+      <c r="AG23" s="124"/>
       <c r="AH23" s="35"/>
       <c r="AI23" s="26"/>
     </row>
     <row r="24" spans="1:35" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="33"/>
       <c r="B24" s="34"/>
-      <c r="C24" s="124" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" s="122"/>
-      <c r="E24" s="122"/>
-      <c r="F24" s="123"/>
-      <c r="G24" s="126"/>
-      <c r="H24" s="122"/>
-      <c r="I24" s="122"/>
-      <c r="J24" s="122"/>
-      <c r="K24" s="123"/>
-      <c r="L24" s="121"/>
-      <c r="M24" s="122"/>
-      <c r="N24" s="122"/>
-      <c r="O24" s="122"/>
-      <c r="P24" s="123"/>
-      <c r="Q24" s="121"/>
-      <c r="R24" s="122"/>
-      <c r="S24" s="122"/>
-      <c r="T24" s="122"/>
-      <c r="U24" s="122"/>
-      <c r="V24" s="123"/>
-      <c r="W24" s="121"/>
-      <c r="X24" s="122"/>
-      <c r="Y24" s="122"/>
-      <c r="Z24" s="122"/>
-      <c r="AA24" s="122"/>
-      <c r="AB24" s="122"/>
-      <c r="AC24" s="122"/>
-      <c r="AD24" s="122"/>
-      <c r="AE24" s="122"/>
-      <c r="AF24" s="122"/>
-      <c r="AG24" s="123"/>
+      <c r="C24" s="130" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="113"/>
+      <c r="E24" s="113"/>
+      <c r="F24" s="124"/>
+      <c r="G24" s="131"/>
+      <c r="H24" s="113"/>
+      <c r="I24" s="113"/>
+      <c r="J24" s="113"/>
+      <c r="K24" s="124"/>
+      <c r="L24" s="126"/>
+      <c r="M24" s="113"/>
+      <c r="N24" s="113"/>
+      <c r="O24" s="113"/>
+      <c r="P24" s="124"/>
+      <c r="Q24" s="126"/>
+      <c r="R24" s="113"/>
+      <c r="S24" s="113"/>
+      <c r="T24" s="113"/>
+      <c r="U24" s="113"/>
+      <c r="V24" s="124"/>
+      <c r="W24" s="126"/>
+      <c r="X24" s="113"/>
+      <c r="Y24" s="113"/>
+      <c r="Z24" s="113"/>
+      <c r="AA24" s="113"/>
+      <c r="AB24" s="113"/>
+      <c r="AC24" s="113"/>
+      <c r="AD24" s="113"/>
+      <c r="AE24" s="113"/>
+      <c r="AF24" s="113"/>
+      <c r="AG24" s="124"/>
       <c r="AH24" s="35"/>
       <c r="AI24" s="26"/>
     </row>
     <row r="25" spans="1:35" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="33"/>
       <c r="B25" s="34"/>
-      <c r="C25" s="124" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="122"/>
-      <c r="E25" s="122"/>
-      <c r="F25" s="123"/>
-      <c r="G25" s="126"/>
-      <c r="H25" s="122"/>
-      <c r="I25" s="122"/>
-      <c r="J25" s="122"/>
-      <c r="K25" s="123"/>
-      <c r="L25" s="121"/>
-      <c r="M25" s="122"/>
-      <c r="N25" s="122"/>
-      <c r="O25" s="122"/>
-      <c r="P25" s="123"/>
-      <c r="Q25" s="121"/>
-      <c r="R25" s="122"/>
-      <c r="S25" s="122"/>
-      <c r="T25" s="122"/>
-      <c r="U25" s="122"/>
-      <c r="V25" s="123"/>
-      <c r="W25" s="121"/>
-      <c r="X25" s="122"/>
-      <c r="Y25" s="122"/>
-      <c r="Z25" s="122"/>
-      <c r="AA25" s="122"/>
-      <c r="AB25" s="122"/>
-      <c r="AC25" s="122"/>
-      <c r="AD25" s="122"/>
-      <c r="AE25" s="122"/>
-      <c r="AF25" s="122"/>
-      <c r="AG25" s="123"/>
+      <c r="C25" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="113"/>
+      <c r="E25" s="113"/>
+      <c r="F25" s="124"/>
+      <c r="G25" s="131"/>
+      <c r="H25" s="113"/>
+      <c r="I25" s="113"/>
+      <c r="J25" s="113"/>
+      <c r="K25" s="124"/>
+      <c r="L25" s="126"/>
+      <c r="M25" s="113"/>
+      <c r="N25" s="113"/>
+      <c r="O25" s="113"/>
+      <c r="P25" s="124"/>
+      <c r="Q25" s="126"/>
+      <c r="R25" s="113"/>
+      <c r="S25" s="113"/>
+      <c r="T25" s="113"/>
+      <c r="U25" s="113"/>
+      <c r="V25" s="124"/>
+      <c r="W25" s="126"/>
+      <c r="X25" s="113"/>
+      <c r="Y25" s="113"/>
+      <c r="Z25" s="113"/>
+      <c r="AA25" s="113"/>
+      <c r="AB25" s="113"/>
+      <c r="AC25" s="113"/>
+      <c r="AD25" s="113"/>
+      <c r="AE25" s="113"/>
+      <c r="AF25" s="113"/>
+      <c r="AG25" s="124"/>
       <c r="AH25" s="35"/>
       <c r="AI25" s="26"/>
     </row>
     <row r="26" spans="1:35" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="33"/>
       <c r="B26" s="34"/>
-      <c r="C26" s="143" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="136"/>
-      <c r="E26" s="136"/>
-      <c r="F26" s="137"/>
-      <c r="G26" s="126"/>
-      <c r="H26" s="122"/>
-      <c r="I26" s="122"/>
-      <c r="J26" s="122"/>
-      <c r="K26" s="123"/>
-      <c r="L26" s="121"/>
-      <c r="M26" s="122"/>
-      <c r="N26" s="122"/>
-      <c r="O26" s="122"/>
-      <c r="P26" s="123"/>
-      <c r="Q26" s="121"/>
-      <c r="R26" s="122"/>
-      <c r="S26" s="122"/>
-      <c r="T26" s="122"/>
-      <c r="U26" s="122"/>
-      <c r="V26" s="123"/>
-      <c r="W26" s="121"/>
-      <c r="X26" s="122"/>
-      <c r="Y26" s="122"/>
-      <c r="Z26" s="122"/>
-      <c r="AA26" s="122"/>
-      <c r="AB26" s="122"/>
-      <c r="AC26" s="122"/>
-      <c r="AD26" s="122"/>
-      <c r="AE26" s="122"/>
-      <c r="AF26" s="122"/>
-      <c r="AG26" s="123"/>
+      <c r="C26" s="138" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="133"/>
+      <c r="E26" s="133"/>
+      <c r="F26" s="134"/>
+      <c r="G26" s="131"/>
+      <c r="H26" s="113"/>
+      <c r="I26" s="113"/>
+      <c r="J26" s="113"/>
+      <c r="K26" s="124"/>
+      <c r="L26" s="126"/>
+      <c r="M26" s="113"/>
+      <c r="N26" s="113"/>
+      <c r="O26" s="113"/>
+      <c r="P26" s="124"/>
+      <c r="Q26" s="126"/>
+      <c r="R26" s="113"/>
+      <c r="S26" s="113"/>
+      <c r="T26" s="113"/>
+      <c r="U26" s="113"/>
+      <c r="V26" s="124"/>
+      <c r="W26" s="126"/>
+      <c r="X26" s="113"/>
+      <c r="Y26" s="113"/>
+      <c r="Z26" s="113"/>
+      <c r="AA26" s="113"/>
+      <c r="AB26" s="113"/>
+      <c r="AC26" s="113"/>
+      <c r="AD26" s="113"/>
+      <c r="AE26" s="113"/>
+      <c r="AF26" s="113"/>
+      <c r="AG26" s="124"/>
       <c r="AH26" s="35"/>
       <c r="AI26" s="26"/>
     </row>
     <row r="27" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33"/>
       <c r="B27" s="34"/>
-      <c r="C27" s="138"/>
-      <c r="D27" s="139"/>
-      <c r="E27" s="139"/>
-      <c r="F27" s="140"/>
-      <c r="G27" s="126"/>
-      <c r="H27" s="122"/>
-      <c r="I27" s="122"/>
-      <c r="J27" s="122"/>
-      <c r="K27" s="123"/>
-      <c r="L27" s="121"/>
-      <c r="M27" s="122"/>
-      <c r="N27" s="122"/>
-      <c r="O27" s="122"/>
-      <c r="P27" s="123"/>
-      <c r="Q27" s="121"/>
-      <c r="R27" s="122"/>
-      <c r="S27" s="122"/>
-      <c r="T27" s="122"/>
-      <c r="U27" s="122"/>
-      <c r="V27" s="123"/>
-      <c r="W27" s="121"/>
-      <c r="X27" s="122"/>
-      <c r="Y27" s="122"/>
-      <c r="Z27" s="122"/>
-      <c r="AA27" s="122"/>
-      <c r="AB27" s="122"/>
-      <c r="AC27" s="122"/>
-      <c r="AD27" s="122"/>
-      <c r="AE27" s="122"/>
-      <c r="AF27" s="122"/>
-      <c r="AG27" s="123"/>
+      <c r="C27" s="106"/>
+      <c r="D27" s="107"/>
+      <c r="E27" s="107"/>
+      <c r="F27" s="108"/>
+      <c r="G27" s="131"/>
+      <c r="H27" s="113"/>
+      <c r="I27" s="113"/>
+      <c r="J27" s="113"/>
+      <c r="K27" s="124"/>
+      <c r="L27" s="126"/>
+      <c r="M27" s="113"/>
+      <c r="N27" s="113"/>
+      <c r="O27" s="113"/>
+      <c r="P27" s="124"/>
+      <c r="Q27" s="126"/>
+      <c r="R27" s="113"/>
+      <c r="S27" s="113"/>
+      <c r="T27" s="113"/>
+      <c r="U27" s="113"/>
+      <c r="V27" s="124"/>
+      <c r="W27" s="126"/>
+      <c r="X27" s="113"/>
+      <c r="Y27" s="113"/>
+      <c r="Z27" s="113"/>
+      <c r="AA27" s="113"/>
+      <c r="AB27" s="113"/>
+      <c r="AC27" s="113"/>
+      <c r="AD27" s="113"/>
+      <c r="AE27" s="113"/>
+      <c r="AF27" s="113"/>
+      <c r="AG27" s="124"/>
       <c r="AH27" s="35"/>
       <c r="AI27" s="26"/>
     </row>
@@ -2729,21 +2762,21 @@
       <c r="P28" s="20"/>
       <c r="Q28" s="20"/>
       <c r="R28" s="125"/>
-      <c r="S28" s="94"/>
-      <c r="T28" s="94"/>
-      <c r="U28" s="94"/>
-      <c r="V28" s="94"/>
-      <c r="W28" s="94"/>
-      <c r="X28" s="94"/>
+      <c r="S28" s="99"/>
+      <c r="T28" s="99"/>
+      <c r="U28" s="99"/>
+      <c r="V28" s="99"/>
+      <c r="W28" s="99"/>
+      <c r="X28" s="99"/>
       <c r="Y28" s="125"/>
-      <c r="Z28" s="94"/>
-      <c r="AA28" s="94"/>
-      <c r="AB28" s="94"/>
-      <c r="AC28" s="94"/>
-      <c r="AD28" s="94"/>
-      <c r="AE28" s="94"/>
-      <c r="AF28" s="94"/>
-      <c r="AG28" s="94"/>
+      <c r="Z28" s="99"/>
+      <c r="AA28" s="99"/>
+      <c r="AB28" s="99"/>
+      <c r="AC28" s="99"/>
+      <c r="AD28" s="99"/>
+      <c r="AE28" s="99"/>
+      <c r="AF28" s="99"/>
+      <c r="AG28" s="99"/>
       <c r="AH28" s="16"/>
       <c r="AI28" s="13"/>
     </row>
@@ -2786,41 +2819,41 @@
     </row>
     <row r="30" spans="1:35" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="23"/>
-      <c r="B30" s="98" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="99"/>
-      <c r="D30" s="99"/>
-      <c r="E30" s="99"/>
-      <c r="F30" s="99"/>
-      <c r="G30" s="99"/>
-      <c r="H30" s="99"/>
-      <c r="I30" s="99"/>
-      <c r="J30" s="99"/>
-      <c r="K30" s="99"/>
-      <c r="L30" s="99"/>
-      <c r="M30" s="99"/>
-      <c r="N30" s="99"/>
-      <c r="O30" s="99"/>
-      <c r="P30" s="99"/>
-      <c r="Q30" s="99"/>
-      <c r="R30" s="99"/>
-      <c r="S30" s="99"/>
-      <c r="T30" s="99"/>
-      <c r="U30" s="99"/>
-      <c r="V30" s="99"/>
-      <c r="W30" s="99"/>
-      <c r="X30" s="99"/>
-      <c r="Y30" s="99"/>
-      <c r="Z30" s="99"/>
-      <c r="AA30" s="99"/>
-      <c r="AB30" s="99"/>
-      <c r="AC30" s="99"/>
-      <c r="AD30" s="99"/>
-      <c r="AE30" s="99"/>
-      <c r="AF30" s="99"/>
-      <c r="AG30" s="99"/>
-      <c r="AH30" s="100"/>
+      <c r="B30" s="120" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="118"/>
+      <c r="D30" s="118"/>
+      <c r="E30" s="118"/>
+      <c r="F30" s="118"/>
+      <c r="G30" s="118"/>
+      <c r="H30" s="118"/>
+      <c r="I30" s="118"/>
+      <c r="J30" s="118"/>
+      <c r="K30" s="118"/>
+      <c r="L30" s="118"/>
+      <c r="M30" s="118"/>
+      <c r="N30" s="118"/>
+      <c r="O30" s="118"/>
+      <c r="P30" s="118"/>
+      <c r="Q30" s="118"/>
+      <c r="R30" s="118"/>
+      <c r="S30" s="118"/>
+      <c r="T30" s="118"/>
+      <c r="U30" s="118"/>
+      <c r="V30" s="118"/>
+      <c r="W30" s="118"/>
+      <c r="X30" s="118"/>
+      <c r="Y30" s="118"/>
+      <c r="Z30" s="118"/>
+      <c r="AA30" s="118"/>
+      <c r="AB30" s="118"/>
+      <c r="AC30" s="118"/>
+      <c r="AD30" s="118"/>
+      <c r="AE30" s="118"/>
+      <c r="AF30" s="118"/>
+      <c r="AG30" s="118"/>
+      <c r="AH30" s="119"/>
       <c r="AI30" s="13"/>
     </row>
     <row r="31" spans="1:35" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2863,54 +2896,54 @@
     <row r="32" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="38"/>
       <c r="B32" s="39"/>
-      <c r="C32" s="135" t="s">
+      <c r="C32" s="132" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" s="133"/>
+      <c r="E32" s="133"/>
+      <c r="F32" s="133"/>
+      <c r="G32" s="133"/>
+      <c r="H32" s="133"/>
+      <c r="I32" s="133"/>
+      <c r="J32" s="134"/>
+      <c r="K32" s="136" t="s">
         <v>25</v>
       </c>
-      <c r="D32" s="136"/>
-      <c r="E32" s="136"/>
-      <c r="F32" s="136"/>
-      <c r="G32" s="136"/>
-      <c r="H32" s="136"/>
-      <c r="I32" s="136"/>
-      <c r="J32" s="137"/>
-      <c r="K32" s="141" t="s">
+      <c r="L32" s="136" t="s">
         <v>26</v>
       </c>
-      <c r="L32" s="141" t="s">
-        <v>27</v>
-      </c>
-      <c r="M32" s="135" t="s">
+      <c r="M32" s="132" t="s">
+        <v>24</v>
+      </c>
+      <c r="N32" s="133"/>
+      <c r="O32" s="133"/>
+      <c r="P32" s="133"/>
+      <c r="Q32" s="133"/>
+      <c r="R32" s="133"/>
+      <c r="S32" s="133"/>
+      <c r="T32" s="134"/>
+      <c r="U32" s="136" t="s">
         <v>25</v>
       </c>
-      <c r="N32" s="136"/>
-      <c r="O32" s="136"/>
-      <c r="P32" s="136"/>
-      <c r="Q32" s="136"/>
-      <c r="R32" s="136"/>
-      <c r="S32" s="136"/>
-      <c r="T32" s="137"/>
-      <c r="U32" s="141" t="s">
+      <c r="V32" s="136" t="s">
         <v>26</v>
       </c>
-      <c r="V32" s="141" t="s">
-        <v>27</v>
-      </c>
-      <c r="W32" s="135" t="s">
+      <c r="W32" s="132" t="s">
+        <v>24</v>
+      </c>
+      <c r="X32" s="133"/>
+      <c r="Y32" s="133"/>
+      <c r="Z32" s="133"/>
+      <c r="AA32" s="133"/>
+      <c r="AB32" s="133"/>
+      <c r="AC32" s="133"/>
+      <c r="AD32" s="133"/>
+      <c r="AE32" s="134"/>
+      <c r="AF32" s="136" t="s">
         <v>25</v>
       </c>
-      <c r="X32" s="136"/>
-      <c r="Y32" s="136"/>
-      <c r="Z32" s="136"/>
-      <c r="AA32" s="136"/>
-      <c r="AB32" s="136"/>
-      <c r="AC32" s="136"/>
-      <c r="AD32" s="136"/>
-      <c r="AE32" s="137"/>
-      <c r="AF32" s="141" t="s">
+      <c r="AG32" s="136" t="s">
         <v>26</v>
-      </c>
-      <c r="AG32" s="141" t="s">
-        <v>27</v>
       </c>
       <c r="AH32" s="40"/>
       <c r="AI32" s="41"/>
@@ -2918,78 +2951,78 @@
     <row r="33" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="38"/>
       <c r="B33" s="39"/>
-      <c r="C33" s="138"/>
-      <c r="D33" s="139"/>
-      <c r="E33" s="139"/>
-      <c r="F33" s="139"/>
-      <c r="G33" s="139"/>
-      <c r="H33" s="139"/>
-      <c r="I33" s="139"/>
-      <c r="J33" s="140"/>
-      <c r="K33" s="142"/>
-      <c r="L33" s="142"/>
-      <c r="M33" s="138"/>
-      <c r="N33" s="139"/>
-      <c r="O33" s="139"/>
-      <c r="P33" s="139"/>
-      <c r="Q33" s="139"/>
-      <c r="R33" s="139"/>
-      <c r="S33" s="139"/>
-      <c r="T33" s="140"/>
-      <c r="U33" s="142"/>
-      <c r="V33" s="142"/>
-      <c r="W33" s="138"/>
-      <c r="X33" s="139"/>
-      <c r="Y33" s="139"/>
-      <c r="Z33" s="139"/>
-      <c r="AA33" s="139"/>
-      <c r="AB33" s="139"/>
-      <c r="AC33" s="139"/>
-      <c r="AD33" s="139"/>
-      <c r="AE33" s="140"/>
-      <c r="AF33" s="142"/>
-      <c r="AG33" s="142"/>
+      <c r="C33" s="106"/>
+      <c r="D33" s="107"/>
+      <c r="E33" s="107"/>
+      <c r="F33" s="107"/>
+      <c r="G33" s="107"/>
+      <c r="H33" s="107"/>
+      <c r="I33" s="107"/>
+      <c r="J33" s="108"/>
+      <c r="K33" s="137"/>
+      <c r="L33" s="137"/>
+      <c r="M33" s="106"/>
+      <c r="N33" s="107"/>
+      <c r="O33" s="107"/>
+      <c r="P33" s="107"/>
+      <c r="Q33" s="107"/>
+      <c r="R33" s="107"/>
+      <c r="S33" s="107"/>
+      <c r="T33" s="108"/>
+      <c r="U33" s="137"/>
+      <c r="V33" s="137"/>
+      <c r="W33" s="106"/>
+      <c r="X33" s="107"/>
+      <c r="Y33" s="107"/>
+      <c r="Z33" s="107"/>
+      <c r="AA33" s="107"/>
+      <c r="AB33" s="107"/>
+      <c r="AC33" s="107"/>
+      <c r="AD33" s="107"/>
+      <c r="AE33" s="108"/>
+      <c r="AF33" s="137"/>
+      <c r="AG33" s="137"/>
       <c r="AH33" s="42"/>
       <c r="AI33" s="43"/>
     </row>
     <row r="34" spans="1:35" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="23"/>
       <c r="B34" s="24"/>
-      <c r="C34" s="134" t="s">
-        <v>28</v>
-      </c>
-      <c r="D34" s="122"/>
-      <c r="E34" s="122"/>
-      <c r="F34" s="122"/>
-      <c r="G34" s="122"/>
-      <c r="H34" s="122"/>
-      <c r="I34" s="122"/>
-      <c r="J34" s="123"/>
+      <c r="C34" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" s="113"/>
+      <c r="E34" s="113"/>
+      <c r="F34" s="113"/>
+      <c r="G34" s="113"/>
+      <c r="H34" s="113"/>
+      <c r="I34" s="113"/>
+      <c r="J34" s="124"/>
       <c r="K34" s="44"/>
       <c r="L34" s="44"/>
-      <c r="M34" s="134" t="s">
-        <v>29</v>
-      </c>
-      <c r="N34" s="122"/>
-      <c r="O34" s="122"/>
-      <c r="P34" s="122"/>
-      <c r="Q34" s="122"/>
-      <c r="R34" s="122"/>
-      <c r="S34" s="122"/>
-      <c r="T34" s="123"/>
+      <c r="M34" s="135" t="s">
+        <v>28</v>
+      </c>
+      <c r="N34" s="113"/>
+      <c r="O34" s="113"/>
+      <c r="P34" s="113"/>
+      <c r="Q34" s="113"/>
+      <c r="R34" s="113"/>
+      <c r="S34" s="113"/>
+      <c r="T34" s="124"/>
       <c r="U34" s="44"/>
       <c r="V34" s="44"/>
-      <c r="W34" s="134" t="s">
-        <v>30</v>
-      </c>
-      <c r="X34" s="122"/>
-      <c r="Y34" s="122"/>
-      <c r="Z34" s="122"/>
-      <c r="AA34" s="122"/>
-      <c r="AB34" s="122"/>
-      <c r="AC34" s="122"/>
-      <c r="AD34" s="122"/>
-      <c r="AE34" s="123"/>
+      <c r="W34" s="135" t="s">
+        <v>29</v>
+      </c>
+      <c r="X34" s="113"/>
+      <c r="Y34" s="113"/>
+      <c r="Z34" s="113"/>
+      <c r="AA34" s="113"/>
+      <c r="AB34" s="113"/>
+      <c r="AC34" s="113"/>
+      <c r="AD34" s="113"/>
+      <c r="AE34" s="124"/>
       <c r="AF34" s="44"/>
       <c r="AG34" s="44"/>
       <c r="AH34" s="42"/>
@@ -2998,41 +3031,41 @@
     <row r="35" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="23"/>
       <c r="B35" s="24"/>
-      <c r="C35" s="134" t="s">
-        <v>31</v>
-      </c>
-      <c r="D35" s="122"/>
-      <c r="E35" s="122"/>
-      <c r="F35" s="122"/>
-      <c r="G35" s="122"/>
-      <c r="H35" s="122"/>
-      <c r="I35" s="122"/>
-      <c r="J35" s="123"/>
+      <c r="C35" s="135" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="113"/>
+      <c r="E35" s="113"/>
+      <c r="F35" s="113"/>
+      <c r="G35" s="113"/>
+      <c r="H35" s="113"/>
+      <c r="I35" s="113"/>
+      <c r="J35" s="124"/>
       <c r="K35" s="44"/>
       <c r="L35" s="44"/>
-      <c r="M35" s="134" t="s">
-        <v>32</v>
-      </c>
-      <c r="N35" s="122"/>
-      <c r="O35" s="122"/>
-      <c r="P35" s="122"/>
-      <c r="Q35" s="122"/>
-      <c r="R35" s="122"/>
-      <c r="S35" s="122"/>
-      <c r="T35" s="123"/>
+      <c r="M35" s="135" t="s">
+        <v>31</v>
+      </c>
+      <c r="N35" s="113"/>
+      <c r="O35" s="113"/>
+      <c r="P35" s="113"/>
+      <c r="Q35" s="113"/>
+      <c r="R35" s="113"/>
+      <c r="S35" s="113"/>
+      <c r="T35" s="124"/>
       <c r="U35" s="44"/>
       <c r="V35" s="44"/>
-      <c r="W35" s="134" t="s">
-        <v>33</v>
-      </c>
-      <c r="X35" s="122"/>
-      <c r="Y35" s="122"/>
-      <c r="Z35" s="122"/>
-      <c r="AA35" s="122"/>
-      <c r="AB35" s="122"/>
-      <c r="AC35" s="122"/>
-      <c r="AD35" s="122"/>
-      <c r="AE35" s="123"/>
+      <c r="W35" s="135" t="s">
+        <v>32</v>
+      </c>
+      <c r="X35" s="113"/>
+      <c r="Y35" s="113"/>
+      <c r="Z35" s="113"/>
+      <c r="AA35" s="113"/>
+      <c r="AB35" s="113"/>
+      <c r="AC35" s="113"/>
+      <c r="AD35" s="113"/>
+      <c r="AE35" s="124"/>
       <c r="AF35" s="44"/>
       <c r="AG35" s="44"/>
       <c r="AH35" s="42"/>
@@ -3041,41 +3074,41 @@
     <row r="36" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="23"/>
       <c r="B36" s="24"/>
-      <c r="C36" s="134" t="s">
-        <v>34</v>
-      </c>
-      <c r="D36" s="122"/>
-      <c r="E36" s="122"/>
-      <c r="F36" s="122"/>
-      <c r="G36" s="122"/>
-      <c r="H36" s="122"/>
-      <c r="I36" s="122"/>
-      <c r="J36" s="123"/>
+      <c r="C36" s="135" t="s">
+        <v>33</v>
+      </c>
+      <c r="D36" s="113"/>
+      <c r="E36" s="113"/>
+      <c r="F36" s="113"/>
+      <c r="G36" s="113"/>
+      <c r="H36" s="113"/>
+      <c r="I36" s="113"/>
+      <c r="J36" s="124"/>
       <c r="K36" s="44"/>
       <c r="L36" s="44"/>
-      <c r="M36" s="134" t="s">
-        <v>35</v>
-      </c>
-      <c r="N36" s="122"/>
-      <c r="O36" s="122"/>
-      <c r="P36" s="122"/>
-      <c r="Q36" s="122"/>
-      <c r="R36" s="122"/>
-      <c r="S36" s="122"/>
-      <c r="T36" s="123"/>
+      <c r="M36" s="135" t="s">
+        <v>34</v>
+      </c>
+      <c r="N36" s="113"/>
+      <c r="O36" s="113"/>
+      <c r="P36" s="113"/>
+      <c r="Q36" s="113"/>
+      <c r="R36" s="113"/>
+      <c r="S36" s="113"/>
+      <c r="T36" s="124"/>
       <c r="U36" s="44"/>
       <c r="V36" s="44"/>
-      <c r="W36" s="134" t="s">
-        <v>36</v>
-      </c>
-      <c r="X36" s="122"/>
-      <c r="Y36" s="122"/>
-      <c r="Z36" s="122"/>
-      <c r="AA36" s="122"/>
-      <c r="AB36" s="122"/>
-      <c r="AC36" s="122"/>
-      <c r="AD36" s="122"/>
-      <c r="AE36" s="123"/>
+      <c r="W36" s="135" t="s">
+        <v>35</v>
+      </c>
+      <c r="X36" s="113"/>
+      <c r="Y36" s="113"/>
+      <c r="Z36" s="113"/>
+      <c r="AA36" s="113"/>
+      <c r="AB36" s="113"/>
+      <c r="AC36" s="113"/>
+      <c r="AD36" s="113"/>
+      <c r="AE36" s="124"/>
       <c r="AF36" s="44"/>
       <c r="AG36" s="44"/>
       <c r="AH36" s="42"/>
@@ -3084,41 +3117,41 @@
     <row r="37" spans="1:35" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="23"/>
       <c r="B37" s="24"/>
-      <c r="C37" s="134" t="s">
-        <v>37</v>
-      </c>
-      <c r="D37" s="122"/>
-      <c r="E37" s="122"/>
-      <c r="F37" s="122"/>
-      <c r="G37" s="122"/>
-      <c r="H37" s="122"/>
-      <c r="I37" s="122"/>
-      <c r="J37" s="123"/>
+      <c r="C37" s="135" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="113"/>
+      <c r="E37" s="113"/>
+      <c r="F37" s="113"/>
+      <c r="G37" s="113"/>
+      <c r="H37" s="113"/>
+      <c r="I37" s="113"/>
+      <c r="J37" s="124"/>
       <c r="K37" s="44"/>
       <c r="L37" s="44"/>
-      <c r="M37" s="134" t="s">
-        <v>38</v>
-      </c>
-      <c r="N37" s="122"/>
-      <c r="O37" s="122"/>
-      <c r="P37" s="122"/>
-      <c r="Q37" s="122"/>
-      <c r="R37" s="122"/>
-      <c r="S37" s="122"/>
-      <c r="T37" s="123"/>
+      <c r="M37" s="135" t="s">
+        <v>37</v>
+      </c>
+      <c r="N37" s="113"/>
+      <c r="O37" s="113"/>
+      <c r="P37" s="113"/>
+      <c r="Q37" s="113"/>
+      <c r="R37" s="113"/>
+      <c r="S37" s="113"/>
+      <c r="T37" s="124"/>
       <c r="U37" s="44"/>
       <c r="V37" s="44"/>
-      <c r="W37" s="134" t="s">
-        <v>39</v>
-      </c>
-      <c r="X37" s="122"/>
-      <c r="Y37" s="122"/>
-      <c r="Z37" s="122"/>
-      <c r="AA37" s="122"/>
-      <c r="AB37" s="122"/>
-      <c r="AC37" s="122"/>
-      <c r="AD37" s="122"/>
-      <c r="AE37" s="123"/>
+      <c r="W37" s="135" t="s">
+        <v>38</v>
+      </c>
+      <c r="X37" s="113"/>
+      <c r="Y37" s="113"/>
+      <c r="Z37" s="113"/>
+      <c r="AA37" s="113"/>
+      <c r="AB37" s="113"/>
+      <c r="AC37" s="113"/>
+      <c r="AD37" s="113"/>
+      <c r="AE37" s="124"/>
       <c r="AF37" s="44"/>
       <c r="AG37" s="44"/>
       <c r="AH37" s="42"/>
@@ -3127,39 +3160,39 @@
     <row r="38" spans="1:35" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="38"/>
       <c r="B38" s="39"/>
-      <c r="C38" s="132" t="s">
-        <v>40</v>
-      </c>
-      <c r="D38" s="122"/>
-      <c r="E38" s="122"/>
-      <c r="F38" s="122"/>
-      <c r="G38" s="122"/>
-      <c r="H38" s="122"/>
-      <c r="I38" s="122"/>
-      <c r="J38" s="123"/>
-      <c r="K38" s="133"/>
-      <c r="L38" s="122"/>
-      <c r="M38" s="122"/>
-      <c r="N38" s="122"/>
-      <c r="O38" s="122"/>
-      <c r="P38" s="122"/>
-      <c r="Q38" s="122"/>
-      <c r="R38" s="122"/>
-      <c r="S38" s="122"/>
-      <c r="T38" s="122"/>
-      <c r="U38" s="122"/>
-      <c r="V38" s="122"/>
-      <c r="W38" s="122"/>
-      <c r="X38" s="122"/>
-      <c r="Y38" s="122"/>
-      <c r="Z38" s="122"/>
-      <c r="AA38" s="122"/>
-      <c r="AB38" s="122"/>
-      <c r="AC38" s="122"/>
-      <c r="AD38" s="122"/>
-      <c r="AE38" s="122"/>
-      <c r="AF38" s="122"/>
-      <c r="AG38" s="123"/>
+      <c r="C38" s="139" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="113"/>
+      <c r="E38" s="113"/>
+      <c r="F38" s="113"/>
+      <c r="G38" s="113"/>
+      <c r="H38" s="113"/>
+      <c r="I38" s="113"/>
+      <c r="J38" s="124"/>
+      <c r="K38" s="140"/>
+      <c r="L38" s="113"/>
+      <c r="M38" s="113"/>
+      <c r="N38" s="113"/>
+      <c r="O38" s="113"/>
+      <c r="P38" s="113"/>
+      <c r="Q38" s="113"/>
+      <c r="R38" s="113"/>
+      <c r="S38" s="113"/>
+      <c r="T38" s="113"/>
+      <c r="U38" s="113"/>
+      <c r="V38" s="113"/>
+      <c r="W38" s="113"/>
+      <c r="X38" s="113"/>
+      <c r="Y38" s="113"/>
+      <c r="Z38" s="113"/>
+      <c r="AA38" s="113"/>
+      <c r="AB38" s="113"/>
+      <c r="AC38" s="113"/>
+      <c r="AD38" s="113"/>
+      <c r="AE38" s="113"/>
+      <c r="AF38" s="113"/>
+      <c r="AG38" s="124"/>
       <c r="AH38" s="42"/>
       <c r="AI38" s="43"/>
     </row>
@@ -3182,61 +3215,61 @@
       <c r="P39" s="20"/>
       <c r="Q39" s="2"/>
       <c r="R39" s="125"/>
-      <c r="S39" s="94"/>
-      <c r="T39" s="94"/>
-      <c r="U39" s="94"/>
-      <c r="V39" s="94"/>
-      <c r="W39" s="94"/>
-      <c r="X39" s="94"/>
+      <c r="S39" s="99"/>
+      <c r="T39" s="99"/>
+      <c r="U39" s="99"/>
+      <c r="V39" s="99"/>
+      <c r="W39" s="99"/>
+      <c r="X39" s="99"/>
       <c r="Y39" s="125"/>
-      <c r="Z39" s="94"/>
-      <c r="AA39" s="94"/>
-      <c r="AB39" s="94"/>
-      <c r="AC39" s="94"/>
-      <c r="AD39" s="94"/>
-      <c r="AE39" s="94"/>
-      <c r="AF39" s="94"/>
-      <c r="AG39" s="94"/>
+      <c r="Z39" s="99"/>
+      <c r="AA39" s="99"/>
+      <c r="AB39" s="99"/>
+      <c r="AC39" s="99"/>
+      <c r="AD39" s="99"/>
+      <c r="AE39" s="99"/>
+      <c r="AF39" s="99"/>
+      <c r="AG39" s="99"/>
       <c r="AH39" s="16"/>
       <c r="AI39" s="13"/>
     </row>
     <row r="40" spans="1:35" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7"/>
-      <c r="B40" s="98" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" s="99"/>
-      <c r="D40" s="99"/>
-      <c r="E40" s="99"/>
-      <c r="F40" s="99"/>
-      <c r="G40" s="99"/>
-      <c r="H40" s="99"/>
-      <c r="I40" s="99"/>
-      <c r="J40" s="99"/>
-      <c r="K40" s="99"/>
-      <c r="L40" s="99"/>
-      <c r="M40" s="99"/>
-      <c r="N40" s="99"/>
-      <c r="O40" s="99"/>
-      <c r="P40" s="99"/>
-      <c r="Q40" s="99"/>
-      <c r="R40" s="99"/>
-      <c r="S40" s="99"/>
-      <c r="T40" s="99"/>
-      <c r="U40" s="99"/>
-      <c r="V40" s="99"/>
-      <c r="W40" s="99"/>
-      <c r="X40" s="99"/>
-      <c r="Y40" s="99"/>
-      <c r="Z40" s="99"/>
-      <c r="AA40" s="99"/>
-      <c r="AB40" s="99"/>
-      <c r="AC40" s="99"/>
-      <c r="AD40" s="99"/>
-      <c r="AE40" s="99"/>
-      <c r="AF40" s="99"/>
-      <c r="AG40" s="99"/>
-      <c r="AH40" s="100"/>
+      <c r="B40" s="120" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="118"/>
+      <c r="D40" s="118"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="118"/>
+      <c r="H40" s="118"/>
+      <c r="I40" s="118"/>
+      <c r="J40" s="118"/>
+      <c r="K40" s="118"/>
+      <c r="L40" s="118"/>
+      <c r="M40" s="118"/>
+      <c r="N40" s="118"/>
+      <c r="O40" s="118"/>
+      <c r="P40" s="118"/>
+      <c r="Q40" s="118"/>
+      <c r="R40" s="118"/>
+      <c r="S40" s="118"/>
+      <c r="T40" s="118"/>
+      <c r="U40" s="118"/>
+      <c r="V40" s="118"/>
+      <c r="W40" s="118"/>
+      <c r="X40" s="118"/>
+      <c r="Y40" s="118"/>
+      <c r="Z40" s="118"/>
+      <c r="AA40" s="118"/>
+      <c r="AB40" s="118"/>
+      <c r="AC40" s="118"/>
+      <c r="AD40" s="118"/>
+      <c r="AE40" s="118"/>
+      <c r="AF40" s="118"/>
+      <c r="AG40" s="118"/>
+      <c r="AH40" s="119"/>
       <c r="AI40" s="7"/>
     </row>
     <row r="41" spans="1:35" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3279,48 +3312,48 @@
     <row r="42" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="49"/>
       <c r="B42" s="50"/>
-      <c r="C42" s="131" t="s">
+      <c r="C42" s="141" t="s">
+        <v>41</v>
+      </c>
+      <c r="D42" s="113"/>
+      <c r="E42" s="113"/>
+      <c r="F42" s="113"/>
+      <c r="G42" s="113"/>
+      <c r="H42" s="113"/>
+      <c r="I42" s="113"/>
+      <c r="J42" s="124"/>
+      <c r="K42" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="D42" s="122"/>
-      <c r="E42" s="122"/>
-      <c r="F42" s="122"/>
-      <c r="G42" s="122"/>
-      <c r="H42" s="122"/>
-      <c r="I42" s="122"/>
-      <c r="J42" s="123"/>
-      <c r="K42" s="51" t="s">
+      <c r="L42" s="52"/>
+      <c r="M42" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="L42" s="52"/>
-      <c r="M42" s="131" t="s">
+      <c r="N42" s="113"/>
+      <c r="O42" s="113"/>
+      <c r="P42" s="113"/>
+      <c r="Q42" s="113"/>
+      <c r="R42" s="113"/>
+      <c r="S42" s="113"/>
+      <c r="T42" s="113"/>
+      <c r="U42" s="124"/>
+      <c r="V42" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="W42" s="53"/>
+      <c r="X42" s="141" t="s">
         <v>44</v>
       </c>
-      <c r="N42" s="122"/>
-      <c r="O42" s="122"/>
-      <c r="P42" s="122"/>
-      <c r="Q42" s="122"/>
-      <c r="R42" s="122"/>
-      <c r="S42" s="122"/>
-      <c r="T42" s="122"/>
-      <c r="U42" s="123"/>
-      <c r="V42" s="51" t="s">
-        <v>43</v>
-      </c>
-      <c r="W42" s="53"/>
-      <c r="X42" s="131" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y42" s="122"/>
-      <c r="Z42" s="122"/>
-      <c r="AA42" s="122"/>
-      <c r="AB42" s="122"/>
-      <c r="AC42" s="122"/>
-      <c r="AD42" s="122"/>
-      <c r="AE42" s="122"/>
-      <c r="AF42" s="123"/>
+      <c r="Y42" s="113"/>
+      <c r="Z42" s="113"/>
+      <c r="AA42" s="113"/>
+      <c r="AB42" s="113"/>
+      <c r="AC42" s="113"/>
+      <c r="AD42" s="113"/>
+      <c r="AE42" s="113"/>
+      <c r="AF42" s="124"/>
       <c r="AG42" s="51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH42" s="54"/>
       <c r="AI42" s="49"/>
@@ -3328,46 +3361,46 @@
     <row r="43" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="55"/>
       <c r="B43" s="56"/>
-      <c r="C43" s="130" t="s">
-        <v>46</v>
-      </c>
-      <c r="D43" s="122"/>
-      <c r="E43" s="122"/>
-      <c r="F43" s="122"/>
-      <c r="G43" s="122"/>
-      <c r="H43" s="122"/>
-      <c r="I43" s="122"/>
-      <c r="J43" s="123"/>
+      <c r="C43" s="142" t="s">
+        <v>45</v>
+      </c>
+      <c r="D43" s="113"/>
+      <c r="E43" s="113"/>
+      <c r="F43" s="113"/>
+      <c r="G43" s="113"/>
+      <c r="H43" s="113"/>
+      <c r="I43" s="113"/>
+      <c r="J43" s="124"/>
       <c r="K43" s="57">
         <v>3</v>
       </c>
       <c r="L43" s="52"/>
-      <c r="M43" s="130" t="s">
-        <v>46</v>
-      </c>
-      <c r="N43" s="122"/>
-      <c r="O43" s="122"/>
-      <c r="P43" s="122"/>
-      <c r="Q43" s="122"/>
-      <c r="R43" s="122"/>
-      <c r="S43" s="122"/>
-      <c r="T43" s="122"/>
-      <c r="U43" s="123"/>
+      <c r="M43" s="142" t="s">
+        <v>45</v>
+      </c>
+      <c r="N43" s="113"/>
+      <c r="O43" s="113"/>
+      <c r="P43" s="113"/>
+      <c r="Q43" s="113"/>
+      <c r="R43" s="113"/>
+      <c r="S43" s="113"/>
+      <c r="T43" s="113"/>
+      <c r="U43" s="124"/>
       <c r="V43" s="57">
         <v>3</v>
       </c>
       <c r="W43" s="58"/>
-      <c r="X43" s="130" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y43" s="122"/>
-      <c r="Z43" s="122"/>
-      <c r="AA43" s="122"/>
-      <c r="AB43" s="122"/>
-      <c r="AC43" s="122"/>
-      <c r="AD43" s="122"/>
-      <c r="AE43" s="122"/>
-      <c r="AF43" s="123"/>
+      <c r="X43" s="142" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y43" s="113"/>
+      <c r="Z43" s="113"/>
+      <c r="AA43" s="113"/>
+      <c r="AB43" s="113"/>
+      <c r="AC43" s="113"/>
+      <c r="AD43" s="113"/>
+      <c r="AE43" s="113"/>
+      <c r="AF43" s="124"/>
       <c r="AG43" s="57">
         <v>3</v>
       </c>
@@ -3377,46 +3410,46 @@
     <row r="44" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="55"/>
       <c r="B44" s="56"/>
-      <c r="C44" s="130" t="s">
-        <v>47</v>
-      </c>
-      <c r="D44" s="122"/>
-      <c r="E44" s="122"/>
-      <c r="F44" s="122"/>
-      <c r="G44" s="122"/>
-      <c r="H44" s="122"/>
-      <c r="I44" s="122"/>
-      <c r="J44" s="123"/>
+      <c r="C44" s="142" t="s">
+        <v>46</v>
+      </c>
+      <c r="D44" s="113"/>
+      <c r="E44" s="113"/>
+      <c r="F44" s="113"/>
+      <c r="G44" s="113"/>
+      <c r="H44" s="113"/>
+      <c r="I44" s="113"/>
+      <c r="J44" s="124"/>
       <c r="K44" s="57">
         <v>2</v>
       </c>
       <c r="L44" s="52"/>
-      <c r="M44" s="130" t="s">
-        <v>47</v>
-      </c>
-      <c r="N44" s="122"/>
-      <c r="O44" s="122"/>
-      <c r="P44" s="122"/>
-      <c r="Q44" s="122"/>
-      <c r="R44" s="122"/>
-      <c r="S44" s="122"/>
-      <c r="T44" s="122"/>
-      <c r="U44" s="123"/>
+      <c r="M44" s="142" t="s">
+        <v>46</v>
+      </c>
+      <c r="N44" s="113"/>
+      <c r="O44" s="113"/>
+      <c r="P44" s="113"/>
+      <c r="Q44" s="113"/>
+      <c r="R44" s="113"/>
+      <c r="S44" s="113"/>
+      <c r="T44" s="113"/>
+      <c r="U44" s="124"/>
       <c r="V44" s="57">
         <v>2</v>
       </c>
       <c r="W44" s="58"/>
-      <c r="X44" s="130" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y44" s="122"/>
-      <c r="Z44" s="122"/>
-      <c r="AA44" s="122"/>
-      <c r="AB44" s="122"/>
-      <c r="AC44" s="122"/>
-      <c r="AD44" s="122"/>
-      <c r="AE44" s="122"/>
-      <c r="AF44" s="123"/>
+      <c r="X44" s="142" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y44" s="113"/>
+      <c r="Z44" s="113"/>
+      <c r="AA44" s="113"/>
+      <c r="AB44" s="113"/>
+      <c r="AC44" s="113"/>
+      <c r="AD44" s="113"/>
+      <c r="AE44" s="113"/>
+      <c r="AF44" s="124"/>
       <c r="AG44" s="57">
         <v>2</v>
       </c>
@@ -3426,46 +3459,46 @@
     <row r="45" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="55"/>
       <c r="B45" s="56"/>
-      <c r="C45" s="130" t="s">
-        <v>48</v>
-      </c>
-      <c r="D45" s="122"/>
-      <c r="E45" s="122"/>
-      <c r="F45" s="122"/>
-      <c r="G45" s="122"/>
-      <c r="H45" s="122"/>
-      <c r="I45" s="122"/>
-      <c r="J45" s="123"/>
+      <c r="C45" s="142" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" s="113"/>
+      <c r="E45" s="113"/>
+      <c r="F45" s="113"/>
+      <c r="G45" s="113"/>
+      <c r="H45" s="113"/>
+      <c r="I45" s="113"/>
+      <c r="J45" s="124"/>
       <c r="K45" s="57">
         <v>1</v>
       </c>
       <c r="L45" s="52"/>
-      <c r="M45" s="130" t="s">
-        <v>48</v>
-      </c>
-      <c r="N45" s="122"/>
-      <c r="O45" s="122"/>
-      <c r="P45" s="122"/>
-      <c r="Q45" s="122"/>
-      <c r="R45" s="122"/>
-      <c r="S45" s="122"/>
-      <c r="T45" s="122"/>
-      <c r="U45" s="123"/>
+      <c r="M45" s="142" t="s">
+        <v>47</v>
+      </c>
+      <c r="N45" s="113"/>
+      <c r="O45" s="113"/>
+      <c r="P45" s="113"/>
+      <c r="Q45" s="113"/>
+      <c r="R45" s="113"/>
+      <c r="S45" s="113"/>
+      <c r="T45" s="113"/>
+      <c r="U45" s="124"/>
       <c r="V45" s="57">
         <v>1</v>
       </c>
       <c r="W45" s="58"/>
-      <c r="X45" s="130" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y45" s="122"/>
-      <c r="Z45" s="122"/>
-      <c r="AA45" s="122"/>
-      <c r="AB45" s="122"/>
-      <c r="AC45" s="122"/>
-      <c r="AD45" s="122"/>
-      <c r="AE45" s="122"/>
-      <c r="AF45" s="123"/>
+      <c r="X45" s="142" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y45" s="113"/>
+      <c r="Z45" s="113"/>
+      <c r="AA45" s="113"/>
+      <c r="AB45" s="113"/>
+      <c r="AC45" s="113"/>
+      <c r="AD45" s="113"/>
+      <c r="AE45" s="113"/>
+      <c r="AF45" s="124"/>
       <c r="AG45" s="57">
         <v>1</v>
       </c>
@@ -3512,48 +3545,48 @@
     <row r="47" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="49"/>
       <c r="B47" s="50"/>
-      <c r="C47" s="131" t="s">
+      <c r="C47" s="141" t="s">
+        <v>48</v>
+      </c>
+      <c r="D47" s="113"/>
+      <c r="E47" s="113"/>
+      <c r="F47" s="113"/>
+      <c r="G47" s="113"/>
+      <c r="H47" s="113"/>
+      <c r="I47" s="113"/>
+      <c r="J47" s="124"/>
+      <c r="K47" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="L47" s="52"/>
+      <c r="M47" s="141" t="s">
         <v>49</v>
       </c>
-      <c r="D47" s="122"/>
-      <c r="E47" s="122"/>
-      <c r="F47" s="122"/>
-      <c r="G47" s="122"/>
-      <c r="H47" s="122"/>
-      <c r="I47" s="122"/>
-      <c r="J47" s="123"/>
-      <c r="K47" s="51" t="s">
-        <v>43</v>
-      </c>
-      <c r="L47" s="52"/>
-      <c r="M47" s="131" t="s">
+      <c r="N47" s="113"/>
+      <c r="O47" s="113"/>
+      <c r="P47" s="113"/>
+      <c r="Q47" s="113"/>
+      <c r="R47" s="113"/>
+      <c r="S47" s="113"/>
+      <c r="T47" s="113"/>
+      <c r="U47" s="124"/>
+      <c r="V47" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="W47" s="62"/>
+      <c r="X47" s="141" t="s">
         <v>50</v>
       </c>
-      <c r="N47" s="122"/>
-      <c r="O47" s="122"/>
-      <c r="P47" s="122"/>
-      <c r="Q47" s="122"/>
-      <c r="R47" s="122"/>
-      <c r="S47" s="122"/>
-      <c r="T47" s="122"/>
-      <c r="U47" s="123"/>
-      <c r="V47" s="51" t="s">
-        <v>43</v>
-      </c>
-      <c r="W47" s="62"/>
-      <c r="X47" s="131" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y47" s="122"/>
-      <c r="Z47" s="122"/>
-      <c r="AA47" s="122"/>
-      <c r="AB47" s="122"/>
-      <c r="AC47" s="122"/>
-      <c r="AD47" s="122"/>
-      <c r="AE47" s="122"/>
-      <c r="AF47" s="123"/>
+      <c r="Y47" s="113"/>
+      <c r="Z47" s="113"/>
+      <c r="AA47" s="113"/>
+      <c r="AB47" s="113"/>
+      <c r="AC47" s="113"/>
+      <c r="AD47" s="113"/>
+      <c r="AE47" s="113"/>
+      <c r="AF47" s="124"/>
       <c r="AG47" s="51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH47" s="54"/>
       <c r="AI47" s="49"/>
@@ -3561,46 +3594,46 @@
     <row r="48" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="55"/>
       <c r="B48" s="56"/>
-      <c r="C48" s="130" t="s">
-        <v>46</v>
-      </c>
-      <c r="D48" s="122"/>
-      <c r="E48" s="122"/>
-      <c r="F48" s="122"/>
-      <c r="G48" s="122"/>
-      <c r="H48" s="122"/>
-      <c r="I48" s="122"/>
-      <c r="J48" s="123"/>
+      <c r="C48" s="142" t="s">
+        <v>45</v>
+      </c>
+      <c r="D48" s="113"/>
+      <c r="E48" s="113"/>
+      <c r="F48" s="113"/>
+      <c r="G48" s="113"/>
+      <c r="H48" s="113"/>
+      <c r="I48" s="113"/>
+      <c r="J48" s="124"/>
       <c r="K48" s="57">
         <v>3</v>
       </c>
       <c r="L48" s="52"/>
-      <c r="M48" s="130" t="s">
-        <v>46</v>
-      </c>
-      <c r="N48" s="122"/>
-      <c r="O48" s="122"/>
-      <c r="P48" s="122"/>
-      <c r="Q48" s="122"/>
-      <c r="R48" s="122"/>
-      <c r="S48" s="122"/>
-      <c r="T48" s="122"/>
-      <c r="U48" s="123"/>
+      <c r="M48" s="142" t="s">
+        <v>45</v>
+      </c>
+      <c r="N48" s="113"/>
+      <c r="O48" s="113"/>
+      <c r="P48" s="113"/>
+      <c r="Q48" s="113"/>
+      <c r="R48" s="113"/>
+      <c r="S48" s="113"/>
+      <c r="T48" s="113"/>
+      <c r="U48" s="124"/>
       <c r="V48" s="57">
         <v>3</v>
       </c>
       <c r="W48" s="62"/>
-      <c r="X48" s="130" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y48" s="122"/>
-      <c r="Z48" s="122"/>
-      <c r="AA48" s="122"/>
-      <c r="AB48" s="122"/>
-      <c r="AC48" s="122"/>
-      <c r="AD48" s="122"/>
-      <c r="AE48" s="122"/>
-      <c r="AF48" s="123"/>
+      <c r="X48" s="142" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y48" s="113"/>
+      <c r="Z48" s="113"/>
+      <c r="AA48" s="113"/>
+      <c r="AB48" s="113"/>
+      <c r="AC48" s="113"/>
+      <c r="AD48" s="113"/>
+      <c r="AE48" s="113"/>
+      <c r="AF48" s="124"/>
       <c r="AG48" s="57">
         <v>3</v>
       </c>
@@ -3610,46 +3643,46 @@
     <row r="49" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="55"/>
       <c r="B49" s="56"/>
-      <c r="C49" s="130" t="s">
-        <v>52</v>
-      </c>
-      <c r="D49" s="122"/>
-      <c r="E49" s="122"/>
-      <c r="F49" s="122"/>
-      <c r="G49" s="122"/>
-      <c r="H49" s="122"/>
-      <c r="I49" s="122"/>
-      <c r="J49" s="123"/>
+      <c r="C49" s="142" t="s">
+        <v>51</v>
+      </c>
+      <c r="D49" s="113"/>
+      <c r="E49" s="113"/>
+      <c r="F49" s="113"/>
+      <c r="G49" s="113"/>
+      <c r="H49" s="113"/>
+      <c r="I49" s="113"/>
+      <c r="J49" s="124"/>
       <c r="K49" s="57">
         <v>2</v>
       </c>
       <c r="L49" s="52"/>
-      <c r="M49" s="130" t="s">
-        <v>47</v>
-      </c>
-      <c r="N49" s="122"/>
-      <c r="O49" s="122"/>
-      <c r="P49" s="122"/>
-      <c r="Q49" s="122"/>
-      <c r="R49" s="122"/>
-      <c r="S49" s="122"/>
-      <c r="T49" s="122"/>
-      <c r="U49" s="123"/>
+      <c r="M49" s="142" t="s">
+        <v>46</v>
+      </c>
+      <c r="N49" s="113"/>
+      <c r="O49" s="113"/>
+      <c r="P49" s="113"/>
+      <c r="Q49" s="113"/>
+      <c r="R49" s="113"/>
+      <c r="S49" s="113"/>
+      <c r="T49" s="113"/>
+      <c r="U49" s="124"/>
       <c r="V49" s="57">
         <v>2</v>
       </c>
       <c r="W49" s="62"/>
-      <c r="X49" s="130" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y49" s="122"/>
-      <c r="Z49" s="122"/>
-      <c r="AA49" s="122"/>
-      <c r="AB49" s="122"/>
-      <c r="AC49" s="122"/>
-      <c r="AD49" s="122"/>
-      <c r="AE49" s="122"/>
-      <c r="AF49" s="123"/>
+      <c r="X49" s="142" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y49" s="113"/>
+      <c r="Z49" s="113"/>
+      <c r="AA49" s="113"/>
+      <c r="AB49" s="113"/>
+      <c r="AC49" s="113"/>
+      <c r="AD49" s="113"/>
+      <c r="AE49" s="113"/>
+      <c r="AF49" s="124"/>
       <c r="AG49" s="57">
         <v>2</v>
       </c>
@@ -3659,46 +3692,46 @@
     <row r="50" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="55"/>
       <c r="B50" s="56"/>
-      <c r="C50" s="130" t="s">
-        <v>48</v>
-      </c>
-      <c r="D50" s="122"/>
-      <c r="E50" s="122"/>
-      <c r="F50" s="122"/>
-      <c r="G50" s="122"/>
-      <c r="H50" s="122"/>
-      <c r="I50" s="122"/>
-      <c r="J50" s="123"/>
+      <c r="C50" s="142" t="s">
+        <v>47</v>
+      </c>
+      <c r="D50" s="113"/>
+      <c r="E50" s="113"/>
+      <c r="F50" s="113"/>
+      <c r="G50" s="113"/>
+      <c r="H50" s="113"/>
+      <c r="I50" s="113"/>
+      <c r="J50" s="124"/>
       <c r="K50" s="57">
         <v>1</v>
       </c>
       <c r="L50" s="62"/>
-      <c r="M50" s="130" t="s">
-        <v>48</v>
-      </c>
-      <c r="N50" s="122"/>
-      <c r="O50" s="122"/>
-      <c r="P50" s="122"/>
-      <c r="Q50" s="122"/>
-      <c r="R50" s="122"/>
-      <c r="S50" s="122"/>
-      <c r="T50" s="122"/>
-      <c r="U50" s="123"/>
+      <c r="M50" s="142" t="s">
+        <v>47</v>
+      </c>
+      <c r="N50" s="113"/>
+      <c r="O50" s="113"/>
+      <c r="P50" s="113"/>
+      <c r="Q50" s="113"/>
+      <c r="R50" s="113"/>
+      <c r="S50" s="113"/>
+      <c r="T50" s="113"/>
+      <c r="U50" s="124"/>
       <c r="V50" s="57">
         <v>1</v>
       </c>
       <c r="W50" s="62"/>
-      <c r="X50" s="130" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y50" s="122"/>
-      <c r="Z50" s="122"/>
-      <c r="AA50" s="122"/>
-      <c r="AB50" s="122"/>
-      <c r="AC50" s="122"/>
-      <c r="AD50" s="122"/>
-      <c r="AE50" s="122"/>
-      <c r="AF50" s="123"/>
+      <c r="X50" s="142" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y50" s="113"/>
+      <c r="Z50" s="113"/>
+      <c r="AA50" s="113"/>
+      <c r="AB50" s="113"/>
+      <c r="AC50" s="113"/>
+      <c r="AD50" s="113"/>
+      <c r="AE50" s="113"/>
+      <c r="AF50" s="124"/>
       <c r="AG50" s="57">
         <v>1</v>
       </c>
@@ -3745,20 +3778,20 @@
     <row r="52" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="49"/>
       <c r="B52" s="50"/>
-      <c r="C52" s="127"/>
-      <c r="D52" s="105"/>
-      <c r="E52" s="105"/>
-      <c r="F52" s="105"/>
-      <c r="G52" s="105"/>
-      <c r="H52" s="105"/>
-      <c r="I52" s="105"/>
-      <c r="J52" s="105"/>
-      <c r="K52" s="105"/>
+      <c r="C52" s="143"/>
+      <c r="D52" s="144"/>
+      <c r="E52" s="144"/>
+      <c r="F52" s="144"/>
+      <c r="G52" s="144"/>
+      <c r="H52" s="144"/>
+      <c r="I52" s="144"/>
+      <c r="J52" s="144"/>
+      <c r="K52" s="144"/>
       <c r="L52" s="66"/>
       <c r="M52" s="67"/>
       <c r="N52" s="67"/>
       <c r="O52" s="68" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P52" s="68"/>
       <c r="Q52" s="68"/>
@@ -3784,316 +3817,316 @@
     <row r="53" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="49"/>
       <c r="B53" s="50"/>
-      <c r="C53" s="128" t="s">
+      <c r="C53" s="145" t="s">
+        <v>53</v>
+      </c>
+      <c r="D53" s="146"/>
+      <c r="E53" s="145" t="s">
         <v>54</v>
       </c>
-      <c r="D53" s="113"/>
-      <c r="E53" s="128" t="s">
+      <c r="F53" s="97"/>
+      <c r="G53" s="97"/>
+      <c r="H53" s="97"/>
+      <c r="I53" s="97"/>
+      <c r="J53" s="97"/>
+      <c r="K53" s="146"/>
+      <c r="L53" s="145" t="s">
         <v>55</v>
       </c>
-      <c r="F53" s="91"/>
-      <c r="G53" s="91"/>
-      <c r="H53" s="91"/>
-      <c r="I53" s="91"/>
-      <c r="J53" s="91"/>
-      <c r="K53" s="113"/>
-      <c r="L53" s="128" t="s">
-        <v>56</v>
-      </c>
-      <c r="M53" s="91"/>
-      <c r="N53" s="91"/>
-      <c r="O53" s="91"/>
-      <c r="P53" s="91"/>
-      <c r="Q53" s="91"/>
-      <c r="R53" s="91"/>
-      <c r="S53" s="91"/>
-      <c r="T53" s="91"/>
-      <c r="U53" s="91"/>
-      <c r="V53" s="91"/>
-      <c r="W53" s="91"/>
-      <c r="X53" s="91"/>
-      <c r="Y53" s="91"/>
-      <c r="Z53" s="91"/>
-      <c r="AA53" s="91"/>
-      <c r="AB53" s="91"/>
-      <c r="AC53" s="91"/>
-      <c r="AD53" s="91"/>
-      <c r="AE53" s="91"/>
-      <c r="AF53" s="91"/>
-      <c r="AG53" s="113"/>
+      <c r="M53" s="97"/>
+      <c r="N53" s="97"/>
+      <c r="O53" s="97"/>
+      <c r="P53" s="97"/>
+      <c r="Q53" s="97"/>
+      <c r="R53" s="97"/>
+      <c r="S53" s="97"/>
+      <c r="T53" s="97"/>
+      <c r="U53" s="97"/>
+      <c r="V53" s="97"/>
+      <c r="W53" s="97"/>
+      <c r="X53" s="97"/>
+      <c r="Y53" s="97"/>
+      <c r="Z53" s="97"/>
+      <c r="AA53" s="97"/>
+      <c r="AB53" s="97"/>
+      <c r="AC53" s="97"/>
+      <c r="AD53" s="97"/>
+      <c r="AE53" s="97"/>
+      <c r="AF53" s="97"/>
+      <c r="AG53" s="146"/>
       <c r="AH53" s="69"/>
       <c r="AI53" s="12"/>
     </row>
     <row r="54" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="55"/>
       <c r="B54" s="56"/>
-      <c r="C54" s="114"/>
-      <c r="D54" s="115"/>
-      <c r="E54" s="114"/>
-      <c r="F54" s="117"/>
-      <c r="G54" s="117"/>
-      <c r="H54" s="117"/>
-      <c r="I54" s="117"/>
-      <c r="J54" s="117"/>
-      <c r="K54" s="115"/>
-      <c r="L54" s="114"/>
-      <c r="M54" s="117"/>
-      <c r="N54" s="117"/>
-      <c r="O54" s="117"/>
-      <c r="P54" s="117"/>
-      <c r="Q54" s="117"/>
-      <c r="R54" s="117"/>
-      <c r="S54" s="117"/>
-      <c r="T54" s="117"/>
-      <c r="U54" s="117"/>
-      <c r="V54" s="117"/>
-      <c r="W54" s="117"/>
-      <c r="X54" s="117"/>
-      <c r="Y54" s="117"/>
-      <c r="Z54" s="117"/>
-      <c r="AA54" s="117"/>
-      <c r="AB54" s="117"/>
-      <c r="AC54" s="117"/>
-      <c r="AD54" s="117"/>
-      <c r="AE54" s="117"/>
-      <c r="AF54" s="117"/>
-      <c r="AG54" s="115"/>
+      <c r="C54" s="100"/>
+      <c r="D54" s="147"/>
+      <c r="E54" s="100"/>
+      <c r="F54" s="101"/>
+      <c r="G54" s="101"/>
+      <c r="H54" s="101"/>
+      <c r="I54" s="101"/>
+      <c r="J54" s="101"/>
+      <c r="K54" s="147"/>
+      <c r="L54" s="100"/>
+      <c r="M54" s="101"/>
+      <c r="N54" s="101"/>
+      <c r="O54" s="101"/>
+      <c r="P54" s="101"/>
+      <c r="Q54" s="101"/>
+      <c r="R54" s="101"/>
+      <c r="S54" s="101"/>
+      <c r="T54" s="101"/>
+      <c r="U54" s="101"/>
+      <c r="V54" s="101"/>
+      <c r="W54" s="101"/>
+      <c r="X54" s="101"/>
+      <c r="Y54" s="101"/>
+      <c r="Z54" s="101"/>
+      <c r="AA54" s="101"/>
+      <c r="AB54" s="101"/>
+      <c r="AC54" s="101"/>
+      <c r="AD54" s="101"/>
+      <c r="AE54" s="101"/>
+      <c r="AF54" s="101"/>
+      <c r="AG54" s="147"/>
       <c r="AH54" s="70"/>
       <c r="AI54" s="25"/>
     </row>
     <row r="55" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="55"/>
       <c r="B55" s="56"/>
-      <c r="C55" s="129"/>
-      <c r="D55" s="113"/>
-      <c r="E55" s="116" t="s">
+      <c r="C55" s="148"/>
+      <c r="D55" s="146"/>
+      <c r="E55" s="149" t="s">
+        <v>56</v>
+      </c>
+      <c r="F55" s="97"/>
+      <c r="G55" s="97"/>
+      <c r="H55" s="97"/>
+      <c r="I55" s="97"/>
+      <c r="J55" s="97"/>
+      <c r="K55" s="146"/>
+      <c r="L55" s="150" t="s">
         <v>57</v>
       </c>
-      <c r="F55" s="91"/>
-      <c r="G55" s="91"/>
-      <c r="H55" s="91"/>
-      <c r="I55" s="91"/>
-      <c r="J55" s="91"/>
-      <c r="K55" s="113"/>
-      <c r="L55" s="118" t="s">
-        <v>58</v>
-      </c>
-      <c r="M55" s="91"/>
-      <c r="N55" s="91"/>
-      <c r="O55" s="91"/>
-      <c r="P55" s="91"/>
-      <c r="Q55" s="91"/>
-      <c r="R55" s="91"/>
-      <c r="S55" s="91"/>
-      <c r="T55" s="91"/>
-      <c r="U55" s="91"/>
-      <c r="V55" s="91"/>
-      <c r="W55" s="91"/>
-      <c r="X55" s="91"/>
-      <c r="Y55" s="91"/>
-      <c r="Z55" s="91"/>
-      <c r="AA55" s="91"/>
-      <c r="AB55" s="91"/>
-      <c r="AC55" s="91"/>
-      <c r="AD55" s="91"/>
-      <c r="AE55" s="91"/>
-      <c r="AF55" s="91"/>
-      <c r="AG55" s="113"/>
+      <c r="M55" s="97"/>
+      <c r="N55" s="97"/>
+      <c r="O55" s="97"/>
+      <c r="P55" s="97"/>
+      <c r="Q55" s="97"/>
+      <c r="R55" s="97"/>
+      <c r="S55" s="97"/>
+      <c r="T55" s="97"/>
+      <c r="U55" s="97"/>
+      <c r="V55" s="97"/>
+      <c r="W55" s="97"/>
+      <c r="X55" s="97"/>
+      <c r="Y55" s="97"/>
+      <c r="Z55" s="97"/>
+      <c r="AA55" s="97"/>
+      <c r="AB55" s="97"/>
+      <c r="AC55" s="97"/>
+      <c r="AD55" s="97"/>
+      <c r="AE55" s="97"/>
+      <c r="AF55" s="97"/>
+      <c r="AG55" s="146"/>
       <c r="AH55" s="70"/>
       <c r="AI55" s="25"/>
     </row>
     <row r="56" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="55"/>
       <c r="B56" s="56"/>
-      <c r="C56" s="114"/>
-      <c r="D56" s="115"/>
-      <c r="E56" s="114"/>
-      <c r="F56" s="117"/>
-      <c r="G56" s="117"/>
-      <c r="H56" s="117"/>
-      <c r="I56" s="117"/>
-      <c r="J56" s="117"/>
-      <c r="K56" s="115"/>
-      <c r="L56" s="114"/>
-      <c r="M56" s="117"/>
-      <c r="N56" s="117"/>
-      <c r="O56" s="117"/>
-      <c r="P56" s="117"/>
-      <c r="Q56" s="117"/>
-      <c r="R56" s="117"/>
-      <c r="S56" s="117"/>
-      <c r="T56" s="117"/>
-      <c r="U56" s="117"/>
-      <c r="V56" s="117"/>
-      <c r="W56" s="117"/>
-      <c r="X56" s="117"/>
-      <c r="Y56" s="117"/>
-      <c r="Z56" s="117"/>
-      <c r="AA56" s="117"/>
-      <c r="AB56" s="117"/>
-      <c r="AC56" s="117"/>
-      <c r="AD56" s="117"/>
-      <c r="AE56" s="117"/>
-      <c r="AF56" s="117"/>
-      <c r="AG56" s="115"/>
+      <c r="C56" s="100"/>
+      <c r="D56" s="147"/>
+      <c r="E56" s="100"/>
+      <c r="F56" s="101"/>
+      <c r="G56" s="101"/>
+      <c r="H56" s="101"/>
+      <c r="I56" s="101"/>
+      <c r="J56" s="101"/>
+      <c r="K56" s="147"/>
+      <c r="L56" s="100"/>
+      <c r="M56" s="101"/>
+      <c r="N56" s="101"/>
+      <c r="O56" s="101"/>
+      <c r="P56" s="101"/>
+      <c r="Q56" s="101"/>
+      <c r="R56" s="101"/>
+      <c r="S56" s="101"/>
+      <c r="T56" s="101"/>
+      <c r="U56" s="101"/>
+      <c r="V56" s="101"/>
+      <c r="W56" s="101"/>
+      <c r="X56" s="101"/>
+      <c r="Y56" s="101"/>
+      <c r="Z56" s="101"/>
+      <c r="AA56" s="101"/>
+      <c r="AB56" s="101"/>
+      <c r="AC56" s="101"/>
+      <c r="AD56" s="101"/>
+      <c r="AE56" s="101"/>
+      <c r="AF56" s="101"/>
+      <c r="AG56" s="147"/>
       <c r="AH56" s="71"/>
       <c r="AI56" s="72"/>
     </row>
     <row r="57" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="26"/>
       <c r="B57" s="73"/>
-      <c r="C57" s="112" t="s">
+      <c r="C57" s="96" t="s">
+        <v>58</v>
+      </c>
+      <c r="D57" s="146"/>
+      <c r="E57" s="149" t="s">
         <v>59</v>
       </c>
-      <c r="D57" s="113"/>
-      <c r="E57" s="116" t="s">
+      <c r="F57" s="97"/>
+      <c r="G57" s="97"/>
+      <c r="H57" s="97"/>
+      <c r="I57" s="97"/>
+      <c r="J57" s="97"/>
+      <c r="K57" s="146"/>
+      <c r="L57" s="150" t="s">
         <v>60</v>
       </c>
-      <c r="F57" s="91"/>
-      <c r="G57" s="91"/>
-      <c r="H57" s="91"/>
-      <c r="I57" s="91"/>
-      <c r="J57" s="91"/>
-      <c r="K57" s="113"/>
-      <c r="L57" s="118" t="s">
-        <v>61</v>
-      </c>
-      <c r="M57" s="91"/>
-      <c r="N57" s="91"/>
-      <c r="O57" s="91"/>
-      <c r="P57" s="91"/>
-      <c r="Q57" s="91"/>
-      <c r="R57" s="91"/>
-      <c r="S57" s="91"/>
-      <c r="T57" s="91"/>
-      <c r="U57" s="91"/>
-      <c r="V57" s="91"/>
-      <c r="W57" s="91"/>
-      <c r="X57" s="91"/>
-      <c r="Y57" s="91"/>
-      <c r="Z57" s="91"/>
-      <c r="AA57" s="91"/>
-      <c r="AB57" s="91"/>
-      <c r="AC57" s="91"/>
-      <c r="AD57" s="91"/>
-      <c r="AE57" s="91"/>
-      <c r="AF57" s="91"/>
-      <c r="AG57" s="113"/>
+      <c r="M57" s="97"/>
+      <c r="N57" s="97"/>
+      <c r="O57" s="97"/>
+      <c r="P57" s="97"/>
+      <c r="Q57" s="97"/>
+      <c r="R57" s="97"/>
+      <c r="S57" s="97"/>
+      <c r="T57" s="97"/>
+      <c r="U57" s="97"/>
+      <c r="V57" s="97"/>
+      <c r="W57" s="97"/>
+      <c r="X57" s="97"/>
+      <c r="Y57" s="97"/>
+      <c r="Z57" s="97"/>
+      <c r="AA57" s="97"/>
+      <c r="AB57" s="97"/>
+      <c r="AC57" s="97"/>
+      <c r="AD57" s="97"/>
+      <c r="AE57" s="97"/>
+      <c r="AF57" s="97"/>
+      <c r="AG57" s="146"/>
       <c r="AH57" s="71"/>
       <c r="AI57" s="72"/>
     </row>
     <row r="58" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="26"/>
       <c r="B58" s="73"/>
-      <c r="C58" s="114"/>
-      <c r="D58" s="115"/>
-      <c r="E58" s="114"/>
-      <c r="F58" s="117"/>
-      <c r="G58" s="117"/>
-      <c r="H58" s="117"/>
-      <c r="I58" s="117"/>
-      <c r="J58" s="117"/>
-      <c r="K58" s="115"/>
-      <c r="L58" s="114"/>
-      <c r="M58" s="117"/>
-      <c r="N58" s="117"/>
-      <c r="O58" s="117"/>
-      <c r="P58" s="117"/>
-      <c r="Q58" s="117"/>
-      <c r="R58" s="117"/>
-      <c r="S58" s="117"/>
-      <c r="T58" s="117"/>
-      <c r="U58" s="117"/>
-      <c r="V58" s="117"/>
-      <c r="W58" s="117"/>
-      <c r="X58" s="117"/>
-      <c r="Y58" s="117"/>
-      <c r="Z58" s="117"/>
-      <c r="AA58" s="117"/>
-      <c r="AB58" s="117"/>
-      <c r="AC58" s="117"/>
-      <c r="AD58" s="117"/>
-      <c r="AE58" s="117"/>
-      <c r="AF58" s="117"/>
-      <c r="AG58" s="115"/>
+      <c r="C58" s="100"/>
+      <c r="D58" s="147"/>
+      <c r="E58" s="100"/>
+      <c r="F58" s="101"/>
+      <c r="G58" s="101"/>
+      <c r="H58" s="101"/>
+      <c r="I58" s="101"/>
+      <c r="J58" s="101"/>
+      <c r="K58" s="147"/>
+      <c r="L58" s="100"/>
+      <c r="M58" s="101"/>
+      <c r="N58" s="101"/>
+      <c r="O58" s="101"/>
+      <c r="P58" s="101"/>
+      <c r="Q58" s="101"/>
+      <c r="R58" s="101"/>
+      <c r="S58" s="101"/>
+      <c r="T58" s="101"/>
+      <c r="U58" s="101"/>
+      <c r="V58" s="101"/>
+      <c r="W58" s="101"/>
+      <c r="X58" s="101"/>
+      <c r="Y58" s="101"/>
+      <c r="Z58" s="101"/>
+      <c r="AA58" s="101"/>
+      <c r="AB58" s="101"/>
+      <c r="AC58" s="101"/>
+      <c r="AD58" s="101"/>
+      <c r="AE58" s="101"/>
+      <c r="AF58" s="101"/>
+      <c r="AG58" s="147"/>
       <c r="AH58" s="70"/>
       <c r="AI58" s="25"/>
     </row>
     <row r="59" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="26"/>
       <c r="B59" s="73"/>
-      <c r="C59" s="112"/>
-      <c r="D59" s="113"/>
-      <c r="E59" s="116" t="s">
+      <c r="C59" s="96"/>
+      <c r="D59" s="146"/>
+      <c r="E59" s="149" t="s">
+        <v>61</v>
+      </c>
+      <c r="F59" s="97"/>
+      <c r="G59" s="97"/>
+      <c r="H59" s="97"/>
+      <c r="I59" s="97"/>
+      <c r="J59" s="97"/>
+      <c r="K59" s="146"/>
+      <c r="L59" s="150" t="s">
         <v>62</v>
       </c>
-      <c r="F59" s="91"/>
-      <c r="G59" s="91"/>
-      <c r="H59" s="91"/>
-      <c r="I59" s="91"/>
-      <c r="J59" s="91"/>
-      <c r="K59" s="113"/>
-      <c r="L59" s="118" t="s">
-        <v>63</v>
-      </c>
-      <c r="M59" s="91"/>
-      <c r="N59" s="91"/>
-      <c r="O59" s="91"/>
-      <c r="P59" s="91"/>
-      <c r="Q59" s="91"/>
-      <c r="R59" s="91"/>
-      <c r="S59" s="91"/>
-      <c r="T59" s="91"/>
-      <c r="U59" s="91"/>
-      <c r="V59" s="91"/>
-      <c r="W59" s="91"/>
-      <c r="X59" s="91"/>
-      <c r="Y59" s="91"/>
-      <c r="Z59" s="91"/>
-      <c r="AA59" s="91"/>
-      <c r="AB59" s="91"/>
-      <c r="AC59" s="91"/>
-      <c r="AD59" s="91"/>
-      <c r="AE59" s="91"/>
-      <c r="AF59" s="91"/>
-      <c r="AG59" s="113"/>
+      <c r="M59" s="97"/>
+      <c r="N59" s="97"/>
+      <c r="O59" s="97"/>
+      <c r="P59" s="97"/>
+      <c r="Q59" s="97"/>
+      <c r="R59" s="97"/>
+      <c r="S59" s="97"/>
+      <c r="T59" s="97"/>
+      <c r="U59" s="97"/>
+      <c r="V59" s="97"/>
+      <c r="W59" s="97"/>
+      <c r="X59" s="97"/>
+      <c r="Y59" s="97"/>
+      <c r="Z59" s="97"/>
+      <c r="AA59" s="97"/>
+      <c r="AB59" s="97"/>
+      <c r="AC59" s="97"/>
+      <c r="AD59" s="97"/>
+      <c r="AE59" s="97"/>
+      <c r="AF59" s="97"/>
+      <c r="AG59" s="146"/>
       <c r="AH59" s="70"/>
       <c r="AI59" s="25"/>
     </row>
     <row r="60" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="26"/>
       <c r="B60" s="73"/>
-      <c r="C60" s="114"/>
-      <c r="D60" s="115"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="115"/>
-      <c r="L60" s="114"/>
-      <c r="M60" s="117"/>
-      <c r="N60" s="117"/>
-      <c r="O60" s="117"/>
-      <c r="P60" s="117"/>
-      <c r="Q60" s="117"/>
-      <c r="R60" s="117"/>
-      <c r="S60" s="117"/>
-      <c r="T60" s="117"/>
-      <c r="U60" s="117"/>
-      <c r="V60" s="117"/>
-      <c r="W60" s="117"/>
-      <c r="X60" s="117"/>
-      <c r="Y60" s="117"/>
-      <c r="Z60" s="117"/>
-      <c r="AA60" s="117"/>
-      <c r="AB60" s="117"/>
-      <c r="AC60" s="117"/>
-      <c r="AD60" s="117"/>
-      <c r="AE60" s="117"/>
-      <c r="AF60" s="117"/>
-      <c r="AG60" s="115"/>
+      <c r="C60" s="100"/>
+      <c r="D60" s="147"/>
+      <c r="E60" s="100"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="147"/>
+      <c r="L60" s="100"/>
+      <c r="M60" s="101"/>
+      <c r="N60" s="101"/>
+      <c r="O60" s="101"/>
+      <c r="P60" s="101"/>
+      <c r="Q60" s="101"/>
+      <c r="R60" s="101"/>
+      <c r="S60" s="101"/>
+      <c r="T60" s="101"/>
+      <c r="U60" s="101"/>
+      <c r="V60" s="101"/>
+      <c r="W60" s="101"/>
+      <c r="X60" s="101"/>
+      <c r="Y60" s="101"/>
+      <c r="Z60" s="101"/>
+      <c r="AA60" s="101"/>
+      <c r="AB60" s="101"/>
+      <c r="AC60" s="101"/>
+      <c r="AD60" s="101"/>
+      <c r="AE60" s="101"/>
+      <c r="AF60" s="101"/>
+      <c r="AG60" s="147"/>
       <c r="AH60" s="74"/>
       <c r="AI60" s="5"/>
     </row>
@@ -4114,9 +4147,9 @@
       <c r="N61" s="77"/>
       <c r="O61" s="77"/>
       <c r="P61" s="77"/>
-      <c r="Q61" s="119"/>
-      <c r="R61" s="120"/>
-      <c r="S61" s="120"/>
+      <c r="Q61" s="151"/>
+      <c r="R61" s="152"/>
+      <c r="S61" s="152"/>
       <c r="T61" s="78"/>
       <c r="U61" s="6"/>
       <c r="V61" s="6"/>
@@ -4247,41 +4280,41 @@
     </row>
     <row r="65" spans="1:35" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7"/>
-      <c r="B65" s="98" t="s">
-        <v>64</v>
-      </c>
-      <c r="C65" s="99"/>
-      <c r="D65" s="99"/>
-      <c r="E65" s="99"/>
-      <c r="F65" s="99"/>
-      <c r="G65" s="99"/>
-      <c r="H65" s="99"/>
-      <c r="I65" s="99"/>
-      <c r="J65" s="99"/>
-      <c r="K65" s="99"/>
-      <c r="L65" s="99"/>
-      <c r="M65" s="99"/>
-      <c r="N65" s="99"/>
-      <c r="O65" s="99"/>
-      <c r="P65" s="99"/>
-      <c r="Q65" s="99"/>
-      <c r="R65" s="99"/>
-      <c r="S65" s="99"/>
-      <c r="T65" s="99"/>
-      <c r="U65" s="99"/>
-      <c r="V65" s="99"/>
-      <c r="W65" s="99"/>
-      <c r="X65" s="99"/>
-      <c r="Y65" s="99"/>
-      <c r="Z65" s="99"/>
-      <c r="AA65" s="99"/>
-      <c r="AB65" s="99"/>
-      <c r="AC65" s="99"/>
-      <c r="AD65" s="99"/>
-      <c r="AE65" s="99"/>
-      <c r="AF65" s="99"/>
-      <c r="AG65" s="99"/>
-      <c r="AH65" s="100"/>
+      <c r="B65" s="120" t="s">
+        <v>63</v>
+      </c>
+      <c r="C65" s="118"/>
+      <c r="D65" s="118"/>
+      <c r="E65" s="118"/>
+      <c r="F65" s="118"/>
+      <c r="G65" s="118"/>
+      <c r="H65" s="118"/>
+      <c r="I65" s="118"/>
+      <c r="J65" s="118"/>
+      <c r="K65" s="118"/>
+      <c r="L65" s="118"/>
+      <c r="M65" s="118"/>
+      <c r="N65" s="118"/>
+      <c r="O65" s="118"/>
+      <c r="P65" s="118"/>
+      <c r="Q65" s="118"/>
+      <c r="R65" s="118"/>
+      <c r="S65" s="118"/>
+      <c r="T65" s="118"/>
+      <c r="U65" s="118"/>
+      <c r="V65" s="118"/>
+      <c r="W65" s="118"/>
+      <c r="X65" s="118"/>
+      <c r="Y65" s="118"/>
+      <c r="Z65" s="118"/>
+      <c r="AA65" s="118"/>
+      <c r="AB65" s="118"/>
+      <c r="AC65" s="118"/>
+      <c r="AD65" s="118"/>
+      <c r="AE65" s="118"/>
+      <c r="AF65" s="118"/>
+      <c r="AG65" s="118"/>
+      <c r="AH65" s="119"/>
       <c r="AI65" s="49"/>
     </row>
     <row r="66" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4324,36 +4357,36 @@
     <row r="67" spans="1:35" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="64"/>
       <c r="B67" s="50"/>
-      <c r="C67" s="158"/>
-      <c r="D67" s="159"/>
-      <c r="E67" s="159"/>
-      <c r="F67" s="159"/>
-      <c r="G67" s="159"/>
-      <c r="H67" s="159"/>
-      <c r="I67" s="159"/>
-      <c r="J67" s="159"/>
-      <c r="K67" s="159"/>
-      <c r="L67" s="159"/>
-      <c r="M67" s="159"/>
-      <c r="N67" s="159"/>
-      <c r="O67" s="159"/>
-      <c r="P67" s="160"/>
-      <c r="Q67" s="101"/>
-      <c r="R67" s="102"/>
-      <c r="S67" s="102"/>
-      <c r="T67" s="102"/>
-      <c r="U67" s="103"/>
-      <c r="V67" s="102"/>
-      <c r="W67" s="102"/>
-      <c r="X67" s="102"/>
-      <c r="Y67" s="102"/>
-      <c r="Z67" s="102"/>
-      <c r="AA67" s="102"/>
-      <c r="AB67" s="102"/>
-      <c r="AC67" s="102"/>
-      <c r="AD67" s="102"/>
-      <c r="AE67" s="102"/>
-      <c r="AF67" s="102"/>
+      <c r="C67" s="91"/>
+      <c r="D67" s="92"/>
+      <c r="E67" s="92"/>
+      <c r="F67" s="92"/>
+      <c r="G67" s="92"/>
+      <c r="H67" s="92"/>
+      <c r="I67" s="92"/>
+      <c r="J67" s="92"/>
+      <c r="K67" s="92"/>
+      <c r="L67" s="92"/>
+      <c r="M67" s="92"/>
+      <c r="N67" s="92"/>
+      <c r="O67" s="92"/>
+      <c r="P67" s="93"/>
+      <c r="Q67" s="154"/>
+      <c r="R67" s="155"/>
+      <c r="S67" s="155"/>
+      <c r="T67" s="155"/>
+      <c r="U67" s="156"/>
+      <c r="V67" s="155"/>
+      <c r="W67" s="155"/>
+      <c r="X67" s="155"/>
+      <c r="Y67" s="155"/>
+      <c r="Z67" s="155"/>
+      <c r="AA67" s="155"/>
+      <c r="AB67" s="155"/>
+      <c r="AC67" s="155"/>
+      <c r="AD67" s="155"/>
+      <c r="AE67" s="155"/>
+      <c r="AF67" s="155"/>
       <c r="AG67" s="82"/>
       <c r="AH67" s="63"/>
       <c r="AI67" s="64"/>
@@ -4361,7 +4394,7 @@
     <row r="68" spans="1:35" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="64"/>
       <c r="B68" s="50"/>
-      <c r="C68" s="161"/>
+      <c r="C68" s="94"/>
       <c r="D68" s="90"/>
       <c r="E68" s="90"/>
       <c r="F68" s="90"/>
@@ -4374,23 +4407,23 @@
       <c r="M68" s="90"/>
       <c r="N68" s="90"/>
       <c r="O68" s="90"/>
-      <c r="P68" s="162"/>
-      <c r="Q68" s="104"/>
-      <c r="R68" s="105"/>
-      <c r="S68" s="105"/>
-      <c r="T68" s="105"/>
-      <c r="U68" s="106"/>
-      <c r="V68" s="105"/>
-      <c r="W68" s="105"/>
-      <c r="X68" s="105"/>
-      <c r="Y68" s="105"/>
-      <c r="Z68" s="105"/>
-      <c r="AA68" s="105"/>
-      <c r="AB68" s="105"/>
-      <c r="AC68" s="105"/>
-      <c r="AD68" s="105"/>
-      <c r="AE68" s="105"/>
-      <c r="AF68" s="105"/>
+      <c r="P68" s="95"/>
+      <c r="Q68" s="157"/>
+      <c r="R68" s="144"/>
+      <c r="S68" s="144"/>
+      <c r="T68" s="144"/>
+      <c r="U68" s="158"/>
+      <c r="V68" s="144"/>
+      <c r="W68" s="144"/>
+      <c r="X68" s="144"/>
+      <c r="Y68" s="144"/>
+      <c r="Z68" s="144"/>
+      <c r="AA68" s="144"/>
+      <c r="AB68" s="144"/>
+      <c r="AC68" s="144"/>
+      <c r="AD68" s="144"/>
+      <c r="AE68" s="144"/>
+      <c r="AF68" s="144"/>
       <c r="AG68" s="63"/>
       <c r="AH68" s="63"/>
       <c r="AI68" s="64"/>
@@ -4398,36 +4431,36 @@
     <row r="69" spans="1:35" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="64"/>
       <c r="B69" s="50"/>
-      <c r="C69" s="161"/>
-      <c r="D69" s="163"/>
-      <c r="E69" s="163"/>
-      <c r="F69" s="163"/>
-      <c r="G69" s="163"/>
-      <c r="H69" s="163"/>
-      <c r="I69" s="163"/>
-      <c r="J69" s="163"/>
-      <c r="K69" s="163"/>
-      <c r="L69" s="163"/>
-      <c r="M69" s="163"/>
+      <c r="C69" s="94"/>
+      <c r="D69" s="164"/>
+      <c r="E69" s="164"/>
+      <c r="F69" s="164"/>
+      <c r="G69" s="164"/>
+      <c r="H69" s="164"/>
+      <c r="I69" s="164"/>
+      <c r="J69" s="164"/>
+      <c r="K69" s="164"/>
+      <c r="L69" s="164"/>
+      <c r="M69" s="164"/>
       <c r="N69" s="90"/>
       <c r="O69" s="90"/>
-      <c r="P69" s="162"/>
-      <c r="Q69" s="104"/>
-      <c r="R69" s="105"/>
-      <c r="S69" s="105"/>
-      <c r="T69" s="105"/>
-      <c r="U69" s="107"/>
-      <c r="V69" s="108"/>
-      <c r="W69" s="108"/>
-      <c r="X69" s="108"/>
-      <c r="Y69" s="108"/>
-      <c r="Z69" s="108"/>
-      <c r="AA69" s="108"/>
-      <c r="AB69" s="108"/>
-      <c r="AC69" s="108"/>
-      <c r="AD69" s="108"/>
-      <c r="AE69" s="108"/>
-      <c r="AF69" s="108"/>
+      <c r="P69" s="95"/>
+      <c r="Q69" s="157"/>
+      <c r="R69" s="144"/>
+      <c r="S69" s="144"/>
+      <c r="T69" s="144"/>
+      <c r="U69" s="159"/>
+      <c r="V69" s="160"/>
+      <c r="W69" s="160"/>
+      <c r="X69" s="160"/>
+      <c r="Y69" s="160"/>
+      <c r="Z69" s="160"/>
+      <c r="AA69" s="160"/>
+      <c r="AB69" s="160"/>
+      <c r="AC69" s="160"/>
+      <c r="AD69" s="160"/>
+      <c r="AE69" s="160"/>
+      <c r="AF69" s="160"/>
       <c r="AG69" s="63"/>
       <c r="AH69" s="63"/>
       <c r="AI69" s="64"/>
@@ -4436,40 +4469,40 @@
       <c r="A70" s="64"/>
       <c r="B70" s="83"/>
       <c r="C70" s="84"/>
-      <c r="D70" s="96" t="s">
-        <v>65</v>
-      </c>
-      <c r="E70" s="97"/>
-      <c r="F70" s="97"/>
-      <c r="G70" s="97"/>
-      <c r="H70" s="97"/>
-      <c r="I70" s="97"/>
-      <c r="J70" s="97"/>
-      <c r="K70" s="97"/>
-      <c r="L70" s="97"/>
-      <c r="M70" s="97"/>
-      <c r="N70" s="97"/>
+      <c r="D70" s="153" t="s">
+        <v>64</v>
+      </c>
+      <c r="E70" s="116"/>
+      <c r="F70" s="116"/>
+      <c r="G70" s="116"/>
+      <c r="H70" s="116"/>
+      <c r="I70" s="116"/>
+      <c r="J70" s="116"/>
+      <c r="K70" s="116"/>
+      <c r="L70" s="116"/>
+      <c r="M70" s="116"/>
+      <c r="N70" s="116"/>
       <c r="O70" s="85"/>
       <c r="P70" s="86"/>
-      <c r="Q70" s="109" t="s">
-        <v>66</v>
-      </c>
-      <c r="R70" s="110"/>
-      <c r="S70" s="110"/>
-      <c r="T70" s="110"/>
-      <c r="U70" s="110"/>
-      <c r="V70" s="110"/>
-      <c r="W70" s="110"/>
-      <c r="X70" s="110"/>
-      <c r="Y70" s="110"/>
-      <c r="Z70" s="110"/>
-      <c r="AA70" s="110"/>
-      <c r="AB70" s="110"/>
-      <c r="AC70" s="110"/>
-      <c r="AD70" s="110"/>
-      <c r="AE70" s="110"/>
-      <c r="AF70" s="110"/>
-      <c r="AG70" s="111"/>
+      <c r="Q70" s="161" t="s">
+        <v>65</v>
+      </c>
+      <c r="R70" s="162"/>
+      <c r="S70" s="162"/>
+      <c r="T70" s="162"/>
+      <c r="U70" s="162"/>
+      <c r="V70" s="162"/>
+      <c r="W70" s="162"/>
+      <c r="X70" s="162"/>
+      <c r="Y70" s="162"/>
+      <c r="Z70" s="162"/>
+      <c r="AA70" s="162"/>
+      <c r="AB70" s="162"/>
+      <c r="AC70" s="162"/>
+      <c r="AD70" s="162"/>
+      <c r="AE70" s="162"/>
+      <c r="AF70" s="162"/>
+      <c r="AG70" s="163"/>
       <c r="AH70" s="63"/>
       <c r="AI70" s="64"/>
     </row>
@@ -5476,37 +5509,97 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="136">
-    <mergeCell ref="B2:F5"/>
-    <mergeCell ref="G2:Y4"/>
-    <mergeCell ref="Z2:AH2"/>
-    <mergeCell ref="Z3:AH3"/>
-    <mergeCell ref="Z4:AH4"/>
-    <mergeCell ref="G5:AH5"/>
-    <mergeCell ref="B7:AH7"/>
-    <mergeCell ref="B9:AH9"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:AG12"/>
-    <mergeCell ref="C13:AG13"/>
-    <mergeCell ref="C14:AG14"/>
-    <mergeCell ref="R16:X16"/>
-    <mergeCell ref="Y16:AG16"/>
-    <mergeCell ref="Q20:V20"/>
-    <mergeCell ref="W20:AG20"/>
-    <mergeCell ref="W21:AG21"/>
-    <mergeCell ref="B17:AH17"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="G19:K19"/>
-    <mergeCell ref="L19:P19"/>
-    <mergeCell ref="Q19:V19"/>
-    <mergeCell ref="W19:AG19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="G20:K20"/>
-    <mergeCell ref="L20:P20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="G21:K21"/>
-    <mergeCell ref="L21:P21"/>
-    <mergeCell ref="Q21:V21"/>
+  <mergeCells count="140">
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="AB7:AH7"/>
+    <mergeCell ref="G11:AG11"/>
+    <mergeCell ref="G12:AG12"/>
+    <mergeCell ref="G13:AG13"/>
+    <mergeCell ref="G14:AG14"/>
+    <mergeCell ref="D70:N70"/>
+    <mergeCell ref="B65:AH65"/>
+    <mergeCell ref="Q67:T67"/>
+    <mergeCell ref="U67:AF67"/>
+    <mergeCell ref="Q68:T68"/>
+    <mergeCell ref="U68:AF68"/>
+    <mergeCell ref="Q69:T69"/>
+    <mergeCell ref="U69:AF69"/>
+    <mergeCell ref="Q70:AG70"/>
+    <mergeCell ref="D69:M69"/>
+    <mergeCell ref="C59:D60"/>
+    <mergeCell ref="E59:K60"/>
+    <mergeCell ref="L59:AG60"/>
+    <mergeCell ref="Q61:S61"/>
+    <mergeCell ref="G22:K22"/>
+    <mergeCell ref="L22:P22"/>
+    <mergeCell ref="W22:AG22"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="G23:K23"/>
+    <mergeCell ref="L23:P23"/>
+    <mergeCell ref="Q23:V23"/>
+    <mergeCell ref="W23:AG23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="L26:P26"/>
+    <mergeCell ref="Q26:V26"/>
+    <mergeCell ref="L27:P27"/>
+    <mergeCell ref="Q27:V27"/>
+    <mergeCell ref="R28:X28"/>
+    <mergeCell ref="Y28:AG28"/>
+    <mergeCell ref="B30:AH30"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="G25:K25"/>
+    <mergeCell ref="L25:P25"/>
+    <mergeCell ref="C52:K52"/>
+    <mergeCell ref="C53:D54"/>
+    <mergeCell ref="E53:K54"/>
+    <mergeCell ref="L53:AG54"/>
+    <mergeCell ref="C55:D56"/>
+    <mergeCell ref="E55:K56"/>
+    <mergeCell ref="L55:AG56"/>
+    <mergeCell ref="C57:D58"/>
+    <mergeCell ref="E57:K58"/>
+    <mergeCell ref="L57:AG58"/>
+    <mergeCell ref="M48:U48"/>
+    <mergeCell ref="X48:AF48"/>
+    <mergeCell ref="C48:J48"/>
+    <mergeCell ref="C49:J49"/>
+    <mergeCell ref="M49:U49"/>
+    <mergeCell ref="X49:AF49"/>
+    <mergeCell ref="C50:J50"/>
+    <mergeCell ref="M50:U50"/>
+    <mergeCell ref="X50:AF50"/>
+    <mergeCell ref="C44:J44"/>
+    <mergeCell ref="X44:AF44"/>
+    <mergeCell ref="C45:J45"/>
+    <mergeCell ref="X45:AF45"/>
+    <mergeCell ref="M44:U44"/>
+    <mergeCell ref="M45:U45"/>
+    <mergeCell ref="C47:J47"/>
+    <mergeCell ref="M47:U47"/>
+    <mergeCell ref="X47:AF47"/>
+    <mergeCell ref="C38:J38"/>
+    <mergeCell ref="K38:AG38"/>
+    <mergeCell ref="R39:X39"/>
+    <mergeCell ref="Y39:AG39"/>
+    <mergeCell ref="B40:AH40"/>
+    <mergeCell ref="M42:U42"/>
+    <mergeCell ref="X42:AF42"/>
+    <mergeCell ref="C42:J42"/>
+    <mergeCell ref="C43:J43"/>
+    <mergeCell ref="M43:U43"/>
+    <mergeCell ref="X43:AF43"/>
+    <mergeCell ref="W36:AE36"/>
+    <mergeCell ref="W37:AE37"/>
+    <mergeCell ref="C35:J35"/>
+    <mergeCell ref="M35:T35"/>
+    <mergeCell ref="W35:AE35"/>
+    <mergeCell ref="C36:J36"/>
+    <mergeCell ref="M36:T36"/>
+    <mergeCell ref="C37:J37"/>
+    <mergeCell ref="M37:T37"/>
     <mergeCell ref="Q22:V22"/>
     <mergeCell ref="G24:K24"/>
     <mergeCell ref="L24:P24"/>
@@ -5531,88 +5624,32 @@
     <mergeCell ref="AF32:AF33"/>
     <mergeCell ref="AG32:AG33"/>
     <mergeCell ref="W34:AE34"/>
-    <mergeCell ref="W36:AE36"/>
-    <mergeCell ref="W37:AE37"/>
-    <mergeCell ref="C35:J35"/>
-    <mergeCell ref="M35:T35"/>
-    <mergeCell ref="W35:AE35"/>
-    <mergeCell ref="C36:J36"/>
-    <mergeCell ref="M36:T36"/>
-    <mergeCell ref="C37:J37"/>
-    <mergeCell ref="M37:T37"/>
-    <mergeCell ref="C38:J38"/>
-    <mergeCell ref="K38:AG38"/>
-    <mergeCell ref="R39:X39"/>
-    <mergeCell ref="Y39:AG39"/>
-    <mergeCell ref="B40:AH40"/>
-    <mergeCell ref="M42:U42"/>
-    <mergeCell ref="X42:AF42"/>
-    <mergeCell ref="C42:J42"/>
-    <mergeCell ref="C43:J43"/>
-    <mergeCell ref="M43:U43"/>
-    <mergeCell ref="X43:AF43"/>
-    <mergeCell ref="C44:J44"/>
-    <mergeCell ref="X44:AF44"/>
-    <mergeCell ref="C45:J45"/>
-    <mergeCell ref="X45:AF45"/>
-    <mergeCell ref="M44:U44"/>
-    <mergeCell ref="M45:U45"/>
-    <mergeCell ref="C47:J47"/>
-    <mergeCell ref="M47:U47"/>
-    <mergeCell ref="X47:AF47"/>
-    <mergeCell ref="M48:U48"/>
-    <mergeCell ref="X48:AF48"/>
-    <mergeCell ref="C48:J48"/>
-    <mergeCell ref="C49:J49"/>
-    <mergeCell ref="M49:U49"/>
-    <mergeCell ref="X49:AF49"/>
-    <mergeCell ref="C50:J50"/>
-    <mergeCell ref="M50:U50"/>
-    <mergeCell ref="X50:AF50"/>
-    <mergeCell ref="C52:K52"/>
-    <mergeCell ref="C53:D54"/>
-    <mergeCell ref="E53:K54"/>
-    <mergeCell ref="L53:AG54"/>
-    <mergeCell ref="C55:D56"/>
-    <mergeCell ref="E55:K56"/>
-    <mergeCell ref="L55:AG56"/>
-    <mergeCell ref="C57:D58"/>
-    <mergeCell ref="E57:K58"/>
-    <mergeCell ref="L57:AG58"/>
-    <mergeCell ref="C59:D60"/>
-    <mergeCell ref="E59:K60"/>
-    <mergeCell ref="L59:AG60"/>
-    <mergeCell ref="Q61:S61"/>
-    <mergeCell ref="G22:K22"/>
-    <mergeCell ref="L22:P22"/>
-    <mergeCell ref="W22:AG22"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="G23:K23"/>
-    <mergeCell ref="L23:P23"/>
-    <mergeCell ref="Q23:V23"/>
-    <mergeCell ref="W23:AG23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="L26:P26"/>
-    <mergeCell ref="Q26:V26"/>
-    <mergeCell ref="L27:P27"/>
-    <mergeCell ref="Q27:V27"/>
-    <mergeCell ref="R28:X28"/>
-    <mergeCell ref="Y28:AG28"/>
-    <mergeCell ref="B30:AH30"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="G25:K25"/>
-    <mergeCell ref="L25:P25"/>
-    <mergeCell ref="D70:N70"/>
-    <mergeCell ref="B65:AH65"/>
-    <mergeCell ref="Q67:T67"/>
-    <mergeCell ref="U67:AF67"/>
-    <mergeCell ref="Q68:T68"/>
-    <mergeCell ref="U68:AF68"/>
-    <mergeCell ref="Q69:T69"/>
-    <mergeCell ref="U69:AF69"/>
-    <mergeCell ref="Q70:AG70"/>
-    <mergeCell ref="D69:M69"/>
+    <mergeCell ref="R16:X16"/>
+    <mergeCell ref="Y16:AG16"/>
+    <mergeCell ref="Q20:V20"/>
+    <mergeCell ref="W20:AG20"/>
+    <mergeCell ref="W21:AG21"/>
+    <mergeCell ref="B17:AH17"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="G19:K19"/>
+    <mergeCell ref="L19:P19"/>
+    <mergeCell ref="Q19:V19"/>
+    <mergeCell ref="W19:AG19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="G20:K20"/>
+    <mergeCell ref="L20:P20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="G21:K21"/>
+    <mergeCell ref="L21:P21"/>
+    <mergeCell ref="Q21:V21"/>
+    <mergeCell ref="B2:F5"/>
+    <mergeCell ref="G2:Y4"/>
+    <mergeCell ref="Z2:AH2"/>
+    <mergeCell ref="Z3:AH3"/>
+    <mergeCell ref="Z4:AH4"/>
+    <mergeCell ref="G5:AH5"/>
+    <mergeCell ref="B9:AH9"/>
+    <mergeCell ref="C11:F11"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/database/controller_excel/FO-DSP-TI-06 Reporte de mantenimiento preventivo a equipo de computo Rev.01.xlsx
+++ b/database/controller_excel/FO-DSP-TI-06 Reporte de mantenimiento preventivo a equipo de computo Rev.01.xlsx
@@ -959,7 +959,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="173">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1236,6 +1236,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1268,42 +1272,25 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1312,29 +1299,36 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1349,10 +1343,31 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1379,24 +1394,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1733,160 +1736,160 @@
     </row>
     <row r="2" spans="1:35" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="102" t="s">
+      <c r="B2" s="98"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="97"/>
-      <c r="L2" s="97"/>
-      <c r="M2" s="97"/>
-      <c r="N2" s="97"/>
-      <c r="O2" s="97"/>
-      <c r="P2" s="97"/>
-      <c r="Q2" s="97"/>
-      <c r="R2" s="97"/>
-      <c r="S2" s="97"/>
-      <c r="T2" s="97"/>
-      <c r="U2" s="97"/>
-      <c r="V2" s="97"/>
-      <c r="W2" s="97"/>
-      <c r="X2" s="97"/>
-      <c r="Y2" s="103"/>
-      <c r="Z2" s="109" t="s">
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
+      <c r="R2" s="99"/>
+      <c r="S2" s="99"/>
+      <c r="T2" s="99"/>
+      <c r="U2" s="99"/>
+      <c r="V2" s="99"/>
+      <c r="W2" s="99"/>
+      <c r="X2" s="99"/>
+      <c r="Y2" s="105"/>
+      <c r="Z2" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="AA2" s="110"/>
-      <c r="AB2" s="110"/>
-      <c r="AC2" s="110"/>
-      <c r="AD2" s="110"/>
-      <c r="AE2" s="110"/>
-      <c r="AF2" s="110"/>
-      <c r="AG2" s="110"/>
-      <c r="AH2" s="111"/>
+      <c r="AA2" s="112"/>
+      <c r="AB2" s="112"/>
+      <c r="AC2" s="112"/>
+      <c r="AD2" s="112"/>
+      <c r="AE2" s="112"/>
+      <c r="AF2" s="112"/>
+      <c r="AG2" s="112"/>
+      <c r="AH2" s="113"/>
       <c r="AI2" s="4"/>
     </row>
     <row r="3" spans="1:35" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="98"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="99"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="99"/>
-      <c r="M3" s="99"/>
-      <c r="N3" s="99"/>
-      <c r="O3" s="99"/>
-      <c r="P3" s="99"/>
-      <c r="Q3" s="99"/>
-      <c r="R3" s="99"/>
-      <c r="S3" s="99"/>
-      <c r="T3" s="99"/>
-      <c r="U3" s="99"/>
-      <c r="V3" s="99"/>
-      <c r="W3" s="99"/>
-      <c r="X3" s="99"/>
-      <c r="Y3" s="105"/>
-      <c r="Z3" s="112" t="s">
+      <c r="B3" s="100"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="101"/>
+      <c r="L3" s="101"/>
+      <c r="M3" s="101"/>
+      <c r="N3" s="101"/>
+      <c r="O3" s="101"/>
+      <c r="P3" s="101"/>
+      <c r="Q3" s="101"/>
+      <c r="R3" s="101"/>
+      <c r="S3" s="101"/>
+      <c r="T3" s="101"/>
+      <c r="U3" s="101"/>
+      <c r="V3" s="101"/>
+      <c r="W3" s="101"/>
+      <c r="X3" s="101"/>
+      <c r="Y3" s="107"/>
+      <c r="Z3" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="AA3" s="113"/>
-      <c r="AB3" s="113"/>
-      <c r="AC3" s="113"/>
-      <c r="AD3" s="113"/>
-      <c r="AE3" s="113"/>
-      <c r="AF3" s="113"/>
-      <c r="AG3" s="113"/>
-      <c r="AH3" s="114"/>
+      <c r="AA3" s="115"/>
+      <c r="AB3" s="115"/>
+      <c r="AC3" s="115"/>
+      <c r="AD3" s="115"/>
+      <c r="AE3" s="115"/>
+      <c r="AF3" s="115"/>
+      <c r="AG3" s="115"/>
+      <c r="AH3" s="116"/>
       <c r="AI3" s="4"/>
     </row>
     <row r="4" spans="1:35" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="98"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="107"/>
-      <c r="M4" s="107"/>
-      <c r="N4" s="107"/>
-      <c r="O4" s="107"/>
-      <c r="P4" s="107"/>
-      <c r="Q4" s="107"/>
-      <c r="R4" s="107"/>
-      <c r="S4" s="107"/>
-      <c r="T4" s="107"/>
-      <c r="U4" s="107"/>
-      <c r="V4" s="107"/>
-      <c r="W4" s="107"/>
-      <c r="X4" s="107"/>
-      <c r="Y4" s="108"/>
-      <c r="Z4" s="112" t="s">
+      <c r="B4" s="100"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="109"/>
+      <c r="L4" s="109"/>
+      <c r="M4" s="109"/>
+      <c r="N4" s="109"/>
+      <c r="O4" s="109"/>
+      <c r="P4" s="109"/>
+      <c r="Q4" s="109"/>
+      <c r="R4" s="109"/>
+      <c r="S4" s="109"/>
+      <c r="T4" s="109"/>
+      <c r="U4" s="109"/>
+      <c r="V4" s="109"/>
+      <c r="W4" s="109"/>
+      <c r="X4" s="109"/>
+      <c r="Y4" s="110"/>
+      <c r="Z4" s="114" t="s">
         <v>3</v>
       </c>
-      <c r="AA4" s="113"/>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="113"/>
-      <c r="AD4" s="113"/>
-      <c r="AE4" s="113"/>
-      <c r="AF4" s="113"/>
-      <c r="AG4" s="113"/>
-      <c r="AH4" s="114"/>
+      <c r="AA4" s="115"/>
+      <c r="AB4" s="115"/>
+      <c r="AC4" s="115"/>
+      <c r="AD4" s="115"/>
+      <c r="AE4" s="115"/>
+      <c r="AF4" s="115"/>
+      <c r="AG4" s="115"/>
+      <c r="AH4" s="116"/>
       <c r="AI4" s="4"/>
     </row>
     <row r="5" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="100"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="115" t="s">
+      <c r="B5" s="102"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="117" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="116"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="116"/>
-      <c r="K5" s="116"/>
-      <c r="L5" s="116"/>
-      <c r="M5" s="116"/>
-      <c r="N5" s="116"/>
-      <c r="O5" s="116"/>
-      <c r="P5" s="116"/>
-      <c r="Q5" s="116"/>
-      <c r="R5" s="116"/>
-      <c r="S5" s="116"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="116"/>
-      <c r="V5" s="116"/>
-      <c r="W5" s="116"/>
-      <c r="X5" s="116"/>
-      <c r="Y5" s="116"/>
-      <c r="Z5" s="116"/>
-      <c r="AA5" s="116"/>
-      <c r="AB5" s="116"/>
-      <c r="AC5" s="116"/>
-      <c r="AD5" s="116"/>
-      <c r="AE5" s="116"/>
-      <c r="AF5" s="116"/>
-      <c r="AG5" s="116"/>
-      <c r="AH5" s="117"/>
+      <c r="H5" s="118"/>
+      <c r="I5" s="118"/>
+      <c r="J5" s="118"/>
+      <c r="K5" s="118"/>
+      <c r="L5" s="118"/>
+      <c r="M5" s="118"/>
+      <c r="N5" s="118"/>
+      <c r="O5" s="118"/>
+      <c r="P5" s="118"/>
+      <c r="Q5" s="118"/>
+      <c r="R5" s="118"/>
+      <c r="S5" s="118"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="118"/>
+      <c r="V5" s="118"/>
+      <c r="W5" s="118"/>
+      <c r="X5" s="118"/>
+      <c r="Y5" s="118"/>
+      <c r="Z5" s="118"/>
+      <c r="AA5" s="118"/>
+      <c r="AB5" s="118"/>
+      <c r="AC5" s="118"/>
+      <c r="AD5" s="118"/>
+      <c r="AE5" s="118"/>
+      <c r="AF5" s="118"/>
+      <c r="AG5" s="118"/>
+      <c r="AH5" s="119"/>
       <c r="AI5" s="4"/>
     </row>
     <row r="6" spans="1:35" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1928,43 +1931,43 @@
     </row>
     <row r="7" spans="1:35" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
-      <c r="B7" s="166" t="s">
+      <c r="B7" s="96" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="167"/>
-      <c r="D7" s="167"/>
-      <c r="E7" s="167"/>
-      <c r="F7" s="167"/>
-      <c r="G7" s="167"/>
-      <c r="H7" s="167"/>
-      <c r="I7" s="167"/>
-      <c r="J7" s="167"/>
-      <c r="K7" s="167"/>
-      <c r="L7" s="167"/>
-      <c r="M7" s="167"/>
-      <c r="N7" s="167"/>
-      <c r="O7" s="167"/>
-      <c r="P7" s="167"/>
-      <c r="Q7" s="167"/>
-      <c r="R7" s="167"/>
-      <c r="S7" s="167"/>
-      <c r="T7" s="167"/>
-      <c r="U7" s="167"/>
-      <c r="V7" s="167"/>
-      <c r="W7" s="167"/>
-      <c r="X7" s="167"/>
-      <c r="Y7" s="167"/>
-      <c r="Z7" s="167"/>
-      <c r="AA7" s="167"/>
-      <c r="AB7" s="168" t="s">
+      <c r="C7" s="97"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="97"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="97"/>
+      <c r="H7" s="97"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
+      <c r="L7" s="97"/>
+      <c r="M7" s="97"/>
+      <c r="N7" s="97"/>
+      <c r="O7" s="97"/>
+      <c r="P7" s="97"/>
+      <c r="Q7" s="97"/>
+      <c r="R7" s="97"/>
+      <c r="S7" s="97"/>
+      <c r="T7" s="97"/>
+      <c r="U7" s="97"/>
+      <c r="V7" s="97"/>
+      <c r="W7" s="97"/>
+      <c r="X7" s="97"/>
+      <c r="Y7" s="97"/>
+      <c r="Z7" s="97"/>
+      <c r="AA7" s="97"/>
+      <c r="AB7" s="153" t="s">
         <v>67</v>
       </c>
-      <c r="AC7" s="169"/>
-      <c r="AD7" s="169"/>
-      <c r="AE7" s="169"/>
-      <c r="AF7" s="169"/>
-      <c r="AG7" s="169"/>
-      <c r="AH7" s="170"/>
+      <c r="AC7" s="154"/>
+      <c r="AD7" s="154"/>
+      <c r="AE7" s="154"/>
+      <c r="AF7" s="154"/>
+      <c r="AG7" s="154"/>
+      <c r="AH7" s="155"/>
       <c r="AI7" s="7"/>
     </row>
     <row r="8" spans="1:35" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2009,38 +2012,38 @@
       <c r="B9" s="120" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="118"/>
-      <c r="G9" s="118"/>
-      <c r="H9" s="118"/>
-      <c r="I9" s="118"/>
-      <c r="J9" s="118"/>
-      <c r="K9" s="118"/>
-      <c r="L9" s="118"/>
-      <c r="M9" s="118"/>
-      <c r="N9" s="118"/>
-      <c r="O9" s="118"/>
-      <c r="P9" s="118"/>
-      <c r="Q9" s="118"/>
-      <c r="R9" s="118"/>
-      <c r="S9" s="118"/>
-      <c r="T9" s="118"/>
-      <c r="U9" s="118"/>
-      <c r="V9" s="118"/>
-      <c r="W9" s="118"/>
-      <c r="X9" s="118"/>
-      <c r="Y9" s="118"/>
-      <c r="Z9" s="118"/>
-      <c r="AA9" s="118"/>
-      <c r="AB9" s="118"/>
-      <c r="AC9" s="118"/>
-      <c r="AD9" s="118"/>
-      <c r="AE9" s="118"/>
-      <c r="AF9" s="118"/>
-      <c r="AG9" s="118"/>
-      <c r="AH9" s="119"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="121"/>
+      <c r="K9" s="121"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="121"/>
+      <c r="R9" s="121"/>
+      <c r="S9" s="121"/>
+      <c r="T9" s="121"/>
+      <c r="U9" s="121"/>
+      <c r="V9" s="121"/>
+      <c r="W9" s="121"/>
+      <c r="X9" s="121"/>
+      <c r="Y9" s="121"/>
+      <c r="Z9" s="121"/>
+      <c r="AA9" s="121"/>
+      <c r="AB9" s="121"/>
+      <c r="AC9" s="121"/>
+      <c r="AD9" s="121"/>
+      <c r="AE9" s="121"/>
+      <c r="AF9" s="121"/>
+      <c r="AG9" s="121"/>
+      <c r="AH9" s="122"/>
       <c r="AI9" s="12"/>
     </row>
     <row r="10" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2086,36 +2089,36 @@
       <c r="C11" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="165"/>
-      <c r="E11" s="165"/>
-      <c r="F11" s="165"/>
-      <c r="G11" s="171"/>
-      <c r="H11" s="171"/>
-      <c r="I11" s="171"/>
-      <c r="J11" s="171"/>
-      <c r="K11" s="171"/>
-      <c r="L11" s="171"/>
-      <c r="M11" s="171"/>
-      <c r="N11" s="171"/>
-      <c r="O11" s="171"/>
-      <c r="P11" s="171"/>
-      <c r="Q11" s="171"/>
-      <c r="R11" s="171"/>
-      <c r="S11" s="171"/>
-      <c r="T11" s="171"/>
-      <c r="U11" s="171"/>
-      <c r="V11" s="171"/>
-      <c r="W11" s="171"/>
-      <c r="X11" s="171"/>
-      <c r="Y11" s="171"/>
-      <c r="Z11" s="171"/>
-      <c r="AA11" s="171"/>
-      <c r="AB11" s="171"/>
-      <c r="AC11" s="171"/>
-      <c r="AD11" s="171"/>
-      <c r="AE11" s="171"/>
-      <c r="AF11" s="171"/>
-      <c r="AG11" s="172"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="124"/>
+      <c r="G11" s="156"/>
+      <c r="H11" s="156"/>
+      <c r="I11" s="156"/>
+      <c r="J11" s="156"/>
+      <c r="K11" s="156"/>
+      <c r="L11" s="156"/>
+      <c r="M11" s="156"/>
+      <c r="N11" s="156"/>
+      <c r="O11" s="156"/>
+      <c r="P11" s="156"/>
+      <c r="Q11" s="156"/>
+      <c r="R11" s="156"/>
+      <c r="S11" s="156"/>
+      <c r="T11" s="156"/>
+      <c r="U11" s="156"/>
+      <c r="V11" s="156"/>
+      <c r="W11" s="156"/>
+      <c r="X11" s="156"/>
+      <c r="Y11" s="156"/>
+      <c r="Z11" s="156"/>
+      <c r="AA11" s="156"/>
+      <c r="AB11" s="156"/>
+      <c r="AC11" s="156"/>
+      <c r="AD11" s="156"/>
+      <c r="AE11" s="156"/>
+      <c r="AF11" s="156"/>
+      <c r="AG11" s="157"/>
       <c r="AH11" s="16"/>
       <c r="AI11" s="13"/>
     </row>
@@ -2125,36 +2128,36 @@
       <c r="C12" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="165"/>
-      <c r="E12" s="165"/>
-      <c r="F12" s="165"/>
-      <c r="G12" s="171"/>
-      <c r="H12" s="171"/>
-      <c r="I12" s="171"/>
-      <c r="J12" s="171"/>
-      <c r="K12" s="171"/>
-      <c r="L12" s="171"/>
-      <c r="M12" s="171"/>
-      <c r="N12" s="171"/>
-      <c r="O12" s="171"/>
-      <c r="P12" s="171"/>
-      <c r="Q12" s="171"/>
-      <c r="R12" s="171"/>
-      <c r="S12" s="171"/>
-      <c r="T12" s="171"/>
-      <c r="U12" s="171"/>
-      <c r="V12" s="171"/>
-      <c r="W12" s="171"/>
-      <c r="X12" s="171"/>
-      <c r="Y12" s="171"/>
-      <c r="Z12" s="171"/>
-      <c r="AA12" s="171"/>
-      <c r="AB12" s="171"/>
-      <c r="AC12" s="171"/>
-      <c r="AD12" s="171"/>
-      <c r="AE12" s="171"/>
-      <c r="AF12" s="171"/>
-      <c r="AG12" s="172"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="124"/>
+      <c r="F12" s="124"/>
+      <c r="G12" s="156"/>
+      <c r="H12" s="156"/>
+      <c r="I12" s="156"/>
+      <c r="J12" s="156"/>
+      <c r="K12" s="156"/>
+      <c r="L12" s="156"/>
+      <c r="M12" s="156"/>
+      <c r="N12" s="156"/>
+      <c r="O12" s="156"/>
+      <c r="P12" s="156"/>
+      <c r="Q12" s="156"/>
+      <c r="R12" s="156"/>
+      <c r="S12" s="156"/>
+      <c r="T12" s="156"/>
+      <c r="U12" s="156"/>
+      <c r="V12" s="156"/>
+      <c r="W12" s="156"/>
+      <c r="X12" s="156"/>
+      <c r="Y12" s="156"/>
+      <c r="Z12" s="156"/>
+      <c r="AA12" s="156"/>
+      <c r="AB12" s="156"/>
+      <c r="AC12" s="156"/>
+      <c r="AD12" s="156"/>
+      <c r="AE12" s="156"/>
+      <c r="AF12" s="156"/>
+      <c r="AG12" s="157"/>
       <c r="AH12" s="16"/>
       <c r="AI12" s="13"/>
     </row>
@@ -2164,75 +2167,75 @@
       <c r="C13" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="165"/>
-      <c r="E13" s="165"/>
-      <c r="F13" s="165"/>
-      <c r="G13" s="171"/>
-      <c r="H13" s="171"/>
-      <c r="I13" s="171"/>
-      <c r="J13" s="171"/>
-      <c r="K13" s="171"/>
-      <c r="L13" s="171"/>
-      <c r="M13" s="171"/>
-      <c r="N13" s="171"/>
-      <c r="O13" s="171"/>
-      <c r="P13" s="171"/>
-      <c r="Q13" s="171"/>
-      <c r="R13" s="171"/>
-      <c r="S13" s="171"/>
-      <c r="T13" s="171"/>
-      <c r="U13" s="171"/>
-      <c r="V13" s="171"/>
-      <c r="W13" s="171"/>
-      <c r="X13" s="171"/>
-      <c r="Y13" s="171"/>
-      <c r="Z13" s="171"/>
-      <c r="AA13" s="171"/>
-      <c r="AB13" s="171"/>
-      <c r="AC13" s="171"/>
-      <c r="AD13" s="171"/>
-      <c r="AE13" s="171"/>
-      <c r="AF13" s="171"/>
-      <c r="AG13" s="172"/>
+      <c r="D13" s="124"/>
+      <c r="E13" s="124"/>
+      <c r="F13" s="124"/>
+      <c r="G13" s="156"/>
+      <c r="H13" s="156"/>
+      <c r="I13" s="156"/>
+      <c r="J13" s="156"/>
+      <c r="K13" s="156"/>
+      <c r="L13" s="156"/>
+      <c r="M13" s="156"/>
+      <c r="N13" s="156"/>
+      <c r="O13" s="156"/>
+      <c r="P13" s="156"/>
+      <c r="Q13" s="156"/>
+      <c r="R13" s="156"/>
+      <c r="S13" s="156"/>
+      <c r="T13" s="156"/>
+      <c r="U13" s="156"/>
+      <c r="V13" s="156"/>
+      <c r="W13" s="156"/>
+      <c r="X13" s="156"/>
+      <c r="Y13" s="156"/>
+      <c r="Z13" s="156"/>
+      <c r="AA13" s="156"/>
+      <c r="AB13" s="156"/>
+      <c r="AC13" s="156"/>
+      <c r="AD13" s="156"/>
+      <c r="AE13" s="156"/>
+      <c r="AF13" s="156"/>
+      <c r="AG13" s="157"/>
       <c r="AH13" s="16"/>
       <c r="AI13" s="13"/>
     </row>
     <row r="14" spans="1:35" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17"/>
       <c r="B14" s="14"/>
-      <c r="C14" s="121" t="s">
+      <c r="C14" s="151" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="171"/>
-      <c r="H14" s="171"/>
-      <c r="I14" s="171"/>
-      <c r="J14" s="171"/>
-      <c r="K14" s="171"/>
-      <c r="L14" s="171"/>
-      <c r="M14" s="171"/>
-      <c r="N14" s="171"/>
-      <c r="O14" s="171"/>
-      <c r="P14" s="171"/>
-      <c r="Q14" s="171"/>
-      <c r="R14" s="171"/>
-      <c r="S14" s="171"/>
-      <c r="T14" s="171"/>
-      <c r="U14" s="171"/>
-      <c r="V14" s="171"/>
-      <c r="W14" s="171"/>
-      <c r="X14" s="171"/>
-      <c r="Y14" s="171"/>
-      <c r="Z14" s="171"/>
-      <c r="AA14" s="171"/>
-      <c r="AB14" s="171"/>
-      <c r="AC14" s="171"/>
-      <c r="AD14" s="171"/>
-      <c r="AE14" s="171"/>
-      <c r="AF14" s="171"/>
-      <c r="AG14" s="172"/>
+      <c r="D14" s="152"/>
+      <c r="E14" s="152"/>
+      <c r="F14" s="152"/>
+      <c r="G14" s="156"/>
+      <c r="H14" s="156"/>
+      <c r="I14" s="156"/>
+      <c r="J14" s="156"/>
+      <c r="K14" s="156"/>
+      <c r="L14" s="156"/>
+      <c r="M14" s="156"/>
+      <c r="N14" s="156"/>
+      <c r="O14" s="156"/>
+      <c r="P14" s="156"/>
+      <c r="Q14" s="156"/>
+      <c r="R14" s="156"/>
+      <c r="S14" s="156"/>
+      <c r="T14" s="156"/>
+      <c r="U14" s="156"/>
+      <c r="V14" s="156"/>
+      <c r="W14" s="156"/>
+      <c r="X14" s="156"/>
+      <c r="Y14" s="156"/>
+      <c r="Z14" s="156"/>
+      <c r="AA14" s="156"/>
+      <c r="AB14" s="156"/>
+      <c r="AC14" s="156"/>
+      <c r="AD14" s="156"/>
+      <c r="AE14" s="156"/>
+      <c r="AF14" s="156"/>
+      <c r="AG14" s="157"/>
       <c r="AH14" s="18"/>
       <c r="AI14" s="2"/>
     </row>
@@ -2291,62 +2294,62 @@
       <c r="O16" s="20"/>
       <c r="P16" s="20"/>
       <c r="Q16" s="20"/>
-      <c r="R16" s="125"/>
-      <c r="S16" s="99"/>
-      <c r="T16" s="99"/>
-      <c r="U16" s="99"/>
-      <c r="V16" s="99"/>
-      <c r="W16" s="99"/>
-      <c r="X16" s="99"/>
-      <c r="Y16" s="125"/>
-      <c r="Z16" s="99"/>
-      <c r="AA16" s="99"/>
-      <c r="AB16" s="99"/>
-      <c r="AC16" s="99"/>
-      <c r="AD16" s="99"/>
-      <c r="AE16" s="99"/>
-      <c r="AF16" s="99"/>
-      <c r="AG16" s="99"/>
+      <c r="R16" s="133"/>
+      <c r="S16" s="101"/>
+      <c r="T16" s="101"/>
+      <c r="U16" s="101"/>
+      <c r="V16" s="101"/>
+      <c r="W16" s="101"/>
+      <c r="X16" s="101"/>
+      <c r="Y16" s="133"/>
+      <c r="Z16" s="101"/>
+      <c r="AA16" s="101"/>
+      <c r="AB16" s="101"/>
+      <c r="AC16" s="101"/>
+      <c r="AD16" s="101"/>
+      <c r="AE16" s="101"/>
+      <c r="AF16" s="101"/>
+      <c r="AG16" s="101"/>
       <c r="AH16" s="16"/>
       <c r="AI16" s="13"/>
     </row>
     <row r="17" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="25"/>
-      <c r="B17" s="127" t="s">
+      <c r="B17" s="134" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="118"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="118"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="118"/>
-      <c r="I17" s="118"/>
-      <c r="J17" s="118"/>
-      <c r="K17" s="118"/>
-      <c r="L17" s="118"/>
-      <c r="M17" s="118"/>
-      <c r="N17" s="118"/>
-      <c r="O17" s="118"/>
-      <c r="P17" s="118"/>
-      <c r="Q17" s="118"/>
-      <c r="R17" s="118"/>
-      <c r="S17" s="118"/>
-      <c r="T17" s="118"/>
-      <c r="U17" s="118"/>
-      <c r="V17" s="118"/>
-      <c r="W17" s="118"/>
-      <c r="X17" s="118"/>
-      <c r="Y17" s="118"/>
-      <c r="Z17" s="118"/>
-      <c r="AA17" s="118"/>
-      <c r="AB17" s="118"/>
-      <c r="AC17" s="118"/>
-      <c r="AD17" s="118"/>
-      <c r="AE17" s="118"/>
-      <c r="AF17" s="118"/>
-      <c r="AG17" s="118"/>
-      <c r="AH17" s="119"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="121"/>
+      <c r="P17" s="121"/>
+      <c r="Q17" s="121"/>
+      <c r="R17" s="121"/>
+      <c r="S17" s="121"/>
+      <c r="T17" s="121"/>
+      <c r="U17" s="121"/>
+      <c r="V17" s="121"/>
+      <c r="W17" s="121"/>
+      <c r="X17" s="121"/>
+      <c r="Y17" s="121"/>
+      <c r="Z17" s="121"/>
+      <c r="AA17" s="121"/>
+      <c r="AB17" s="121"/>
+      <c r="AC17" s="121"/>
+      <c r="AD17" s="121"/>
+      <c r="AE17" s="121"/>
+      <c r="AF17" s="121"/>
+      <c r="AG17" s="121"/>
+      <c r="AH17" s="122"/>
       <c r="AI17" s="26"/>
     </row>
     <row r="18" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2389,281 +2392,281 @@
     <row r="19" spans="1:35" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="33"/>
       <c r="B19" s="34"/>
-      <c r="C19" s="128" t="s">
+      <c r="C19" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="113"/>
-      <c r="E19" s="113"/>
-      <c r="F19" s="124"/>
-      <c r="G19" s="129" t="s">
+      <c r="D19" s="115"/>
+      <c r="E19" s="115"/>
+      <c r="F19" s="126"/>
+      <c r="G19" s="136" t="s">
         <v>12</v>
       </c>
-      <c r="H19" s="113"/>
-      <c r="I19" s="113"/>
-      <c r="J19" s="113"/>
-      <c r="K19" s="124"/>
-      <c r="L19" s="129" t="s">
+      <c r="H19" s="115"/>
+      <c r="I19" s="115"/>
+      <c r="J19" s="115"/>
+      <c r="K19" s="126"/>
+      <c r="L19" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="M19" s="113"/>
-      <c r="N19" s="113"/>
-      <c r="O19" s="113"/>
-      <c r="P19" s="124"/>
-      <c r="Q19" s="129" t="s">
+      <c r="M19" s="115"/>
+      <c r="N19" s="115"/>
+      <c r="O19" s="115"/>
+      <c r="P19" s="126"/>
+      <c r="Q19" s="136" t="s">
         <v>14</v>
       </c>
-      <c r="R19" s="113"/>
-      <c r="S19" s="113"/>
-      <c r="T19" s="113"/>
-      <c r="U19" s="113"/>
-      <c r="V19" s="124"/>
-      <c r="W19" s="129" t="s">
+      <c r="R19" s="115"/>
+      <c r="S19" s="115"/>
+      <c r="T19" s="115"/>
+      <c r="U19" s="115"/>
+      <c r="V19" s="126"/>
+      <c r="W19" s="136" t="s">
         <v>15</v>
       </c>
-      <c r="X19" s="113"/>
-      <c r="Y19" s="113"/>
-      <c r="Z19" s="113"/>
-      <c r="AA19" s="113"/>
-      <c r="AB19" s="113"/>
-      <c r="AC19" s="113"/>
-      <c r="AD19" s="113"/>
-      <c r="AE19" s="113"/>
-      <c r="AF19" s="113"/>
-      <c r="AG19" s="124"/>
+      <c r="X19" s="115"/>
+      <c r="Y19" s="115"/>
+      <c r="Z19" s="115"/>
+      <c r="AA19" s="115"/>
+      <c r="AB19" s="115"/>
+      <c r="AC19" s="115"/>
+      <c r="AD19" s="115"/>
+      <c r="AE19" s="115"/>
+      <c r="AF19" s="115"/>
+      <c r="AG19" s="126"/>
       <c r="AH19" s="35"/>
       <c r="AI19" s="26"/>
     </row>
     <row r="20" spans="1:35" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="33"/>
       <c r="B20" s="34"/>
-      <c r="C20" s="130" t="s">
+      <c r="C20" s="137" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="113"/>
-      <c r="E20" s="113"/>
-      <c r="F20" s="124"/>
-      <c r="G20" s="126"/>
-      <c r="H20" s="113"/>
-      <c r="I20" s="113"/>
-      <c r="J20" s="113"/>
-      <c r="K20" s="124"/>
-      <c r="L20" s="126"/>
-      <c r="M20" s="113"/>
-      <c r="N20" s="113"/>
-      <c r="O20" s="113"/>
-      <c r="P20" s="124"/>
-      <c r="Q20" s="126"/>
-      <c r="R20" s="113"/>
-      <c r="S20" s="113"/>
-      <c r="T20" s="113"/>
-      <c r="U20" s="113"/>
-      <c r="V20" s="124"/>
-      <c r="W20" s="126"/>
-      <c r="X20" s="113"/>
-      <c r="Y20" s="113"/>
-      <c r="Z20" s="113"/>
-      <c r="AA20" s="113"/>
-      <c r="AB20" s="113"/>
-      <c r="AC20" s="113"/>
-      <c r="AD20" s="113"/>
-      <c r="AE20" s="113"/>
-      <c r="AF20" s="113"/>
-      <c r="AG20" s="124"/>
+      <c r="D20" s="115"/>
+      <c r="E20" s="115"/>
+      <c r="F20" s="126"/>
+      <c r="G20" s="125"/>
+      <c r="H20" s="115"/>
+      <c r="I20" s="115"/>
+      <c r="J20" s="115"/>
+      <c r="K20" s="126"/>
+      <c r="L20" s="125"/>
+      <c r="M20" s="115"/>
+      <c r="N20" s="115"/>
+      <c r="O20" s="115"/>
+      <c r="P20" s="126"/>
+      <c r="Q20" s="125"/>
+      <c r="R20" s="115"/>
+      <c r="S20" s="115"/>
+      <c r="T20" s="115"/>
+      <c r="U20" s="115"/>
+      <c r="V20" s="126"/>
+      <c r="W20" s="125"/>
+      <c r="X20" s="115"/>
+      <c r="Y20" s="115"/>
+      <c r="Z20" s="115"/>
+      <c r="AA20" s="115"/>
+      <c r="AB20" s="115"/>
+      <c r="AC20" s="115"/>
+      <c r="AD20" s="115"/>
+      <c r="AE20" s="115"/>
+      <c r="AF20" s="115"/>
+      <c r="AG20" s="126"/>
       <c r="AH20" s="35"/>
       <c r="AI20" s="26"/>
     </row>
     <row r="21" spans="1:35" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="33"/>
       <c r="B21" s="34"/>
-      <c r="C21" s="130" t="s">
+      <c r="C21" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="124"/>
-      <c r="G21" s="126"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="113"/>
-      <c r="J21" s="113"/>
-      <c r="K21" s="124"/>
-      <c r="L21" s="126"/>
-      <c r="M21" s="113"/>
-      <c r="N21" s="113"/>
-      <c r="O21" s="113"/>
-      <c r="P21" s="124"/>
-      <c r="Q21" s="126"/>
-      <c r="R21" s="113"/>
-      <c r="S21" s="113"/>
-      <c r="T21" s="113"/>
-      <c r="U21" s="113"/>
-      <c r="V21" s="124"/>
-      <c r="W21" s="126"/>
-      <c r="X21" s="113"/>
-      <c r="Y21" s="113"/>
-      <c r="Z21" s="113"/>
-      <c r="AA21" s="113"/>
-      <c r="AB21" s="113"/>
-      <c r="AC21" s="113"/>
-      <c r="AD21" s="113"/>
-      <c r="AE21" s="113"/>
-      <c r="AF21" s="113"/>
-      <c r="AG21" s="124"/>
+      <c r="D21" s="115"/>
+      <c r="E21" s="115"/>
+      <c r="F21" s="126"/>
+      <c r="G21" s="125"/>
+      <c r="H21" s="115"/>
+      <c r="I21" s="115"/>
+      <c r="J21" s="115"/>
+      <c r="K21" s="126"/>
+      <c r="L21" s="125"/>
+      <c r="M21" s="115"/>
+      <c r="N21" s="115"/>
+      <c r="O21" s="115"/>
+      <c r="P21" s="126"/>
+      <c r="Q21" s="125"/>
+      <c r="R21" s="115"/>
+      <c r="S21" s="115"/>
+      <c r="T21" s="115"/>
+      <c r="U21" s="115"/>
+      <c r="V21" s="126"/>
+      <c r="W21" s="125"/>
+      <c r="X21" s="115"/>
+      <c r="Y21" s="115"/>
+      <c r="Z21" s="115"/>
+      <c r="AA21" s="115"/>
+      <c r="AB21" s="115"/>
+      <c r="AC21" s="115"/>
+      <c r="AD21" s="115"/>
+      <c r="AE21" s="115"/>
+      <c r="AF21" s="115"/>
+      <c r="AG21" s="126"/>
       <c r="AH21" s="35"/>
       <c r="AI21" s="26"/>
     </row>
     <row r="22" spans="1:35" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="33"/>
       <c r="B22" s="34"/>
-      <c r="C22" s="130" t="s">
+      <c r="C22" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="113"/>
-      <c r="E22" s="113"/>
-      <c r="F22" s="124"/>
-      <c r="G22" s="126"/>
-      <c r="H22" s="113"/>
-      <c r="I22" s="113"/>
-      <c r="J22" s="113"/>
-      <c r="K22" s="124"/>
-      <c r="L22" s="126"/>
-      <c r="M22" s="113"/>
-      <c r="N22" s="113"/>
-      <c r="O22" s="113"/>
-      <c r="P22" s="124"/>
-      <c r="Q22" s="126"/>
-      <c r="R22" s="113"/>
-      <c r="S22" s="113"/>
-      <c r="T22" s="113"/>
-      <c r="U22" s="113"/>
-      <c r="V22" s="124"/>
-      <c r="W22" s="126"/>
-      <c r="X22" s="113"/>
-      <c r="Y22" s="113"/>
-      <c r="Z22" s="113"/>
-      <c r="AA22" s="113"/>
-      <c r="AB22" s="113"/>
-      <c r="AC22" s="113"/>
-      <c r="AD22" s="113"/>
-      <c r="AE22" s="113"/>
-      <c r="AF22" s="113"/>
-      <c r="AG22" s="124"/>
+      <c r="D22" s="115"/>
+      <c r="E22" s="115"/>
+      <c r="F22" s="126"/>
+      <c r="G22" s="125"/>
+      <c r="H22" s="115"/>
+      <c r="I22" s="115"/>
+      <c r="J22" s="115"/>
+      <c r="K22" s="126"/>
+      <c r="L22" s="125"/>
+      <c r="M22" s="115"/>
+      <c r="N22" s="115"/>
+      <c r="O22" s="115"/>
+      <c r="P22" s="126"/>
+      <c r="Q22" s="125"/>
+      <c r="R22" s="115"/>
+      <c r="S22" s="115"/>
+      <c r="T22" s="115"/>
+      <c r="U22" s="115"/>
+      <c r="V22" s="126"/>
+      <c r="W22" s="125"/>
+      <c r="X22" s="115"/>
+      <c r="Y22" s="115"/>
+      <c r="Z22" s="115"/>
+      <c r="AA22" s="115"/>
+      <c r="AB22" s="115"/>
+      <c r="AC22" s="115"/>
+      <c r="AD22" s="115"/>
+      <c r="AE22" s="115"/>
+      <c r="AF22" s="115"/>
+      <c r="AG22" s="126"/>
       <c r="AH22" s="35"/>
       <c r="AI22" s="26"/>
     </row>
     <row r="23" spans="1:35" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="33"/>
       <c r="B23" s="34"/>
-      <c r="C23" s="130" t="s">
+      <c r="C23" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="113"/>
-      <c r="E23" s="113"/>
-      <c r="F23" s="124"/>
-      <c r="G23" s="126"/>
-      <c r="H23" s="113"/>
-      <c r="I23" s="113"/>
-      <c r="J23" s="113"/>
-      <c r="K23" s="124"/>
-      <c r="L23" s="126"/>
-      <c r="M23" s="113"/>
-      <c r="N23" s="113"/>
-      <c r="O23" s="113"/>
-      <c r="P23" s="124"/>
-      <c r="Q23" s="126"/>
-      <c r="R23" s="113"/>
-      <c r="S23" s="113"/>
-      <c r="T23" s="113"/>
-      <c r="U23" s="113"/>
-      <c r="V23" s="124"/>
-      <c r="W23" s="126"/>
-      <c r="X23" s="113"/>
-      <c r="Y23" s="113"/>
-      <c r="Z23" s="113"/>
-      <c r="AA23" s="113"/>
-      <c r="AB23" s="113"/>
-      <c r="AC23" s="113"/>
-      <c r="AD23" s="113"/>
-      <c r="AE23" s="113"/>
-      <c r="AF23" s="113"/>
-      <c r="AG23" s="124"/>
+      <c r="D23" s="115"/>
+      <c r="E23" s="115"/>
+      <c r="F23" s="126"/>
+      <c r="G23" s="125"/>
+      <c r="H23" s="115"/>
+      <c r="I23" s="115"/>
+      <c r="J23" s="115"/>
+      <c r="K23" s="126"/>
+      <c r="L23" s="125"/>
+      <c r="M23" s="115"/>
+      <c r="N23" s="115"/>
+      <c r="O23" s="115"/>
+      <c r="P23" s="126"/>
+      <c r="Q23" s="125"/>
+      <c r="R23" s="115"/>
+      <c r="S23" s="115"/>
+      <c r="T23" s="115"/>
+      <c r="U23" s="115"/>
+      <c r="V23" s="126"/>
+      <c r="W23" s="125"/>
+      <c r="X23" s="115"/>
+      <c r="Y23" s="115"/>
+      <c r="Z23" s="115"/>
+      <c r="AA23" s="115"/>
+      <c r="AB23" s="115"/>
+      <c r="AC23" s="115"/>
+      <c r="AD23" s="115"/>
+      <c r="AE23" s="115"/>
+      <c r="AF23" s="115"/>
+      <c r="AG23" s="126"/>
       <c r="AH23" s="35"/>
       <c r="AI23" s="26"/>
     </row>
     <row r="24" spans="1:35" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="33"/>
       <c r="B24" s="34"/>
-      <c r="C24" s="130" t="s">
+      <c r="C24" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="113"/>
-      <c r="E24" s="113"/>
-      <c r="F24" s="124"/>
-      <c r="G24" s="131"/>
-      <c r="H24" s="113"/>
-      <c r="I24" s="113"/>
-      <c r="J24" s="113"/>
-      <c r="K24" s="124"/>
-      <c r="L24" s="126"/>
-      <c r="M24" s="113"/>
-      <c r="N24" s="113"/>
-      <c r="O24" s="113"/>
-      <c r="P24" s="124"/>
-      <c r="Q24" s="126"/>
-      <c r="R24" s="113"/>
-      <c r="S24" s="113"/>
-      <c r="T24" s="113"/>
-      <c r="U24" s="113"/>
-      <c r="V24" s="124"/>
-      <c r="W24" s="126"/>
-      <c r="X24" s="113"/>
-      <c r="Y24" s="113"/>
-      <c r="Z24" s="113"/>
-      <c r="AA24" s="113"/>
-      <c r="AB24" s="113"/>
-      <c r="AC24" s="113"/>
-      <c r="AD24" s="113"/>
-      <c r="AE24" s="113"/>
-      <c r="AF24" s="113"/>
-      <c r="AG24" s="124"/>
+      <c r="D24" s="115"/>
+      <c r="E24" s="115"/>
+      <c r="F24" s="126"/>
+      <c r="G24" s="125"/>
+      <c r="H24" s="172"/>
+      <c r="I24" s="172"/>
+      <c r="J24" s="172"/>
+      <c r="K24" s="173"/>
+      <c r="L24" s="125"/>
+      <c r="M24" s="115"/>
+      <c r="N24" s="115"/>
+      <c r="O24" s="115"/>
+      <c r="P24" s="126"/>
+      <c r="Q24" s="125"/>
+      <c r="R24" s="115"/>
+      <c r="S24" s="115"/>
+      <c r="T24" s="115"/>
+      <c r="U24" s="115"/>
+      <c r="V24" s="126"/>
+      <c r="W24" s="125"/>
+      <c r="X24" s="115"/>
+      <c r="Y24" s="115"/>
+      <c r="Z24" s="115"/>
+      <c r="AA24" s="115"/>
+      <c r="AB24" s="115"/>
+      <c r="AC24" s="115"/>
+      <c r="AD24" s="115"/>
+      <c r="AE24" s="115"/>
+      <c r="AF24" s="115"/>
+      <c r="AG24" s="126"/>
       <c r="AH24" s="35"/>
       <c r="AI24" s="26"/>
     </row>
     <row r="25" spans="1:35" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="33"/>
       <c r="B25" s="34"/>
-      <c r="C25" s="130" t="s">
+      <c r="C25" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="113"/>
-      <c r="E25" s="113"/>
-      <c r="F25" s="124"/>
-      <c r="G25" s="131"/>
-      <c r="H25" s="113"/>
-      <c r="I25" s="113"/>
-      <c r="J25" s="113"/>
-      <c r="K25" s="124"/>
-      <c r="L25" s="126"/>
-      <c r="M25" s="113"/>
-      <c r="N25" s="113"/>
-      <c r="O25" s="113"/>
-      <c r="P25" s="124"/>
-      <c r="Q25" s="126"/>
-      <c r="R25" s="113"/>
-      <c r="S25" s="113"/>
-      <c r="T25" s="113"/>
-      <c r="U25" s="113"/>
-      <c r="V25" s="124"/>
-      <c r="W25" s="126"/>
-      <c r="X25" s="113"/>
-      <c r="Y25" s="113"/>
-      <c r="Z25" s="113"/>
-      <c r="AA25" s="113"/>
-      <c r="AB25" s="113"/>
-      <c r="AC25" s="113"/>
-      <c r="AD25" s="113"/>
-      <c r="AE25" s="113"/>
-      <c r="AF25" s="113"/>
-      <c r="AG25" s="124"/>
+      <c r="D25" s="115"/>
+      <c r="E25" s="115"/>
+      <c r="F25" s="126"/>
+      <c r="G25" s="125"/>
+      <c r="H25" s="172"/>
+      <c r="I25" s="172"/>
+      <c r="J25" s="172"/>
+      <c r="K25" s="173"/>
+      <c r="L25" s="125"/>
+      <c r="M25" s="115"/>
+      <c r="N25" s="115"/>
+      <c r="O25" s="115"/>
+      <c r="P25" s="126"/>
+      <c r="Q25" s="125"/>
+      <c r="R25" s="115"/>
+      <c r="S25" s="115"/>
+      <c r="T25" s="115"/>
+      <c r="U25" s="115"/>
+      <c r="V25" s="126"/>
+      <c r="W25" s="125"/>
+      <c r="X25" s="115"/>
+      <c r="Y25" s="115"/>
+      <c r="Z25" s="115"/>
+      <c r="AA25" s="115"/>
+      <c r="AB25" s="115"/>
+      <c r="AC25" s="115"/>
+      <c r="AD25" s="115"/>
+      <c r="AE25" s="115"/>
+      <c r="AF25" s="115"/>
+      <c r="AG25" s="126"/>
       <c r="AH25" s="35"/>
       <c r="AI25" s="26"/>
     </row>
@@ -2673,73 +2676,73 @@
       <c r="C26" s="138" t="s">
         <v>22</v>
       </c>
-      <c r="D26" s="133"/>
-      <c r="E26" s="133"/>
-      <c r="F26" s="134"/>
-      <c r="G26" s="131"/>
-      <c r="H26" s="113"/>
-      <c r="I26" s="113"/>
-      <c r="J26" s="113"/>
-      <c r="K26" s="124"/>
-      <c r="L26" s="126"/>
-      <c r="M26" s="113"/>
-      <c r="N26" s="113"/>
-      <c r="O26" s="113"/>
-      <c r="P26" s="124"/>
-      <c r="Q26" s="126"/>
-      <c r="R26" s="113"/>
-      <c r="S26" s="113"/>
-      <c r="T26" s="113"/>
-      <c r="U26" s="113"/>
-      <c r="V26" s="124"/>
-      <c r="W26" s="126"/>
-      <c r="X26" s="113"/>
-      <c r="Y26" s="113"/>
-      <c r="Z26" s="113"/>
-      <c r="AA26" s="113"/>
-      <c r="AB26" s="113"/>
-      <c r="AC26" s="113"/>
-      <c r="AD26" s="113"/>
-      <c r="AE26" s="113"/>
-      <c r="AF26" s="113"/>
-      <c r="AG26" s="124"/>
+      <c r="D26" s="130"/>
+      <c r="E26" s="130"/>
+      <c r="F26" s="131"/>
+      <c r="G26" s="125"/>
+      <c r="H26" s="172"/>
+      <c r="I26" s="172"/>
+      <c r="J26" s="172"/>
+      <c r="K26" s="173"/>
+      <c r="L26" s="125"/>
+      <c r="M26" s="115"/>
+      <c r="N26" s="115"/>
+      <c r="O26" s="115"/>
+      <c r="P26" s="126"/>
+      <c r="Q26" s="125"/>
+      <c r="R26" s="115"/>
+      <c r="S26" s="115"/>
+      <c r="T26" s="115"/>
+      <c r="U26" s="115"/>
+      <c r="V26" s="126"/>
+      <c r="W26" s="125"/>
+      <c r="X26" s="115"/>
+      <c r="Y26" s="115"/>
+      <c r="Z26" s="115"/>
+      <c r="AA26" s="115"/>
+      <c r="AB26" s="115"/>
+      <c r="AC26" s="115"/>
+      <c r="AD26" s="115"/>
+      <c r="AE26" s="115"/>
+      <c r="AF26" s="115"/>
+      <c r="AG26" s="126"/>
       <c r="AH26" s="35"/>
       <c r="AI26" s="26"/>
     </row>
     <row r="27" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33"/>
       <c r="B27" s="34"/>
-      <c r="C27" s="106"/>
-      <c r="D27" s="107"/>
-      <c r="E27" s="107"/>
-      <c r="F27" s="108"/>
-      <c r="G27" s="131"/>
-      <c r="H27" s="113"/>
-      <c r="I27" s="113"/>
-      <c r="J27" s="113"/>
-      <c r="K27" s="124"/>
-      <c r="L27" s="126"/>
-      <c r="M27" s="113"/>
-      <c r="N27" s="113"/>
-      <c r="O27" s="113"/>
-      <c r="P27" s="124"/>
-      <c r="Q27" s="126"/>
-      <c r="R27" s="113"/>
-      <c r="S27" s="113"/>
-      <c r="T27" s="113"/>
-      <c r="U27" s="113"/>
-      <c r="V27" s="124"/>
-      <c r="W27" s="126"/>
-      <c r="X27" s="113"/>
-      <c r="Y27" s="113"/>
-      <c r="Z27" s="113"/>
-      <c r="AA27" s="113"/>
-      <c r="AB27" s="113"/>
-      <c r="AC27" s="113"/>
-      <c r="AD27" s="113"/>
-      <c r="AE27" s="113"/>
-      <c r="AF27" s="113"/>
-      <c r="AG27" s="124"/>
+      <c r="C27" s="108"/>
+      <c r="D27" s="109"/>
+      <c r="E27" s="109"/>
+      <c r="F27" s="110"/>
+      <c r="G27" s="125"/>
+      <c r="H27" s="172"/>
+      <c r="I27" s="172"/>
+      <c r="J27" s="172"/>
+      <c r="K27" s="173"/>
+      <c r="L27" s="125"/>
+      <c r="M27" s="115"/>
+      <c r="N27" s="115"/>
+      <c r="O27" s="115"/>
+      <c r="P27" s="126"/>
+      <c r="Q27" s="125"/>
+      <c r="R27" s="115"/>
+      <c r="S27" s="115"/>
+      <c r="T27" s="115"/>
+      <c r="U27" s="115"/>
+      <c r="V27" s="126"/>
+      <c r="W27" s="125"/>
+      <c r="X27" s="115"/>
+      <c r="Y27" s="115"/>
+      <c r="Z27" s="115"/>
+      <c r="AA27" s="115"/>
+      <c r="AB27" s="115"/>
+      <c r="AC27" s="115"/>
+      <c r="AD27" s="115"/>
+      <c r="AE27" s="115"/>
+      <c r="AF27" s="115"/>
+      <c r="AG27" s="126"/>
       <c r="AH27" s="35"/>
       <c r="AI27" s="26"/>
     </row>
@@ -2761,22 +2764,22 @@
       <c r="O28" s="20"/>
       <c r="P28" s="20"/>
       <c r="Q28" s="20"/>
-      <c r="R28" s="125"/>
-      <c r="S28" s="99"/>
-      <c r="T28" s="99"/>
-      <c r="U28" s="99"/>
-      <c r="V28" s="99"/>
-      <c r="W28" s="99"/>
-      <c r="X28" s="99"/>
-      <c r="Y28" s="125"/>
-      <c r="Z28" s="99"/>
-      <c r="AA28" s="99"/>
-      <c r="AB28" s="99"/>
-      <c r="AC28" s="99"/>
-      <c r="AD28" s="99"/>
-      <c r="AE28" s="99"/>
-      <c r="AF28" s="99"/>
-      <c r="AG28" s="99"/>
+      <c r="R28" s="133"/>
+      <c r="S28" s="101"/>
+      <c r="T28" s="101"/>
+      <c r="U28" s="101"/>
+      <c r="V28" s="101"/>
+      <c r="W28" s="101"/>
+      <c r="X28" s="101"/>
+      <c r="Y28" s="133"/>
+      <c r="Z28" s="101"/>
+      <c r="AA28" s="101"/>
+      <c r="AB28" s="101"/>
+      <c r="AC28" s="101"/>
+      <c r="AD28" s="101"/>
+      <c r="AE28" s="101"/>
+      <c r="AF28" s="101"/>
+      <c r="AG28" s="101"/>
       <c r="AH28" s="16"/>
       <c r="AI28" s="13"/>
     </row>
@@ -2822,38 +2825,38 @@
       <c r="B30" s="120" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="118"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="118"/>
-      <c r="F30" s="118"/>
-      <c r="G30" s="118"/>
-      <c r="H30" s="118"/>
-      <c r="I30" s="118"/>
-      <c r="J30" s="118"/>
-      <c r="K30" s="118"/>
-      <c r="L30" s="118"/>
-      <c r="M30" s="118"/>
-      <c r="N30" s="118"/>
-      <c r="O30" s="118"/>
-      <c r="P30" s="118"/>
-      <c r="Q30" s="118"/>
-      <c r="R30" s="118"/>
-      <c r="S30" s="118"/>
-      <c r="T30" s="118"/>
-      <c r="U30" s="118"/>
-      <c r="V30" s="118"/>
-      <c r="W30" s="118"/>
-      <c r="X30" s="118"/>
-      <c r="Y30" s="118"/>
-      <c r="Z30" s="118"/>
-      <c r="AA30" s="118"/>
-      <c r="AB30" s="118"/>
-      <c r="AC30" s="118"/>
-      <c r="AD30" s="118"/>
-      <c r="AE30" s="118"/>
-      <c r="AF30" s="118"/>
-      <c r="AG30" s="118"/>
-      <c r="AH30" s="119"/>
+      <c r="C30" s="121"/>
+      <c r="D30" s="121"/>
+      <c r="E30" s="121"/>
+      <c r="F30" s="121"/>
+      <c r="G30" s="121"/>
+      <c r="H30" s="121"/>
+      <c r="I30" s="121"/>
+      <c r="J30" s="121"/>
+      <c r="K30" s="121"/>
+      <c r="L30" s="121"/>
+      <c r="M30" s="121"/>
+      <c r="N30" s="121"/>
+      <c r="O30" s="121"/>
+      <c r="P30" s="121"/>
+      <c r="Q30" s="121"/>
+      <c r="R30" s="121"/>
+      <c r="S30" s="121"/>
+      <c r="T30" s="121"/>
+      <c r="U30" s="121"/>
+      <c r="V30" s="121"/>
+      <c r="W30" s="121"/>
+      <c r="X30" s="121"/>
+      <c r="Y30" s="121"/>
+      <c r="Z30" s="121"/>
+      <c r="AA30" s="121"/>
+      <c r="AB30" s="121"/>
+      <c r="AC30" s="121"/>
+      <c r="AD30" s="121"/>
+      <c r="AE30" s="121"/>
+      <c r="AF30" s="121"/>
+      <c r="AG30" s="121"/>
+      <c r="AH30" s="122"/>
       <c r="AI30" s="13"/>
     </row>
     <row r="31" spans="1:35" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2896,53 +2899,53 @@
     <row r="32" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="38"/>
       <c r="B32" s="39"/>
-      <c r="C32" s="132" t="s">
+      <c r="C32" s="129" t="s">
         <v>24</v>
       </c>
-      <c r="D32" s="133"/>
-      <c r="E32" s="133"/>
-      <c r="F32" s="133"/>
-      <c r="G32" s="133"/>
-      <c r="H32" s="133"/>
-      <c r="I32" s="133"/>
-      <c r="J32" s="134"/>
-      <c r="K32" s="136" t="s">
+      <c r="D32" s="130"/>
+      <c r="E32" s="130"/>
+      <c r="F32" s="130"/>
+      <c r="G32" s="130"/>
+      <c r="H32" s="130"/>
+      <c r="I32" s="130"/>
+      <c r="J32" s="131"/>
+      <c r="K32" s="127" t="s">
         <v>25</v>
       </c>
-      <c r="L32" s="136" t="s">
+      <c r="L32" s="127" t="s">
         <v>26</v>
       </c>
-      <c r="M32" s="132" t="s">
+      <c r="M32" s="129" t="s">
         <v>24</v>
       </c>
-      <c r="N32" s="133"/>
-      <c r="O32" s="133"/>
-      <c r="P32" s="133"/>
-      <c r="Q32" s="133"/>
-      <c r="R32" s="133"/>
-      <c r="S32" s="133"/>
-      <c r="T32" s="134"/>
-      <c r="U32" s="136" t="s">
+      <c r="N32" s="130"/>
+      <c r="O32" s="130"/>
+      <c r="P32" s="130"/>
+      <c r="Q32" s="130"/>
+      <c r="R32" s="130"/>
+      <c r="S32" s="130"/>
+      <c r="T32" s="131"/>
+      <c r="U32" s="127" t="s">
         <v>25</v>
       </c>
-      <c r="V32" s="136" t="s">
+      <c r="V32" s="127" t="s">
         <v>26</v>
       </c>
-      <c r="W32" s="132" t="s">
+      <c r="W32" s="129" t="s">
         <v>24</v>
       </c>
-      <c r="X32" s="133"/>
-      <c r="Y32" s="133"/>
-      <c r="Z32" s="133"/>
-      <c r="AA32" s="133"/>
-      <c r="AB32" s="133"/>
-      <c r="AC32" s="133"/>
-      <c r="AD32" s="133"/>
-      <c r="AE32" s="134"/>
-      <c r="AF32" s="136" t="s">
+      <c r="X32" s="130"/>
+      <c r="Y32" s="130"/>
+      <c r="Z32" s="130"/>
+      <c r="AA32" s="130"/>
+      <c r="AB32" s="130"/>
+      <c r="AC32" s="130"/>
+      <c r="AD32" s="130"/>
+      <c r="AE32" s="131"/>
+      <c r="AF32" s="127" t="s">
         <v>25</v>
       </c>
-      <c r="AG32" s="136" t="s">
+      <c r="AG32" s="127" t="s">
         <v>26</v>
       </c>
       <c r="AH32" s="40"/>
@@ -2951,78 +2954,78 @@
     <row r="33" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="38"/>
       <c r="B33" s="39"/>
-      <c r="C33" s="106"/>
-      <c r="D33" s="107"/>
-      <c r="E33" s="107"/>
-      <c r="F33" s="107"/>
-      <c r="G33" s="107"/>
-      <c r="H33" s="107"/>
-      <c r="I33" s="107"/>
-      <c r="J33" s="108"/>
-      <c r="K33" s="137"/>
-      <c r="L33" s="137"/>
-      <c r="M33" s="106"/>
-      <c r="N33" s="107"/>
-      <c r="O33" s="107"/>
-      <c r="P33" s="107"/>
-      <c r="Q33" s="107"/>
-      <c r="R33" s="107"/>
-      <c r="S33" s="107"/>
-      <c r="T33" s="108"/>
-      <c r="U33" s="137"/>
-      <c r="V33" s="137"/>
-      <c r="W33" s="106"/>
-      <c r="X33" s="107"/>
-      <c r="Y33" s="107"/>
-      <c r="Z33" s="107"/>
-      <c r="AA33" s="107"/>
-      <c r="AB33" s="107"/>
-      <c r="AC33" s="107"/>
-      <c r="AD33" s="107"/>
-      <c r="AE33" s="108"/>
-      <c r="AF33" s="137"/>
-      <c r="AG33" s="137"/>
+      <c r="C33" s="108"/>
+      <c r="D33" s="109"/>
+      <c r="E33" s="109"/>
+      <c r="F33" s="109"/>
+      <c r="G33" s="109"/>
+      <c r="H33" s="109"/>
+      <c r="I33" s="109"/>
+      <c r="J33" s="110"/>
+      <c r="K33" s="128"/>
+      <c r="L33" s="128"/>
+      <c r="M33" s="108"/>
+      <c r="N33" s="109"/>
+      <c r="O33" s="109"/>
+      <c r="P33" s="109"/>
+      <c r="Q33" s="109"/>
+      <c r="R33" s="109"/>
+      <c r="S33" s="109"/>
+      <c r="T33" s="110"/>
+      <c r="U33" s="128"/>
+      <c r="V33" s="128"/>
+      <c r="W33" s="108"/>
+      <c r="X33" s="109"/>
+      <c r="Y33" s="109"/>
+      <c r="Z33" s="109"/>
+      <c r="AA33" s="109"/>
+      <c r="AB33" s="109"/>
+      <c r="AC33" s="109"/>
+      <c r="AD33" s="109"/>
+      <c r="AE33" s="110"/>
+      <c r="AF33" s="128"/>
+      <c r="AG33" s="128"/>
       <c r="AH33" s="42"/>
       <c r="AI33" s="43"/>
     </row>
     <row r="34" spans="1:35" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="23"/>
       <c r="B34" s="24"/>
-      <c r="C34" s="135" t="s">
+      <c r="C34" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="D34" s="113"/>
-      <c r="E34" s="113"/>
-      <c r="F34" s="113"/>
-      <c r="G34" s="113"/>
-      <c r="H34" s="113"/>
-      <c r="I34" s="113"/>
-      <c r="J34" s="124"/>
+      <c r="D34" s="115"/>
+      <c r="E34" s="115"/>
+      <c r="F34" s="115"/>
+      <c r="G34" s="115"/>
+      <c r="H34" s="115"/>
+      <c r="I34" s="115"/>
+      <c r="J34" s="126"/>
       <c r="K34" s="44"/>
       <c r="L34" s="44"/>
-      <c r="M34" s="135" t="s">
+      <c r="M34" s="132" t="s">
         <v>28</v>
       </c>
-      <c r="N34" s="113"/>
-      <c r="O34" s="113"/>
-      <c r="P34" s="113"/>
-      <c r="Q34" s="113"/>
-      <c r="R34" s="113"/>
-      <c r="S34" s="113"/>
-      <c r="T34" s="124"/>
+      <c r="N34" s="115"/>
+      <c r="O34" s="115"/>
+      <c r="P34" s="115"/>
+      <c r="Q34" s="115"/>
+      <c r="R34" s="115"/>
+      <c r="S34" s="115"/>
+      <c r="T34" s="126"/>
       <c r="U34" s="44"/>
       <c r="V34" s="44"/>
-      <c r="W34" s="135" t="s">
+      <c r="W34" s="132" t="s">
         <v>29</v>
       </c>
-      <c r="X34" s="113"/>
-      <c r="Y34" s="113"/>
-      <c r="Z34" s="113"/>
-      <c r="AA34" s="113"/>
-      <c r="AB34" s="113"/>
-      <c r="AC34" s="113"/>
-      <c r="AD34" s="113"/>
-      <c r="AE34" s="124"/>
+      <c r="X34" s="115"/>
+      <c r="Y34" s="115"/>
+      <c r="Z34" s="115"/>
+      <c r="AA34" s="115"/>
+      <c r="AB34" s="115"/>
+      <c r="AC34" s="115"/>
+      <c r="AD34" s="115"/>
+      <c r="AE34" s="126"/>
       <c r="AF34" s="44"/>
       <c r="AG34" s="44"/>
       <c r="AH34" s="42"/>
@@ -3031,41 +3034,41 @@
     <row r="35" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="23"/>
       <c r="B35" s="24"/>
-      <c r="C35" s="135" t="s">
+      <c r="C35" s="132" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="113"/>
-      <c r="E35" s="113"/>
-      <c r="F35" s="113"/>
-      <c r="G35" s="113"/>
-      <c r="H35" s="113"/>
-      <c r="I35" s="113"/>
-      <c r="J35" s="124"/>
+      <c r="D35" s="115"/>
+      <c r="E35" s="115"/>
+      <c r="F35" s="115"/>
+      <c r="G35" s="115"/>
+      <c r="H35" s="115"/>
+      <c r="I35" s="115"/>
+      <c r="J35" s="126"/>
       <c r="K35" s="44"/>
       <c r="L35" s="44"/>
-      <c r="M35" s="135" t="s">
+      <c r="M35" s="132" t="s">
         <v>31</v>
       </c>
-      <c r="N35" s="113"/>
-      <c r="O35" s="113"/>
-      <c r="P35" s="113"/>
-      <c r="Q35" s="113"/>
-      <c r="R35" s="113"/>
-      <c r="S35" s="113"/>
-      <c r="T35" s="124"/>
+      <c r="N35" s="115"/>
+      <c r="O35" s="115"/>
+      <c r="P35" s="115"/>
+      <c r="Q35" s="115"/>
+      <c r="R35" s="115"/>
+      <c r="S35" s="115"/>
+      <c r="T35" s="126"/>
       <c r="U35" s="44"/>
       <c r="V35" s="44"/>
-      <c r="W35" s="135" t="s">
+      <c r="W35" s="132" t="s">
         <v>32</v>
       </c>
-      <c r="X35" s="113"/>
-      <c r="Y35" s="113"/>
-      <c r="Z35" s="113"/>
-      <c r="AA35" s="113"/>
-      <c r="AB35" s="113"/>
-      <c r="AC35" s="113"/>
-      <c r="AD35" s="113"/>
-      <c r="AE35" s="124"/>
+      <c r="X35" s="115"/>
+      <c r="Y35" s="115"/>
+      <c r="Z35" s="115"/>
+      <c r="AA35" s="115"/>
+      <c r="AB35" s="115"/>
+      <c r="AC35" s="115"/>
+      <c r="AD35" s="115"/>
+      <c r="AE35" s="126"/>
       <c r="AF35" s="44"/>
       <c r="AG35" s="44"/>
       <c r="AH35" s="42"/>
@@ -3074,41 +3077,41 @@
     <row r="36" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="23"/>
       <c r="B36" s="24"/>
-      <c r="C36" s="135" t="s">
+      <c r="C36" s="132" t="s">
         <v>33</v>
       </c>
-      <c r="D36" s="113"/>
-      <c r="E36" s="113"/>
-      <c r="F36" s="113"/>
-      <c r="G36" s="113"/>
-      <c r="H36" s="113"/>
-      <c r="I36" s="113"/>
-      <c r="J36" s="124"/>
+      <c r="D36" s="115"/>
+      <c r="E36" s="115"/>
+      <c r="F36" s="115"/>
+      <c r="G36" s="115"/>
+      <c r="H36" s="115"/>
+      <c r="I36" s="115"/>
+      <c r="J36" s="126"/>
       <c r="K36" s="44"/>
       <c r="L36" s="44"/>
-      <c r="M36" s="135" t="s">
+      <c r="M36" s="132" t="s">
         <v>34</v>
       </c>
-      <c r="N36" s="113"/>
-      <c r="O36" s="113"/>
-      <c r="P36" s="113"/>
-      <c r="Q36" s="113"/>
-      <c r="R36" s="113"/>
-      <c r="S36" s="113"/>
-      <c r="T36" s="124"/>
+      <c r="N36" s="115"/>
+      <c r="O36" s="115"/>
+      <c r="P36" s="115"/>
+      <c r="Q36" s="115"/>
+      <c r="R36" s="115"/>
+      <c r="S36" s="115"/>
+      <c r="T36" s="126"/>
       <c r="U36" s="44"/>
       <c r="V36" s="44"/>
-      <c r="W36" s="135" t="s">
+      <c r="W36" s="132" t="s">
         <v>35</v>
       </c>
-      <c r="X36" s="113"/>
-      <c r="Y36" s="113"/>
-      <c r="Z36" s="113"/>
-      <c r="AA36" s="113"/>
-      <c r="AB36" s="113"/>
-      <c r="AC36" s="113"/>
-      <c r="AD36" s="113"/>
-      <c r="AE36" s="124"/>
+      <c r="X36" s="115"/>
+      <c r="Y36" s="115"/>
+      <c r="Z36" s="115"/>
+      <c r="AA36" s="115"/>
+      <c r="AB36" s="115"/>
+      <c r="AC36" s="115"/>
+      <c r="AD36" s="115"/>
+      <c r="AE36" s="126"/>
       <c r="AF36" s="44"/>
       <c r="AG36" s="44"/>
       <c r="AH36" s="42"/>
@@ -3117,41 +3120,41 @@
     <row r="37" spans="1:35" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="23"/>
       <c r="B37" s="24"/>
-      <c r="C37" s="135" t="s">
+      <c r="C37" s="132" t="s">
         <v>36</v>
       </c>
-      <c r="D37" s="113"/>
-      <c r="E37" s="113"/>
-      <c r="F37" s="113"/>
-      <c r="G37" s="113"/>
-      <c r="H37" s="113"/>
-      <c r="I37" s="113"/>
-      <c r="J37" s="124"/>
+      <c r="D37" s="115"/>
+      <c r="E37" s="115"/>
+      <c r="F37" s="115"/>
+      <c r="G37" s="115"/>
+      <c r="H37" s="115"/>
+      <c r="I37" s="115"/>
+      <c r="J37" s="126"/>
       <c r="K37" s="44"/>
       <c r="L37" s="44"/>
-      <c r="M37" s="135" t="s">
+      <c r="M37" s="132" t="s">
         <v>37</v>
       </c>
-      <c r="N37" s="113"/>
-      <c r="O37" s="113"/>
-      <c r="P37" s="113"/>
-      <c r="Q37" s="113"/>
-      <c r="R37" s="113"/>
-      <c r="S37" s="113"/>
-      <c r="T37" s="124"/>
+      <c r="N37" s="115"/>
+      <c r="O37" s="115"/>
+      <c r="P37" s="115"/>
+      <c r="Q37" s="115"/>
+      <c r="R37" s="115"/>
+      <c r="S37" s="115"/>
+      <c r="T37" s="126"/>
       <c r="U37" s="44"/>
       <c r="V37" s="44"/>
-      <c r="W37" s="135" t="s">
+      <c r="W37" s="132" t="s">
         <v>38</v>
       </c>
-      <c r="X37" s="113"/>
-      <c r="Y37" s="113"/>
-      <c r="Z37" s="113"/>
-      <c r="AA37" s="113"/>
-      <c r="AB37" s="113"/>
-      <c r="AC37" s="113"/>
-      <c r="AD37" s="113"/>
-      <c r="AE37" s="124"/>
+      <c r="X37" s="115"/>
+      <c r="Y37" s="115"/>
+      <c r="Z37" s="115"/>
+      <c r="AA37" s="115"/>
+      <c r="AB37" s="115"/>
+      <c r="AC37" s="115"/>
+      <c r="AD37" s="115"/>
+      <c r="AE37" s="126"/>
       <c r="AF37" s="44"/>
       <c r="AG37" s="44"/>
       <c r="AH37" s="42"/>
@@ -3160,39 +3163,39 @@
     <row r="38" spans="1:35" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="38"/>
       <c r="B38" s="39"/>
-      <c r="C38" s="139" t="s">
+      <c r="C38" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="D38" s="113"/>
-      <c r="E38" s="113"/>
-      <c r="F38" s="113"/>
-      <c r="G38" s="113"/>
-      <c r="H38" s="113"/>
-      <c r="I38" s="113"/>
-      <c r="J38" s="124"/>
-      <c r="K38" s="140"/>
-      <c r="L38" s="113"/>
-      <c r="M38" s="113"/>
-      <c r="N38" s="113"/>
-      <c r="O38" s="113"/>
-      <c r="P38" s="113"/>
-      <c r="Q38" s="113"/>
-      <c r="R38" s="113"/>
-      <c r="S38" s="113"/>
-      <c r="T38" s="113"/>
-      <c r="U38" s="113"/>
-      <c r="V38" s="113"/>
-      <c r="W38" s="113"/>
-      <c r="X38" s="113"/>
-      <c r="Y38" s="113"/>
-      <c r="Z38" s="113"/>
-      <c r="AA38" s="113"/>
-      <c r="AB38" s="113"/>
-      <c r="AC38" s="113"/>
-      <c r="AD38" s="113"/>
-      <c r="AE38" s="113"/>
-      <c r="AF38" s="113"/>
-      <c r="AG38" s="124"/>
+      <c r="D38" s="115"/>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="115"/>
+      <c r="H38" s="115"/>
+      <c r="I38" s="115"/>
+      <c r="J38" s="126"/>
+      <c r="K38" s="141"/>
+      <c r="L38" s="115"/>
+      <c r="M38" s="115"/>
+      <c r="N38" s="115"/>
+      <c r="O38" s="115"/>
+      <c r="P38" s="115"/>
+      <c r="Q38" s="115"/>
+      <c r="R38" s="115"/>
+      <c r="S38" s="115"/>
+      <c r="T38" s="115"/>
+      <c r="U38" s="115"/>
+      <c r="V38" s="115"/>
+      <c r="W38" s="115"/>
+      <c r="X38" s="115"/>
+      <c r="Y38" s="115"/>
+      <c r="Z38" s="115"/>
+      <c r="AA38" s="115"/>
+      <c r="AB38" s="115"/>
+      <c r="AC38" s="115"/>
+      <c r="AD38" s="115"/>
+      <c r="AE38" s="115"/>
+      <c r="AF38" s="115"/>
+      <c r="AG38" s="126"/>
       <c r="AH38" s="42"/>
       <c r="AI38" s="43"/>
     </row>
@@ -3214,22 +3217,22 @@
       <c r="O39" s="20"/>
       <c r="P39" s="20"/>
       <c r="Q39" s="2"/>
-      <c r="R39" s="125"/>
-      <c r="S39" s="99"/>
-      <c r="T39" s="99"/>
-      <c r="U39" s="99"/>
-      <c r="V39" s="99"/>
-      <c r="W39" s="99"/>
-      <c r="X39" s="99"/>
-      <c r="Y39" s="125"/>
-      <c r="Z39" s="99"/>
-      <c r="AA39" s="99"/>
-      <c r="AB39" s="99"/>
-      <c r="AC39" s="99"/>
-      <c r="AD39" s="99"/>
-      <c r="AE39" s="99"/>
-      <c r="AF39" s="99"/>
-      <c r="AG39" s="99"/>
+      <c r="R39" s="133"/>
+      <c r="S39" s="101"/>
+      <c r="T39" s="101"/>
+      <c r="U39" s="101"/>
+      <c r="V39" s="101"/>
+      <c r="W39" s="101"/>
+      <c r="X39" s="101"/>
+      <c r="Y39" s="133"/>
+      <c r="Z39" s="101"/>
+      <c r="AA39" s="101"/>
+      <c r="AB39" s="101"/>
+      <c r="AC39" s="101"/>
+      <c r="AD39" s="101"/>
+      <c r="AE39" s="101"/>
+      <c r="AF39" s="101"/>
+      <c r="AG39" s="101"/>
       <c r="AH39" s="16"/>
       <c r="AI39" s="13"/>
     </row>
@@ -3238,38 +3241,38 @@
       <c r="B40" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="118"/>
-      <c r="D40" s="118"/>
-      <c r="E40" s="118"/>
-      <c r="F40" s="118"/>
-      <c r="G40" s="118"/>
-      <c r="H40" s="118"/>
-      <c r="I40" s="118"/>
-      <c r="J40" s="118"/>
-      <c r="K40" s="118"/>
-      <c r="L40" s="118"/>
-      <c r="M40" s="118"/>
-      <c r="N40" s="118"/>
-      <c r="O40" s="118"/>
-      <c r="P40" s="118"/>
-      <c r="Q40" s="118"/>
-      <c r="R40" s="118"/>
-      <c r="S40" s="118"/>
-      <c r="T40" s="118"/>
-      <c r="U40" s="118"/>
-      <c r="V40" s="118"/>
-      <c r="W40" s="118"/>
-      <c r="X40" s="118"/>
-      <c r="Y40" s="118"/>
-      <c r="Z40" s="118"/>
-      <c r="AA40" s="118"/>
-      <c r="AB40" s="118"/>
-      <c r="AC40" s="118"/>
-      <c r="AD40" s="118"/>
-      <c r="AE40" s="118"/>
-      <c r="AF40" s="118"/>
-      <c r="AG40" s="118"/>
-      <c r="AH40" s="119"/>
+      <c r="C40" s="121"/>
+      <c r="D40" s="121"/>
+      <c r="E40" s="121"/>
+      <c r="F40" s="121"/>
+      <c r="G40" s="121"/>
+      <c r="H40" s="121"/>
+      <c r="I40" s="121"/>
+      <c r="J40" s="121"/>
+      <c r="K40" s="121"/>
+      <c r="L40" s="121"/>
+      <c r="M40" s="121"/>
+      <c r="N40" s="121"/>
+      <c r="O40" s="121"/>
+      <c r="P40" s="121"/>
+      <c r="Q40" s="121"/>
+      <c r="R40" s="121"/>
+      <c r="S40" s="121"/>
+      <c r="T40" s="121"/>
+      <c r="U40" s="121"/>
+      <c r="V40" s="121"/>
+      <c r="W40" s="121"/>
+      <c r="X40" s="121"/>
+      <c r="Y40" s="121"/>
+      <c r="Z40" s="121"/>
+      <c r="AA40" s="121"/>
+      <c r="AB40" s="121"/>
+      <c r="AC40" s="121"/>
+      <c r="AD40" s="121"/>
+      <c r="AE40" s="121"/>
+      <c r="AF40" s="121"/>
+      <c r="AG40" s="121"/>
+      <c r="AH40" s="122"/>
       <c r="AI40" s="7"/>
     </row>
     <row r="41" spans="1:35" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3312,46 +3315,46 @@
     <row r="42" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="49"/>
       <c r="B42" s="50"/>
-      <c r="C42" s="141" t="s">
+      <c r="C42" s="139" t="s">
         <v>41</v>
       </c>
-      <c r="D42" s="113"/>
-      <c r="E42" s="113"/>
-      <c r="F42" s="113"/>
-      <c r="G42" s="113"/>
-      <c r="H42" s="113"/>
-      <c r="I42" s="113"/>
-      <c r="J42" s="124"/>
+      <c r="D42" s="115"/>
+      <c r="E42" s="115"/>
+      <c r="F42" s="115"/>
+      <c r="G42" s="115"/>
+      <c r="H42" s="115"/>
+      <c r="I42" s="115"/>
+      <c r="J42" s="126"/>
       <c r="K42" s="51" t="s">
         <v>42</v>
       </c>
       <c r="L42" s="52"/>
-      <c r="M42" s="141" t="s">
+      <c r="M42" s="139" t="s">
         <v>43</v>
       </c>
-      <c r="N42" s="113"/>
-      <c r="O42" s="113"/>
-      <c r="P42" s="113"/>
-      <c r="Q42" s="113"/>
-      <c r="R42" s="113"/>
-      <c r="S42" s="113"/>
-      <c r="T42" s="113"/>
-      <c r="U42" s="124"/>
+      <c r="N42" s="115"/>
+      <c r="O42" s="115"/>
+      <c r="P42" s="115"/>
+      <c r="Q42" s="115"/>
+      <c r="R42" s="115"/>
+      <c r="S42" s="115"/>
+      <c r="T42" s="115"/>
+      <c r="U42" s="126"/>
       <c r="V42" s="51" t="s">
         <v>42</v>
       </c>
       <c r="W42" s="53"/>
-      <c r="X42" s="141" t="s">
+      <c r="X42" s="139" t="s">
         <v>44</v>
       </c>
-      <c r="Y42" s="113"/>
-      <c r="Z42" s="113"/>
-      <c r="AA42" s="113"/>
-      <c r="AB42" s="113"/>
-      <c r="AC42" s="113"/>
-      <c r="AD42" s="113"/>
-      <c r="AE42" s="113"/>
-      <c r="AF42" s="124"/>
+      <c r="Y42" s="115"/>
+      <c r="Z42" s="115"/>
+      <c r="AA42" s="115"/>
+      <c r="AB42" s="115"/>
+      <c r="AC42" s="115"/>
+      <c r="AD42" s="115"/>
+      <c r="AE42" s="115"/>
+      <c r="AF42" s="126"/>
       <c r="AG42" s="51" t="s">
         <v>42</v>
       </c>
@@ -3364,13 +3367,13 @@
       <c r="C43" s="142" t="s">
         <v>45</v>
       </c>
-      <c r="D43" s="113"/>
-      <c r="E43" s="113"/>
-      <c r="F43" s="113"/>
-      <c r="G43" s="113"/>
-      <c r="H43" s="113"/>
-      <c r="I43" s="113"/>
-      <c r="J43" s="124"/>
+      <c r="D43" s="115"/>
+      <c r="E43" s="115"/>
+      <c r="F43" s="115"/>
+      <c r="G43" s="115"/>
+      <c r="H43" s="115"/>
+      <c r="I43" s="115"/>
+      <c r="J43" s="126"/>
       <c r="K43" s="57">
         <v>3</v>
       </c>
@@ -3378,14 +3381,14 @@
       <c r="M43" s="142" t="s">
         <v>45</v>
       </c>
-      <c r="N43" s="113"/>
-      <c r="O43" s="113"/>
-      <c r="P43" s="113"/>
-      <c r="Q43" s="113"/>
-      <c r="R43" s="113"/>
-      <c r="S43" s="113"/>
-      <c r="T43" s="113"/>
-      <c r="U43" s="124"/>
+      <c r="N43" s="115"/>
+      <c r="O43" s="115"/>
+      <c r="P43" s="115"/>
+      <c r="Q43" s="115"/>
+      <c r="R43" s="115"/>
+      <c r="S43" s="115"/>
+      <c r="T43" s="115"/>
+      <c r="U43" s="126"/>
       <c r="V43" s="57">
         <v>3</v>
       </c>
@@ -3393,14 +3396,14 @@
       <c r="X43" s="142" t="s">
         <v>45</v>
       </c>
-      <c r="Y43" s="113"/>
-      <c r="Z43" s="113"/>
-      <c r="AA43" s="113"/>
-      <c r="AB43" s="113"/>
-      <c r="AC43" s="113"/>
-      <c r="AD43" s="113"/>
-      <c r="AE43" s="113"/>
-      <c r="AF43" s="124"/>
+      <c r="Y43" s="115"/>
+      <c r="Z43" s="115"/>
+      <c r="AA43" s="115"/>
+      <c r="AB43" s="115"/>
+      <c r="AC43" s="115"/>
+      <c r="AD43" s="115"/>
+      <c r="AE43" s="115"/>
+      <c r="AF43" s="126"/>
       <c r="AG43" s="57">
         <v>3</v>
       </c>
@@ -3413,13 +3416,13 @@
       <c r="C44" s="142" t="s">
         <v>46</v>
       </c>
-      <c r="D44" s="113"/>
-      <c r="E44" s="113"/>
-      <c r="F44" s="113"/>
-      <c r="G44" s="113"/>
-      <c r="H44" s="113"/>
-      <c r="I44" s="113"/>
-      <c r="J44" s="124"/>
+      <c r="D44" s="115"/>
+      <c r="E44" s="115"/>
+      <c r="F44" s="115"/>
+      <c r="G44" s="115"/>
+      <c r="H44" s="115"/>
+      <c r="I44" s="115"/>
+      <c r="J44" s="126"/>
       <c r="K44" s="57">
         <v>2</v>
       </c>
@@ -3427,14 +3430,14 @@
       <c r="M44" s="142" t="s">
         <v>46</v>
       </c>
-      <c r="N44" s="113"/>
-      <c r="O44" s="113"/>
-      <c r="P44" s="113"/>
-      <c r="Q44" s="113"/>
-      <c r="R44" s="113"/>
-      <c r="S44" s="113"/>
-      <c r="T44" s="113"/>
-      <c r="U44" s="124"/>
+      <c r="N44" s="115"/>
+      <c r="O44" s="115"/>
+      <c r="P44" s="115"/>
+      <c r="Q44" s="115"/>
+      <c r="R44" s="115"/>
+      <c r="S44" s="115"/>
+      <c r="T44" s="115"/>
+      <c r="U44" s="126"/>
       <c r="V44" s="57">
         <v>2</v>
       </c>
@@ -3442,14 +3445,14 @@
       <c r="X44" s="142" t="s">
         <v>46</v>
       </c>
-      <c r="Y44" s="113"/>
-      <c r="Z44" s="113"/>
-      <c r="AA44" s="113"/>
-      <c r="AB44" s="113"/>
-      <c r="AC44" s="113"/>
-      <c r="AD44" s="113"/>
-      <c r="AE44" s="113"/>
-      <c r="AF44" s="124"/>
+      <c r="Y44" s="115"/>
+      <c r="Z44" s="115"/>
+      <c r="AA44" s="115"/>
+      <c r="AB44" s="115"/>
+      <c r="AC44" s="115"/>
+      <c r="AD44" s="115"/>
+      <c r="AE44" s="115"/>
+      <c r="AF44" s="126"/>
       <c r="AG44" s="57">
         <v>2</v>
       </c>
@@ -3462,13 +3465,13 @@
       <c r="C45" s="142" t="s">
         <v>47</v>
       </c>
-      <c r="D45" s="113"/>
-      <c r="E45" s="113"/>
-      <c r="F45" s="113"/>
-      <c r="G45" s="113"/>
-      <c r="H45" s="113"/>
-      <c r="I45" s="113"/>
-      <c r="J45" s="124"/>
+      <c r="D45" s="115"/>
+      <c r="E45" s="115"/>
+      <c r="F45" s="115"/>
+      <c r="G45" s="115"/>
+      <c r="H45" s="115"/>
+      <c r="I45" s="115"/>
+      <c r="J45" s="126"/>
       <c r="K45" s="57">
         <v>1</v>
       </c>
@@ -3476,14 +3479,14 @@
       <c r="M45" s="142" t="s">
         <v>47</v>
       </c>
-      <c r="N45" s="113"/>
-      <c r="O45" s="113"/>
-      <c r="P45" s="113"/>
-      <c r="Q45" s="113"/>
-      <c r="R45" s="113"/>
-      <c r="S45" s="113"/>
-      <c r="T45" s="113"/>
-      <c r="U45" s="124"/>
+      <c r="N45" s="115"/>
+      <c r="O45" s="115"/>
+      <c r="P45" s="115"/>
+      <c r="Q45" s="115"/>
+      <c r="R45" s="115"/>
+      <c r="S45" s="115"/>
+      <c r="T45" s="115"/>
+      <c r="U45" s="126"/>
       <c r="V45" s="57">
         <v>1</v>
       </c>
@@ -3491,14 +3494,14 @@
       <c r="X45" s="142" t="s">
         <v>47</v>
       </c>
-      <c r="Y45" s="113"/>
-      <c r="Z45" s="113"/>
-      <c r="AA45" s="113"/>
-      <c r="AB45" s="113"/>
-      <c r="AC45" s="113"/>
-      <c r="AD45" s="113"/>
-      <c r="AE45" s="113"/>
-      <c r="AF45" s="124"/>
+      <c r="Y45" s="115"/>
+      <c r="Z45" s="115"/>
+      <c r="AA45" s="115"/>
+      <c r="AB45" s="115"/>
+      <c r="AC45" s="115"/>
+      <c r="AD45" s="115"/>
+      <c r="AE45" s="115"/>
+      <c r="AF45" s="126"/>
       <c r="AG45" s="57">
         <v>1</v>
       </c>
@@ -3545,46 +3548,46 @@
     <row r="47" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="49"/>
       <c r="B47" s="50"/>
-      <c r="C47" s="141" t="s">
+      <c r="C47" s="139" t="s">
         <v>48</v>
       </c>
-      <c r="D47" s="113"/>
-      <c r="E47" s="113"/>
-      <c r="F47" s="113"/>
-      <c r="G47" s="113"/>
-      <c r="H47" s="113"/>
-      <c r="I47" s="113"/>
-      <c r="J47" s="124"/>
+      <c r="D47" s="115"/>
+      <c r="E47" s="115"/>
+      <c r="F47" s="115"/>
+      <c r="G47" s="115"/>
+      <c r="H47" s="115"/>
+      <c r="I47" s="115"/>
+      <c r="J47" s="126"/>
       <c r="K47" s="51" t="s">
         <v>42</v>
       </c>
       <c r="L47" s="52"/>
-      <c r="M47" s="141" t="s">
+      <c r="M47" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="N47" s="113"/>
-      <c r="O47" s="113"/>
-      <c r="P47" s="113"/>
-      <c r="Q47" s="113"/>
-      <c r="R47" s="113"/>
-      <c r="S47" s="113"/>
-      <c r="T47" s="113"/>
-      <c r="U47" s="124"/>
+      <c r="N47" s="115"/>
+      <c r="O47" s="115"/>
+      <c r="P47" s="115"/>
+      <c r="Q47" s="115"/>
+      <c r="R47" s="115"/>
+      <c r="S47" s="115"/>
+      <c r="T47" s="115"/>
+      <c r="U47" s="126"/>
       <c r="V47" s="51" t="s">
         <v>42</v>
       </c>
       <c r="W47" s="62"/>
-      <c r="X47" s="141" t="s">
+      <c r="X47" s="139" t="s">
         <v>50</v>
       </c>
-      <c r="Y47" s="113"/>
-      <c r="Z47" s="113"/>
-      <c r="AA47" s="113"/>
-      <c r="AB47" s="113"/>
-      <c r="AC47" s="113"/>
-      <c r="AD47" s="113"/>
-      <c r="AE47" s="113"/>
-      <c r="AF47" s="124"/>
+      <c r="Y47" s="115"/>
+      <c r="Z47" s="115"/>
+      <c r="AA47" s="115"/>
+      <c r="AB47" s="115"/>
+      <c r="AC47" s="115"/>
+      <c r="AD47" s="115"/>
+      <c r="AE47" s="115"/>
+      <c r="AF47" s="126"/>
       <c r="AG47" s="51" t="s">
         <v>42</v>
       </c>
@@ -3597,13 +3600,13 @@
       <c r="C48" s="142" t="s">
         <v>45</v>
       </c>
-      <c r="D48" s="113"/>
-      <c r="E48" s="113"/>
-      <c r="F48" s="113"/>
-      <c r="G48" s="113"/>
-      <c r="H48" s="113"/>
-      <c r="I48" s="113"/>
-      <c r="J48" s="124"/>
+      <c r="D48" s="115"/>
+      <c r="E48" s="115"/>
+      <c r="F48" s="115"/>
+      <c r="G48" s="115"/>
+      <c r="H48" s="115"/>
+      <c r="I48" s="115"/>
+      <c r="J48" s="126"/>
       <c r="K48" s="57">
         <v>3</v>
       </c>
@@ -3611,14 +3614,14 @@
       <c r="M48" s="142" t="s">
         <v>45</v>
       </c>
-      <c r="N48" s="113"/>
-      <c r="O48" s="113"/>
-      <c r="P48" s="113"/>
-      <c r="Q48" s="113"/>
-      <c r="R48" s="113"/>
-      <c r="S48" s="113"/>
-      <c r="T48" s="113"/>
-      <c r="U48" s="124"/>
+      <c r="N48" s="115"/>
+      <c r="O48" s="115"/>
+      <c r="P48" s="115"/>
+      <c r="Q48" s="115"/>
+      <c r="R48" s="115"/>
+      <c r="S48" s="115"/>
+      <c r="T48" s="115"/>
+      <c r="U48" s="126"/>
       <c r="V48" s="57">
         <v>3</v>
       </c>
@@ -3626,14 +3629,14 @@
       <c r="X48" s="142" t="s">
         <v>45</v>
       </c>
-      <c r="Y48" s="113"/>
-      <c r="Z48" s="113"/>
-      <c r="AA48" s="113"/>
-      <c r="AB48" s="113"/>
-      <c r="AC48" s="113"/>
-      <c r="AD48" s="113"/>
-      <c r="AE48" s="113"/>
-      <c r="AF48" s="124"/>
+      <c r="Y48" s="115"/>
+      <c r="Z48" s="115"/>
+      <c r="AA48" s="115"/>
+      <c r="AB48" s="115"/>
+      <c r="AC48" s="115"/>
+      <c r="AD48" s="115"/>
+      <c r="AE48" s="115"/>
+      <c r="AF48" s="126"/>
       <c r="AG48" s="57">
         <v>3</v>
       </c>
@@ -3646,13 +3649,13 @@
       <c r="C49" s="142" t="s">
         <v>51</v>
       </c>
-      <c r="D49" s="113"/>
-      <c r="E49" s="113"/>
-      <c r="F49" s="113"/>
-      <c r="G49" s="113"/>
-      <c r="H49" s="113"/>
-      <c r="I49" s="113"/>
-      <c r="J49" s="124"/>
+      <c r="D49" s="115"/>
+      <c r="E49" s="115"/>
+      <c r="F49" s="115"/>
+      <c r="G49" s="115"/>
+      <c r="H49" s="115"/>
+      <c r="I49" s="115"/>
+      <c r="J49" s="126"/>
       <c r="K49" s="57">
         <v>2</v>
       </c>
@@ -3660,14 +3663,14 @@
       <c r="M49" s="142" t="s">
         <v>46</v>
       </c>
-      <c r="N49" s="113"/>
-      <c r="O49" s="113"/>
-      <c r="P49" s="113"/>
-      <c r="Q49" s="113"/>
-      <c r="R49" s="113"/>
-      <c r="S49" s="113"/>
-      <c r="T49" s="113"/>
-      <c r="U49" s="124"/>
+      <c r="N49" s="115"/>
+      <c r="O49" s="115"/>
+      <c r="P49" s="115"/>
+      <c r="Q49" s="115"/>
+      <c r="R49" s="115"/>
+      <c r="S49" s="115"/>
+      <c r="T49" s="115"/>
+      <c r="U49" s="126"/>
       <c r="V49" s="57">
         <v>2</v>
       </c>
@@ -3675,14 +3678,14 @@
       <c r="X49" s="142" t="s">
         <v>46</v>
       </c>
-      <c r="Y49" s="113"/>
-      <c r="Z49" s="113"/>
-      <c r="AA49" s="113"/>
-      <c r="AB49" s="113"/>
-      <c r="AC49" s="113"/>
-      <c r="AD49" s="113"/>
-      <c r="AE49" s="113"/>
-      <c r="AF49" s="124"/>
+      <c r="Y49" s="115"/>
+      <c r="Z49" s="115"/>
+      <c r="AA49" s="115"/>
+      <c r="AB49" s="115"/>
+      <c r="AC49" s="115"/>
+      <c r="AD49" s="115"/>
+      <c r="AE49" s="115"/>
+      <c r="AF49" s="126"/>
       <c r="AG49" s="57">
         <v>2</v>
       </c>
@@ -3695,13 +3698,13 @@
       <c r="C50" s="142" t="s">
         <v>47</v>
       </c>
-      <c r="D50" s="113"/>
-      <c r="E50" s="113"/>
-      <c r="F50" s="113"/>
-      <c r="G50" s="113"/>
-      <c r="H50" s="113"/>
-      <c r="I50" s="113"/>
-      <c r="J50" s="124"/>
+      <c r="D50" s="115"/>
+      <c r="E50" s="115"/>
+      <c r="F50" s="115"/>
+      <c r="G50" s="115"/>
+      <c r="H50" s="115"/>
+      <c r="I50" s="115"/>
+      <c r="J50" s="126"/>
       <c r="K50" s="57">
         <v>1</v>
       </c>
@@ -3709,14 +3712,14 @@
       <c r="M50" s="142" t="s">
         <v>47</v>
       </c>
-      <c r="N50" s="113"/>
-      <c r="O50" s="113"/>
-      <c r="P50" s="113"/>
-      <c r="Q50" s="113"/>
-      <c r="R50" s="113"/>
-      <c r="S50" s="113"/>
-      <c r="T50" s="113"/>
-      <c r="U50" s="124"/>
+      <c r="N50" s="115"/>
+      <c r="O50" s="115"/>
+      <c r="P50" s="115"/>
+      <c r="Q50" s="115"/>
+      <c r="R50" s="115"/>
+      <c r="S50" s="115"/>
+      <c r="T50" s="115"/>
+      <c r="U50" s="126"/>
       <c r="V50" s="57">
         <v>1</v>
       </c>
@@ -3724,14 +3727,14 @@
       <c r="X50" s="142" t="s">
         <v>47</v>
       </c>
-      <c r="Y50" s="113"/>
-      <c r="Z50" s="113"/>
-      <c r="AA50" s="113"/>
-      <c r="AB50" s="113"/>
-      <c r="AC50" s="113"/>
-      <c r="AD50" s="113"/>
-      <c r="AE50" s="113"/>
-      <c r="AF50" s="124"/>
+      <c r="Y50" s="115"/>
+      <c r="Z50" s="115"/>
+      <c r="AA50" s="115"/>
+      <c r="AB50" s="115"/>
+      <c r="AC50" s="115"/>
+      <c r="AD50" s="115"/>
+      <c r="AE50" s="115"/>
+      <c r="AF50" s="126"/>
       <c r="AG50" s="57">
         <v>1</v>
       </c>
@@ -3778,15 +3781,15 @@
     <row r="52" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="49"/>
       <c r="B52" s="50"/>
-      <c r="C52" s="143"/>
-      <c r="D52" s="144"/>
-      <c r="E52" s="144"/>
-      <c r="F52" s="144"/>
-      <c r="G52" s="144"/>
-      <c r="H52" s="144"/>
-      <c r="I52" s="144"/>
-      <c r="J52" s="144"/>
-      <c r="K52" s="144"/>
+      <c r="C52" s="149"/>
+      <c r="D52" s="150"/>
+      <c r="E52" s="150"/>
+      <c r="F52" s="150"/>
+      <c r="G52" s="150"/>
+      <c r="H52" s="150"/>
+      <c r="I52" s="150"/>
+      <c r="J52" s="150"/>
+      <c r="K52" s="150"/>
       <c r="L52" s="66"/>
       <c r="M52" s="67"/>
       <c r="N52" s="67"/>
@@ -3817,316 +3820,316 @@
     <row r="53" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="49"/>
       <c r="B53" s="50"/>
-      <c r="C53" s="145" t="s">
+      <c r="C53" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="D53" s="146"/>
-      <c r="E53" s="145" t="s">
+      <c r="D53" s="144"/>
+      <c r="E53" s="143" t="s">
         <v>54</v>
       </c>
-      <c r="F53" s="97"/>
-      <c r="G53" s="97"/>
-      <c r="H53" s="97"/>
-      <c r="I53" s="97"/>
-      <c r="J53" s="97"/>
-      <c r="K53" s="146"/>
-      <c r="L53" s="145" t="s">
+      <c r="F53" s="99"/>
+      <c r="G53" s="99"/>
+      <c r="H53" s="99"/>
+      <c r="I53" s="99"/>
+      <c r="J53" s="99"/>
+      <c r="K53" s="144"/>
+      <c r="L53" s="143" t="s">
         <v>55</v>
       </c>
-      <c r="M53" s="97"/>
-      <c r="N53" s="97"/>
-      <c r="O53" s="97"/>
-      <c r="P53" s="97"/>
-      <c r="Q53" s="97"/>
-      <c r="R53" s="97"/>
-      <c r="S53" s="97"/>
-      <c r="T53" s="97"/>
-      <c r="U53" s="97"/>
-      <c r="V53" s="97"/>
-      <c r="W53" s="97"/>
-      <c r="X53" s="97"/>
-      <c r="Y53" s="97"/>
-      <c r="Z53" s="97"/>
-      <c r="AA53" s="97"/>
-      <c r="AB53" s="97"/>
-      <c r="AC53" s="97"/>
-      <c r="AD53" s="97"/>
-      <c r="AE53" s="97"/>
-      <c r="AF53" s="97"/>
-      <c r="AG53" s="146"/>
+      <c r="M53" s="99"/>
+      <c r="N53" s="99"/>
+      <c r="O53" s="99"/>
+      <c r="P53" s="99"/>
+      <c r="Q53" s="99"/>
+      <c r="R53" s="99"/>
+      <c r="S53" s="99"/>
+      <c r="T53" s="99"/>
+      <c r="U53" s="99"/>
+      <c r="V53" s="99"/>
+      <c r="W53" s="99"/>
+      <c r="X53" s="99"/>
+      <c r="Y53" s="99"/>
+      <c r="Z53" s="99"/>
+      <c r="AA53" s="99"/>
+      <c r="AB53" s="99"/>
+      <c r="AC53" s="99"/>
+      <c r="AD53" s="99"/>
+      <c r="AE53" s="99"/>
+      <c r="AF53" s="99"/>
+      <c r="AG53" s="144"/>
       <c r="AH53" s="69"/>
       <c r="AI53" s="12"/>
     </row>
     <row r="54" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="55"/>
       <c r="B54" s="56"/>
-      <c r="C54" s="100"/>
-      <c r="D54" s="147"/>
-      <c r="E54" s="100"/>
-      <c r="F54" s="101"/>
-      <c r="G54" s="101"/>
-      <c r="H54" s="101"/>
-      <c r="I54" s="101"/>
-      <c r="J54" s="101"/>
-      <c r="K54" s="147"/>
-      <c r="L54" s="100"/>
-      <c r="M54" s="101"/>
-      <c r="N54" s="101"/>
-      <c r="O54" s="101"/>
-      <c r="P54" s="101"/>
-      <c r="Q54" s="101"/>
-      <c r="R54" s="101"/>
-      <c r="S54" s="101"/>
-      <c r="T54" s="101"/>
-      <c r="U54" s="101"/>
-      <c r="V54" s="101"/>
-      <c r="W54" s="101"/>
-      <c r="X54" s="101"/>
-      <c r="Y54" s="101"/>
-      <c r="Z54" s="101"/>
-      <c r="AA54" s="101"/>
-      <c r="AB54" s="101"/>
-      <c r="AC54" s="101"/>
-      <c r="AD54" s="101"/>
-      <c r="AE54" s="101"/>
-      <c r="AF54" s="101"/>
-      <c r="AG54" s="147"/>
+      <c r="C54" s="102"/>
+      <c r="D54" s="145"/>
+      <c r="E54" s="102"/>
+      <c r="F54" s="103"/>
+      <c r="G54" s="103"/>
+      <c r="H54" s="103"/>
+      <c r="I54" s="103"/>
+      <c r="J54" s="103"/>
+      <c r="K54" s="145"/>
+      <c r="L54" s="102"/>
+      <c r="M54" s="103"/>
+      <c r="N54" s="103"/>
+      <c r="O54" s="103"/>
+      <c r="P54" s="103"/>
+      <c r="Q54" s="103"/>
+      <c r="R54" s="103"/>
+      <c r="S54" s="103"/>
+      <c r="T54" s="103"/>
+      <c r="U54" s="103"/>
+      <c r="V54" s="103"/>
+      <c r="W54" s="103"/>
+      <c r="X54" s="103"/>
+      <c r="Y54" s="103"/>
+      <c r="Z54" s="103"/>
+      <c r="AA54" s="103"/>
+      <c r="AB54" s="103"/>
+      <c r="AC54" s="103"/>
+      <c r="AD54" s="103"/>
+      <c r="AE54" s="103"/>
+      <c r="AF54" s="103"/>
+      <c r="AG54" s="145"/>
       <c r="AH54" s="70"/>
       <c r="AI54" s="25"/>
     </row>
     <row r="55" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="55"/>
       <c r="B55" s="56"/>
-      <c r="C55" s="148"/>
-      <c r="D55" s="146"/>
-      <c r="E55" s="149" t="s">
+      <c r="C55" s="146"/>
+      <c r="D55" s="144"/>
+      <c r="E55" s="147" t="s">
         <v>56</v>
       </c>
-      <c r="F55" s="97"/>
-      <c r="G55" s="97"/>
-      <c r="H55" s="97"/>
-      <c r="I55" s="97"/>
-      <c r="J55" s="97"/>
-      <c r="K55" s="146"/>
-      <c r="L55" s="150" t="s">
+      <c r="F55" s="99"/>
+      <c r="G55" s="99"/>
+      <c r="H55" s="99"/>
+      <c r="I55" s="99"/>
+      <c r="J55" s="99"/>
+      <c r="K55" s="144"/>
+      <c r="L55" s="148" t="s">
         <v>57</v>
       </c>
-      <c r="M55" s="97"/>
-      <c r="N55" s="97"/>
-      <c r="O55" s="97"/>
-      <c r="P55" s="97"/>
-      <c r="Q55" s="97"/>
-      <c r="R55" s="97"/>
-      <c r="S55" s="97"/>
-      <c r="T55" s="97"/>
-      <c r="U55" s="97"/>
-      <c r="V55" s="97"/>
-      <c r="W55" s="97"/>
-      <c r="X55" s="97"/>
-      <c r="Y55" s="97"/>
-      <c r="Z55" s="97"/>
-      <c r="AA55" s="97"/>
-      <c r="AB55" s="97"/>
-      <c r="AC55" s="97"/>
-      <c r="AD55" s="97"/>
-      <c r="AE55" s="97"/>
-      <c r="AF55" s="97"/>
-      <c r="AG55" s="146"/>
+      <c r="M55" s="99"/>
+      <c r="N55" s="99"/>
+      <c r="O55" s="99"/>
+      <c r="P55" s="99"/>
+      <c r="Q55" s="99"/>
+      <c r="R55" s="99"/>
+      <c r="S55" s="99"/>
+      <c r="T55" s="99"/>
+      <c r="U55" s="99"/>
+      <c r="V55" s="99"/>
+      <c r="W55" s="99"/>
+      <c r="X55" s="99"/>
+      <c r="Y55" s="99"/>
+      <c r="Z55" s="99"/>
+      <c r="AA55" s="99"/>
+      <c r="AB55" s="99"/>
+      <c r="AC55" s="99"/>
+      <c r="AD55" s="99"/>
+      <c r="AE55" s="99"/>
+      <c r="AF55" s="99"/>
+      <c r="AG55" s="144"/>
       <c r="AH55" s="70"/>
       <c r="AI55" s="25"/>
     </row>
     <row r="56" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="55"/>
       <c r="B56" s="56"/>
-      <c r="C56" s="100"/>
-      <c r="D56" s="147"/>
-      <c r="E56" s="100"/>
-      <c r="F56" s="101"/>
-      <c r="G56" s="101"/>
-      <c r="H56" s="101"/>
-      <c r="I56" s="101"/>
-      <c r="J56" s="101"/>
-      <c r="K56" s="147"/>
-      <c r="L56" s="100"/>
-      <c r="M56" s="101"/>
-      <c r="N56" s="101"/>
-      <c r="O56" s="101"/>
-      <c r="P56" s="101"/>
-      <c r="Q56" s="101"/>
-      <c r="R56" s="101"/>
-      <c r="S56" s="101"/>
-      <c r="T56" s="101"/>
-      <c r="U56" s="101"/>
-      <c r="V56" s="101"/>
-      <c r="W56" s="101"/>
-      <c r="X56" s="101"/>
-      <c r="Y56" s="101"/>
-      <c r="Z56" s="101"/>
-      <c r="AA56" s="101"/>
-      <c r="AB56" s="101"/>
-      <c r="AC56" s="101"/>
-      <c r="AD56" s="101"/>
-      <c r="AE56" s="101"/>
-      <c r="AF56" s="101"/>
-      <c r="AG56" s="147"/>
+      <c r="C56" s="102"/>
+      <c r="D56" s="145"/>
+      <c r="E56" s="102"/>
+      <c r="F56" s="103"/>
+      <c r="G56" s="103"/>
+      <c r="H56" s="103"/>
+      <c r="I56" s="103"/>
+      <c r="J56" s="103"/>
+      <c r="K56" s="145"/>
+      <c r="L56" s="102"/>
+      <c r="M56" s="103"/>
+      <c r="N56" s="103"/>
+      <c r="O56" s="103"/>
+      <c r="P56" s="103"/>
+      <c r="Q56" s="103"/>
+      <c r="R56" s="103"/>
+      <c r="S56" s="103"/>
+      <c r="T56" s="103"/>
+      <c r="U56" s="103"/>
+      <c r="V56" s="103"/>
+      <c r="W56" s="103"/>
+      <c r="X56" s="103"/>
+      <c r="Y56" s="103"/>
+      <c r="Z56" s="103"/>
+      <c r="AA56" s="103"/>
+      <c r="AB56" s="103"/>
+      <c r="AC56" s="103"/>
+      <c r="AD56" s="103"/>
+      <c r="AE56" s="103"/>
+      <c r="AF56" s="103"/>
+      <c r="AG56" s="145"/>
       <c r="AH56" s="71"/>
       <c r="AI56" s="72"/>
     </row>
     <row r="57" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="26"/>
       <c r="B57" s="73"/>
-      <c r="C57" s="96" t="s">
+      <c r="C57" s="98" t="s">
         <v>58</v>
       </c>
-      <c r="D57" s="146"/>
-      <c r="E57" s="149" t="s">
+      <c r="D57" s="144"/>
+      <c r="E57" s="147" t="s">
         <v>59</v>
       </c>
-      <c r="F57" s="97"/>
-      <c r="G57" s="97"/>
-      <c r="H57" s="97"/>
-      <c r="I57" s="97"/>
-      <c r="J57" s="97"/>
-      <c r="K57" s="146"/>
-      <c r="L57" s="150" t="s">
+      <c r="F57" s="99"/>
+      <c r="G57" s="99"/>
+      <c r="H57" s="99"/>
+      <c r="I57" s="99"/>
+      <c r="J57" s="99"/>
+      <c r="K57" s="144"/>
+      <c r="L57" s="148" t="s">
         <v>60</v>
       </c>
-      <c r="M57" s="97"/>
-      <c r="N57" s="97"/>
-      <c r="O57" s="97"/>
-      <c r="P57" s="97"/>
-      <c r="Q57" s="97"/>
-      <c r="R57" s="97"/>
-      <c r="S57" s="97"/>
-      <c r="T57" s="97"/>
-      <c r="U57" s="97"/>
-      <c r="V57" s="97"/>
-      <c r="W57" s="97"/>
-      <c r="X57" s="97"/>
-      <c r="Y57" s="97"/>
-      <c r="Z57" s="97"/>
-      <c r="AA57" s="97"/>
-      <c r="AB57" s="97"/>
-      <c r="AC57" s="97"/>
-      <c r="AD57" s="97"/>
-      <c r="AE57" s="97"/>
-      <c r="AF57" s="97"/>
-      <c r="AG57" s="146"/>
+      <c r="M57" s="99"/>
+      <c r="N57" s="99"/>
+      <c r="O57" s="99"/>
+      <c r="P57" s="99"/>
+      <c r="Q57" s="99"/>
+      <c r="R57" s="99"/>
+      <c r="S57" s="99"/>
+      <c r="T57" s="99"/>
+      <c r="U57" s="99"/>
+      <c r="V57" s="99"/>
+      <c r="W57" s="99"/>
+      <c r="X57" s="99"/>
+      <c r="Y57" s="99"/>
+      <c r="Z57" s="99"/>
+      <c r="AA57" s="99"/>
+      <c r="AB57" s="99"/>
+      <c r="AC57" s="99"/>
+      <c r="AD57" s="99"/>
+      <c r="AE57" s="99"/>
+      <c r="AF57" s="99"/>
+      <c r="AG57" s="144"/>
       <c r="AH57" s="71"/>
       <c r="AI57" s="72"/>
     </row>
     <row r="58" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="26"/>
       <c r="B58" s="73"/>
-      <c r="C58" s="100"/>
-      <c r="D58" s="147"/>
-      <c r="E58" s="100"/>
-      <c r="F58" s="101"/>
-      <c r="G58" s="101"/>
-      <c r="H58" s="101"/>
-      <c r="I58" s="101"/>
-      <c r="J58" s="101"/>
-      <c r="K58" s="147"/>
-      <c r="L58" s="100"/>
-      <c r="M58" s="101"/>
-      <c r="N58" s="101"/>
-      <c r="O58" s="101"/>
-      <c r="P58" s="101"/>
-      <c r="Q58" s="101"/>
-      <c r="R58" s="101"/>
-      <c r="S58" s="101"/>
-      <c r="T58" s="101"/>
-      <c r="U58" s="101"/>
-      <c r="V58" s="101"/>
-      <c r="W58" s="101"/>
-      <c r="X58" s="101"/>
-      <c r="Y58" s="101"/>
-      <c r="Z58" s="101"/>
-      <c r="AA58" s="101"/>
-      <c r="AB58" s="101"/>
-      <c r="AC58" s="101"/>
-      <c r="AD58" s="101"/>
-      <c r="AE58" s="101"/>
-      <c r="AF58" s="101"/>
-      <c r="AG58" s="147"/>
+      <c r="C58" s="102"/>
+      <c r="D58" s="145"/>
+      <c r="E58" s="102"/>
+      <c r="F58" s="103"/>
+      <c r="G58" s="103"/>
+      <c r="H58" s="103"/>
+      <c r="I58" s="103"/>
+      <c r="J58" s="103"/>
+      <c r="K58" s="145"/>
+      <c r="L58" s="102"/>
+      <c r="M58" s="103"/>
+      <c r="N58" s="103"/>
+      <c r="O58" s="103"/>
+      <c r="P58" s="103"/>
+      <c r="Q58" s="103"/>
+      <c r="R58" s="103"/>
+      <c r="S58" s="103"/>
+      <c r="T58" s="103"/>
+      <c r="U58" s="103"/>
+      <c r="V58" s="103"/>
+      <c r="W58" s="103"/>
+      <c r="X58" s="103"/>
+      <c r="Y58" s="103"/>
+      <c r="Z58" s="103"/>
+      <c r="AA58" s="103"/>
+      <c r="AB58" s="103"/>
+      <c r="AC58" s="103"/>
+      <c r="AD58" s="103"/>
+      <c r="AE58" s="103"/>
+      <c r="AF58" s="103"/>
+      <c r="AG58" s="145"/>
       <c r="AH58" s="70"/>
       <c r="AI58" s="25"/>
     </row>
     <row r="59" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="26"/>
       <c r="B59" s="73"/>
-      <c r="C59" s="96"/>
-      <c r="D59" s="146"/>
-      <c r="E59" s="149" t="s">
+      <c r="C59" s="98"/>
+      <c r="D59" s="144"/>
+      <c r="E59" s="147" t="s">
         <v>61</v>
       </c>
-      <c r="F59" s="97"/>
-      <c r="G59" s="97"/>
-      <c r="H59" s="97"/>
-      <c r="I59" s="97"/>
-      <c r="J59" s="97"/>
-      <c r="K59" s="146"/>
-      <c r="L59" s="150" t="s">
+      <c r="F59" s="99"/>
+      <c r="G59" s="99"/>
+      <c r="H59" s="99"/>
+      <c r="I59" s="99"/>
+      <c r="J59" s="99"/>
+      <c r="K59" s="144"/>
+      <c r="L59" s="148" t="s">
         <v>62</v>
       </c>
-      <c r="M59" s="97"/>
-      <c r="N59" s="97"/>
-      <c r="O59" s="97"/>
-      <c r="P59" s="97"/>
-      <c r="Q59" s="97"/>
-      <c r="R59" s="97"/>
-      <c r="S59" s="97"/>
-      <c r="T59" s="97"/>
-      <c r="U59" s="97"/>
-      <c r="V59" s="97"/>
-      <c r="W59" s="97"/>
-      <c r="X59" s="97"/>
-      <c r="Y59" s="97"/>
-      <c r="Z59" s="97"/>
-      <c r="AA59" s="97"/>
-      <c r="AB59" s="97"/>
-      <c r="AC59" s="97"/>
-      <c r="AD59" s="97"/>
-      <c r="AE59" s="97"/>
-      <c r="AF59" s="97"/>
-      <c r="AG59" s="146"/>
+      <c r="M59" s="99"/>
+      <c r="N59" s="99"/>
+      <c r="O59" s="99"/>
+      <c r="P59" s="99"/>
+      <c r="Q59" s="99"/>
+      <c r="R59" s="99"/>
+      <c r="S59" s="99"/>
+      <c r="T59" s="99"/>
+      <c r="U59" s="99"/>
+      <c r="V59" s="99"/>
+      <c r="W59" s="99"/>
+      <c r="X59" s="99"/>
+      <c r="Y59" s="99"/>
+      <c r="Z59" s="99"/>
+      <c r="AA59" s="99"/>
+      <c r="AB59" s="99"/>
+      <c r="AC59" s="99"/>
+      <c r="AD59" s="99"/>
+      <c r="AE59" s="99"/>
+      <c r="AF59" s="99"/>
+      <c r="AG59" s="144"/>
       <c r="AH59" s="70"/>
       <c r="AI59" s="25"/>
     </row>
     <row r="60" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="26"/>
       <c r="B60" s="73"/>
-      <c r="C60" s="100"/>
-      <c r="D60" s="147"/>
-      <c r="E60" s="100"/>
-      <c r="F60" s="101"/>
-      <c r="G60" s="101"/>
-      <c r="H60" s="101"/>
-      <c r="I60" s="101"/>
-      <c r="J60" s="101"/>
-      <c r="K60" s="147"/>
-      <c r="L60" s="100"/>
-      <c r="M60" s="101"/>
-      <c r="N60" s="101"/>
-      <c r="O60" s="101"/>
-      <c r="P60" s="101"/>
-      <c r="Q60" s="101"/>
-      <c r="R60" s="101"/>
-      <c r="S60" s="101"/>
-      <c r="T60" s="101"/>
-      <c r="U60" s="101"/>
-      <c r="V60" s="101"/>
-      <c r="W60" s="101"/>
-      <c r="X60" s="101"/>
-      <c r="Y60" s="101"/>
-      <c r="Z60" s="101"/>
-      <c r="AA60" s="101"/>
-      <c r="AB60" s="101"/>
-      <c r="AC60" s="101"/>
-      <c r="AD60" s="101"/>
-      <c r="AE60" s="101"/>
-      <c r="AF60" s="101"/>
-      <c r="AG60" s="147"/>
+      <c r="C60" s="102"/>
+      <c r="D60" s="145"/>
+      <c r="E60" s="102"/>
+      <c r="F60" s="103"/>
+      <c r="G60" s="103"/>
+      <c r="H60" s="103"/>
+      <c r="I60" s="103"/>
+      <c r="J60" s="103"/>
+      <c r="K60" s="145"/>
+      <c r="L60" s="102"/>
+      <c r="M60" s="103"/>
+      <c r="N60" s="103"/>
+      <c r="O60" s="103"/>
+      <c r="P60" s="103"/>
+      <c r="Q60" s="103"/>
+      <c r="R60" s="103"/>
+      <c r="S60" s="103"/>
+      <c r="T60" s="103"/>
+      <c r="U60" s="103"/>
+      <c r="V60" s="103"/>
+      <c r="W60" s="103"/>
+      <c r="X60" s="103"/>
+      <c r="Y60" s="103"/>
+      <c r="Z60" s="103"/>
+      <c r="AA60" s="103"/>
+      <c r="AB60" s="103"/>
+      <c r="AC60" s="103"/>
+      <c r="AD60" s="103"/>
+      <c r="AE60" s="103"/>
+      <c r="AF60" s="103"/>
+      <c r="AG60" s="145"/>
       <c r="AH60" s="74"/>
       <c r="AI60" s="5"/>
     </row>
@@ -4147,9 +4150,9 @@
       <c r="N61" s="77"/>
       <c r="O61" s="77"/>
       <c r="P61" s="77"/>
-      <c r="Q61" s="151"/>
-      <c r="R61" s="152"/>
-      <c r="S61" s="152"/>
+      <c r="Q61" s="170"/>
+      <c r="R61" s="171"/>
+      <c r="S61" s="171"/>
       <c r="T61" s="78"/>
       <c r="U61" s="6"/>
       <c r="V61" s="6"/>
@@ -4283,38 +4286,38 @@
       <c r="B65" s="120" t="s">
         <v>63</v>
       </c>
-      <c r="C65" s="118"/>
-      <c r="D65" s="118"/>
-      <c r="E65" s="118"/>
-      <c r="F65" s="118"/>
-      <c r="G65" s="118"/>
-      <c r="H65" s="118"/>
-      <c r="I65" s="118"/>
-      <c r="J65" s="118"/>
-      <c r="K65" s="118"/>
-      <c r="L65" s="118"/>
-      <c r="M65" s="118"/>
-      <c r="N65" s="118"/>
-      <c r="O65" s="118"/>
-      <c r="P65" s="118"/>
-      <c r="Q65" s="118"/>
-      <c r="R65" s="118"/>
-      <c r="S65" s="118"/>
-      <c r="T65" s="118"/>
-      <c r="U65" s="118"/>
-      <c r="V65" s="118"/>
-      <c r="W65" s="118"/>
-      <c r="X65" s="118"/>
-      <c r="Y65" s="118"/>
-      <c r="Z65" s="118"/>
-      <c r="AA65" s="118"/>
-      <c r="AB65" s="118"/>
-      <c r="AC65" s="118"/>
-      <c r="AD65" s="118"/>
-      <c r="AE65" s="118"/>
-      <c r="AF65" s="118"/>
-      <c r="AG65" s="118"/>
-      <c r="AH65" s="119"/>
+      <c r="C65" s="121"/>
+      <c r="D65" s="121"/>
+      <c r="E65" s="121"/>
+      <c r="F65" s="121"/>
+      <c r="G65" s="121"/>
+      <c r="H65" s="121"/>
+      <c r="I65" s="121"/>
+      <c r="J65" s="121"/>
+      <c r="K65" s="121"/>
+      <c r="L65" s="121"/>
+      <c r="M65" s="121"/>
+      <c r="N65" s="121"/>
+      <c r="O65" s="121"/>
+      <c r="P65" s="121"/>
+      <c r="Q65" s="121"/>
+      <c r="R65" s="121"/>
+      <c r="S65" s="121"/>
+      <c r="T65" s="121"/>
+      <c r="U65" s="121"/>
+      <c r="V65" s="121"/>
+      <c r="W65" s="121"/>
+      <c r="X65" s="121"/>
+      <c r="Y65" s="121"/>
+      <c r="Z65" s="121"/>
+      <c r="AA65" s="121"/>
+      <c r="AB65" s="121"/>
+      <c r="AC65" s="121"/>
+      <c r="AD65" s="121"/>
+      <c r="AE65" s="121"/>
+      <c r="AF65" s="121"/>
+      <c r="AG65" s="121"/>
+      <c r="AH65" s="122"/>
       <c r="AI65" s="49"/>
     </row>
     <row r="66" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4371,22 +4374,22 @@
       <c r="N67" s="92"/>
       <c r="O67" s="92"/>
       <c r="P67" s="93"/>
-      <c r="Q67" s="154"/>
-      <c r="R67" s="155"/>
-      <c r="S67" s="155"/>
-      <c r="T67" s="155"/>
-      <c r="U67" s="156"/>
-      <c r="V67" s="155"/>
-      <c r="W67" s="155"/>
-      <c r="X67" s="155"/>
-      <c r="Y67" s="155"/>
-      <c r="Z67" s="155"/>
-      <c r="AA67" s="155"/>
-      <c r="AB67" s="155"/>
-      <c r="AC67" s="155"/>
-      <c r="AD67" s="155"/>
-      <c r="AE67" s="155"/>
-      <c r="AF67" s="155"/>
+      <c r="Q67" s="159"/>
+      <c r="R67" s="160"/>
+      <c r="S67" s="160"/>
+      <c r="T67" s="160"/>
+      <c r="U67" s="161"/>
+      <c r="V67" s="160"/>
+      <c r="W67" s="160"/>
+      <c r="X67" s="160"/>
+      <c r="Y67" s="160"/>
+      <c r="Z67" s="160"/>
+      <c r="AA67" s="160"/>
+      <c r="AB67" s="160"/>
+      <c r="AC67" s="160"/>
+      <c r="AD67" s="160"/>
+      <c r="AE67" s="160"/>
+      <c r="AF67" s="160"/>
       <c r="AG67" s="82"/>
       <c r="AH67" s="63"/>
       <c r="AI67" s="64"/>
@@ -4408,22 +4411,22 @@
       <c r="N68" s="90"/>
       <c r="O68" s="90"/>
       <c r="P68" s="95"/>
-      <c r="Q68" s="157"/>
-      <c r="R68" s="144"/>
-      <c r="S68" s="144"/>
-      <c r="T68" s="144"/>
-      <c r="U68" s="158"/>
-      <c r="V68" s="144"/>
-      <c r="W68" s="144"/>
-      <c r="X68" s="144"/>
-      <c r="Y68" s="144"/>
-      <c r="Z68" s="144"/>
-      <c r="AA68" s="144"/>
-      <c r="AB68" s="144"/>
-      <c r="AC68" s="144"/>
-      <c r="AD68" s="144"/>
-      <c r="AE68" s="144"/>
-      <c r="AF68" s="144"/>
+      <c r="Q68" s="162"/>
+      <c r="R68" s="150"/>
+      <c r="S68" s="150"/>
+      <c r="T68" s="150"/>
+      <c r="U68" s="163"/>
+      <c r="V68" s="150"/>
+      <c r="W68" s="150"/>
+      <c r="X68" s="150"/>
+      <c r="Y68" s="150"/>
+      <c r="Z68" s="150"/>
+      <c r="AA68" s="150"/>
+      <c r="AB68" s="150"/>
+      <c r="AC68" s="150"/>
+      <c r="AD68" s="150"/>
+      <c r="AE68" s="150"/>
+      <c r="AF68" s="150"/>
       <c r="AG68" s="63"/>
       <c r="AH68" s="63"/>
       <c r="AI68" s="64"/>
@@ -4432,35 +4435,35 @@
       <c r="A69" s="64"/>
       <c r="B69" s="50"/>
       <c r="C69" s="94"/>
-      <c r="D69" s="164"/>
-      <c r="E69" s="164"/>
-      <c r="F69" s="164"/>
-      <c r="G69" s="164"/>
-      <c r="H69" s="164"/>
-      <c r="I69" s="164"/>
-      <c r="J69" s="164"/>
-      <c r="K69" s="164"/>
-      <c r="L69" s="164"/>
-      <c r="M69" s="164"/>
+      <c r="D69" s="169"/>
+      <c r="E69" s="169"/>
+      <c r="F69" s="169"/>
+      <c r="G69" s="169"/>
+      <c r="H69" s="169"/>
+      <c r="I69" s="169"/>
+      <c r="J69" s="169"/>
+      <c r="K69" s="169"/>
+      <c r="L69" s="169"/>
+      <c r="M69" s="169"/>
       <c r="N69" s="90"/>
       <c r="O69" s="90"/>
       <c r="P69" s="95"/>
-      <c r="Q69" s="157"/>
-      <c r="R69" s="144"/>
-      <c r="S69" s="144"/>
-      <c r="T69" s="144"/>
-      <c r="U69" s="159"/>
-      <c r="V69" s="160"/>
-      <c r="W69" s="160"/>
-      <c r="X69" s="160"/>
-      <c r="Y69" s="160"/>
-      <c r="Z69" s="160"/>
-      <c r="AA69" s="160"/>
-      <c r="AB69" s="160"/>
-      <c r="AC69" s="160"/>
-      <c r="AD69" s="160"/>
-      <c r="AE69" s="160"/>
-      <c r="AF69" s="160"/>
+      <c r="Q69" s="162"/>
+      <c r="R69" s="150"/>
+      <c r="S69" s="150"/>
+      <c r="T69" s="150"/>
+      <c r="U69" s="164"/>
+      <c r="V69" s="165"/>
+      <c r="W69" s="165"/>
+      <c r="X69" s="165"/>
+      <c r="Y69" s="165"/>
+      <c r="Z69" s="165"/>
+      <c r="AA69" s="165"/>
+      <c r="AB69" s="165"/>
+      <c r="AC69" s="165"/>
+      <c r="AD69" s="165"/>
+      <c r="AE69" s="165"/>
+      <c r="AF69" s="165"/>
       <c r="AG69" s="63"/>
       <c r="AH69" s="63"/>
       <c r="AI69" s="64"/>
@@ -4469,40 +4472,40 @@
       <c r="A70" s="64"/>
       <c r="B70" s="83"/>
       <c r="C70" s="84"/>
-      <c r="D70" s="153" t="s">
+      <c r="D70" s="158" t="s">
         <v>64</v>
       </c>
-      <c r="E70" s="116"/>
-      <c r="F70" s="116"/>
-      <c r="G70" s="116"/>
-      <c r="H70" s="116"/>
-      <c r="I70" s="116"/>
-      <c r="J70" s="116"/>
-      <c r="K70" s="116"/>
-      <c r="L70" s="116"/>
-      <c r="M70" s="116"/>
-      <c r="N70" s="116"/>
+      <c r="E70" s="118"/>
+      <c r="F70" s="118"/>
+      <c r="G70" s="118"/>
+      <c r="H70" s="118"/>
+      <c r="I70" s="118"/>
+      <c r="J70" s="118"/>
+      <c r="K70" s="118"/>
+      <c r="L70" s="118"/>
+      <c r="M70" s="118"/>
+      <c r="N70" s="118"/>
       <c r="O70" s="85"/>
       <c r="P70" s="86"/>
-      <c r="Q70" s="161" t="s">
+      <c r="Q70" s="166" t="s">
         <v>65</v>
       </c>
-      <c r="R70" s="162"/>
-      <c r="S70" s="162"/>
-      <c r="T70" s="162"/>
-      <c r="U70" s="162"/>
-      <c r="V70" s="162"/>
-      <c r="W70" s="162"/>
-      <c r="X70" s="162"/>
-      <c r="Y70" s="162"/>
-      <c r="Z70" s="162"/>
-      <c r="AA70" s="162"/>
-      <c r="AB70" s="162"/>
-      <c r="AC70" s="162"/>
-      <c r="AD70" s="162"/>
-      <c r="AE70" s="162"/>
-      <c r="AF70" s="162"/>
-      <c r="AG70" s="163"/>
+      <c r="R70" s="167"/>
+      <c r="S70" s="167"/>
+      <c r="T70" s="167"/>
+      <c r="U70" s="167"/>
+      <c r="V70" s="167"/>
+      <c r="W70" s="167"/>
+      <c r="X70" s="167"/>
+      <c r="Y70" s="167"/>
+      <c r="Z70" s="167"/>
+      <c r="AA70" s="167"/>
+      <c r="AB70" s="167"/>
+      <c r="AC70" s="167"/>
+      <c r="AD70" s="167"/>
+      <c r="AE70" s="167"/>
+      <c r="AF70" s="167"/>
+      <c r="AG70" s="168"/>
       <c r="AH70" s="63"/>
       <c r="AI70" s="64"/>
     </row>
@@ -5510,7 +5513,6 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="140">
-    <mergeCell ref="C14:F14"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="AB7:AH7"/>
@@ -5534,34 +5536,12 @@
     <mergeCell ref="Q61:S61"/>
     <mergeCell ref="G22:K22"/>
     <mergeCell ref="L22:P22"/>
-    <mergeCell ref="W22:AG22"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="G23:K23"/>
-    <mergeCell ref="L23:P23"/>
-    <mergeCell ref="Q23:V23"/>
-    <mergeCell ref="W23:AG23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="L26:P26"/>
-    <mergeCell ref="Q26:V26"/>
-    <mergeCell ref="L27:P27"/>
-    <mergeCell ref="Q27:V27"/>
-    <mergeCell ref="R28:X28"/>
     <mergeCell ref="Y28:AG28"/>
     <mergeCell ref="B30:AH30"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="G25:K25"/>
     <mergeCell ref="L25:P25"/>
     <mergeCell ref="C52:K52"/>
-    <mergeCell ref="C53:D54"/>
-    <mergeCell ref="E53:K54"/>
-    <mergeCell ref="L53:AG54"/>
-    <mergeCell ref="C55:D56"/>
-    <mergeCell ref="E55:K56"/>
-    <mergeCell ref="L55:AG56"/>
-    <mergeCell ref="C57:D58"/>
-    <mergeCell ref="E57:K58"/>
-    <mergeCell ref="L57:AG58"/>
     <mergeCell ref="M48:U48"/>
     <mergeCell ref="X48:AF48"/>
     <mergeCell ref="C48:J48"/>
@@ -5577,6 +5557,18 @@
     <mergeCell ref="X45:AF45"/>
     <mergeCell ref="M44:U44"/>
     <mergeCell ref="M45:U45"/>
+    <mergeCell ref="L26:P26"/>
+    <mergeCell ref="Q26:V26"/>
+    <mergeCell ref="Q25:V25"/>
+    <mergeCell ref="C53:D54"/>
+    <mergeCell ref="E53:K54"/>
+    <mergeCell ref="L53:AG54"/>
+    <mergeCell ref="C55:D56"/>
+    <mergeCell ref="E55:K56"/>
+    <mergeCell ref="L55:AG56"/>
+    <mergeCell ref="C57:D58"/>
+    <mergeCell ref="E57:K58"/>
+    <mergeCell ref="L57:AG58"/>
     <mergeCell ref="C47:J47"/>
     <mergeCell ref="M47:U47"/>
     <mergeCell ref="X47:AF47"/>
@@ -5600,12 +5592,6 @@
     <mergeCell ref="M36:T36"/>
     <mergeCell ref="C37:J37"/>
     <mergeCell ref="M37:T37"/>
-    <mergeCell ref="Q22:V22"/>
-    <mergeCell ref="G24:K24"/>
-    <mergeCell ref="L24:P24"/>
-    <mergeCell ref="Q24:V24"/>
-    <mergeCell ref="W24:AG24"/>
-    <mergeCell ref="M32:T33"/>
     <mergeCell ref="M34:T34"/>
     <mergeCell ref="G26:K26"/>
     <mergeCell ref="G27:K27"/>
@@ -5614,11 +5600,11 @@
     <mergeCell ref="L32:L33"/>
     <mergeCell ref="U32:U33"/>
     <mergeCell ref="C34:J34"/>
-    <mergeCell ref="Q25:V25"/>
-    <mergeCell ref="W25:AG25"/>
     <mergeCell ref="C26:F27"/>
+    <mergeCell ref="L27:P27"/>
+    <mergeCell ref="Q27:V27"/>
+    <mergeCell ref="R28:X28"/>
     <mergeCell ref="W26:AG26"/>
-    <mergeCell ref="W27:AG27"/>
     <mergeCell ref="V32:V33"/>
     <mergeCell ref="W32:AE33"/>
     <mergeCell ref="AF32:AF33"/>
@@ -5642,6 +5628,7 @@
     <mergeCell ref="G21:K21"/>
     <mergeCell ref="L21:P21"/>
     <mergeCell ref="Q21:V21"/>
+    <mergeCell ref="M32:T33"/>
     <mergeCell ref="B2:F5"/>
     <mergeCell ref="G2:Y4"/>
     <mergeCell ref="Z2:AH2"/>
@@ -5650,6 +5637,22 @@
     <mergeCell ref="G5:AH5"/>
     <mergeCell ref="B9:AH9"/>
     <mergeCell ref="C11:F11"/>
+    <mergeCell ref="W27:AG27"/>
+    <mergeCell ref="W22:AG22"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="G23:K23"/>
+    <mergeCell ref="L23:P23"/>
+    <mergeCell ref="Q23:V23"/>
+    <mergeCell ref="W23:AG23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="Q22:V22"/>
+    <mergeCell ref="G24:K24"/>
+    <mergeCell ref="L24:P24"/>
+    <mergeCell ref="Q24:V24"/>
+    <mergeCell ref="W24:AG24"/>
+    <mergeCell ref="W25:AG25"/>
+    <mergeCell ref="C14:F14"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/database/controller_excel/FO-DSP-TI-06 Reporte de mantenimiento preventivo a equipo de computo Rev.01.xlsx
+++ b/database/controller_excel/FO-DSP-TI-06 Reporte de mantenimiento preventivo a equipo de computo Rev.01.xlsx
@@ -229,7 +229,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -301,6 +301,17 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1240,23 +1251,149 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,147 +1402,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1736,160 +1747,160 @@
     </row>
     <row r="2" spans="1:35" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="104" t="s">
+      <c r="B2" s="120"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="159" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
-      <c r="R2" s="99"/>
-      <c r="S2" s="99"/>
-      <c r="T2" s="99"/>
-      <c r="U2" s="99"/>
-      <c r="V2" s="99"/>
-      <c r="W2" s="99"/>
-      <c r="X2" s="99"/>
-      <c r="Y2" s="105"/>
-      <c r="Z2" s="111" t="s">
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="125"/>
+      <c r="O2" s="125"/>
+      <c r="P2" s="125"/>
+      <c r="Q2" s="125"/>
+      <c r="R2" s="125"/>
+      <c r="S2" s="125"/>
+      <c r="T2" s="125"/>
+      <c r="U2" s="125"/>
+      <c r="V2" s="125"/>
+      <c r="W2" s="125"/>
+      <c r="X2" s="125"/>
+      <c r="Y2" s="160"/>
+      <c r="Z2" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="AA2" s="112"/>
-      <c r="AB2" s="112"/>
-      <c r="AC2" s="112"/>
-      <c r="AD2" s="112"/>
-      <c r="AE2" s="112"/>
-      <c r="AF2" s="112"/>
-      <c r="AG2" s="112"/>
-      <c r="AH2" s="113"/>
+      <c r="AA2" s="164"/>
+      <c r="AB2" s="164"/>
+      <c r="AC2" s="164"/>
+      <c r="AD2" s="164"/>
+      <c r="AE2" s="164"/>
+      <c r="AF2" s="164"/>
+      <c r="AG2" s="164"/>
+      <c r="AH2" s="165"/>
       <c r="AI2" s="4"/>
     </row>
     <row r="3" spans="1:35" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="100"/>
-      <c r="C3" s="101"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="101"/>
-      <c r="F3" s="101"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="101"/>
-      <c r="K3" s="101"/>
-      <c r="L3" s="101"/>
-      <c r="M3" s="101"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="101"/>
-      <c r="R3" s="101"/>
-      <c r="S3" s="101"/>
-      <c r="T3" s="101"/>
-      <c r="U3" s="101"/>
-      <c r="V3" s="101"/>
-      <c r="W3" s="101"/>
-      <c r="X3" s="101"/>
-      <c r="Y3" s="107"/>
-      <c r="Z3" s="114" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="161"/>
+      <c r="H3" s="134"/>
+      <c r="I3" s="134"/>
+      <c r="J3" s="134"/>
+      <c r="K3" s="134"/>
+      <c r="L3" s="134"/>
+      <c r="M3" s="134"/>
+      <c r="N3" s="134"/>
+      <c r="O3" s="134"/>
+      <c r="P3" s="134"/>
+      <c r="Q3" s="134"/>
+      <c r="R3" s="134"/>
+      <c r="S3" s="134"/>
+      <c r="T3" s="134"/>
+      <c r="U3" s="134"/>
+      <c r="V3" s="134"/>
+      <c r="W3" s="134"/>
+      <c r="X3" s="134"/>
+      <c r="Y3" s="162"/>
+      <c r="Z3" s="166" t="s">
         <v>2</v>
       </c>
-      <c r="AA3" s="115"/>
-      <c r="AB3" s="115"/>
-      <c r="AC3" s="115"/>
-      <c r="AD3" s="115"/>
-      <c r="AE3" s="115"/>
-      <c r="AF3" s="115"/>
-      <c r="AG3" s="115"/>
-      <c r="AH3" s="116"/>
+      <c r="AA3" s="131"/>
+      <c r="AB3" s="131"/>
+      <c r="AC3" s="131"/>
+      <c r="AD3" s="131"/>
+      <c r="AE3" s="131"/>
+      <c r="AF3" s="131"/>
+      <c r="AG3" s="131"/>
+      <c r="AH3" s="167"/>
       <c r="AI3" s="4"/>
     </row>
     <row r="4" spans="1:35" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="100"/>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="109"/>
-      <c r="L4" s="109"/>
-      <c r="M4" s="109"/>
-      <c r="N4" s="109"/>
-      <c r="O4" s="109"/>
-      <c r="P4" s="109"/>
-      <c r="Q4" s="109"/>
-      <c r="R4" s="109"/>
-      <c r="S4" s="109"/>
-      <c r="T4" s="109"/>
-      <c r="U4" s="109"/>
-      <c r="V4" s="109"/>
-      <c r="W4" s="109"/>
-      <c r="X4" s="109"/>
-      <c r="Y4" s="110"/>
-      <c r="Z4" s="114" t="s">
+      <c r="B4" s="158"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="134"/>
+      <c r="F4" s="134"/>
+      <c r="G4" s="149"/>
+      <c r="H4" s="150"/>
+      <c r="I4" s="150"/>
+      <c r="J4" s="150"/>
+      <c r="K4" s="150"/>
+      <c r="L4" s="150"/>
+      <c r="M4" s="150"/>
+      <c r="N4" s="150"/>
+      <c r="O4" s="150"/>
+      <c r="P4" s="150"/>
+      <c r="Q4" s="150"/>
+      <c r="R4" s="150"/>
+      <c r="S4" s="150"/>
+      <c r="T4" s="150"/>
+      <c r="U4" s="150"/>
+      <c r="V4" s="150"/>
+      <c r="W4" s="150"/>
+      <c r="X4" s="150"/>
+      <c r="Y4" s="151"/>
+      <c r="Z4" s="166" t="s">
         <v>3</v>
       </c>
-      <c r="AA4" s="115"/>
-      <c r="AB4" s="115"/>
-      <c r="AC4" s="115"/>
-      <c r="AD4" s="115"/>
-      <c r="AE4" s="115"/>
-      <c r="AF4" s="115"/>
-      <c r="AG4" s="115"/>
-      <c r="AH4" s="116"/>
+      <c r="AA4" s="131"/>
+      <c r="AB4" s="131"/>
+      <c r="AC4" s="131"/>
+      <c r="AD4" s="131"/>
+      <c r="AE4" s="131"/>
+      <c r="AF4" s="131"/>
+      <c r="AG4" s="131"/>
+      <c r="AH4" s="167"/>
       <c r="AI4" s="4"/>
     </row>
     <row r="5" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="102"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="117" t="s">
+      <c r="B5" s="122"/>
+      <c r="C5" s="126"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="168" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
-      <c r="M5" s="118"/>
-      <c r="N5" s="118"/>
-      <c r="O5" s="118"/>
-      <c r="P5" s="118"/>
-      <c r="Q5" s="118"/>
-      <c r="R5" s="118"/>
-      <c r="S5" s="118"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="118"/>
-      <c r="W5" s="118"/>
-      <c r="X5" s="118"/>
-      <c r="Y5" s="118"/>
-      <c r="Z5" s="118"/>
-      <c r="AA5" s="118"/>
-      <c r="AB5" s="118"/>
-      <c r="AC5" s="118"/>
-      <c r="AD5" s="118"/>
-      <c r="AE5" s="118"/>
-      <c r="AF5" s="118"/>
-      <c r="AG5" s="118"/>
-      <c r="AH5" s="119"/>
+      <c r="H5" s="106"/>
+      <c r="I5" s="106"/>
+      <c r="J5" s="106"/>
+      <c r="K5" s="106"/>
+      <c r="L5" s="106"/>
+      <c r="M5" s="106"/>
+      <c r="N5" s="106"/>
+      <c r="O5" s="106"/>
+      <c r="P5" s="106"/>
+      <c r="Q5" s="106"/>
+      <c r="R5" s="106"/>
+      <c r="S5" s="106"/>
+      <c r="T5" s="106"/>
+      <c r="U5" s="106"/>
+      <c r="V5" s="106"/>
+      <c r="W5" s="106"/>
+      <c r="X5" s="106"/>
+      <c r="Y5" s="106"/>
+      <c r="Z5" s="106"/>
+      <c r="AA5" s="106"/>
+      <c r="AB5" s="106"/>
+      <c r="AC5" s="106"/>
+      <c r="AD5" s="106"/>
+      <c r="AE5" s="106"/>
+      <c r="AF5" s="106"/>
+      <c r="AG5" s="106"/>
+      <c r="AH5" s="169"/>
       <c r="AI5" s="4"/>
     </row>
     <row r="6" spans="1:35" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1959,15 +1970,15 @@
       <c r="Y7" s="97"/>
       <c r="Z7" s="97"/>
       <c r="AA7" s="97"/>
-      <c r="AB7" s="153" t="s">
+      <c r="AB7" s="100" t="s">
         <v>67</v>
       </c>
-      <c r="AC7" s="154"/>
-      <c r="AD7" s="154"/>
-      <c r="AE7" s="154"/>
-      <c r="AF7" s="154"/>
-      <c r="AG7" s="154"/>
-      <c r="AH7" s="155"/>
+      <c r="AC7" s="101"/>
+      <c r="AD7" s="101"/>
+      <c r="AE7" s="101"/>
+      <c r="AF7" s="101"/>
+      <c r="AG7" s="101"/>
+      <c r="AH7" s="102"/>
       <c r="AI7" s="7"/>
     </row>
     <row r="8" spans="1:35" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2009,41 +2020,41 @@
     </row>
     <row r="9" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
-      <c r="B9" s="120" t="s">
+      <c r="B9" s="107" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="121"/>
-      <c r="K9" s="121"/>
-      <c r="L9" s="121"/>
-      <c r="M9" s="121"/>
-      <c r="N9" s="121"/>
-      <c r="O9" s="121"/>
-      <c r="P9" s="121"/>
-      <c r="Q9" s="121"/>
-      <c r="R9" s="121"/>
-      <c r="S9" s="121"/>
-      <c r="T9" s="121"/>
-      <c r="U9" s="121"/>
-      <c r="V9" s="121"/>
-      <c r="W9" s="121"/>
-      <c r="X9" s="121"/>
-      <c r="Y9" s="121"/>
-      <c r="Z9" s="121"/>
-      <c r="AA9" s="121"/>
-      <c r="AB9" s="121"/>
-      <c r="AC9" s="121"/>
-      <c r="AD9" s="121"/>
-      <c r="AE9" s="121"/>
-      <c r="AF9" s="121"/>
-      <c r="AG9" s="121"/>
-      <c r="AH9" s="122"/>
+      <c r="C9" s="108"/>
+      <c r="D9" s="108"/>
+      <c r="E9" s="108"/>
+      <c r="F9" s="108"/>
+      <c r="G9" s="108"/>
+      <c r="H9" s="108"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="108"/>
+      <c r="K9" s="108"/>
+      <c r="L9" s="108"/>
+      <c r="M9" s="108"/>
+      <c r="N9" s="108"/>
+      <c r="O9" s="108"/>
+      <c r="P9" s="108"/>
+      <c r="Q9" s="108"/>
+      <c r="R9" s="108"/>
+      <c r="S9" s="108"/>
+      <c r="T9" s="108"/>
+      <c r="U9" s="108"/>
+      <c r="V9" s="108"/>
+      <c r="W9" s="108"/>
+      <c r="X9" s="108"/>
+      <c r="Y9" s="108"/>
+      <c r="Z9" s="108"/>
+      <c r="AA9" s="108"/>
+      <c r="AB9" s="108"/>
+      <c r="AC9" s="108"/>
+      <c r="AD9" s="108"/>
+      <c r="AE9" s="108"/>
+      <c r="AF9" s="108"/>
+      <c r="AG9" s="108"/>
+      <c r="AH9" s="109"/>
       <c r="AI9" s="12"/>
     </row>
     <row r="10" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2086,156 +2097,156 @@
     <row r="11" spans="1:35" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="14"/>
-      <c r="C11" s="123" t="s">
+      <c r="C11" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="124"/>
-      <c r="E11" s="124"/>
-      <c r="F11" s="124"/>
-      <c r="G11" s="156"/>
-      <c r="H11" s="156"/>
-      <c r="I11" s="156"/>
-      <c r="J11" s="156"/>
-      <c r="K11" s="156"/>
-      <c r="L11" s="156"/>
-      <c r="M11" s="156"/>
-      <c r="N11" s="156"/>
-      <c r="O11" s="156"/>
-      <c r="P11" s="156"/>
-      <c r="Q11" s="156"/>
-      <c r="R11" s="156"/>
-      <c r="S11" s="156"/>
-      <c r="T11" s="156"/>
-      <c r="U11" s="156"/>
-      <c r="V11" s="156"/>
-      <c r="W11" s="156"/>
-      <c r="X11" s="156"/>
-      <c r="Y11" s="156"/>
-      <c r="Z11" s="156"/>
-      <c r="AA11" s="156"/>
-      <c r="AB11" s="156"/>
-      <c r="AC11" s="156"/>
-      <c r="AD11" s="156"/>
-      <c r="AE11" s="156"/>
-      <c r="AF11" s="156"/>
-      <c r="AG11" s="157"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="103"/>
+      <c r="H11" s="103"/>
+      <c r="I11" s="103"/>
+      <c r="J11" s="103"/>
+      <c r="K11" s="103"/>
+      <c r="L11" s="103"/>
+      <c r="M11" s="103"/>
+      <c r="N11" s="103"/>
+      <c r="O11" s="103"/>
+      <c r="P11" s="103"/>
+      <c r="Q11" s="103"/>
+      <c r="R11" s="103"/>
+      <c r="S11" s="103"/>
+      <c r="T11" s="103"/>
+      <c r="U11" s="103"/>
+      <c r="V11" s="103"/>
+      <c r="W11" s="103"/>
+      <c r="X11" s="103"/>
+      <c r="Y11" s="103"/>
+      <c r="Z11" s="103"/>
+      <c r="AA11" s="103"/>
+      <c r="AB11" s="103"/>
+      <c r="AC11" s="103"/>
+      <c r="AD11" s="103"/>
+      <c r="AE11" s="103"/>
+      <c r="AF11" s="103"/>
+      <c r="AG11" s="104"/>
       <c r="AH11" s="16"/>
       <c r="AI11" s="13"/>
     </row>
     <row r="12" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="14"/>
-      <c r="C12" s="123" t="s">
+      <c r="C12" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="124"/>
-      <c r="E12" s="124"/>
-      <c r="F12" s="124"/>
-      <c r="G12" s="156"/>
-      <c r="H12" s="156"/>
-      <c r="I12" s="156"/>
-      <c r="J12" s="156"/>
-      <c r="K12" s="156"/>
-      <c r="L12" s="156"/>
-      <c r="M12" s="156"/>
-      <c r="N12" s="156"/>
-      <c r="O12" s="156"/>
-      <c r="P12" s="156"/>
-      <c r="Q12" s="156"/>
-      <c r="R12" s="156"/>
-      <c r="S12" s="156"/>
-      <c r="T12" s="156"/>
-      <c r="U12" s="156"/>
-      <c r="V12" s="156"/>
-      <c r="W12" s="156"/>
-      <c r="X12" s="156"/>
-      <c r="Y12" s="156"/>
-      <c r="Z12" s="156"/>
-      <c r="AA12" s="156"/>
-      <c r="AB12" s="156"/>
-      <c r="AC12" s="156"/>
-      <c r="AD12" s="156"/>
-      <c r="AE12" s="156"/>
-      <c r="AF12" s="156"/>
-      <c r="AG12" s="157"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="103"/>
+      <c r="H12" s="103"/>
+      <c r="I12" s="103"/>
+      <c r="J12" s="103"/>
+      <c r="K12" s="103"/>
+      <c r="L12" s="103"/>
+      <c r="M12" s="103"/>
+      <c r="N12" s="103"/>
+      <c r="O12" s="103"/>
+      <c r="P12" s="103"/>
+      <c r="Q12" s="103"/>
+      <c r="R12" s="103"/>
+      <c r="S12" s="103"/>
+      <c r="T12" s="103"/>
+      <c r="U12" s="103"/>
+      <c r="V12" s="103"/>
+      <c r="W12" s="103"/>
+      <c r="X12" s="103"/>
+      <c r="Y12" s="103"/>
+      <c r="Z12" s="103"/>
+      <c r="AA12" s="103"/>
+      <c r="AB12" s="103"/>
+      <c r="AC12" s="103"/>
+      <c r="AD12" s="103"/>
+      <c r="AE12" s="103"/>
+      <c r="AF12" s="103"/>
+      <c r="AG12" s="104"/>
       <c r="AH12" s="16"/>
       <c r="AI12" s="13"/>
     </row>
     <row r="13" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>
       <c r="B13" s="14"/>
-      <c r="C13" s="123" t="s">
+      <c r="C13" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="124"/>
-      <c r="E13" s="124"/>
-      <c r="F13" s="124"/>
-      <c r="G13" s="156"/>
-      <c r="H13" s="156"/>
-      <c r="I13" s="156"/>
-      <c r="J13" s="156"/>
-      <c r="K13" s="156"/>
-      <c r="L13" s="156"/>
-      <c r="M13" s="156"/>
-      <c r="N13" s="156"/>
-      <c r="O13" s="156"/>
-      <c r="P13" s="156"/>
-      <c r="Q13" s="156"/>
-      <c r="R13" s="156"/>
-      <c r="S13" s="156"/>
-      <c r="T13" s="156"/>
-      <c r="U13" s="156"/>
-      <c r="V13" s="156"/>
-      <c r="W13" s="156"/>
-      <c r="X13" s="156"/>
-      <c r="Y13" s="156"/>
-      <c r="Z13" s="156"/>
-      <c r="AA13" s="156"/>
-      <c r="AB13" s="156"/>
-      <c r="AC13" s="156"/>
-      <c r="AD13" s="156"/>
-      <c r="AE13" s="156"/>
-      <c r="AF13" s="156"/>
-      <c r="AG13" s="157"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="103"/>
+      <c r="H13" s="103"/>
+      <c r="I13" s="103"/>
+      <c r="J13" s="103"/>
+      <c r="K13" s="103"/>
+      <c r="L13" s="103"/>
+      <c r="M13" s="103"/>
+      <c r="N13" s="103"/>
+      <c r="O13" s="103"/>
+      <c r="P13" s="103"/>
+      <c r="Q13" s="103"/>
+      <c r="R13" s="103"/>
+      <c r="S13" s="103"/>
+      <c r="T13" s="103"/>
+      <c r="U13" s="103"/>
+      <c r="V13" s="103"/>
+      <c r="W13" s="103"/>
+      <c r="X13" s="103"/>
+      <c r="Y13" s="103"/>
+      <c r="Z13" s="103"/>
+      <c r="AA13" s="103"/>
+      <c r="AB13" s="103"/>
+      <c r="AC13" s="103"/>
+      <c r="AD13" s="103"/>
+      <c r="AE13" s="103"/>
+      <c r="AF13" s="103"/>
+      <c r="AG13" s="104"/>
       <c r="AH13" s="16"/>
       <c r="AI13" s="13"/>
     </row>
     <row r="14" spans="1:35" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17"/>
       <c r="B14" s="14"/>
-      <c r="C14" s="151" t="s">
+      <c r="C14" s="170" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="152"/>
-      <c r="E14" s="152"/>
-      <c r="F14" s="152"/>
-      <c r="G14" s="156"/>
-      <c r="H14" s="156"/>
-      <c r="I14" s="156"/>
-      <c r="J14" s="156"/>
-      <c r="K14" s="156"/>
-      <c r="L14" s="156"/>
-      <c r="M14" s="156"/>
-      <c r="N14" s="156"/>
-      <c r="O14" s="156"/>
-      <c r="P14" s="156"/>
-      <c r="Q14" s="156"/>
-      <c r="R14" s="156"/>
-      <c r="S14" s="156"/>
-      <c r="T14" s="156"/>
-      <c r="U14" s="156"/>
-      <c r="V14" s="156"/>
-      <c r="W14" s="156"/>
-      <c r="X14" s="156"/>
-      <c r="Y14" s="156"/>
-      <c r="Z14" s="156"/>
-      <c r="AA14" s="156"/>
-      <c r="AB14" s="156"/>
-      <c r="AC14" s="156"/>
-      <c r="AD14" s="156"/>
-      <c r="AE14" s="156"/>
-      <c r="AF14" s="156"/>
-      <c r="AG14" s="157"/>
+      <c r="D14" s="171"/>
+      <c r="E14" s="171"/>
+      <c r="F14" s="171"/>
+      <c r="G14" s="103"/>
+      <c r="H14" s="103"/>
+      <c r="I14" s="103"/>
+      <c r="J14" s="103"/>
+      <c r="K14" s="103"/>
+      <c r="L14" s="103"/>
+      <c r="M14" s="103"/>
+      <c r="N14" s="103"/>
+      <c r="O14" s="103"/>
+      <c r="P14" s="103"/>
+      <c r="Q14" s="103"/>
+      <c r="R14" s="103"/>
+      <c r="S14" s="103"/>
+      <c r="T14" s="103"/>
+      <c r="U14" s="103"/>
+      <c r="V14" s="103"/>
+      <c r="W14" s="103"/>
+      <c r="X14" s="103"/>
+      <c r="Y14" s="103"/>
+      <c r="Z14" s="103"/>
+      <c r="AA14" s="103"/>
+      <c r="AB14" s="103"/>
+      <c r="AC14" s="103"/>
+      <c r="AD14" s="103"/>
+      <c r="AE14" s="103"/>
+      <c r="AF14" s="103"/>
+      <c r="AG14" s="104"/>
       <c r="AH14" s="18"/>
       <c r="AI14" s="2"/>
     </row>
@@ -2295,61 +2306,61 @@
       <c r="P16" s="20"/>
       <c r="Q16" s="20"/>
       <c r="R16" s="133"/>
-      <c r="S16" s="101"/>
-      <c r="T16" s="101"/>
-      <c r="U16" s="101"/>
-      <c r="V16" s="101"/>
-      <c r="W16" s="101"/>
-      <c r="X16" s="101"/>
+      <c r="S16" s="134"/>
+      <c r="T16" s="134"/>
+      <c r="U16" s="134"/>
+      <c r="V16" s="134"/>
+      <c r="W16" s="134"/>
+      <c r="X16" s="134"/>
       <c r="Y16" s="133"/>
-      <c r="Z16" s="101"/>
-      <c r="AA16" s="101"/>
-      <c r="AB16" s="101"/>
-      <c r="AC16" s="101"/>
-      <c r="AD16" s="101"/>
-      <c r="AE16" s="101"/>
-      <c r="AF16" s="101"/>
-      <c r="AG16" s="101"/>
+      <c r="Z16" s="134"/>
+      <c r="AA16" s="134"/>
+      <c r="AB16" s="134"/>
+      <c r="AC16" s="134"/>
+      <c r="AD16" s="134"/>
+      <c r="AE16" s="134"/>
+      <c r="AF16" s="134"/>
+      <c r="AG16" s="134"/>
       <c r="AH16" s="16"/>
       <c r="AI16" s="13"/>
     </row>
     <row r="17" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="25"/>
-      <c r="B17" s="134" t="s">
+      <c r="B17" s="155" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="121"/>
-      <c r="P17" s="121"/>
-      <c r="Q17" s="121"/>
-      <c r="R17" s="121"/>
-      <c r="S17" s="121"/>
-      <c r="T17" s="121"/>
-      <c r="U17" s="121"/>
-      <c r="V17" s="121"/>
-      <c r="W17" s="121"/>
-      <c r="X17" s="121"/>
-      <c r="Y17" s="121"/>
-      <c r="Z17" s="121"/>
-      <c r="AA17" s="121"/>
-      <c r="AB17" s="121"/>
-      <c r="AC17" s="121"/>
-      <c r="AD17" s="121"/>
-      <c r="AE17" s="121"/>
-      <c r="AF17" s="121"/>
-      <c r="AG17" s="121"/>
-      <c r="AH17" s="122"/>
+      <c r="C17" s="108"/>
+      <c r="D17" s="108"/>
+      <c r="E17" s="108"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="108"/>
+      <c r="H17" s="108"/>
+      <c r="I17" s="108"/>
+      <c r="J17" s="108"/>
+      <c r="K17" s="108"/>
+      <c r="L17" s="108"/>
+      <c r="M17" s="108"/>
+      <c r="N17" s="108"/>
+      <c r="O17" s="108"/>
+      <c r="P17" s="108"/>
+      <c r="Q17" s="108"/>
+      <c r="R17" s="108"/>
+      <c r="S17" s="108"/>
+      <c r="T17" s="108"/>
+      <c r="U17" s="108"/>
+      <c r="V17" s="108"/>
+      <c r="W17" s="108"/>
+      <c r="X17" s="108"/>
+      <c r="Y17" s="108"/>
+      <c r="Z17" s="108"/>
+      <c r="AA17" s="108"/>
+      <c r="AB17" s="108"/>
+      <c r="AC17" s="108"/>
+      <c r="AD17" s="108"/>
+      <c r="AE17" s="108"/>
+      <c r="AF17" s="108"/>
+      <c r="AG17" s="108"/>
+      <c r="AH17" s="109"/>
       <c r="AI17" s="26"/>
     </row>
     <row r="18" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2392,357 +2403,357 @@
     <row r="19" spans="1:35" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="33"/>
       <c r="B19" s="34"/>
-      <c r="C19" s="135" t="s">
+      <c r="C19" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="115"/>
-      <c r="E19" s="115"/>
-      <c r="F19" s="126"/>
-      <c r="G19" s="136" t="s">
+      <c r="D19" s="131"/>
+      <c r="E19" s="131"/>
+      <c r="F19" s="132"/>
+      <c r="G19" s="157" t="s">
         <v>12</v>
       </c>
-      <c r="H19" s="115"/>
-      <c r="I19" s="115"/>
-      <c r="J19" s="115"/>
-      <c r="K19" s="126"/>
-      <c r="L19" s="136" t="s">
+      <c r="H19" s="131"/>
+      <c r="I19" s="131"/>
+      <c r="J19" s="131"/>
+      <c r="K19" s="132"/>
+      <c r="L19" s="157" t="s">
         <v>13</v>
       </c>
-      <c r="M19" s="115"/>
-      <c r="N19" s="115"/>
-      <c r="O19" s="115"/>
-      <c r="P19" s="126"/>
-      <c r="Q19" s="136" t="s">
+      <c r="M19" s="131"/>
+      <c r="N19" s="131"/>
+      <c r="O19" s="131"/>
+      <c r="P19" s="132"/>
+      <c r="Q19" s="157" t="s">
         <v>14</v>
       </c>
-      <c r="R19" s="115"/>
-      <c r="S19" s="115"/>
-      <c r="T19" s="115"/>
-      <c r="U19" s="115"/>
-      <c r="V19" s="126"/>
-      <c r="W19" s="136" t="s">
+      <c r="R19" s="131"/>
+      <c r="S19" s="131"/>
+      <c r="T19" s="131"/>
+      <c r="U19" s="131"/>
+      <c r="V19" s="132"/>
+      <c r="W19" s="157" t="s">
         <v>15</v>
       </c>
-      <c r="X19" s="115"/>
-      <c r="Y19" s="115"/>
-      <c r="Z19" s="115"/>
-      <c r="AA19" s="115"/>
-      <c r="AB19" s="115"/>
-      <c r="AC19" s="115"/>
-      <c r="AD19" s="115"/>
-      <c r="AE19" s="115"/>
-      <c r="AF19" s="115"/>
-      <c r="AG19" s="126"/>
+      <c r="X19" s="131"/>
+      <c r="Y19" s="131"/>
+      <c r="Z19" s="131"/>
+      <c r="AA19" s="131"/>
+      <c r="AB19" s="131"/>
+      <c r="AC19" s="131"/>
+      <c r="AD19" s="131"/>
+      <c r="AE19" s="131"/>
+      <c r="AF19" s="131"/>
+      <c r="AG19" s="132"/>
       <c r="AH19" s="35"/>
       <c r="AI19" s="26"/>
     </row>
     <row r="20" spans="1:35" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="33"/>
       <c r="B20" s="34"/>
-      <c r="C20" s="137" t="s">
+      <c r="C20" s="135" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="115"/>
-      <c r="E20" s="115"/>
-      <c r="F20" s="126"/>
-      <c r="G20" s="125"/>
-      <c r="H20" s="115"/>
-      <c r="I20" s="115"/>
-      <c r="J20" s="115"/>
-      <c r="K20" s="126"/>
-      <c r="L20" s="125"/>
-      <c r="M20" s="115"/>
-      <c r="N20" s="115"/>
-      <c r="O20" s="115"/>
-      <c r="P20" s="126"/>
-      <c r="Q20" s="125"/>
-      <c r="R20" s="115"/>
-      <c r="S20" s="115"/>
-      <c r="T20" s="115"/>
-      <c r="U20" s="115"/>
-      <c r="V20" s="126"/>
-      <c r="W20" s="125"/>
-      <c r="X20" s="115"/>
-      <c r="Y20" s="115"/>
-      <c r="Z20" s="115"/>
-      <c r="AA20" s="115"/>
-      <c r="AB20" s="115"/>
-      <c r="AC20" s="115"/>
-      <c r="AD20" s="115"/>
-      <c r="AE20" s="115"/>
-      <c r="AF20" s="115"/>
-      <c r="AG20" s="126"/>
+      <c r="D20" s="131"/>
+      <c r="E20" s="131"/>
+      <c r="F20" s="132"/>
+      <c r="G20" s="130"/>
+      <c r="H20" s="131"/>
+      <c r="I20" s="131"/>
+      <c r="J20" s="131"/>
+      <c r="K20" s="132"/>
+      <c r="L20" s="130"/>
+      <c r="M20" s="131"/>
+      <c r="N20" s="131"/>
+      <c r="O20" s="131"/>
+      <c r="P20" s="132"/>
+      <c r="Q20" s="130"/>
+      <c r="R20" s="131"/>
+      <c r="S20" s="131"/>
+      <c r="T20" s="131"/>
+      <c r="U20" s="131"/>
+      <c r="V20" s="132"/>
+      <c r="W20" s="130"/>
+      <c r="X20" s="131"/>
+      <c r="Y20" s="131"/>
+      <c r="Z20" s="131"/>
+      <c r="AA20" s="131"/>
+      <c r="AB20" s="131"/>
+      <c r="AC20" s="131"/>
+      <c r="AD20" s="131"/>
+      <c r="AE20" s="131"/>
+      <c r="AF20" s="131"/>
+      <c r="AG20" s="132"/>
       <c r="AH20" s="35"/>
       <c r="AI20" s="26"/>
     </row>
     <row r="21" spans="1:35" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="33"/>
       <c r="B21" s="34"/>
-      <c r="C21" s="137" t="s">
+      <c r="C21" s="135" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="115"/>
-      <c r="E21" s="115"/>
-      <c r="F21" s="126"/>
-      <c r="G21" s="125"/>
-      <c r="H21" s="115"/>
-      <c r="I21" s="115"/>
-      <c r="J21" s="115"/>
-      <c r="K21" s="126"/>
-      <c r="L21" s="125"/>
-      <c r="M21" s="115"/>
-      <c r="N21" s="115"/>
-      <c r="O21" s="115"/>
-      <c r="P21" s="126"/>
-      <c r="Q21" s="125"/>
-      <c r="R21" s="115"/>
-      <c r="S21" s="115"/>
-      <c r="T21" s="115"/>
-      <c r="U21" s="115"/>
-      <c r="V21" s="126"/>
-      <c r="W21" s="125"/>
-      <c r="X21" s="115"/>
-      <c r="Y21" s="115"/>
-      <c r="Z21" s="115"/>
-      <c r="AA21" s="115"/>
-      <c r="AB21" s="115"/>
-      <c r="AC21" s="115"/>
-      <c r="AD21" s="115"/>
-      <c r="AE21" s="115"/>
-      <c r="AF21" s="115"/>
-      <c r="AG21" s="126"/>
+      <c r="D21" s="131"/>
+      <c r="E21" s="131"/>
+      <c r="F21" s="132"/>
+      <c r="G21" s="130"/>
+      <c r="H21" s="131"/>
+      <c r="I21" s="131"/>
+      <c r="J21" s="131"/>
+      <c r="K21" s="132"/>
+      <c r="L21" s="130"/>
+      <c r="M21" s="131"/>
+      <c r="N21" s="131"/>
+      <c r="O21" s="131"/>
+      <c r="P21" s="132"/>
+      <c r="Q21" s="130"/>
+      <c r="R21" s="131"/>
+      <c r="S21" s="131"/>
+      <c r="T21" s="131"/>
+      <c r="U21" s="131"/>
+      <c r="V21" s="132"/>
+      <c r="W21" s="130"/>
+      <c r="X21" s="131"/>
+      <c r="Y21" s="131"/>
+      <c r="Z21" s="131"/>
+      <c r="AA21" s="131"/>
+      <c r="AB21" s="131"/>
+      <c r="AC21" s="131"/>
+      <c r="AD21" s="131"/>
+      <c r="AE21" s="131"/>
+      <c r="AF21" s="131"/>
+      <c r="AG21" s="132"/>
       <c r="AH21" s="35"/>
       <c r="AI21" s="26"/>
     </row>
     <row r="22" spans="1:35" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="33"/>
       <c r="B22" s="34"/>
-      <c r="C22" s="137" t="s">
+      <c r="C22" s="135" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="115"/>
-      <c r="E22" s="115"/>
-      <c r="F22" s="126"/>
-      <c r="G22" s="125"/>
-      <c r="H22" s="115"/>
-      <c r="I22" s="115"/>
-      <c r="J22" s="115"/>
-      <c r="K22" s="126"/>
-      <c r="L22" s="125"/>
-      <c r="M22" s="115"/>
-      <c r="N22" s="115"/>
-      <c r="O22" s="115"/>
-      <c r="P22" s="126"/>
-      <c r="Q22" s="125"/>
-      <c r="R22" s="115"/>
-      <c r="S22" s="115"/>
-      <c r="T22" s="115"/>
-      <c r="U22" s="115"/>
-      <c r="V22" s="126"/>
-      <c r="W22" s="125"/>
-      <c r="X22" s="115"/>
-      <c r="Y22" s="115"/>
-      <c r="Z22" s="115"/>
-      <c r="AA22" s="115"/>
-      <c r="AB22" s="115"/>
-      <c r="AC22" s="115"/>
-      <c r="AD22" s="115"/>
-      <c r="AE22" s="115"/>
-      <c r="AF22" s="115"/>
-      <c r="AG22" s="126"/>
+      <c r="D22" s="131"/>
+      <c r="E22" s="131"/>
+      <c r="F22" s="132"/>
+      <c r="G22" s="130"/>
+      <c r="H22" s="131"/>
+      <c r="I22" s="131"/>
+      <c r="J22" s="131"/>
+      <c r="K22" s="132"/>
+      <c r="L22" s="130"/>
+      <c r="M22" s="131"/>
+      <c r="N22" s="131"/>
+      <c r="O22" s="131"/>
+      <c r="P22" s="132"/>
+      <c r="Q22" s="130"/>
+      <c r="R22" s="131"/>
+      <c r="S22" s="131"/>
+      <c r="T22" s="131"/>
+      <c r="U22" s="131"/>
+      <c r="V22" s="132"/>
+      <c r="W22" s="130"/>
+      <c r="X22" s="131"/>
+      <c r="Y22" s="131"/>
+      <c r="Z22" s="131"/>
+      <c r="AA22" s="131"/>
+      <c r="AB22" s="131"/>
+      <c r="AC22" s="131"/>
+      <c r="AD22" s="131"/>
+      <c r="AE22" s="131"/>
+      <c r="AF22" s="131"/>
+      <c r="AG22" s="132"/>
       <c r="AH22" s="35"/>
       <c r="AI22" s="26"/>
     </row>
     <row r="23" spans="1:35" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="33"/>
       <c r="B23" s="34"/>
-      <c r="C23" s="137" t="s">
+      <c r="C23" s="135" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="115"/>
-      <c r="E23" s="115"/>
-      <c r="F23" s="126"/>
-      <c r="G23" s="125"/>
-      <c r="H23" s="115"/>
-      <c r="I23" s="115"/>
-      <c r="J23" s="115"/>
-      <c r="K23" s="126"/>
-      <c r="L23" s="125"/>
-      <c r="M23" s="115"/>
-      <c r="N23" s="115"/>
-      <c r="O23" s="115"/>
-      <c r="P23" s="126"/>
-      <c r="Q23" s="125"/>
-      <c r="R23" s="115"/>
-      <c r="S23" s="115"/>
-      <c r="T23" s="115"/>
-      <c r="U23" s="115"/>
-      <c r="V23" s="126"/>
-      <c r="W23" s="125"/>
-      <c r="X23" s="115"/>
-      <c r="Y23" s="115"/>
-      <c r="Z23" s="115"/>
-      <c r="AA23" s="115"/>
-      <c r="AB23" s="115"/>
-      <c r="AC23" s="115"/>
-      <c r="AD23" s="115"/>
-      <c r="AE23" s="115"/>
-      <c r="AF23" s="115"/>
-      <c r="AG23" s="126"/>
+      <c r="D23" s="131"/>
+      <c r="E23" s="131"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="130"/>
+      <c r="H23" s="131"/>
+      <c r="I23" s="131"/>
+      <c r="J23" s="131"/>
+      <c r="K23" s="132"/>
+      <c r="L23" s="130"/>
+      <c r="M23" s="131"/>
+      <c r="N23" s="131"/>
+      <c r="O23" s="131"/>
+      <c r="P23" s="132"/>
+      <c r="Q23" s="130"/>
+      <c r="R23" s="131"/>
+      <c r="S23" s="131"/>
+      <c r="T23" s="131"/>
+      <c r="U23" s="131"/>
+      <c r="V23" s="132"/>
+      <c r="W23" s="130"/>
+      <c r="X23" s="131"/>
+      <c r="Y23" s="131"/>
+      <c r="Z23" s="131"/>
+      <c r="AA23" s="131"/>
+      <c r="AB23" s="131"/>
+      <c r="AC23" s="131"/>
+      <c r="AD23" s="131"/>
+      <c r="AE23" s="131"/>
+      <c r="AF23" s="131"/>
+      <c r="AG23" s="132"/>
       <c r="AH23" s="35"/>
       <c r="AI23" s="26"/>
     </row>
     <row r="24" spans="1:35" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="33"/>
       <c r="B24" s="34"/>
-      <c r="C24" s="137" t="s">
+      <c r="C24" s="135" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="115"/>
-      <c r="E24" s="115"/>
-      <c r="F24" s="126"/>
-      <c r="G24" s="125"/>
-      <c r="H24" s="172"/>
-      <c r="I24" s="172"/>
-      <c r="J24" s="172"/>
-      <c r="K24" s="173"/>
-      <c r="L24" s="125"/>
-      <c r="M24" s="115"/>
-      <c r="N24" s="115"/>
-      <c r="O24" s="115"/>
-      <c r="P24" s="126"/>
-      <c r="Q24" s="125"/>
-      <c r="R24" s="115"/>
-      <c r="S24" s="115"/>
-      <c r="T24" s="115"/>
-      <c r="U24" s="115"/>
-      <c r="V24" s="126"/>
-      <c r="W24" s="125"/>
-      <c r="X24" s="115"/>
-      <c r="Y24" s="115"/>
-      <c r="Z24" s="115"/>
-      <c r="AA24" s="115"/>
-      <c r="AB24" s="115"/>
-      <c r="AC24" s="115"/>
-      <c r="AD24" s="115"/>
-      <c r="AE24" s="115"/>
-      <c r="AF24" s="115"/>
-      <c r="AG24" s="126"/>
+      <c r="D24" s="131"/>
+      <c r="E24" s="131"/>
+      <c r="F24" s="132"/>
+      <c r="G24" s="130"/>
+      <c r="H24" s="136"/>
+      <c r="I24" s="136"/>
+      <c r="J24" s="136"/>
+      <c r="K24" s="137"/>
+      <c r="L24" s="130"/>
+      <c r="M24" s="131"/>
+      <c r="N24" s="131"/>
+      <c r="O24" s="131"/>
+      <c r="P24" s="132"/>
+      <c r="Q24" s="130"/>
+      <c r="R24" s="131"/>
+      <c r="S24" s="131"/>
+      <c r="T24" s="131"/>
+      <c r="U24" s="131"/>
+      <c r="V24" s="132"/>
+      <c r="W24" s="130"/>
+      <c r="X24" s="131"/>
+      <c r="Y24" s="131"/>
+      <c r="Z24" s="131"/>
+      <c r="AA24" s="131"/>
+      <c r="AB24" s="131"/>
+      <c r="AC24" s="131"/>
+      <c r="AD24" s="131"/>
+      <c r="AE24" s="131"/>
+      <c r="AF24" s="131"/>
+      <c r="AG24" s="132"/>
       <c r="AH24" s="35"/>
       <c r="AI24" s="26"/>
     </row>
     <row r="25" spans="1:35" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="33"/>
       <c r="B25" s="34"/>
-      <c r="C25" s="137" t="s">
+      <c r="C25" s="135" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="115"/>
-      <c r="E25" s="115"/>
-      <c r="F25" s="126"/>
-      <c r="G25" s="125"/>
-      <c r="H25" s="172"/>
-      <c r="I25" s="172"/>
-      <c r="J25" s="172"/>
-      <c r="K25" s="173"/>
-      <c r="L25" s="125"/>
-      <c r="M25" s="115"/>
-      <c r="N25" s="115"/>
-      <c r="O25" s="115"/>
-      <c r="P25" s="126"/>
-      <c r="Q25" s="125"/>
-      <c r="R25" s="115"/>
-      <c r="S25" s="115"/>
-      <c r="T25" s="115"/>
-      <c r="U25" s="115"/>
-      <c r="V25" s="126"/>
-      <c r="W25" s="125"/>
-      <c r="X25" s="115"/>
-      <c r="Y25" s="115"/>
-      <c r="Z25" s="115"/>
-      <c r="AA25" s="115"/>
-      <c r="AB25" s="115"/>
-      <c r="AC25" s="115"/>
-      <c r="AD25" s="115"/>
-      <c r="AE25" s="115"/>
-      <c r="AF25" s="115"/>
-      <c r="AG25" s="126"/>
+      <c r="D25" s="131"/>
+      <c r="E25" s="131"/>
+      <c r="F25" s="132"/>
+      <c r="G25" s="130"/>
+      <c r="H25" s="136"/>
+      <c r="I25" s="136"/>
+      <c r="J25" s="136"/>
+      <c r="K25" s="137"/>
+      <c r="L25" s="130"/>
+      <c r="M25" s="131"/>
+      <c r="N25" s="131"/>
+      <c r="O25" s="131"/>
+      <c r="P25" s="132"/>
+      <c r="Q25" s="130"/>
+      <c r="R25" s="131"/>
+      <c r="S25" s="131"/>
+      <c r="T25" s="131"/>
+      <c r="U25" s="131"/>
+      <c r="V25" s="132"/>
+      <c r="W25" s="130"/>
+      <c r="X25" s="131"/>
+      <c r="Y25" s="131"/>
+      <c r="Z25" s="131"/>
+      <c r="AA25" s="131"/>
+      <c r="AB25" s="131"/>
+      <c r="AC25" s="131"/>
+      <c r="AD25" s="131"/>
+      <c r="AE25" s="131"/>
+      <c r="AF25" s="131"/>
+      <c r="AG25" s="132"/>
       <c r="AH25" s="35"/>
       <c r="AI25" s="26"/>
     </row>
     <row r="26" spans="1:35" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="33"/>
       <c r="B26" s="34"/>
-      <c r="C26" s="138" t="s">
+      <c r="C26" s="154" t="s">
         <v>22</v>
       </c>
-      <c r="D26" s="130"/>
-      <c r="E26" s="130"/>
-      <c r="F26" s="131"/>
-      <c r="G26" s="125"/>
-      <c r="H26" s="172"/>
-      <c r="I26" s="172"/>
-      <c r="J26" s="172"/>
-      <c r="K26" s="173"/>
-      <c r="L26" s="125"/>
-      <c r="M26" s="115"/>
-      <c r="N26" s="115"/>
-      <c r="O26" s="115"/>
-      <c r="P26" s="126"/>
-      <c r="Q26" s="125"/>
-      <c r="R26" s="115"/>
-      <c r="S26" s="115"/>
-      <c r="T26" s="115"/>
-      <c r="U26" s="115"/>
-      <c r="V26" s="126"/>
-      <c r="W26" s="125"/>
-      <c r="X26" s="115"/>
-      <c r="Y26" s="115"/>
-      <c r="Z26" s="115"/>
-      <c r="AA26" s="115"/>
-      <c r="AB26" s="115"/>
-      <c r="AC26" s="115"/>
-      <c r="AD26" s="115"/>
-      <c r="AE26" s="115"/>
-      <c r="AF26" s="115"/>
-      <c r="AG26" s="126"/>
+      <c r="D26" s="147"/>
+      <c r="E26" s="147"/>
+      <c r="F26" s="148"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="136"/>
+      <c r="I26" s="136"/>
+      <c r="J26" s="136"/>
+      <c r="K26" s="137"/>
+      <c r="L26" s="130"/>
+      <c r="M26" s="131"/>
+      <c r="N26" s="131"/>
+      <c r="O26" s="131"/>
+      <c r="P26" s="132"/>
+      <c r="Q26" s="130"/>
+      <c r="R26" s="131"/>
+      <c r="S26" s="131"/>
+      <c r="T26" s="131"/>
+      <c r="U26" s="131"/>
+      <c r="V26" s="132"/>
+      <c r="W26" s="130"/>
+      <c r="X26" s="131"/>
+      <c r="Y26" s="131"/>
+      <c r="Z26" s="131"/>
+      <c r="AA26" s="131"/>
+      <c r="AB26" s="131"/>
+      <c r="AC26" s="131"/>
+      <c r="AD26" s="131"/>
+      <c r="AE26" s="131"/>
+      <c r="AF26" s="131"/>
+      <c r="AG26" s="132"/>
       <c r="AH26" s="35"/>
       <c r="AI26" s="26"/>
     </row>
     <row r="27" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33"/>
       <c r="B27" s="34"/>
-      <c r="C27" s="108"/>
-      <c r="D27" s="109"/>
-      <c r="E27" s="109"/>
-      <c r="F27" s="110"/>
-      <c r="G27" s="125"/>
-      <c r="H27" s="172"/>
-      <c r="I27" s="172"/>
-      <c r="J27" s="172"/>
-      <c r="K27" s="173"/>
-      <c r="L27" s="125"/>
-      <c r="M27" s="115"/>
-      <c r="N27" s="115"/>
-      <c r="O27" s="115"/>
-      <c r="P27" s="126"/>
-      <c r="Q27" s="125"/>
-      <c r="R27" s="115"/>
-      <c r="S27" s="115"/>
-      <c r="T27" s="115"/>
-      <c r="U27" s="115"/>
-      <c r="V27" s="126"/>
-      <c r="W27" s="125"/>
-      <c r="X27" s="115"/>
-      <c r="Y27" s="115"/>
-      <c r="Z27" s="115"/>
-      <c r="AA27" s="115"/>
-      <c r="AB27" s="115"/>
-      <c r="AC27" s="115"/>
-      <c r="AD27" s="115"/>
-      <c r="AE27" s="115"/>
-      <c r="AF27" s="115"/>
-      <c r="AG27" s="126"/>
+      <c r="C27" s="149"/>
+      <c r="D27" s="150"/>
+      <c r="E27" s="150"/>
+      <c r="F27" s="151"/>
+      <c r="G27" s="130"/>
+      <c r="H27" s="136"/>
+      <c r="I27" s="136"/>
+      <c r="J27" s="136"/>
+      <c r="K27" s="137"/>
+      <c r="L27" s="130"/>
+      <c r="M27" s="131"/>
+      <c r="N27" s="131"/>
+      <c r="O27" s="131"/>
+      <c r="P27" s="132"/>
+      <c r="Q27" s="130"/>
+      <c r="R27" s="131"/>
+      <c r="S27" s="131"/>
+      <c r="T27" s="131"/>
+      <c r="U27" s="131"/>
+      <c r="V27" s="132"/>
+      <c r="W27" s="130"/>
+      <c r="X27" s="131"/>
+      <c r="Y27" s="131"/>
+      <c r="Z27" s="131"/>
+      <c r="AA27" s="131"/>
+      <c r="AB27" s="131"/>
+      <c r="AC27" s="131"/>
+      <c r="AD27" s="131"/>
+      <c r="AE27" s="131"/>
+      <c r="AF27" s="131"/>
+      <c r="AG27" s="132"/>
       <c r="AH27" s="35"/>
       <c r="AI27" s="26"/>
     </row>
@@ -2765,21 +2776,21 @@
       <c r="P28" s="20"/>
       <c r="Q28" s="20"/>
       <c r="R28" s="133"/>
-      <c r="S28" s="101"/>
-      <c r="T28" s="101"/>
-      <c r="U28" s="101"/>
-      <c r="V28" s="101"/>
-      <c r="W28" s="101"/>
-      <c r="X28" s="101"/>
+      <c r="S28" s="134"/>
+      <c r="T28" s="134"/>
+      <c r="U28" s="134"/>
+      <c r="V28" s="134"/>
+      <c r="W28" s="134"/>
+      <c r="X28" s="134"/>
       <c r="Y28" s="133"/>
-      <c r="Z28" s="101"/>
-      <c r="AA28" s="101"/>
-      <c r="AB28" s="101"/>
-      <c r="AC28" s="101"/>
-      <c r="AD28" s="101"/>
-      <c r="AE28" s="101"/>
-      <c r="AF28" s="101"/>
-      <c r="AG28" s="101"/>
+      <c r="Z28" s="134"/>
+      <c r="AA28" s="134"/>
+      <c r="AB28" s="134"/>
+      <c r="AC28" s="134"/>
+      <c r="AD28" s="134"/>
+      <c r="AE28" s="134"/>
+      <c r="AF28" s="134"/>
+      <c r="AG28" s="134"/>
       <c r="AH28" s="16"/>
       <c r="AI28" s="13"/>
     </row>
@@ -2822,41 +2833,41 @@
     </row>
     <row r="30" spans="1:35" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="23"/>
-      <c r="B30" s="120" t="s">
+      <c r="B30" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="121"/>
-      <c r="D30" s="121"/>
-      <c r="E30" s="121"/>
-      <c r="F30" s="121"/>
-      <c r="G30" s="121"/>
-      <c r="H30" s="121"/>
-      <c r="I30" s="121"/>
-      <c r="J30" s="121"/>
-      <c r="K30" s="121"/>
-      <c r="L30" s="121"/>
-      <c r="M30" s="121"/>
-      <c r="N30" s="121"/>
-      <c r="O30" s="121"/>
-      <c r="P30" s="121"/>
-      <c r="Q30" s="121"/>
-      <c r="R30" s="121"/>
-      <c r="S30" s="121"/>
-      <c r="T30" s="121"/>
-      <c r="U30" s="121"/>
-      <c r="V30" s="121"/>
-      <c r="W30" s="121"/>
-      <c r="X30" s="121"/>
-      <c r="Y30" s="121"/>
-      <c r="Z30" s="121"/>
-      <c r="AA30" s="121"/>
-      <c r="AB30" s="121"/>
-      <c r="AC30" s="121"/>
-      <c r="AD30" s="121"/>
-      <c r="AE30" s="121"/>
-      <c r="AF30" s="121"/>
-      <c r="AG30" s="121"/>
-      <c r="AH30" s="122"/>
+      <c r="C30" s="108"/>
+      <c r="D30" s="108"/>
+      <c r="E30" s="108"/>
+      <c r="F30" s="108"/>
+      <c r="G30" s="108"/>
+      <c r="H30" s="108"/>
+      <c r="I30" s="108"/>
+      <c r="J30" s="108"/>
+      <c r="K30" s="108"/>
+      <c r="L30" s="108"/>
+      <c r="M30" s="108"/>
+      <c r="N30" s="108"/>
+      <c r="O30" s="108"/>
+      <c r="P30" s="108"/>
+      <c r="Q30" s="108"/>
+      <c r="R30" s="108"/>
+      <c r="S30" s="108"/>
+      <c r="T30" s="108"/>
+      <c r="U30" s="108"/>
+      <c r="V30" s="108"/>
+      <c r="W30" s="108"/>
+      <c r="X30" s="108"/>
+      <c r="Y30" s="108"/>
+      <c r="Z30" s="108"/>
+      <c r="AA30" s="108"/>
+      <c r="AB30" s="108"/>
+      <c r="AC30" s="108"/>
+      <c r="AD30" s="108"/>
+      <c r="AE30" s="108"/>
+      <c r="AF30" s="108"/>
+      <c r="AG30" s="108"/>
+      <c r="AH30" s="109"/>
       <c r="AI30" s="13"/>
     </row>
     <row r="31" spans="1:35" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2899,53 +2910,53 @@
     <row r="32" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="38"/>
       <c r="B32" s="39"/>
-      <c r="C32" s="129" t="s">
+      <c r="C32" s="146" t="s">
         <v>24</v>
       </c>
-      <c r="D32" s="130"/>
-      <c r="E32" s="130"/>
-      <c r="F32" s="130"/>
-      <c r="G32" s="130"/>
-      <c r="H32" s="130"/>
-      <c r="I32" s="130"/>
-      <c r="J32" s="131"/>
-      <c r="K32" s="127" t="s">
+      <c r="D32" s="147"/>
+      <c r="E32" s="147"/>
+      <c r="F32" s="147"/>
+      <c r="G32" s="147"/>
+      <c r="H32" s="147"/>
+      <c r="I32" s="147"/>
+      <c r="J32" s="148"/>
+      <c r="K32" s="152" t="s">
         <v>25</v>
       </c>
-      <c r="L32" s="127" t="s">
+      <c r="L32" s="152" t="s">
         <v>26</v>
       </c>
-      <c r="M32" s="129" t="s">
+      <c r="M32" s="146" t="s">
         <v>24</v>
       </c>
-      <c r="N32" s="130"/>
-      <c r="O32" s="130"/>
-      <c r="P32" s="130"/>
-      <c r="Q32" s="130"/>
-      <c r="R32" s="130"/>
-      <c r="S32" s="130"/>
-      <c r="T32" s="131"/>
-      <c r="U32" s="127" t="s">
+      <c r="N32" s="147"/>
+      <c r="O32" s="147"/>
+      <c r="P32" s="147"/>
+      <c r="Q32" s="147"/>
+      <c r="R32" s="147"/>
+      <c r="S32" s="147"/>
+      <c r="T32" s="148"/>
+      <c r="U32" s="152" t="s">
         <v>25</v>
       </c>
-      <c r="V32" s="127" t="s">
+      <c r="V32" s="152" t="s">
         <v>26</v>
       </c>
-      <c r="W32" s="129" t="s">
+      <c r="W32" s="146" t="s">
         <v>24</v>
       </c>
-      <c r="X32" s="130"/>
-      <c r="Y32" s="130"/>
-      <c r="Z32" s="130"/>
-      <c r="AA32" s="130"/>
-      <c r="AB32" s="130"/>
-      <c r="AC32" s="130"/>
-      <c r="AD32" s="130"/>
-      <c r="AE32" s="131"/>
-      <c r="AF32" s="127" t="s">
+      <c r="X32" s="147"/>
+      <c r="Y32" s="147"/>
+      <c r="Z32" s="147"/>
+      <c r="AA32" s="147"/>
+      <c r="AB32" s="147"/>
+      <c r="AC32" s="147"/>
+      <c r="AD32" s="147"/>
+      <c r="AE32" s="148"/>
+      <c r="AF32" s="152" t="s">
         <v>25</v>
       </c>
-      <c r="AG32" s="127" t="s">
+      <c r="AG32" s="152" t="s">
         <v>26</v>
       </c>
       <c r="AH32" s="40"/>
@@ -2954,78 +2965,78 @@
     <row r="33" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="38"/>
       <c r="B33" s="39"/>
-      <c r="C33" s="108"/>
-      <c r="D33" s="109"/>
-      <c r="E33" s="109"/>
-      <c r="F33" s="109"/>
-      <c r="G33" s="109"/>
-      <c r="H33" s="109"/>
-      <c r="I33" s="109"/>
-      <c r="J33" s="110"/>
-      <c r="K33" s="128"/>
-      <c r="L33" s="128"/>
-      <c r="M33" s="108"/>
-      <c r="N33" s="109"/>
-      <c r="O33" s="109"/>
-      <c r="P33" s="109"/>
-      <c r="Q33" s="109"/>
-      <c r="R33" s="109"/>
-      <c r="S33" s="109"/>
-      <c r="T33" s="110"/>
-      <c r="U33" s="128"/>
-      <c r="V33" s="128"/>
-      <c r="W33" s="108"/>
-      <c r="X33" s="109"/>
-      <c r="Y33" s="109"/>
-      <c r="Z33" s="109"/>
-      <c r="AA33" s="109"/>
-      <c r="AB33" s="109"/>
-      <c r="AC33" s="109"/>
-      <c r="AD33" s="109"/>
-      <c r="AE33" s="110"/>
-      <c r="AF33" s="128"/>
-      <c r="AG33" s="128"/>
+      <c r="C33" s="149"/>
+      <c r="D33" s="150"/>
+      <c r="E33" s="150"/>
+      <c r="F33" s="150"/>
+      <c r="G33" s="150"/>
+      <c r="H33" s="150"/>
+      <c r="I33" s="150"/>
+      <c r="J33" s="151"/>
+      <c r="K33" s="153"/>
+      <c r="L33" s="153"/>
+      <c r="M33" s="149"/>
+      <c r="N33" s="150"/>
+      <c r="O33" s="150"/>
+      <c r="P33" s="150"/>
+      <c r="Q33" s="150"/>
+      <c r="R33" s="150"/>
+      <c r="S33" s="150"/>
+      <c r="T33" s="151"/>
+      <c r="U33" s="153"/>
+      <c r="V33" s="153"/>
+      <c r="W33" s="149"/>
+      <c r="X33" s="150"/>
+      <c r="Y33" s="150"/>
+      <c r="Z33" s="150"/>
+      <c r="AA33" s="150"/>
+      <c r="AB33" s="150"/>
+      <c r="AC33" s="150"/>
+      <c r="AD33" s="150"/>
+      <c r="AE33" s="151"/>
+      <c r="AF33" s="153"/>
+      <c r="AG33" s="153"/>
       <c r="AH33" s="42"/>
       <c r="AI33" s="43"/>
     </row>
     <row r="34" spans="1:35" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="23"/>
       <c r="B34" s="24"/>
-      <c r="C34" s="132" t="s">
+      <c r="C34" s="145" t="s">
         <v>27</v>
       </c>
-      <c r="D34" s="115"/>
-      <c r="E34" s="115"/>
-      <c r="F34" s="115"/>
-      <c r="G34" s="115"/>
-      <c r="H34" s="115"/>
-      <c r="I34" s="115"/>
-      <c r="J34" s="126"/>
+      <c r="D34" s="131"/>
+      <c r="E34" s="131"/>
+      <c r="F34" s="131"/>
+      <c r="G34" s="131"/>
+      <c r="H34" s="131"/>
+      <c r="I34" s="131"/>
+      <c r="J34" s="132"/>
       <c r="K34" s="44"/>
       <c r="L34" s="44"/>
-      <c r="M34" s="132" t="s">
+      <c r="M34" s="145" t="s">
         <v>28</v>
       </c>
-      <c r="N34" s="115"/>
-      <c r="O34" s="115"/>
-      <c r="P34" s="115"/>
-      <c r="Q34" s="115"/>
-      <c r="R34" s="115"/>
-      <c r="S34" s="115"/>
-      <c r="T34" s="126"/>
+      <c r="N34" s="131"/>
+      <c r="O34" s="131"/>
+      <c r="P34" s="131"/>
+      <c r="Q34" s="131"/>
+      <c r="R34" s="131"/>
+      <c r="S34" s="131"/>
+      <c r="T34" s="132"/>
       <c r="U34" s="44"/>
       <c r="V34" s="44"/>
-      <c r="W34" s="132" t="s">
+      <c r="W34" s="145" t="s">
         <v>29</v>
       </c>
-      <c r="X34" s="115"/>
-      <c r="Y34" s="115"/>
-      <c r="Z34" s="115"/>
-      <c r="AA34" s="115"/>
-      <c r="AB34" s="115"/>
-      <c r="AC34" s="115"/>
-      <c r="AD34" s="115"/>
-      <c r="AE34" s="126"/>
+      <c r="X34" s="131"/>
+      <c r="Y34" s="131"/>
+      <c r="Z34" s="131"/>
+      <c r="AA34" s="131"/>
+      <c r="AB34" s="131"/>
+      <c r="AC34" s="131"/>
+      <c r="AD34" s="131"/>
+      <c r="AE34" s="132"/>
       <c r="AF34" s="44"/>
       <c r="AG34" s="44"/>
       <c r="AH34" s="42"/>
@@ -3034,41 +3045,41 @@
     <row r="35" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="23"/>
       <c r="B35" s="24"/>
-      <c r="C35" s="132" t="s">
+      <c r="C35" s="145" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="115"/>
-      <c r="E35" s="115"/>
-      <c r="F35" s="115"/>
-      <c r="G35" s="115"/>
-      <c r="H35" s="115"/>
-      <c r="I35" s="115"/>
-      <c r="J35" s="126"/>
+      <c r="D35" s="131"/>
+      <c r="E35" s="131"/>
+      <c r="F35" s="131"/>
+      <c r="G35" s="131"/>
+      <c r="H35" s="131"/>
+      <c r="I35" s="131"/>
+      <c r="J35" s="132"/>
       <c r="K35" s="44"/>
       <c r="L35" s="44"/>
-      <c r="M35" s="132" t="s">
+      <c r="M35" s="145" t="s">
         <v>31</v>
       </c>
-      <c r="N35" s="115"/>
-      <c r="O35" s="115"/>
-      <c r="P35" s="115"/>
-      <c r="Q35" s="115"/>
-      <c r="R35" s="115"/>
-      <c r="S35" s="115"/>
-      <c r="T35" s="126"/>
+      <c r="N35" s="131"/>
+      <c r="O35" s="131"/>
+      <c r="P35" s="131"/>
+      <c r="Q35" s="131"/>
+      <c r="R35" s="131"/>
+      <c r="S35" s="131"/>
+      <c r="T35" s="132"/>
       <c r="U35" s="44"/>
       <c r="V35" s="44"/>
-      <c r="W35" s="132" t="s">
+      <c r="W35" s="145" t="s">
         <v>32</v>
       </c>
-      <c r="X35" s="115"/>
-      <c r="Y35" s="115"/>
-      <c r="Z35" s="115"/>
-      <c r="AA35" s="115"/>
-      <c r="AB35" s="115"/>
-      <c r="AC35" s="115"/>
-      <c r="AD35" s="115"/>
-      <c r="AE35" s="126"/>
+      <c r="X35" s="131"/>
+      <c r="Y35" s="131"/>
+      <c r="Z35" s="131"/>
+      <c r="AA35" s="131"/>
+      <c r="AB35" s="131"/>
+      <c r="AC35" s="131"/>
+      <c r="AD35" s="131"/>
+      <c r="AE35" s="132"/>
       <c r="AF35" s="44"/>
       <c r="AG35" s="44"/>
       <c r="AH35" s="42"/>
@@ -3077,41 +3088,41 @@
     <row r="36" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="23"/>
       <c r="B36" s="24"/>
-      <c r="C36" s="132" t="s">
+      <c r="C36" s="145" t="s">
         <v>33</v>
       </c>
-      <c r="D36" s="115"/>
-      <c r="E36" s="115"/>
-      <c r="F36" s="115"/>
-      <c r="G36" s="115"/>
-      <c r="H36" s="115"/>
-      <c r="I36" s="115"/>
-      <c r="J36" s="126"/>
+      <c r="D36" s="131"/>
+      <c r="E36" s="131"/>
+      <c r="F36" s="131"/>
+      <c r="G36" s="131"/>
+      <c r="H36" s="131"/>
+      <c r="I36" s="131"/>
+      <c r="J36" s="132"/>
       <c r="K36" s="44"/>
       <c r="L36" s="44"/>
-      <c r="M36" s="132" t="s">
+      <c r="M36" s="145" t="s">
         <v>34</v>
       </c>
-      <c r="N36" s="115"/>
-      <c r="O36" s="115"/>
-      <c r="P36" s="115"/>
-      <c r="Q36" s="115"/>
-      <c r="R36" s="115"/>
-      <c r="S36" s="115"/>
-      <c r="T36" s="126"/>
+      <c r="N36" s="131"/>
+      <c r="O36" s="131"/>
+      <c r="P36" s="131"/>
+      <c r="Q36" s="131"/>
+      <c r="R36" s="131"/>
+      <c r="S36" s="131"/>
+      <c r="T36" s="132"/>
       <c r="U36" s="44"/>
       <c r="V36" s="44"/>
-      <c r="W36" s="132" t="s">
+      <c r="W36" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="X36" s="115"/>
-      <c r="Y36" s="115"/>
-      <c r="Z36" s="115"/>
-      <c r="AA36" s="115"/>
-      <c r="AB36" s="115"/>
-      <c r="AC36" s="115"/>
-      <c r="AD36" s="115"/>
-      <c r="AE36" s="126"/>
+      <c r="X36" s="131"/>
+      <c r="Y36" s="131"/>
+      <c r="Z36" s="131"/>
+      <c r="AA36" s="131"/>
+      <c r="AB36" s="131"/>
+      <c r="AC36" s="131"/>
+      <c r="AD36" s="131"/>
+      <c r="AE36" s="132"/>
       <c r="AF36" s="44"/>
       <c r="AG36" s="44"/>
       <c r="AH36" s="42"/>
@@ -3120,41 +3131,41 @@
     <row r="37" spans="1:35" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="23"/>
       <c r="B37" s="24"/>
-      <c r="C37" s="132" t="s">
+      <c r="C37" s="145" t="s">
         <v>36</v>
       </c>
-      <c r="D37" s="115"/>
-      <c r="E37" s="115"/>
-      <c r="F37" s="115"/>
-      <c r="G37" s="115"/>
-      <c r="H37" s="115"/>
-      <c r="I37" s="115"/>
-      <c r="J37" s="126"/>
+      <c r="D37" s="131"/>
+      <c r="E37" s="131"/>
+      <c r="F37" s="131"/>
+      <c r="G37" s="131"/>
+      <c r="H37" s="131"/>
+      <c r="I37" s="131"/>
+      <c r="J37" s="132"/>
       <c r="K37" s="44"/>
       <c r="L37" s="44"/>
-      <c r="M37" s="132" t="s">
+      <c r="M37" s="145" t="s">
         <v>37</v>
       </c>
-      <c r="N37" s="115"/>
-      <c r="O37" s="115"/>
-      <c r="P37" s="115"/>
-      <c r="Q37" s="115"/>
-      <c r="R37" s="115"/>
-      <c r="S37" s="115"/>
-      <c r="T37" s="126"/>
+      <c r="N37" s="131"/>
+      <c r="O37" s="131"/>
+      <c r="P37" s="131"/>
+      <c r="Q37" s="131"/>
+      <c r="R37" s="131"/>
+      <c r="S37" s="131"/>
+      <c r="T37" s="132"/>
       <c r="U37" s="44"/>
       <c r="V37" s="44"/>
-      <c r="W37" s="132" t="s">
+      <c r="W37" s="145" t="s">
         <v>38</v>
       </c>
-      <c r="X37" s="115"/>
-      <c r="Y37" s="115"/>
-      <c r="Z37" s="115"/>
-      <c r="AA37" s="115"/>
-      <c r="AB37" s="115"/>
-      <c r="AC37" s="115"/>
-      <c r="AD37" s="115"/>
-      <c r="AE37" s="126"/>
+      <c r="X37" s="131"/>
+      <c r="Y37" s="131"/>
+      <c r="Z37" s="131"/>
+      <c r="AA37" s="131"/>
+      <c r="AB37" s="131"/>
+      <c r="AC37" s="131"/>
+      <c r="AD37" s="131"/>
+      <c r="AE37" s="132"/>
       <c r="AF37" s="44"/>
       <c r="AG37" s="44"/>
       <c r="AH37" s="42"/>
@@ -3163,39 +3174,39 @@
     <row r="38" spans="1:35" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="38"/>
       <c r="B38" s="39"/>
-      <c r="C38" s="140" t="s">
+      <c r="C38" s="143" t="s">
         <v>39</v>
       </c>
-      <c r="D38" s="115"/>
-      <c r="E38" s="115"/>
-      <c r="F38" s="115"/>
-      <c r="G38" s="115"/>
-      <c r="H38" s="115"/>
-      <c r="I38" s="115"/>
-      <c r="J38" s="126"/>
-      <c r="K38" s="141"/>
-      <c r="L38" s="115"/>
-      <c r="M38" s="115"/>
-      <c r="N38" s="115"/>
-      <c r="O38" s="115"/>
-      <c r="P38" s="115"/>
-      <c r="Q38" s="115"/>
-      <c r="R38" s="115"/>
-      <c r="S38" s="115"/>
-      <c r="T38" s="115"/>
-      <c r="U38" s="115"/>
-      <c r="V38" s="115"/>
-      <c r="W38" s="115"/>
-      <c r="X38" s="115"/>
-      <c r="Y38" s="115"/>
-      <c r="Z38" s="115"/>
-      <c r="AA38" s="115"/>
-      <c r="AB38" s="115"/>
-      <c r="AC38" s="115"/>
-      <c r="AD38" s="115"/>
-      <c r="AE38" s="115"/>
-      <c r="AF38" s="115"/>
-      <c r="AG38" s="126"/>
+      <c r="D38" s="131"/>
+      <c r="E38" s="131"/>
+      <c r="F38" s="131"/>
+      <c r="G38" s="131"/>
+      <c r="H38" s="131"/>
+      <c r="I38" s="131"/>
+      <c r="J38" s="132"/>
+      <c r="K38" s="144"/>
+      <c r="L38" s="131"/>
+      <c r="M38" s="131"/>
+      <c r="N38" s="131"/>
+      <c r="O38" s="131"/>
+      <c r="P38" s="131"/>
+      <c r="Q38" s="131"/>
+      <c r="R38" s="131"/>
+      <c r="S38" s="131"/>
+      <c r="T38" s="131"/>
+      <c r="U38" s="131"/>
+      <c r="V38" s="131"/>
+      <c r="W38" s="131"/>
+      <c r="X38" s="131"/>
+      <c r="Y38" s="131"/>
+      <c r="Z38" s="131"/>
+      <c r="AA38" s="131"/>
+      <c r="AB38" s="131"/>
+      <c r="AC38" s="131"/>
+      <c r="AD38" s="131"/>
+      <c r="AE38" s="131"/>
+      <c r="AF38" s="131"/>
+      <c r="AG38" s="132"/>
       <c r="AH38" s="42"/>
       <c r="AI38" s="43"/>
     </row>
@@ -3218,61 +3229,61 @@
       <c r="P39" s="20"/>
       <c r="Q39" s="2"/>
       <c r="R39" s="133"/>
-      <c r="S39" s="101"/>
-      <c r="T39" s="101"/>
-      <c r="U39" s="101"/>
-      <c r="V39" s="101"/>
-      <c r="W39" s="101"/>
-      <c r="X39" s="101"/>
+      <c r="S39" s="134"/>
+      <c r="T39" s="134"/>
+      <c r="U39" s="134"/>
+      <c r="V39" s="134"/>
+      <c r="W39" s="134"/>
+      <c r="X39" s="134"/>
       <c r="Y39" s="133"/>
-      <c r="Z39" s="101"/>
-      <c r="AA39" s="101"/>
-      <c r="AB39" s="101"/>
-      <c r="AC39" s="101"/>
-      <c r="AD39" s="101"/>
-      <c r="AE39" s="101"/>
-      <c r="AF39" s="101"/>
-      <c r="AG39" s="101"/>
+      <c r="Z39" s="134"/>
+      <c r="AA39" s="134"/>
+      <c r="AB39" s="134"/>
+      <c r="AC39" s="134"/>
+      <c r="AD39" s="134"/>
+      <c r="AE39" s="134"/>
+      <c r="AF39" s="134"/>
+      <c r="AG39" s="134"/>
       <c r="AH39" s="16"/>
       <c r="AI39" s="13"/>
     </row>
     <row r="40" spans="1:35" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7"/>
-      <c r="B40" s="120" t="s">
+      <c r="B40" s="107" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="121"/>
-      <c r="D40" s="121"/>
-      <c r="E40" s="121"/>
-      <c r="F40" s="121"/>
-      <c r="G40" s="121"/>
-      <c r="H40" s="121"/>
-      <c r="I40" s="121"/>
-      <c r="J40" s="121"/>
-      <c r="K40" s="121"/>
-      <c r="L40" s="121"/>
-      <c r="M40" s="121"/>
-      <c r="N40" s="121"/>
-      <c r="O40" s="121"/>
-      <c r="P40" s="121"/>
-      <c r="Q40" s="121"/>
-      <c r="R40" s="121"/>
-      <c r="S40" s="121"/>
-      <c r="T40" s="121"/>
-      <c r="U40" s="121"/>
-      <c r="V40" s="121"/>
-      <c r="W40" s="121"/>
-      <c r="X40" s="121"/>
-      <c r="Y40" s="121"/>
-      <c r="Z40" s="121"/>
-      <c r="AA40" s="121"/>
-      <c r="AB40" s="121"/>
-      <c r="AC40" s="121"/>
-      <c r="AD40" s="121"/>
-      <c r="AE40" s="121"/>
-      <c r="AF40" s="121"/>
-      <c r="AG40" s="121"/>
-      <c r="AH40" s="122"/>
+      <c r="C40" s="108"/>
+      <c r="D40" s="108"/>
+      <c r="E40" s="108"/>
+      <c r="F40" s="108"/>
+      <c r="G40" s="108"/>
+      <c r="H40" s="108"/>
+      <c r="I40" s="108"/>
+      <c r="J40" s="108"/>
+      <c r="K40" s="108"/>
+      <c r="L40" s="108"/>
+      <c r="M40" s="108"/>
+      <c r="N40" s="108"/>
+      <c r="O40" s="108"/>
+      <c r="P40" s="108"/>
+      <c r="Q40" s="108"/>
+      <c r="R40" s="108"/>
+      <c r="S40" s="108"/>
+      <c r="T40" s="108"/>
+      <c r="U40" s="108"/>
+      <c r="V40" s="108"/>
+      <c r="W40" s="108"/>
+      <c r="X40" s="108"/>
+      <c r="Y40" s="108"/>
+      <c r="Z40" s="108"/>
+      <c r="AA40" s="108"/>
+      <c r="AB40" s="108"/>
+      <c r="AC40" s="108"/>
+      <c r="AD40" s="108"/>
+      <c r="AE40" s="108"/>
+      <c r="AF40" s="108"/>
+      <c r="AG40" s="108"/>
+      <c r="AH40" s="109"/>
       <c r="AI40" s="7"/>
     </row>
     <row r="41" spans="1:35" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3315,46 +3326,46 @@
     <row r="42" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="49"/>
       <c r="B42" s="50"/>
-      <c r="C42" s="139" t="s">
+      <c r="C42" s="142" t="s">
         <v>41</v>
       </c>
-      <c r="D42" s="115"/>
-      <c r="E42" s="115"/>
-      <c r="F42" s="115"/>
-      <c r="G42" s="115"/>
-      <c r="H42" s="115"/>
-      <c r="I42" s="115"/>
-      <c r="J42" s="126"/>
+      <c r="D42" s="131"/>
+      <c r="E42" s="131"/>
+      <c r="F42" s="131"/>
+      <c r="G42" s="131"/>
+      <c r="H42" s="131"/>
+      <c r="I42" s="131"/>
+      <c r="J42" s="132"/>
       <c r="K42" s="51" t="s">
         <v>42</v>
       </c>
       <c r="L42" s="52"/>
-      <c r="M42" s="139" t="s">
+      <c r="M42" s="142" t="s">
         <v>43</v>
       </c>
-      <c r="N42" s="115"/>
-      <c r="O42" s="115"/>
-      <c r="P42" s="115"/>
-      <c r="Q42" s="115"/>
-      <c r="R42" s="115"/>
-      <c r="S42" s="115"/>
-      <c r="T42" s="115"/>
-      <c r="U42" s="126"/>
+      <c r="N42" s="131"/>
+      <c r="O42" s="131"/>
+      <c r="P42" s="131"/>
+      <c r="Q42" s="131"/>
+      <c r="R42" s="131"/>
+      <c r="S42" s="131"/>
+      <c r="T42" s="131"/>
+      <c r="U42" s="132"/>
       <c r="V42" s="51" t="s">
         <v>42</v>
       </c>
       <c r="W42" s="53"/>
-      <c r="X42" s="139" t="s">
+      <c r="X42" s="142" t="s">
         <v>44</v>
       </c>
-      <c r="Y42" s="115"/>
-      <c r="Z42" s="115"/>
-      <c r="AA42" s="115"/>
-      <c r="AB42" s="115"/>
-      <c r="AC42" s="115"/>
-      <c r="AD42" s="115"/>
-      <c r="AE42" s="115"/>
-      <c r="AF42" s="126"/>
+      <c r="Y42" s="131"/>
+      <c r="Z42" s="131"/>
+      <c r="AA42" s="131"/>
+      <c r="AB42" s="131"/>
+      <c r="AC42" s="131"/>
+      <c r="AD42" s="131"/>
+      <c r="AE42" s="131"/>
+      <c r="AF42" s="132"/>
       <c r="AG42" s="51" t="s">
         <v>42</v>
       </c>
@@ -3364,46 +3375,46 @@
     <row r="43" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="55"/>
       <c r="B43" s="56"/>
-      <c r="C43" s="142" t="s">
+      <c r="C43" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="D43" s="115"/>
-      <c r="E43" s="115"/>
-      <c r="F43" s="115"/>
-      <c r="G43" s="115"/>
-      <c r="H43" s="115"/>
-      <c r="I43" s="115"/>
-      <c r="J43" s="126"/>
+      <c r="D43" s="131"/>
+      <c r="E43" s="131"/>
+      <c r="F43" s="131"/>
+      <c r="G43" s="131"/>
+      <c r="H43" s="131"/>
+      <c r="I43" s="131"/>
+      <c r="J43" s="132"/>
       <c r="K43" s="57">
         <v>3</v>
       </c>
       <c r="L43" s="52"/>
-      <c r="M43" s="142" t="s">
+      <c r="M43" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="N43" s="115"/>
-      <c r="O43" s="115"/>
-      <c r="P43" s="115"/>
-      <c r="Q43" s="115"/>
-      <c r="R43" s="115"/>
-      <c r="S43" s="115"/>
-      <c r="T43" s="115"/>
-      <c r="U43" s="126"/>
+      <c r="N43" s="131"/>
+      <c r="O43" s="131"/>
+      <c r="P43" s="131"/>
+      <c r="Q43" s="131"/>
+      <c r="R43" s="131"/>
+      <c r="S43" s="131"/>
+      <c r="T43" s="131"/>
+      <c r="U43" s="132"/>
       <c r="V43" s="57">
         <v>3</v>
       </c>
       <c r="W43" s="58"/>
-      <c r="X43" s="142" t="s">
+      <c r="X43" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="Y43" s="115"/>
-      <c r="Z43" s="115"/>
-      <c r="AA43" s="115"/>
-      <c r="AB43" s="115"/>
-      <c r="AC43" s="115"/>
-      <c r="AD43" s="115"/>
-      <c r="AE43" s="115"/>
-      <c r="AF43" s="126"/>
+      <c r="Y43" s="131"/>
+      <c r="Z43" s="131"/>
+      <c r="AA43" s="131"/>
+      <c r="AB43" s="131"/>
+      <c r="AC43" s="131"/>
+      <c r="AD43" s="131"/>
+      <c r="AE43" s="131"/>
+      <c r="AF43" s="132"/>
       <c r="AG43" s="57">
         <v>3</v>
       </c>
@@ -3413,46 +3424,46 @@
     <row r="44" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="55"/>
       <c r="B44" s="56"/>
-      <c r="C44" s="142" t="s">
+      <c r="C44" s="139" t="s">
         <v>46</v>
       </c>
-      <c r="D44" s="115"/>
-      <c r="E44" s="115"/>
-      <c r="F44" s="115"/>
-      <c r="G44" s="115"/>
-      <c r="H44" s="115"/>
-      <c r="I44" s="115"/>
-      <c r="J44" s="126"/>
+      <c r="D44" s="131"/>
+      <c r="E44" s="131"/>
+      <c r="F44" s="131"/>
+      <c r="G44" s="131"/>
+      <c r="H44" s="131"/>
+      <c r="I44" s="131"/>
+      <c r="J44" s="132"/>
       <c r="K44" s="57">
         <v>2</v>
       </c>
       <c r="L44" s="52"/>
-      <c r="M44" s="142" t="s">
+      <c r="M44" s="139" t="s">
         <v>46</v>
       </c>
-      <c r="N44" s="115"/>
-      <c r="O44" s="115"/>
-      <c r="P44" s="115"/>
-      <c r="Q44" s="115"/>
-      <c r="R44" s="115"/>
-      <c r="S44" s="115"/>
-      <c r="T44" s="115"/>
-      <c r="U44" s="126"/>
+      <c r="N44" s="131"/>
+      <c r="O44" s="131"/>
+      <c r="P44" s="131"/>
+      <c r="Q44" s="131"/>
+      <c r="R44" s="131"/>
+      <c r="S44" s="131"/>
+      <c r="T44" s="131"/>
+      <c r="U44" s="132"/>
       <c r="V44" s="57">
         <v>2</v>
       </c>
       <c r="W44" s="58"/>
-      <c r="X44" s="142" t="s">
+      <c r="X44" s="139" t="s">
         <v>46</v>
       </c>
-      <c r="Y44" s="115"/>
-      <c r="Z44" s="115"/>
-      <c r="AA44" s="115"/>
-      <c r="AB44" s="115"/>
-      <c r="AC44" s="115"/>
-      <c r="AD44" s="115"/>
-      <c r="AE44" s="115"/>
-      <c r="AF44" s="126"/>
+      <c r="Y44" s="131"/>
+      <c r="Z44" s="131"/>
+      <c r="AA44" s="131"/>
+      <c r="AB44" s="131"/>
+      <c r="AC44" s="131"/>
+      <c r="AD44" s="131"/>
+      <c r="AE44" s="131"/>
+      <c r="AF44" s="132"/>
       <c r="AG44" s="57">
         <v>2</v>
       </c>
@@ -3462,46 +3473,46 @@
     <row r="45" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="55"/>
       <c r="B45" s="56"/>
-      <c r="C45" s="142" t="s">
+      <c r="C45" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="D45" s="115"/>
-      <c r="E45" s="115"/>
-      <c r="F45" s="115"/>
-      <c r="G45" s="115"/>
-      <c r="H45" s="115"/>
-      <c r="I45" s="115"/>
-      <c r="J45" s="126"/>
+      <c r="D45" s="131"/>
+      <c r="E45" s="131"/>
+      <c r="F45" s="131"/>
+      <c r="G45" s="131"/>
+      <c r="H45" s="131"/>
+      <c r="I45" s="131"/>
+      <c r="J45" s="132"/>
       <c r="K45" s="57">
         <v>1</v>
       </c>
       <c r="L45" s="52"/>
-      <c r="M45" s="142" t="s">
+      <c r="M45" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="N45" s="115"/>
-      <c r="O45" s="115"/>
-      <c r="P45" s="115"/>
-      <c r="Q45" s="115"/>
-      <c r="R45" s="115"/>
-      <c r="S45" s="115"/>
-      <c r="T45" s="115"/>
-      <c r="U45" s="126"/>
+      <c r="N45" s="131"/>
+      <c r="O45" s="131"/>
+      <c r="P45" s="131"/>
+      <c r="Q45" s="131"/>
+      <c r="R45" s="131"/>
+      <c r="S45" s="131"/>
+      <c r="T45" s="131"/>
+      <c r="U45" s="132"/>
       <c r="V45" s="57">
         <v>1</v>
       </c>
       <c r="W45" s="58"/>
-      <c r="X45" s="142" t="s">
+      <c r="X45" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="Y45" s="115"/>
-      <c r="Z45" s="115"/>
-      <c r="AA45" s="115"/>
-      <c r="AB45" s="115"/>
-      <c r="AC45" s="115"/>
-      <c r="AD45" s="115"/>
-      <c r="AE45" s="115"/>
-      <c r="AF45" s="126"/>
+      <c r="Y45" s="131"/>
+      <c r="Z45" s="131"/>
+      <c r="AA45" s="131"/>
+      <c r="AB45" s="131"/>
+      <c r="AC45" s="131"/>
+      <c r="AD45" s="131"/>
+      <c r="AE45" s="131"/>
+      <c r="AF45" s="132"/>
       <c r="AG45" s="57">
         <v>1</v>
       </c>
@@ -3548,46 +3559,46 @@
     <row r="47" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="49"/>
       <c r="B47" s="50"/>
-      <c r="C47" s="139" t="s">
+      <c r="C47" s="142" t="s">
         <v>48</v>
       </c>
-      <c r="D47" s="115"/>
-      <c r="E47" s="115"/>
-      <c r="F47" s="115"/>
-      <c r="G47" s="115"/>
-      <c r="H47" s="115"/>
-      <c r="I47" s="115"/>
-      <c r="J47" s="126"/>
+      <c r="D47" s="131"/>
+      <c r="E47" s="131"/>
+      <c r="F47" s="131"/>
+      <c r="G47" s="131"/>
+      <c r="H47" s="131"/>
+      <c r="I47" s="131"/>
+      <c r="J47" s="132"/>
       <c r="K47" s="51" t="s">
         <v>42</v>
       </c>
       <c r="L47" s="52"/>
-      <c r="M47" s="139" t="s">
+      <c r="M47" s="142" t="s">
         <v>49</v>
       </c>
-      <c r="N47" s="115"/>
-      <c r="O47" s="115"/>
-      <c r="P47" s="115"/>
-      <c r="Q47" s="115"/>
-      <c r="R47" s="115"/>
-      <c r="S47" s="115"/>
-      <c r="T47" s="115"/>
-      <c r="U47" s="126"/>
+      <c r="N47" s="131"/>
+      <c r="O47" s="131"/>
+      <c r="P47" s="131"/>
+      <c r="Q47" s="131"/>
+      <c r="R47" s="131"/>
+      <c r="S47" s="131"/>
+      <c r="T47" s="131"/>
+      <c r="U47" s="132"/>
       <c r="V47" s="51" t="s">
         <v>42</v>
       </c>
       <c r="W47" s="62"/>
-      <c r="X47" s="139" t="s">
+      <c r="X47" s="142" t="s">
         <v>50</v>
       </c>
-      <c r="Y47" s="115"/>
-      <c r="Z47" s="115"/>
-      <c r="AA47" s="115"/>
-      <c r="AB47" s="115"/>
-      <c r="AC47" s="115"/>
-      <c r="AD47" s="115"/>
-      <c r="AE47" s="115"/>
-      <c r="AF47" s="126"/>
+      <c r="Y47" s="131"/>
+      <c r="Z47" s="131"/>
+      <c r="AA47" s="131"/>
+      <c r="AB47" s="131"/>
+      <c r="AC47" s="131"/>
+      <c r="AD47" s="131"/>
+      <c r="AE47" s="131"/>
+      <c r="AF47" s="132"/>
       <c r="AG47" s="51" t="s">
         <v>42</v>
       </c>
@@ -3597,46 +3608,46 @@
     <row r="48" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="55"/>
       <c r="B48" s="56"/>
-      <c r="C48" s="142" t="s">
+      <c r="C48" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="D48" s="115"/>
-      <c r="E48" s="115"/>
-      <c r="F48" s="115"/>
-      <c r="G48" s="115"/>
-      <c r="H48" s="115"/>
-      <c r="I48" s="115"/>
-      <c r="J48" s="126"/>
+      <c r="D48" s="131"/>
+      <c r="E48" s="131"/>
+      <c r="F48" s="131"/>
+      <c r="G48" s="131"/>
+      <c r="H48" s="131"/>
+      <c r="I48" s="131"/>
+      <c r="J48" s="132"/>
       <c r="K48" s="57">
         <v>3</v>
       </c>
       <c r="L48" s="52"/>
-      <c r="M48" s="142" t="s">
+      <c r="M48" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="N48" s="115"/>
-      <c r="O48" s="115"/>
-      <c r="P48" s="115"/>
-      <c r="Q48" s="115"/>
-      <c r="R48" s="115"/>
-      <c r="S48" s="115"/>
-      <c r="T48" s="115"/>
-      <c r="U48" s="126"/>
+      <c r="N48" s="131"/>
+      <c r="O48" s="131"/>
+      <c r="P48" s="131"/>
+      <c r="Q48" s="131"/>
+      <c r="R48" s="131"/>
+      <c r="S48" s="131"/>
+      <c r="T48" s="131"/>
+      <c r="U48" s="132"/>
       <c r="V48" s="57">
         <v>3</v>
       </c>
       <c r="W48" s="62"/>
-      <c r="X48" s="142" t="s">
+      <c r="X48" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="Y48" s="115"/>
-      <c r="Z48" s="115"/>
-      <c r="AA48" s="115"/>
-      <c r="AB48" s="115"/>
-      <c r="AC48" s="115"/>
-      <c r="AD48" s="115"/>
-      <c r="AE48" s="115"/>
-      <c r="AF48" s="126"/>
+      <c r="Y48" s="131"/>
+      <c r="Z48" s="131"/>
+      <c r="AA48" s="131"/>
+      <c r="AB48" s="131"/>
+      <c r="AC48" s="131"/>
+      <c r="AD48" s="131"/>
+      <c r="AE48" s="131"/>
+      <c r="AF48" s="132"/>
       <c r="AG48" s="57">
         <v>3</v>
       </c>
@@ -3646,46 +3657,46 @@
     <row r="49" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="55"/>
       <c r="B49" s="56"/>
-      <c r="C49" s="142" t="s">
+      <c r="C49" s="139" t="s">
         <v>51</v>
       </c>
-      <c r="D49" s="115"/>
-      <c r="E49" s="115"/>
-      <c r="F49" s="115"/>
-      <c r="G49" s="115"/>
-      <c r="H49" s="115"/>
-      <c r="I49" s="115"/>
-      <c r="J49" s="126"/>
+      <c r="D49" s="131"/>
+      <c r="E49" s="131"/>
+      <c r="F49" s="131"/>
+      <c r="G49" s="131"/>
+      <c r="H49" s="131"/>
+      <c r="I49" s="131"/>
+      <c r="J49" s="132"/>
       <c r="K49" s="57">
         <v>2</v>
       </c>
       <c r="L49" s="52"/>
-      <c r="M49" s="142" t="s">
+      <c r="M49" s="139" t="s">
         <v>46</v>
       </c>
-      <c r="N49" s="115"/>
-      <c r="O49" s="115"/>
-      <c r="P49" s="115"/>
-      <c r="Q49" s="115"/>
-      <c r="R49" s="115"/>
-      <c r="S49" s="115"/>
-      <c r="T49" s="115"/>
-      <c r="U49" s="126"/>
+      <c r="N49" s="131"/>
+      <c r="O49" s="131"/>
+      <c r="P49" s="131"/>
+      <c r="Q49" s="131"/>
+      <c r="R49" s="131"/>
+      <c r="S49" s="131"/>
+      <c r="T49" s="131"/>
+      <c r="U49" s="132"/>
       <c r="V49" s="57">
         <v>2</v>
       </c>
       <c r="W49" s="62"/>
-      <c r="X49" s="142" t="s">
+      <c r="X49" s="139" t="s">
         <v>46</v>
       </c>
-      <c r="Y49" s="115"/>
-      <c r="Z49" s="115"/>
-      <c r="AA49" s="115"/>
-      <c r="AB49" s="115"/>
-      <c r="AC49" s="115"/>
-      <c r="AD49" s="115"/>
-      <c r="AE49" s="115"/>
-      <c r="AF49" s="126"/>
+      <c r="Y49" s="131"/>
+      <c r="Z49" s="131"/>
+      <c r="AA49" s="131"/>
+      <c r="AB49" s="131"/>
+      <c r="AC49" s="131"/>
+      <c r="AD49" s="131"/>
+      <c r="AE49" s="131"/>
+      <c r="AF49" s="132"/>
       <c r="AG49" s="57">
         <v>2</v>
       </c>
@@ -3695,46 +3706,46 @@
     <row r="50" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="55"/>
       <c r="B50" s="56"/>
-      <c r="C50" s="142" t="s">
+      <c r="C50" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="D50" s="115"/>
-      <c r="E50" s="115"/>
-      <c r="F50" s="115"/>
-      <c r="G50" s="115"/>
-      <c r="H50" s="115"/>
-      <c r="I50" s="115"/>
-      <c r="J50" s="126"/>
+      <c r="D50" s="131"/>
+      <c r="E50" s="131"/>
+      <c r="F50" s="131"/>
+      <c r="G50" s="131"/>
+      <c r="H50" s="131"/>
+      <c r="I50" s="131"/>
+      <c r="J50" s="132"/>
       <c r="K50" s="57">
         <v>1</v>
       </c>
       <c r="L50" s="62"/>
-      <c r="M50" s="142" t="s">
+      <c r="M50" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="N50" s="115"/>
-      <c r="O50" s="115"/>
-      <c r="P50" s="115"/>
-      <c r="Q50" s="115"/>
-      <c r="R50" s="115"/>
-      <c r="S50" s="115"/>
-      <c r="T50" s="115"/>
-      <c r="U50" s="126"/>
+      <c r="N50" s="131"/>
+      <c r="O50" s="131"/>
+      <c r="P50" s="131"/>
+      <c r="Q50" s="131"/>
+      <c r="R50" s="131"/>
+      <c r="S50" s="131"/>
+      <c r="T50" s="131"/>
+      <c r="U50" s="132"/>
       <c r="V50" s="57">
         <v>1</v>
       </c>
       <c r="W50" s="62"/>
-      <c r="X50" s="142" t="s">
+      <c r="X50" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="Y50" s="115"/>
-      <c r="Z50" s="115"/>
-      <c r="AA50" s="115"/>
-      <c r="AB50" s="115"/>
-      <c r="AC50" s="115"/>
-      <c r="AD50" s="115"/>
-      <c r="AE50" s="115"/>
-      <c r="AF50" s="126"/>
+      <c r="Y50" s="131"/>
+      <c r="Z50" s="131"/>
+      <c r="AA50" s="131"/>
+      <c r="AB50" s="131"/>
+      <c r="AC50" s="131"/>
+      <c r="AD50" s="131"/>
+      <c r="AE50" s="131"/>
+      <c r="AF50" s="132"/>
       <c r="AG50" s="57">
         <v>1</v>
       </c>
@@ -3781,15 +3792,15 @@
     <row r="52" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="49"/>
       <c r="B52" s="50"/>
-      <c r="C52" s="149"/>
-      <c r="D52" s="150"/>
-      <c r="E52" s="150"/>
-      <c r="F52" s="150"/>
-      <c r="G52" s="150"/>
-      <c r="H52" s="150"/>
-      <c r="I52" s="150"/>
-      <c r="J52" s="150"/>
-      <c r="K52" s="150"/>
+      <c r="C52" s="138"/>
+      <c r="D52" s="114"/>
+      <c r="E52" s="114"/>
+      <c r="F52" s="114"/>
+      <c r="G52" s="114"/>
+      <c r="H52" s="114"/>
+      <c r="I52" s="114"/>
+      <c r="J52" s="114"/>
+      <c r="K52" s="114"/>
       <c r="L52" s="66"/>
       <c r="M52" s="67"/>
       <c r="N52" s="67"/>
@@ -3820,316 +3831,316 @@
     <row r="53" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="49"/>
       <c r="B53" s="50"/>
-      <c r="C53" s="143" t="s">
+      <c r="C53" s="140" t="s">
         <v>53</v>
       </c>
-      <c r="D53" s="144"/>
-      <c r="E53" s="143" t="s">
+      <c r="D53" s="121"/>
+      <c r="E53" s="140" t="s">
         <v>54</v>
       </c>
-      <c r="F53" s="99"/>
-      <c r="G53" s="99"/>
-      <c r="H53" s="99"/>
-      <c r="I53" s="99"/>
-      <c r="J53" s="99"/>
-      <c r="K53" s="144"/>
-      <c r="L53" s="143" t="s">
+      <c r="F53" s="125"/>
+      <c r="G53" s="125"/>
+      <c r="H53" s="125"/>
+      <c r="I53" s="125"/>
+      <c r="J53" s="125"/>
+      <c r="K53" s="121"/>
+      <c r="L53" s="140" t="s">
         <v>55</v>
       </c>
-      <c r="M53" s="99"/>
-      <c r="N53" s="99"/>
-      <c r="O53" s="99"/>
-      <c r="P53" s="99"/>
-      <c r="Q53" s="99"/>
-      <c r="R53" s="99"/>
-      <c r="S53" s="99"/>
-      <c r="T53" s="99"/>
-      <c r="U53" s="99"/>
-      <c r="V53" s="99"/>
-      <c r="W53" s="99"/>
-      <c r="X53" s="99"/>
-      <c r="Y53" s="99"/>
-      <c r="Z53" s="99"/>
-      <c r="AA53" s="99"/>
-      <c r="AB53" s="99"/>
-      <c r="AC53" s="99"/>
-      <c r="AD53" s="99"/>
-      <c r="AE53" s="99"/>
-      <c r="AF53" s="99"/>
-      <c r="AG53" s="144"/>
+      <c r="M53" s="125"/>
+      <c r="N53" s="125"/>
+      <c r="O53" s="125"/>
+      <c r="P53" s="125"/>
+      <c r="Q53" s="125"/>
+      <c r="R53" s="125"/>
+      <c r="S53" s="125"/>
+      <c r="T53" s="125"/>
+      <c r="U53" s="125"/>
+      <c r="V53" s="125"/>
+      <c r="W53" s="125"/>
+      <c r="X53" s="125"/>
+      <c r="Y53" s="125"/>
+      <c r="Z53" s="125"/>
+      <c r="AA53" s="125"/>
+      <c r="AB53" s="125"/>
+      <c r="AC53" s="125"/>
+      <c r="AD53" s="125"/>
+      <c r="AE53" s="125"/>
+      <c r="AF53" s="125"/>
+      <c r="AG53" s="121"/>
       <c r="AH53" s="69"/>
       <c r="AI53" s="12"/>
     </row>
     <row r="54" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="55"/>
       <c r="B54" s="56"/>
-      <c r="C54" s="102"/>
-      <c r="D54" s="145"/>
-      <c r="E54" s="102"/>
-      <c r="F54" s="103"/>
-      <c r="G54" s="103"/>
-      <c r="H54" s="103"/>
-      <c r="I54" s="103"/>
-      <c r="J54" s="103"/>
-      <c r="K54" s="145"/>
-      <c r="L54" s="102"/>
-      <c r="M54" s="103"/>
-      <c r="N54" s="103"/>
-      <c r="O54" s="103"/>
-      <c r="P54" s="103"/>
-      <c r="Q54" s="103"/>
-      <c r="R54" s="103"/>
-      <c r="S54" s="103"/>
-      <c r="T54" s="103"/>
-      <c r="U54" s="103"/>
-      <c r="V54" s="103"/>
-      <c r="W54" s="103"/>
-      <c r="X54" s="103"/>
-      <c r="Y54" s="103"/>
-      <c r="Z54" s="103"/>
-      <c r="AA54" s="103"/>
-      <c r="AB54" s="103"/>
-      <c r="AC54" s="103"/>
-      <c r="AD54" s="103"/>
-      <c r="AE54" s="103"/>
-      <c r="AF54" s="103"/>
-      <c r="AG54" s="145"/>
+      <c r="C54" s="122"/>
+      <c r="D54" s="123"/>
+      <c r="E54" s="122"/>
+      <c r="F54" s="126"/>
+      <c r="G54" s="126"/>
+      <c r="H54" s="126"/>
+      <c r="I54" s="126"/>
+      <c r="J54" s="126"/>
+      <c r="K54" s="123"/>
+      <c r="L54" s="122"/>
+      <c r="M54" s="126"/>
+      <c r="N54" s="126"/>
+      <c r="O54" s="126"/>
+      <c r="P54" s="126"/>
+      <c r="Q54" s="126"/>
+      <c r="R54" s="126"/>
+      <c r="S54" s="126"/>
+      <c r="T54" s="126"/>
+      <c r="U54" s="126"/>
+      <c r="V54" s="126"/>
+      <c r="W54" s="126"/>
+      <c r="X54" s="126"/>
+      <c r="Y54" s="126"/>
+      <c r="Z54" s="126"/>
+      <c r="AA54" s="126"/>
+      <c r="AB54" s="126"/>
+      <c r="AC54" s="126"/>
+      <c r="AD54" s="126"/>
+      <c r="AE54" s="126"/>
+      <c r="AF54" s="126"/>
+      <c r="AG54" s="123"/>
       <c r="AH54" s="70"/>
       <c r="AI54" s="25"/>
     </row>
     <row r="55" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="55"/>
       <c r="B55" s="56"/>
-      <c r="C55" s="146"/>
-      <c r="D55" s="144"/>
-      <c r="E55" s="147" t="s">
+      <c r="C55" s="141"/>
+      <c r="D55" s="121"/>
+      <c r="E55" s="124" t="s">
         <v>56</v>
       </c>
-      <c r="F55" s="99"/>
-      <c r="G55" s="99"/>
-      <c r="H55" s="99"/>
-      <c r="I55" s="99"/>
-      <c r="J55" s="99"/>
-      <c r="K55" s="144"/>
-      <c r="L55" s="148" t="s">
+      <c r="F55" s="125"/>
+      <c r="G55" s="125"/>
+      <c r="H55" s="125"/>
+      <c r="I55" s="125"/>
+      <c r="J55" s="125"/>
+      <c r="K55" s="121"/>
+      <c r="L55" s="127" t="s">
         <v>57</v>
       </c>
-      <c r="M55" s="99"/>
-      <c r="N55" s="99"/>
-      <c r="O55" s="99"/>
-      <c r="P55" s="99"/>
-      <c r="Q55" s="99"/>
-      <c r="R55" s="99"/>
-      <c r="S55" s="99"/>
-      <c r="T55" s="99"/>
-      <c r="U55" s="99"/>
-      <c r="V55" s="99"/>
-      <c r="W55" s="99"/>
-      <c r="X55" s="99"/>
-      <c r="Y55" s="99"/>
-      <c r="Z55" s="99"/>
-      <c r="AA55" s="99"/>
-      <c r="AB55" s="99"/>
-      <c r="AC55" s="99"/>
-      <c r="AD55" s="99"/>
-      <c r="AE55" s="99"/>
-      <c r="AF55" s="99"/>
-      <c r="AG55" s="144"/>
+      <c r="M55" s="125"/>
+      <c r="N55" s="125"/>
+      <c r="O55" s="125"/>
+      <c r="P55" s="125"/>
+      <c r="Q55" s="125"/>
+      <c r="R55" s="125"/>
+      <c r="S55" s="125"/>
+      <c r="T55" s="125"/>
+      <c r="U55" s="125"/>
+      <c r="V55" s="125"/>
+      <c r="W55" s="125"/>
+      <c r="X55" s="125"/>
+      <c r="Y55" s="125"/>
+      <c r="Z55" s="125"/>
+      <c r="AA55" s="125"/>
+      <c r="AB55" s="125"/>
+      <c r="AC55" s="125"/>
+      <c r="AD55" s="125"/>
+      <c r="AE55" s="125"/>
+      <c r="AF55" s="125"/>
+      <c r="AG55" s="121"/>
       <c r="AH55" s="70"/>
       <c r="AI55" s="25"/>
     </row>
     <row r="56" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="55"/>
       <c r="B56" s="56"/>
-      <c r="C56" s="102"/>
-      <c r="D56" s="145"/>
-      <c r="E56" s="102"/>
-      <c r="F56" s="103"/>
-      <c r="G56" s="103"/>
-      <c r="H56" s="103"/>
-      <c r="I56" s="103"/>
-      <c r="J56" s="103"/>
-      <c r="K56" s="145"/>
-      <c r="L56" s="102"/>
-      <c r="M56" s="103"/>
-      <c r="N56" s="103"/>
-      <c r="O56" s="103"/>
-      <c r="P56" s="103"/>
-      <c r="Q56" s="103"/>
-      <c r="R56" s="103"/>
-      <c r="S56" s="103"/>
-      <c r="T56" s="103"/>
-      <c r="U56" s="103"/>
-      <c r="V56" s="103"/>
-      <c r="W56" s="103"/>
-      <c r="X56" s="103"/>
-      <c r="Y56" s="103"/>
-      <c r="Z56" s="103"/>
-      <c r="AA56" s="103"/>
-      <c r="AB56" s="103"/>
-      <c r="AC56" s="103"/>
-      <c r="AD56" s="103"/>
-      <c r="AE56" s="103"/>
-      <c r="AF56" s="103"/>
-      <c r="AG56" s="145"/>
+      <c r="C56" s="122"/>
+      <c r="D56" s="123"/>
+      <c r="E56" s="122"/>
+      <c r="F56" s="126"/>
+      <c r="G56" s="126"/>
+      <c r="H56" s="126"/>
+      <c r="I56" s="126"/>
+      <c r="J56" s="126"/>
+      <c r="K56" s="123"/>
+      <c r="L56" s="122"/>
+      <c r="M56" s="126"/>
+      <c r="N56" s="126"/>
+      <c r="O56" s="126"/>
+      <c r="P56" s="126"/>
+      <c r="Q56" s="126"/>
+      <c r="R56" s="126"/>
+      <c r="S56" s="126"/>
+      <c r="T56" s="126"/>
+      <c r="U56" s="126"/>
+      <c r="V56" s="126"/>
+      <c r="W56" s="126"/>
+      <c r="X56" s="126"/>
+      <c r="Y56" s="126"/>
+      <c r="Z56" s="126"/>
+      <c r="AA56" s="126"/>
+      <c r="AB56" s="126"/>
+      <c r="AC56" s="126"/>
+      <c r="AD56" s="126"/>
+      <c r="AE56" s="126"/>
+      <c r="AF56" s="126"/>
+      <c r="AG56" s="123"/>
       <c r="AH56" s="71"/>
       <c r="AI56" s="72"/>
     </row>
     <row r="57" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="26"/>
       <c r="B57" s="73"/>
-      <c r="C57" s="98" t="s">
+      <c r="C57" s="120" t="s">
         <v>58</v>
       </c>
-      <c r="D57" s="144"/>
-      <c r="E57" s="147" t="s">
+      <c r="D57" s="121"/>
+      <c r="E57" s="124" t="s">
         <v>59</v>
       </c>
-      <c r="F57" s="99"/>
-      <c r="G57" s="99"/>
-      <c r="H57" s="99"/>
-      <c r="I57" s="99"/>
-      <c r="J57" s="99"/>
-      <c r="K57" s="144"/>
-      <c r="L57" s="148" t="s">
+      <c r="F57" s="125"/>
+      <c r="G57" s="125"/>
+      <c r="H57" s="125"/>
+      <c r="I57" s="125"/>
+      <c r="J57" s="125"/>
+      <c r="K57" s="121"/>
+      <c r="L57" s="127" t="s">
         <v>60</v>
       </c>
-      <c r="M57" s="99"/>
-      <c r="N57" s="99"/>
-      <c r="O57" s="99"/>
-      <c r="P57" s="99"/>
-      <c r="Q57" s="99"/>
-      <c r="R57" s="99"/>
-      <c r="S57" s="99"/>
-      <c r="T57" s="99"/>
-      <c r="U57" s="99"/>
-      <c r="V57" s="99"/>
-      <c r="W57" s="99"/>
-      <c r="X57" s="99"/>
-      <c r="Y57" s="99"/>
-      <c r="Z57" s="99"/>
-      <c r="AA57" s="99"/>
-      <c r="AB57" s="99"/>
-      <c r="AC57" s="99"/>
-      <c r="AD57" s="99"/>
-      <c r="AE57" s="99"/>
-      <c r="AF57" s="99"/>
-      <c r="AG57" s="144"/>
+      <c r="M57" s="125"/>
+      <c r="N57" s="125"/>
+      <c r="O57" s="125"/>
+      <c r="P57" s="125"/>
+      <c r="Q57" s="125"/>
+      <c r="R57" s="125"/>
+      <c r="S57" s="125"/>
+      <c r="T57" s="125"/>
+      <c r="U57" s="125"/>
+      <c r="V57" s="125"/>
+      <c r="W57" s="125"/>
+      <c r="X57" s="125"/>
+      <c r="Y57" s="125"/>
+      <c r="Z57" s="125"/>
+      <c r="AA57" s="125"/>
+      <c r="AB57" s="125"/>
+      <c r="AC57" s="125"/>
+      <c r="AD57" s="125"/>
+      <c r="AE57" s="125"/>
+      <c r="AF57" s="125"/>
+      <c r="AG57" s="121"/>
       <c r="AH57" s="71"/>
       <c r="AI57" s="72"/>
     </row>
     <row r="58" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="26"/>
       <c r="B58" s="73"/>
-      <c r="C58" s="102"/>
-      <c r="D58" s="145"/>
-      <c r="E58" s="102"/>
-      <c r="F58" s="103"/>
-      <c r="G58" s="103"/>
-      <c r="H58" s="103"/>
-      <c r="I58" s="103"/>
-      <c r="J58" s="103"/>
-      <c r="K58" s="145"/>
-      <c r="L58" s="102"/>
-      <c r="M58" s="103"/>
-      <c r="N58" s="103"/>
-      <c r="O58" s="103"/>
-      <c r="P58" s="103"/>
-      <c r="Q58" s="103"/>
-      <c r="R58" s="103"/>
-      <c r="S58" s="103"/>
-      <c r="T58" s="103"/>
-      <c r="U58" s="103"/>
-      <c r="V58" s="103"/>
-      <c r="W58" s="103"/>
-      <c r="X58" s="103"/>
-      <c r="Y58" s="103"/>
-      <c r="Z58" s="103"/>
-      <c r="AA58" s="103"/>
-      <c r="AB58" s="103"/>
-      <c r="AC58" s="103"/>
-      <c r="AD58" s="103"/>
-      <c r="AE58" s="103"/>
-      <c r="AF58" s="103"/>
-      <c r="AG58" s="145"/>
+      <c r="C58" s="122"/>
+      <c r="D58" s="123"/>
+      <c r="E58" s="122"/>
+      <c r="F58" s="126"/>
+      <c r="G58" s="126"/>
+      <c r="H58" s="126"/>
+      <c r="I58" s="126"/>
+      <c r="J58" s="126"/>
+      <c r="K58" s="123"/>
+      <c r="L58" s="122"/>
+      <c r="M58" s="126"/>
+      <c r="N58" s="126"/>
+      <c r="O58" s="126"/>
+      <c r="P58" s="126"/>
+      <c r="Q58" s="126"/>
+      <c r="R58" s="126"/>
+      <c r="S58" s="126"/>
+      <c r="T58" s="126"/>
+      <c r="U58" s="126"/>
+      <c r="V58" s="126"/>
+      <c r="W58" s="126"/>
+      <c r="X58" s="126"/>
+      <c r="Y58" s="126"/>
+      <c r="Z58" s="126"/>
+      <c r="AA58" s="126"/>
+      <c r="AB58" s="126"/>
+      <c r="AC58" s="126"/>
+      <c r="AD58" s="126"/>
+      <c r="AE58" s="126"/>
+      <c r="AF58" s="126"/>
+      <c r="AG58" s="123"/>
       <c r="AH58" s="70"/>
       <c r="AI58" s="25"/>
     </row>
     <row r="59" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="26"/>
       <c r="B59" s="73"/>
-      <c r="C59" s="98"/>
-      <c r="D59" s="144"/>
-      <c r="E59" s="147" t="s">
+      <c r="C59" s="120"/>
+      <c r="D59" s="121"/>
+      <c r="E59" s="124" t="s">
         <v>61</v>
       </c>
-      <c r="F59" s="99"/>
-      <c r="G59" s="99"/>
-      <c r="H59" s="99"/>
-      <c r="I59" s="99"/>
-      <c r="J59" s="99"/>
-      <c r="K59" s="144"/>
-      <c r="L59" s="148" t="s">
+      <c r="F59" s="125"/>
+      <c r="G59" s="125"/>
+      <c r="H59" s="125"/>
+      <c r="I59" s="125"/>
+      <c r="J59" s="125"/>
+      <c r="K59" s="121"/>
+      <c r="L59" s="127" t="s">
         <v>62</v>
       </c>
-      <c r="M59" s="99"/>
-      <c r="N59" s="99"/>
-      <c r="O59" s="99"/>
-      <c r="P59" s="99"/>
-      <c r="Q59" s="99"/>
-      <c r="R59" s="99"/>
-      <c r="S59" s="99"/>
-      <c r="T59" s="99"/>
-      <c r="U59" s="99"/>
-      <c r="V59" s="99"/>
-      <c r="W59" s="99"/>
-      <c r="X59" s="99"/>
-      <c r="Y59" s="99"/>
-      <c r="Z59" s="99"/>
-      <c r="AA59" s="99"/>
-      <c r="AB59" s="99"/>
-      <c r="AC59" s="99"/>
-      <c r="AD59" s="99"/>
-      <c r="AE59" s="99"/>
-      <c r="AF59" s="99"/>
-      <c r="AG59" s="144"/>
+      <c r="M59" s="125"/>
+      <c r="N59" s="125"/>
+      <c r="O59" s="125"/>
+      <c r="P59" s="125"/>
+      <c r="Q59" s="125"/>
+      <c r="R59" s="125"/>
+      <c r="S59" s="125"/>
+      <c r="T59" s="125"/>
+      <c r="U59" s="125"/>
+      <c r="V59" s="125"/>
+      <c r="W59" s="125"/>
+      <c r="X59" s="125"/>
+      <c r="Y59" s="125"/>
+      <c r="Z59" s="125"/>
+      <c r="AA59" s="125"/>
+      <c r="AB59" s="125"/>
+      <c r="AC59" s="125"/>
+      <c r="AD59" s="125"/>
+      <c r="AE59" s="125"/>
+      <c r="AF59" s="125"/>
+      <c r="AG59" s="121"/>
       <c r="AH59" s="70"/>
       <c r="AI59" s="25"/>
     </row>
     <row r="60" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="26"/>
       <c r="B60" s="73"/>
-      <c r="C60" s="102"/>
-      <c r="D60" s="145"/>
-      <c r="E60" s="102"/>
-      <c r="F60" s="103"/>
-      <c r="G60" s="103"/>
-      <c r="H60" s="103"/>
-      <c r="I60" s="103"/>
-      <c r="J60" s="103"/>
-      <c r="K60" s="145"/>
-      <c r="L60" s="102"/>
-      <c r="M60" s="103"/>
-      <c r="N60" s="103"/>
-      <c r="O60" s="103"/>
-      <c r="P60" s="103"/>
-      <c r="Q60" s="103"/>
-      <c r="R60" s="103"/>
-      <c r="S60" s="103"/>
-      <c r="T60" s="103"/>
-      <c r="U60" s="103"/>
-      <c r="V60" s="103"/>
-      <c r="W60" s="103"/>
-      <c r="X60" s="103"/>
-      <c r="Y60" s="103"/>
-      <c r="Z60" s="103"/>
-      <c r="AA60" s="103"/>
-      <c r="AB60" s="103"/>
-      <c r="AC60" s="103"/>
-      <c r="AD60" s="103"/>
-      <c r="AE60" s="103"/>
-      <c r="AF60" s="103"/>
-      <c r="AG60" s="145"/>
+      <c r="C60" s="122"/>
+      <c r="D60" s="123"/>
+      <c r="E60" s="122"/>
+      <c r="F60" s="126"/>
+      <c r="G60" s="126"/>
+      <c r="H60" s="126"/>
+      <c r="I60" s="126"/>
+      <c r="J60" s="126"/>
+      <c r="K60" s="123"/>
+      <c r="L60" s="122"/>
+      <c r="M60" s="126"/>
+      <c r="N60" s="126"/>
+      <c r="O60" s="126"/>
+      <c r="P60" s="126"/>
+      <c r="Q60" s="126"/>
+      <c r="R60" s="126"/>
+      <c r="S60" s="126"/>
+      <c r="T60" s="126"/>
+      <c r="U60" s="126"/>
+      <c r="V60" s="126"/>
+      <c r="W60" s="126"/>
+      <c r="X60" s="126"/>
+      <c r="Y60" s="126"/>
+      <c r="Z60" s="126"/>
+      <c r="AA60" s="126"/>
+      <c r="AB60" s="126"/>
+      <c r="AC60" s="126"/>
+      <c r="AD60" s="126"/>
+      <c r="AE60" s="126"/>
+      <c r="AF60" s="126"/>
+      <c r="AG60" s="123"/>
       <c r="AH60" s="74"/>
       <c r="AI60" s="5"/>
     </row>
@@ -4150,9 +4161,9 @@
       <c r="N61" s="77"/>
       <c r="O61" s="77"/>
       <c r="P61" s="77"/>
-      <c r="Q61" s="170"/>
-      <c r="R61" s="171"/>
-      <c r="S61" s="171"/>
+      <c r="Q61" s="128"/>
+      <c r="R61" s="129"/>
+      <c r="S61" s="129"/>
       <c r="T61" s="78"/>
       <c r="U61" s="6"/>
       <c r="V61" s="6"/>
@@ -4283,41 +4294,41 @@
     </row>
     <row r="65" spans="1:35" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7"/>
-      <c r="B65" s="120" t="s">
+      <c r="B65" s="107" t="s">
         <v>63</v>
       </c>
-      <c r="C65" s="121"/>
-      <c r="D65" s="121"/>
-      <c r="E65" s="121"/>
-      <c r="F65" s="121"/>
-      <c r="G65" s="121"/>
-      <c r="H65" s="121"/>
-      <c r="I65" s="121"/>
-      <c r="J65" s="121"/>
-      <c r="K65" s="121"/>
-      <c r="L65" s="121"/>
-      <c r="M65" s="121"/>
-      <c r="N65" s="121"/>
-      <c r="O65" s="121"/>
-      <c r="P65" s="121"/>
-      <c r="Q65" s="121"/>
-      <c r="R65" s="121"/>
-      <c r="S65" s="121"/>
-      <c r="T65" s="121"/>
-      <c r="U65" s="121"/>
-      <c r="V65" s="121"/>
-      <c r="W65" s="121"/>
-      <c r="X65" s="121"/>
-      <c r="Y65" s="121"/>
-      <c r="Z65" s="121"/>
-      <c r="AA65" s="121"/>
-      <c r="AB65" s="121"/>
-      <c r="AC65" s="121"/>
-      <c r="AD65" s="121"/>
-      <c r="AE65" s="121"/>
-      <c r="AF65" s="121"/>
-      <c r="AG65" s="121"/>
-      <c r="AH65" s="122"/>
+      <c r="C65" s="108"/>
+      <c r="D65" s="108"/>
+      <c r="E65" s="108"/>
+      <c r="F65" s="108"/>
+      <c r="G65" s="108"/>
+      <c r="H65" s="108"/>
+      <c r="I65" s="108"/>
+      <c r="J65" s="108"/>
+      <c r="K65" s="108"/>
+      <c r="L65" s="108"/>
+      <c r="M65" s="108"/>
+      <c r="N65" s="108"/>
+      <c r="O65" s="108"/>
+      <c r="P65" s="108"/>
+      <c r="Q65" s="108"/>
+      <c r="R65" s="108"/>
+      <c r="S65" s="108"/>
+      <c r="T65" s="108"/>
+      <c r="U65" s="108"/>
+      <c r="V65" s="108"/>
+      <c r="W65" s="108"/>
+      <c r="X65" s="108"/>
+      <c r="Y65" s="108"/>
+      <c r="Z65" s="108"/>
+      <c r="AA65" s="108"/>
+      <c r="AB65" s="108"/>
+      <c r="AC65" s="108"/>
+      <c r="AD65" s="108"/>
+      <c r="AE65" s="108"/>
+      <c r="AF65" s="108"/>
+      <c r="AG65" s="108"/>
+      <c r="AH65" s="109"/>
       <c r="AI65" s="49"/>
     </row>
     <row r="66" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4374,22 +4385,22 @@
       <c r="N67" s="92"/>
       <c r="O67" s="92"/>
       <c r="P67" s="93"/>
-      <c r="Q67" s="159"/>
-      <c r="R67" s="160"/>
-      <c r="S67" s="160"/>
-      <c r="T67" s="160"/>
-      <c r="U67" s="161"/>
-      <c r="V67" s="160"/>
-      <c r="W67" s="160"/>
-      <c r="X67" s="160"/>
-      <c r="Y67" s="160"/>
-      <c r="Z67" s="160"/>
-      <c r="AA67" s="160"/>
-      <c r="AB67" s="160"/>
-      <c r="AC67" s="160"/>
-      <c r="AD67" s="160"/>
-      <c r="AE67" s="160"/>
-      <c r="AF67" s="160"/>
+      <c r="Q67" s="110"/>
+      <c r="R67" s="111"/>
+      <c r="S67" s="111"/>
+      <c r="T67" s="111"/>
+      <c r="U67" s="112"/>
+      <c r="V67" s="111"/>
+      <c r="W67" s="111"/>
+      <c r="X67" s="111"/>
+      <c r="Y67" s="111"/>
+      <c r="Z67" s="111"/>
+      <c r="AA67" s="111"/>
+      <c r="AB67" s="111"/>
+      <c r="AC67" s="111"/>
+      <c r="AD67" s="111"/>
+      <c r="AE67" s="111"/>
+      <c r="AF67" s="111"/>
       <c r="AG67" s="82"/>
       <c r="AH67" s="63"/>
       <c r="AI67" s="64"/>
@@ -4411,22 +4422,22 @@
       <c r="N68" s="90"/>
       <c r="O68" s="90"/>
       <c r="P68" s="95"/>
-      <c r="Q68" s="162"/>
-      <c r="R68" s="150"/>
-      <c r="S68" s="150"/>
-      <c r="T68" s="150"/>
-      <c r="U68" s="163"/>
-      <c r="V68" s="150"/>
-      <c r="W68" s="150"/>
-      <c r="X68" s="150"/>
-      <c r="Y68" s="150"/>
-      <c r="Z68" s="150"/>
-      <c r="AA68" s="150"/>
-      <c r="AB68" s="150"/>
-      <c r="AC68" s="150"/>
-      <c r="AD68" s="150"/>
-      <c r="AE68" s="150"/>
-      <c r="AF68" s="150"/>
+      <c r="Q68" s="113"/>
+      <c r="R68" s="114"/>
+      <c r="S68" s="114"/>
+      <c r="T68" s="114"/>
+      <c r="U68" s="115"/>
+      <c r="V68" s="114"/>
+      <c r="W68" s="114"/>
+      <c r="X68" s="114"/>
+      <c r="Y68" s="114"/>
+      <c r="Z68" s="114"/>
+      <c r="AA68" s="114"/>
+      <c r="AB68" s="114"/>
+      <c r="AC68" s="114"/>
+      <c r="AD68" s="114"/>
+      <c r="AE68" s="114"/>
+      <c r="AF68" s="114"/>
       <c r="AG68" s="63"/>
       <c r="AH68" s="63"/>
       <c r="AI68" s="64"/>
@@ -4435,35 +4446,35 @@
       <c r="A69" s="64"/>
       <c r="B69" s="50"/>
       <c r="C69" s="94"/>
-      <c r="D69" s="169"/>
-      <c r="E69" s="169"/>
-      <c r="F69" s="169"/>
-      <c r="G69" s="169"/>
-      <c r="H69" s="169"/>
-      <c r="I69" s="169"/>
-      <c r="J69" s="169"/>
-      <c r="K69" s="169"/>
-      <c r="L69" s="169"/>
-      <c r="M69" s="169"/>
+      <c r="D69" s="119"/>
+      <c r="E69" s="119"/>
+      <c r="F69" s="119"/>
+      <c r="G69" s="119"/>
+      <c r="H69" s="119"/>
+      <c r="I69" s="119"/>
+      <c r="J69" s="119"/>
+      <c r="K69" s="119"/>
+      <c r="L69" s="119"/>
+      <c r="M69" s="119"/>
       <c r="N69" s="90"/>
       <c r="O69" s="90"/>
       <c r="P69" s="95"/>
-      <c r="Q69" s="162"/>
-      <c r="R69" s="150"/>
-      <c r="S69" s="150"/>
-      <c r="T69" s="150"/>
-      <c r="U69" s="164"/>
-      <c r="V69" s="165"/>
-      <c r="W69" s="165"/>
-      <c r="X69" s="165"/>
-      <c r="Y69" s="165"/>
-      <c r="Z69" s="165"/>
-      <c r="AA69" s="165"/>
-      <c r="AB69" s="165"/>
-      <c r="AC69" s="165"/>
-      <c r="AD69" s="165"/>
-      <c r="AE69" s="165"/>
-      <c r="AF69" s="165"/>
+      <c r="Q69" s="113"/>
+      <c r="R69" s="114"/>
+      <c r="S69" s="114"/>
+      <c r="T69" s="114"/>
+      <c r="U69" s="172"/>
+      <c r="V69" s="173"/>
+      <c r="W69" s="173"/>
+      <c r="X69" s="173"/>
+      <c r="Y69" s="173"/>
+      <c r="Z69" s="173"/>
+      <c r="AA69" s="173"/>
+      <c r="AB69" s="173"/>
+      <c r="AC69" s="173"/>
+      <c r="AD69" s="173"/>
+      <c r="AE69" s="173"/>
+      <c r="AF69" s="173"/>
       <c r="AG69" s="63"/>
       <c r="AH69" s="63"/>
       <c r="AI69" s="64"/>
@@ -4472,40 +4483,40 @@
       <c r="A70" s="64"/>
       <c r="B70" s="83"/>
       <c r="C70" s="84"/>
-      <c r="D70" s="158" t="s">
+      <c r="D70" s="105" t="s">
         <v>64</v>
       </c>
-      <c r="E70" s="118"/>
-      <c r="F70" s="118"/>
-      <c r="G70" s="118"/>
-      <c r="H70" s="118"/>
-      <c r="I70" s="118"/>
-      <c r="J70" s="118"/>
-      <c r="K70" s="118"/>
-      <c r="L70" s="118"/>
-      <c r="M70" s="118"/>
-      <c r="N70" s="118"/>
+      <c r="E70" s="106"/>
+      <c r="F70" s="106"/>
+      <c r="G70" s="106"/>
+      <c r="H70" s="106"/>
+      <c r="I70" s="106"/>
+      <c r="J70" s="106"/>
+      <c r="K70" s="106"/>
+      <c r="L70" s="106"/>
+      <c r="M70" s="106"/>
+      <c r="N70" s="106"/>
       <c r="O70" s="85"/>
       <c r="P70" s="86"/>
-      <c r="Q70" s="166" t="s">
+      <c r="Q70" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="R70" s="167"/>
-      <c r="S70" s="167"/>
-      <c r="T70" s="167"/>
-      <c r="U70" s="167"/>
-      <c r="V70" s="167"/>
-      <c r="W70" s="167"/>
-      <c r="X70" s="167"/>
-      <c r="Y70" s="167"/>
-      <c r="Z70" s="167"/>
-      <c r="AA70" s="167"/>
-      <c r="AB70" s="167"/>
-      <c r="AC70" s="167"/>
-      <c r="AD70" s="167"/>
-      <c r="AE70" s="167"/>
-      <c r="AF70" s="167"/>
-      <c r="AG70" s="168"/>
+      <c r="R70" s="117"/>
+      <c r="S70" s="117"/>
+      <c r="T70" s="117"/>
+      <c r="U70" s="117"/>
+      <c r="V70" s="117"/>
+      <c r="W70" s="117"/>
+      <c r="X70" s="117"/>
+      <c r="Y70" s="117"/>
+      <c r="Z70" s="117"/>
+      <c r="AA70" s="117"/>
+      <c r="AB70" s="117"/>
+      <c r="AC70" s="117"/>
+      <c r="AD70" s="117"/>
+      <c r="AE70" s="117"/>
+      <c r="AF70" s="117"/>
+      <c r="AG70" s="118"/>
       <c r="AH70" s="63"/>
       <c r="AI70" s="64"/>
     </row>
@@ -5513,6 +5524,122 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="140">
+    <mergeCell ref="B2:F5"/>
+    <mergeCell ref="G2:Y4"/>
+    <mergeCell ref="Z2:AH2"/>
+    <mergeCell ref="Z3:AH3"/>
+    <mergeCell ref="Z4:AH4"/>
+    <mergeCell ref="G5:AH5"/>
+    <mergeCell ref="B9:AH9"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="W27:AG27"/>
+    <mergeCell ref="W22:AG22"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="G23:K23"/>
+    <mergeCell ref="L23:P23"/>
+    <mergeCell ref="Q23:V23"/>
+    <mergeCell ref="W23:AG23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="Q22:V22"/>
+    <mergeCell ref="G24:K24"/>
+    <mergeCell ref="L24:P24"/>
+    <mergeCell ref="Q24:V24"/>
+    <mergeCell ref="W24:AG24"/>
+    <mergeCell ref="W25:AG25"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="R16:X16"/>
+    <mergeCell ref="Y16:AG16"/>
+    <mergeCell ref="Q20:V20"/>
+    <mergeCell ref="W20:AG20"/>
+    <mergeCell ref="W21:AG21"/>
+    <mergeCell ref="B17:AH17"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="G19:K19"/>
+    <mergeCell ref="L19:P19"/>
+    <mergeCell ref="Q19:V19"/>
+    <mergeCell ref="W19:AG19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="G20:K20"/>
+    <mergeCell ref="L20:P20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="G21:K21"/>
+    <mergeCell ref="L21:P21"/>
+    <mergeCell ref="Q21:V21"/>
+    <mergeCell ref="M34:T34"/>
+    <mergeCell ref="G26:K26"/>
+    <mergeCell ref="G27:K27"/>
+    <mergeCell ref="C32:J33"/>
+    <mergeCell ref="K32:K33"/>
+    <mergeCell ref="L32:L33"/>
+    <mergeCell ref="U32:U33"/>
+    <mergeCell ref="C34:J34"/>
+    <mergeCell ref="C26:F27"/>
+    <mergeCell ref="L27:P27"/>
+    <mergeCell ref="Q27:V27"/>
+    <mergeCell ref="R28:X28"/>
+    <mergeCell ref="W26:AG26"/>
+    <mergeCell ref="V32:V33"/>
+    <mergeCell ref="W32:AE33"/>
+    <mergeCell ref="AF32:AF33"/>
+    <mergeCell ref="AG32:AG33"/>
+    <mergeCell ref="W34:AE34"/>
+    <mergeCell ref="M32:T33"/>
+    <mergeCell ref="W36:AE36"/>
+    <mergeCell ref="W37:AE37"/>
+    <mergeCell ref="C35:J35"/>
+    <mergeCell ref="M35:T35"/>
+    <mergeCell ref="W35:AE35"/>
+    <mergeCell ref="C36:J36"/>
+    <mergeCell ref="M36:T36"/>
+    <mergeCell ref="C37:J37"/>
+    <mergeCell ref="M37:T37"/>
+    <mergeCell ref="M47:U47"/>
+    <mergeCell ref="X47:AF47"/>
+    <mergeCell ref="C38:J38"/>
+    <mergeCell ref="K38:AG38"/>
+    <mergeCell ref="R39:X39"/>
+    <mergeCell ref="Y39:AG39"/>
+    <mergeCell ref="B40:AH40"/>
+    <mergeCell ref="M42:U42"/>
+    <mergeCell ref="X42:AF42"/>
+    <mergeCell ref="C42:J42"/>
+    <mergeCell ref="C43:J43"/>
+    <mergeCell ref="M43:U43"/>
+    <mergeCell ref="X43:AF43"/>
+    <mergeCell ref="C53:D54"/>
+    <mergeCell ref="E53:K54"/>
+    <mergeCell ref="L53:AG54"/>
+    <mergeCell ref="C55:D56"/>
+    <mergeCell ref="E55:K56"/>
+    <mergeCell ref="L55:AG56"/>
+    <mergeCell ref="C57:D58"/>
+    <mergeCell ref="E57:K58"/>
+    <mergeCell ref="L57:AG58"/>
+    <mergeCell ref="B30:AH30"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="G25:K25"/>
+    <mergeCell ref="L25:P25"/>
+    <mergeCell ref="C52:K52"/>
+    <mergeCell ref="M48:U48"/>
+    <mergeCell ref="X48:AF48"/>
+    <mergeCell ref="C48:J48"/>
+    <mergeCell ref="C49:J49"/>
+    <mergeCell ref="M49:U49"/>
+    <mergeCell ref="X49:AF49"/>
+    <mergeCell ref="C50:J50"/>
+    <mergeCell ref="M50:U50"/>
+    <mergeCell ref="X50:AF50"/>
+    <mergeCell ref="C44:J44"/>
+    <mergeCell ref="X44:AF44"/>
+    <mergeCell ref="C45:J45"/>
+    <mergeCell ref="X45:AF45"/>
+    <mergeCell ref="M44:U44"/>
+    <mergeCell ref="M45:U45"/>
+    <mergeCell ref="L26:P26"/>
+    <mergeCell ref="Q26:V26"/>
+    <mergeCell ref="Q25:V25"/>
+    <mergeCell ref="C47:J47"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="AB7:AH7"/>
@@ -5537,122 +5664,6 @@
     <mergeCell ref="G22:K22"/>
     <mergeCell ref="L22:P22"/>
     <mergeCell ref="Y28:AG28"/>
-    <mergeCell ref="B30:AH30"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="G25:K25"/>
-    <mergeCell ref="L25:P25"/>
-    <mergeCell ref="C52:K52"/>
-    <mergeCell ref="M48:U48"/>
-    <mergeCell ref="X48:AF48"/>
-    <mergeCell ref="C48:J48"/>
-    <mergeCell ref="C49:J49"/>
-    <mergeCell ref="M49:U49"/>
-    <mergeCell ref="X49:AF49"/>
-    <mergeCell ref="C50:J50"/>
-    <mergeCell ref="M50:U50"/>
-    <mergeCell ref="X50:AF50"/>
-    <mergeCell ref="C44:J44"/>
-    <mergeCell ref="X44:AF44"/>
-    <mergeCell ref="C45:J45"/>
-    <mergeCell ref="X45:AF45"/>
-    <mergeCell ref="M44:U44"/>
-    <mergeCell ref="M45:U45"/>
-    <mergeCell ref="L26:P26"/>
-    <mergeCell ref="Q26:V26"/>
-    <mergeCell ref="Q25:V25"/>
-    <mergeCell ref="C53:D54"/>
-    <mergeCell ref="E53:K54"/>
-    <mergeCell ref="L53:AG54"/>
-    <mergeCell ref="C55:D56"/>
-    <mergeCell ref="E55:K56"/>
-    <mergeCell ref="L55:AG56"/>
-    <mergeCell ref="C57:D58"/>
-    <mergeCell ref="E57:K58"/>
-    <mergeCell ref="L57:AG58"/>
-    <mergeCell ref="C47:J47"/>
-    <mergeCell ref="M47:U47"/>
-    <mergeCell ref="X47:AF47"/>
-    <mergeCell ref="C38:J38"/>
-    <mergeCell ref="K38:AG38"/>
-    <mergeCell ref="R39:X39"/>
-    <mergeCell ref="Y39:AG39"/>
-    <mergeCell ref="B40:AH40"/>
-    <mergeCell ref="M42:U42"/>
-    <mergeCell ref="X42:AF42"/>
-    <mergeCell ref="C42:J42"/>
-    <mergeCell ref="C43:J43"/>
-    <mergeCell ref="M43:U43"/>
-    <mergeCell ref="X43:AF43"/>
-    <mergeCell ref="W36:AE36"/>
-    <mergeCell ref="W37:AE37"/>
-    <mergeCell ref="C35:J35"/>
-    <mergeCell ref="M35:T35"/>
-    <mergeCell ref="W35:AE35"/>
-    <mergeCell ref="C36:J36"/>
-    <mergeCell ref="M36:T36"/>
-    <mergeCell ref="C37:J37"/>
-    <mergeCell ref="M37:T37"/>
-    <mergeCell ref="M34:T34"/>
-    <mergeCell ref="G26:K26"/>
-    <mergeCell ref="G27:K27"/>
-    <mergeCell ref="C32:J33"/>
-    <mergeCell ref="K32:K33"/>
-    <mergeCell ref="L32:L33"/>
-    <mergeCell ref="U32:U33"/>
-    <mergeCell ref="C34:J34"/>
-    <mergeCell ref="C26:F27"/>
-    <mergeCell ref="L27:P27"/>
-    <mergeCell ref="Q27:V27"/>
-    <mergeCell ref="R28:X28"/>
-    <mergeCell ref="W26:AG26"/>
-    <mergeCell ref="V32:V33"/>
-    <mergeCell ref="W32:AE33"/>
-    <mergeCell ref="AF32:AF33"/>
-    <mergeCell ref="AG32:AG33"/>
-    <mergeCell ref="W34:AE34"/>
-    <mergeCell ref="R16:X16"/>
-    <mergeCell ref="Y16:AG16"/>
-    <mergeCell ref="Q20:V20"/>
-    <mergeCell ref="W20:AG20"/>
-    <mergeCell ref="W21:AG21"/>
-    <mergeCell ref="B17:AH17"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="G19:K19"/>
-    <mergeCell ref="L19:P19"/>
-    <mergeCell ref="Q19:V19"/>
-    <mergeCell ref="W19:AG19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="G20:K20"/>
-    <mergeCell ref="L20:P20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="G21:K21"/>
-    <mergeCell ref="L21:P21"/>
-    <mergeCell ref="Q21:V21"/>
-    <mergeCell ref="M32:T33"/>
-    <mergeCell ref="B2:F5"/>
-    <mergeCell ref="G2:Y4"/>
-    <mergeCell ref="Z2:AH2"/>
-    <mergeCell ref="Z3:AH3"/>
-    <mergeCell ref="Z4:AH4"/>
-    <mergeCell ref="G5:AH5"/>
-    <mergeCell ref="B9:AH9"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="W27:AG27"/>
-    <mergeCell ref="W22:AG22"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="G23:K23"/>
-    <mergeCell ref="L23:P23"/>
-    <mergeCell ref="Q23:V23"/>
-    <mergeCell ref="W23:AG23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="Q22:V22"/>
-    <mergeCell ref="G24:K24"/>
-    <mergeCell ref="L24:P24"/>
-    <mergeCell ref="Q24:V24"/>
-    <mergeCell ref="W24:AG24"/>
-    <mergeCell ref="W25:AG25"/>
-    <mergeCell ref="C14:F14"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
